--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -12,8 +12,8 @@
     <sheet name="3. Проектирование" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Построено (вторичка)'!$A$1:$Q$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Строится'!$A$1:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Построено (вторичка)'!$A$1:$Q$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Строится'!$A$1:$P$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Проектирование'!$A$1:$Q$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -712,27 +712,23 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Большая Дмитровка IX</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
+          <t>Armani/Casa Moscow Residences (Армани/Каса Москоу Резиденсес)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2021–2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большая Дмитровка, 9А</t>
+          <t>Москва, Старомонетный, 19/11</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Тверской</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -741,33 +737,33 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2372881</v>
+        <v>2750000</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>3250803</v>
+        <v>3630000</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>3813559</v>
+        <v>8000000</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54–192</t>
+          <t>176–421</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -777,7 +773,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/325322186/</t>
+          <t>https://www.cian.ru/sale/flat/328853365/</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -785,27 +781,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Stella di Mosca Hotel &amp; Residences (Стелла ди Моска Хотел энд Резиденсиз)</t>
+          <t>Большая Дмитровка IX</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Bulgari Hotel &amp; Residences</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2023–2024</t>
+          <t>2021–2025</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большая Никитская, 9</t>
+          <t>Москва, Большая Дмитровка, 9А</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Тверской</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -814,33 +810,33 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3240741</v>
+        <v>2372881</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>3249768</v>
+        <v>3250803</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>5584363</v>
+        <v>3813559</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>107–198</t>
+          <t>54–192</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -850,7 +846,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/320386160/</t>
+          <t>https://www.cian.ru/sale/flat/325322186/</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -858,27 +854,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Stoleshnikov 7 (Столешников 7)</t>
+          <t>Stella di Mosca Hotel &amp; Residences (Стелла ди Моска Хотел энд Резиденсиз)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Vesper</t>
+          <t>Bulgari Hotel &amp; Residences</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023–2024</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Москва, Столешников, 7С1</t>
+          <t>Москва, Большая Никитская, 9</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Тверской</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -891,7 +887,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -900,20 +896,20 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2977612</v>
+        <v>3240741</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>3229296</v>
+        <v>3249768</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3242801</v>
+        <v>5584363</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>134–158</t>
+          <t>107–198</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -923,7 +919,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333340431/</t>
+          <t>https://www.cian.ru/sale/flat/320386160/</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -931,10 +927,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Armani/Casa Moscow Residences (Армани/Каса Москоу Резиденсес)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr"/>
+          <t>Stoleshnikov 7 (Столешников 7)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>2024</t>
@@ -942,12 +942,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Москва, Старомонетный, 19/11С1</t>
+          <t>Москва, Столешников, 7С1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Тверской</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -969,30 +969,30 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3196444</v>
+        <v>2977612</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>3196444</v>
+        <v>3229296</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3196444</v>
+        <v>3242801</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>180–180</t>
+          <t>134–158</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>делюкс</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/323682886/</t>
+          <t>https://www.cian.ru/sale/flat/333340431/</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -1073,23 +1073,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Клубный дом TURGENEV (Тургенев)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr"/>
+          <t>Дом Лаврушинский</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024–2025</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Москва, Костянский, 13</t>
+          <t>Москва, Большой Толмачевский, 5С1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Красносельский</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1098,11 +1102,11 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3-14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1111,20 +1115,20 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1902180</v>
+        <v>1956522</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2523717</v>
+        <v>3118040</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5642162</v>
+        <v>7453392</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70–310</t>
+          <t>66–980</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1134,7 +1138,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332431882/</t>
+          <t>https://www.cian.ru/sale/flat/331610087/</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
@@ -1142,23 +1146,23 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Дом Бакст на Патриарших</t>
+          <t>Клубный дом TURGENEV (Тургенев)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большой Козихинский, 15</t>
+          <t>Москва, Костянский, 13</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Красносельский</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1171,7 +1175,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1180,20 +1184,20 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2488540</v>
+        <v>1902180</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>2500000</v>
+        <v>2523717</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>3333333</v>
+        <v>5642162</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>152–498</t>
+          <t>70–310</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1203,7 +1207,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333483562/</t>
+          <t>https://www.cian.ru/sale/flat/332431882/</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -1211,23 +1215,23 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Клубный дом Фон Дессин</t>
+          <t>Дом Бакст на Патриарших</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Москва, Потаповский, 5С4</t>
+          <t>Москва, Большой Козихинский, 15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1240,7 +1244,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1249,20 +1253,20 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1419298</v>
+        <v>2488540</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>2460514</v>
+        <v>2500000</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>4191066</v>
+        <v>3333333</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79–394</t>
+          <t>152–498</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1272,39 +1276,31 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333380198/</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>сдан в 2026, продажи от застройщика</t>
-        </is>
-      </c>
+          <t>https://www.cian.ru/sale/flat/333483562/</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Дом Лаврушинский</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Sminex</t>
-        </is>
-      </c>
+          <t>Клубный дом Фон Дессин</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2024–2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большой Толмачевский, 5С1</t>
+          <t>Москва, Потаповский, 5С4</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Басманный</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1313,11 +1309,11 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3-14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1326,20 +1322,20 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1956522</v>
+        <v>1419298</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2377118</v>
+        <v>2460514</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4074074</v>
+        <v>4191066</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>113–270</t>
+          <t>79–394</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1349,31 +1345,35 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/327695906/</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>https://www.cian.ru/sale/flat/333380198/</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>сдан в 2026, продажи от застройщика</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
+          <t>Золотой, жилой квартал</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021–2023</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Москва, Звонарский, 3</t>
+          <t>Москва, Софийская, 18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Мещанский</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1382,11 +1382,11 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1395,20 +1395,20 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2321429</v>
+        <v>2083333</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>2321429</v>
+        <v>2448000</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>2321429</v>
+        <v>3200000</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>168–168</t>
+          <t>87–269</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/313842757/</t>
+          <t>https://www.cian.ru/sale/flat/315109130/</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -1426,23 +1426,23 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Золотой, жилой квартал</t>
+          <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2021–2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 18</t>
+          <t>Москва, Звонарский, 3</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Мещанский</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1464,30 +1464,30 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>2083333</v>
+        <v>2321429</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2297951</v>
+        <v>2321429</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>3042409</v>
+        <v>2321429</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>162–269</t>
+          <t>168–168</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>делюкс</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/330217072/</t>
+          <t>https://www.cian.ru/sale/flat/313842757/</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>делюкс</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>делюкс</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -1840,23 +1840,23 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Абрикосов</t>
+          <t>Клубный дом CULT (Клубный дом Культ)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2025–2026</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Москва, Потаповский, 6С1</t>
+          <t>Москва, Ленинский, 2</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1869,29 +1869,29 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>9-16</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1558355</v>
+        <v>1000000</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1785730</v>
+        <v>1799500</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2094241</v>
+        <v>3035672</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>67–191</t>
+          <t>26–336</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/326531270/</t>
+          <t>https://www.cian.ru/sale/flat/333091841/</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -1909,23 +1909,23 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Artisan (Артисан)</t>
+          <t>Абрикосов</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022–2023</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Москва, Арбат, 39</t>
+          <t>Москва, Потаповский, 6С1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Арбат</t>
+          <t>Басманный</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1947,20 +1947,20 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1769663</v>
+        <v>1558355</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1769663</v>
+        <v>1785730</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>1769663</v>
+        <v>2094241</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>178–178</t>
+          <t>67–191</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332958719/</t>
+          <t>https://www.cian.ru/sale/flat/326531270/</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
@@ -1978,23 +1978,23 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Тессинский, 1</t>
+          <t>Artisan (Артисан)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2020–2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Москва, Тессинский, 1</t>
+          <t>Москва, Арбат, 39</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Арбат</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2016,20 +2016,20 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1106420</v>
+        <v>1769663</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>1657000</v>
+        <v>1769663</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>1800000</v>
+        <v>1769663</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>57–458</t>
+          <t>178–178</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332120866/</t>
+          <t>https://www.cian.ru/sale/flat/332958719/</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr"/>
@@ -2047,23 +2047,23 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Софийский</t>
+          <t>Тессинский, 1</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2018–2019</t>
+          <t>2020–2023</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 34</t>
+          <t>Москва, Тессинский, 1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Таганский</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2072,33 +2072,33 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4-9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1333333</v>
+        <v>1106420</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1549419</v>
+        <v>1657000</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2066667</v>
+        <v>1800000</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>53–155</t>
+          <t>57–458</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/318593959/</t>
+          <t>https://www.cian.ru/sale/flat/332120866/</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -2116,23 +2116,23 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Дом NV/9</t>
+          <t>Резиденция 1864</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большой Николоворобинский, 9к1</t>
+          <t>Москва, Софийская, 36</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2145,29 +2145,29 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1454693</v>
+        <v>1510567</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1467116</v>
+        <v>1617861</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1504854</v>
+        <v>3213511</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>61–118</t>
+          <t>289–1062</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333345222/</t>
+          <t>https://www.cian.ru/sale/flat/325133439/</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -2185,23 +2185,23 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Собрание клубных домов ORDYNKA (Ордынка)</t>
+          <t>Софийский</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018–2019</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большой Ордынский, 4С4</t>
+          <t>Москва, Софийская, 34</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2210,11 +2210,11 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2223,20 +2223,20 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1465909</v>
+        <v>1333333</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1465909</v>
+        <v>1549419</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>1465909</v>
+        <v>2066667</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>88–88</t>
+          <t>53–155</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/331685961/</t>
+          <t>https://www.cian.ru/sale/flat/318593959/</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -2254,18 +2254,18 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>A.Residence (А Резиденс)</t>
+          <t>Клубный дом Космо 4/22</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2024–2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Москва, Садовническая, 82</t>
+          <t>Москва, Космодамианская, 4/22</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2279,33 +2279,33 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5-9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>664234</v>
+        <v>1326531</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1452248</v>
+        <v>1531532</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>1500000</v>
+        <v>5300745</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>60–137</t>
+          <t>47–174</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332802762/</t>
+          <t>https://www.cian.ru/sale/flat/328309502/</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -2323,23 +2323,23 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Клубный дом Космо 4/22</t>
+          <t>Дом NV/9</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Москва, Космодамианская, 4/22</t>
+          <t>Москва, Большой Николоворобинский, 9к1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
+          <t>Таганский</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2348,11 +2348,11 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2361,20 +2361,20 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1326531</v>
+        <v>1454693</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1400000</v>
+        <v>1467116</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>3325000</v>
+        <v>1504854</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>48–122</t>
+          <t>61–118</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/327263882/</t>
+          <t>https://www.cian.ru/sale/flat/333345222/</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
@@ -2392,23 +2392,23 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Клубный дом ЦВЕТ32</t>
+          <t>Собрание клубных домов ORDYNKA (Ордынка)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Москва, Цветной, 32А</t>
+          <t>Москва, Большой Ордынский, 4С4</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Мещанский</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2430,20 +2430,20 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1120690</v>
+        <v>1465909</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>1363636</v>
+        <v>1465909</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1972477</v>
+        <v>1465909</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>37–218</t>
+          <t>88–88</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/317801090/</t>
+          <t>https://www.cian.ru/sale/flat/331685961/</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -2461,23 +2461,23 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Титул на Якиманке</t>
+          <t>A.Residence (А Резиденс)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024–2025</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Москва, 2-й Хвостов, 8</t>
+          <t>Москва, Садовническая, 82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2490,29 +2490,29 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-9</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1281646</v>
+        <v>664234</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1281646</v>
+        <v>1365000</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1281646</v>
+        <v>2894000</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>63–63</t>
+          <t>47–210</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/330420858/</t>
+          <t>https://www.cian.ru/sale/flat/324615659/</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
@@ -2530,23 +2530,23 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
+          <t>Клубный дом ЦВЕТ32</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Москва, Садовническая, 7</t>
+          <t>Москва, Цветной, 32А</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
+          <t>Мещанский</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2568,20 +2568,20 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1094488</v>
+        <v>1120690</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>1268025</v>
+        <v>1363636</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>1927419</v>
+        <v>1972477</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>124–400</t>
+          <t>37–218</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/320969979/</t>
+          <t>https://www.cian.ru/sale/flat/317801090/</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -2599,23 +2599,23 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Bogenhouse (Богенхаус)</t>
+          <t>Титул на Якиманке</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2020–2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Москва, Озерковская, 6</t>
+          <t>Москва, 2-й Хвостов, 8</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2628,29 +2628,29 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>985887</v>
+        <v>1281646</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1247727</v>
+        <v>1281646</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>2000000</v>
+        <v>1281646</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>43–355</t>
+          <t>63–63</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/323818010/</t>
+          <t>https://www.cian.ru/sale/flat/330420858/</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
@@ -2668,23 +2668,23 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Титул на Серебрянической</t>
+          <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Москва, Серебрянический, 8</t>
+          <t>Москва, Садовническая, 7</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2706,20 +2706,20 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1200000</v>
+        <v>1094488</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1229434</v>
+        <v>1268025</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1439394</v>
+        <v>1927419</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>62–276</t>
+          <t>124–400</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/311744163/</t>
+          <t>https://www.cian.ru/sale/flat/320969979/</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -2737,23 +2737,23 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Полянка/44</t>
+          <t>Bogenhouse (Богенхаус)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020–2021</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большая Полянка, 44</t>
+          <t>Москва, Озерковская, 6</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2766,29 +2766,29 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6-7</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1135408</v>
+        <v>985887</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1200000</v>
+        <v>1247727</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2109833</v>
+        <v>2000000</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>117–271</t>
+          <t>43–355</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332337813/</t>
+          <t>https://www.cian.ru/sale/flat/323818010/</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
@@ -2806,23 +2806,23 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Современник</t>
+          <t>Титул на Серебрянической</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Москва, Машкова, 13С1</t>
+          <t>Москва, Серебрянический, 8</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Таганский</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2831,11 +2831,11 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2844,20 +2844,20 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>1111959</v>
+        <v>1229434</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>1123919</v>
+        <v>1439394</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>34–34</t>
+          <t>62–276</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/330783642/</t>
+          <t>https://www.cian.ru/sale/flat/311744163/</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -2875,23 +2875,23 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Уланский, 13</t>
+          <t>Полянка/44</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Москва, Уланский, 13С1</t>
+          <t>Москва, Большая Полянка, 44</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Красносельский</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2904,29 +2904,29 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1100000</v>
+        <v>1135408</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1100000</v>
+        <v>1214499</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>1100000</v>
+        <v>2109833</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>123–179</t>
+          <t>117–271</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/328571404/</t>
+          <t>https://www.cian.ru/sale/flat/332405952/</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
@@ -2944,27 +2944,23 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LUMIN (ЛЮМИН)</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Hutton</t>
-        </is>
-      </c>
+          <t>Современник</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Москва, Славянская, 2/5с1</t>
+          <t>Москва, Машкова, 13С1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Басманный</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2977,7 +2973,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2986,20 +2982,20 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>900901</v>
+        <v>1100000</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1070076</v>
+        <v>1111959</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>2658908</v>
+        <v>1123919</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>52–213</t>
+          <t>34–34</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3009,7 +3005,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/328747959/</t>
+          <t>https://www.cian.ru/sale/flat/330783642/</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -3017,23 +3013,23 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Клубный дом CULT (Клубный дом Культ)</t>
+          <t>Уланский, 13</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2025–2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Москва, Ленинский, 2</t>
+          <t>Москва, Уланский, 13С1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Красносельский</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3046,7 +3042,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9-16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -3055,20 +3051,20 @@
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1000000</v>
+        <v>1100000</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1068014</v>
+        <v>1100000</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1136029</v>
+        <v>1100000</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>2</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>27–33</t>
+          <t>123–179</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3078,7 +3074,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/331293819/</t>
+          <t>https://www.cian.ru/sale/flat/328571404/</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
@@ -3086,27 +3082,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>The Book (Бук)</t>
+          <t>LUMIN (ЛЮМИН)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>Hutton</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2020–2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Москва, Новый Арбат, 15</t>
+          <t>Москва, Славянская, 2/5с1</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Арбат</t>
+          <t>Таганский</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3119,7 +3115,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -3128,20 +3124,20 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>859729</v>
+        <v>900901</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>900000</v>
+        <v>1070076</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>953125</v>
+        <v>2658908</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>7</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>27–65</t>
+          <t>52–213</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3151,7 +3147,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/331607422/</t>
+          <t>https://www.cian.ru/sale/flat/328747959/</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -3159,23 +3155,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Меценат</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr"/>
+          <t>The Book (Бук)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020–2021</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Москва, 2-й Кадашевский, 5с2</t>
+          <t>Москва, Новый Арбат, 15</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Арбат</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3188,29 +3188,29 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>848033</v>
+        <v>859729</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>848033</v>
+        <v>900000</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>2988731</v>
+        <v>953125</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>204–589</t>
+          <t>27–65</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332410727/</t>
+          <t>https://www.cian.ru/sale/flat/331607422/</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -3228,7 +3228,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Жизнь на Плющихе</t>
+          <t>Меценат</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
@@ -3239,17 +3239,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Москва, Погодинская, 2</t>
+          <t>Москва, 2-й Кадашевский, 5с2</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Хамовники</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Хамовники</t>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3266,20 +3266,20 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1253669</v>
+        <v>848033</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>3000000</v>
+        <v>848033</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>3680336</v>
+        <v>2988731</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>95–254</t>
+          <t>204–589</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/331461063/</t>
+          <t>https://www.cian.ru/sale/flat/332410727/</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -3297,22 +3297,18 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Carré Blanc (Карре Бланк)</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
+          <t>Хамовники 12</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Москва, Пречистенская, 43</t>
+          <t>Москва, 1-й Тружеников, 12</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3326,43 +3322,43 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>3000000</v>
+        <v>2800000</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>3000000</v>
+        <v>3151207</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>3000000</v>
+        <v>3502415</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>147–147</t>
+          <t>104–207</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/331222940/</t>
+          <t>https://www.cian.ru/sale/flat/317328150/</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -3370,7 +3366,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Хамовники 12</t>
+          <t>Саввинская 27</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
@@ -3381,7 +3377,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Москва, 1-й Тружеников, 12А</t>
+          <t>Москва, Саввинская, 27</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3399,39 +3395,39 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>2800000</v>
+        <v>3060713</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>2800000</v>
+        <v>3095494</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>2800000</v>
+        <v>3130275</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>104–104</t>
+          <t>81–131</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>делюкс</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/327417697/</t>
+          <t>https://www.cian.ru/sale/flat/330582804/</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -3439,22 +3435,18 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Brodsky (Бродский)</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
+          <t>Жизнь на Плющихе</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Москва, 1-й Тружеников, 16</t>
+          <t>Москва, Погодинская, 2</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3472,7 +3464,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14-16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3481,30 +3473,30 @@
         </is>
       </c>
       <c r="J43" s="3" t="n">
-        <v>2446043</v>
+        <v>1253669</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>2698752</v>
+        <v>3000000</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>3339278</v>
+        <v>3680336</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>139–224</t>
+          <t>95–254</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/330386808/</t>
+          <t>https://www.cian.ru/sale/flat/331461063/</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -3512,18 +3504,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Villa Grace (Вилла Грейс)</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr"/>
+          <t>Carré Blanc (Карре Бланк)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2020–2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Москва, Пожарский, 3</t>
+          <t>Москва, Пречистенская, 43</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3541,29 +3537,29 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>2635581</v>
+        <v>3000000</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>2635659</v>
+        <v>3000000</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>2637704</v>
+        <v>3000000</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>128–129</t>
+          <t>147–147</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3573,7 +3569,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/318719181/</t>
+          <t>https://www.cian.ru/sale/flat/331222940/</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -3581,18 +3577,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Magnum (Магнум)</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr"/>
+          <t>Brodsky (Бродский)</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2020–2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Москва, Усачева, 9</t>
+          <t>Москва, 1-й Тружеников, 16</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3610,29 +3610,29 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14-16</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1568381</v>
+        <v>2446043</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2490110</v>
+        <v>2698752</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>2738095</v>
+        <v>3339278</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>84–215</t>
+          <t>139–224</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332629082/</t>
+          <t>https://www.cian.ru/sale/flat/330386808/</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -3650,22 +3650,18 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>White Khamovniki (Вайт Хамовники)</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Hutton</t>
-        </is>
-      </c>
+          <t>Villa Grace (Вилла Грейс)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020–2023</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Москва, Олсуфьевский, 9к1</t>
+          <t>Москва, Пожарский, 3</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3683,7 +3679,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3692,20 +3688,20 @@
         </is>
       </c>
       <c r="J46" s="3" t="n">
-        <v>2387268</v>
+        <v>2635581</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>2387268</v>
+        <v>2635659</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>2657480</v>
+        <v>2637704</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>3</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>75–152</t>
+          <t>128–129</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -3715,7 +3711,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/319352551/</t>
+          <t>https://www.cian.ru/sale/flat/318719181/</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -3723,18 +3719,18 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Саввинская 17</t>
+          <t>Magnum (Магнум)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020–2022</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 17</t>
+          <t>Москва, Усачева, 9</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3752,29 +3748,29 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J47" s="3" t="n">
-        <v>2337858</v>
+        <v>1568381</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>2348485</v>
+        <v>2490110</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>2588055</v>
+        <v>2738095</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>65–66</t>
+          <t>84–215</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -3784,7 +3780,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/329280427/</t>
+          <t>https://www.cian.ru/sale/flat/332629082/</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -3792,22 +3788,18 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Садовые кварталы</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Интеко</t>
-        </is>
-      </c>
+          <t>Саввинская 17</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2018–2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Москва, Усачева, 15А</t>
+          <t>Москва, Саввинская, 17</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3821,11 +3813,11 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5-18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3834,53 +3826,53 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1328904</v>
+        <v>2337858</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2111111</v>
+        <v>2453400</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3718750</v>
+        <v>2588055</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>54–342</t>
+          <t>65–82</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>делюкс</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332375457/</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>очереди 2012–2023; в выборку попали корпуса 2018+</t>
-        </is>
-      </c>
+          <t>https://www.cian.ru/sale/flat/330707597/</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Пироговская 14</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr"/>
+          <t>White Khamovniki (Вайт Хамовники)</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Hutton</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2021–2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Москва, Малая Пироговская, 12</t>
+          <t>Москва, Олсуфьевский, 9к1</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3898,29 +3890,29 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J49" s="3" t="n">
-        <v>1397059</v>
+        <v>2387268</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>2033898</v>
+        <v>2387268</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>2774566</v>
+        <v>2657480</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>66–254</t>
+          <t>75–152</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -3930,7 +3922,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/329965347/</t>
+          <t>https://www.cian.ru/sale/flat/319352551/</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -3938,18 +3930,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr"/>
+          <t>Садовые кварталы</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Интеко</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2018–2023</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 13</t>
+          <t>Москва, Усачева, 15А</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3963,11 +3959,11 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5-18</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -3976,53 +3972,53 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>1869231</v>
+        <v>1328904</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>1884615</v>
+        <v>2111111</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>3751412</v>
+        <v>3718750</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>125–177</t>
+          <t>54–342</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/324116883/</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr"/>
+          <t>https://www.cian.ru/sale/flat/332375457/</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>очереди 2012–2023; в выборку попали корпуса 2018+</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Roza Rossa (Роза Росса)</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>KR Properties</t>
-        </is>
-      </c>
+          <t>Пироговская 14</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2020–2023</t>
+          <t>2021–2023</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Москва, Зубовская, 7</t>
+          <t>Москва, Малая Пироговская, 12</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4040,7 +4036,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8-9</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -4049,30 +4045,30 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1010101</v>
+        <v>1397059</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>1380000</v>
+        <v>2033898</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>1408163</v>
+        <v>2774566</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>49–316</t>
+          <t>66–254</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>делюкс</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332883877/</t>
+          <t>https://www.cian.ru/sale/flat/329965347/</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -4080,40 +4076,36 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Capital Towers (Капитал Тауэрс)</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Capital Group</t>
-        </is>
-      </c>
+          <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Москва, Краснопресненская, 14Ак3</t>
+          <t>Москва, Саввинская, 13</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Сити</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>51-72</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -4122,30 +4114,30 @@
         </is>
       </c>
       <c r="J52" s="3" t="n">
-        <v>428266</v>
+        <v>1869231</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>1269231</v>
+        <v>1884615</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>2000000</v>
+        <v>3751412</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>28–212</t>
+          <t>125–177</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>делюкс</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332938835/</t>
+          <t>https://www.cian.ru/sale/flat/324116883/</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -4153,58 +4145,62 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>City Park (Сити Парк)</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr"/>
+          <t>Roza Rossa (Роза Росса)</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>KR Properties</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2019–2023</t>
+          <t>2020–2023</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Москва, Мантулинская, 9к4</t>
+          <t>Москва, Зубовская, 7</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Сити</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>6-24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J53" s="3" t="n">
-        <v>788028</v>
+        <v>1010101</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>1183147</v>
+        <v>1380000</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>2129032</v>
+        <v>1408163</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>34–251</t>
+          <t>49–316</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
@@ -4214,7 +4210,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/329981804/</t>
+          <t>https://www.cian.ru/sale/flat/332883877/</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -4222,22 +4218,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>NEVA TOWERS (Нева Тауэрс)</t>
+          <t>Capital Towers (Капитал Тауэрс)</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Renaissance Development</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2018–2025</t>
+          <t>2022–2023</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Москва, 1-й Красногвардейский, 22с2</t>
+          <t>Москва, Краснопресненская, 14Ак3</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4251,33 +4247,33 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>63-79</t>
+          <t>51-72</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J54" s="3" t="n">
-        <v>615385</v>
+        <v>428266</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>854530</v>
+        <v>1269231</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>1968504</v>
+        <v>2000000</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>39–254</t>
+          <t>28–212</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -4287,7 +4283,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332591457/</t>
+          <t>https://www.cian.ru/sale/flat/332938835/</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -4295,62 +4291,58 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Дом Chkalov (Чкалов)</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Ikon Development</t>
-        </is>
-      </c>
+          <t>City Park (Сити Парк)</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2021–2025</t>
+          <t>2019–2023</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Москва, Курского Вокзала, 1</t>
+          <t>Москва, Мантулинская, 9к4</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
+          <t>Сити</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>6-24</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J55" s="3" t="n">
-        <v>796915</v>
+        <v>788028</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>967043</v>
+        <v>1183147</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>1500000</v>
+        <v>2129032</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>31–174</t>
+          <t>34–251</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -4360,7 +4352,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332033533/</t>
+          <t>https://www.cian.ru/sale/flat/329981804/</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -4368,28 +4360,32 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Bauman House (Бауман Хаус)</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr"/>
+          <t>NEVA TOWERS (Нева Тауэрс)</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Renaissance Development</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2020–2022</t>
+          <t>2018–2025</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Москва, Новая Дорога, 9</t>
+          <t>Москва, 1-й Красногвардейский, 22с2</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
+          <t>Сити</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
@@ -4397,29 +4393,29 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15-16</t>
+          <t>63-79</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>536585</v>
+        <v>615385</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>786687</v>
+        <v>854530</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>812500</v>
+        <v>1968504</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>49–82</t>
+          <t>39–254</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4429,7 +4425,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/283281477/</t>
+          <t>https://www.cian.ru/sale/flat/332591457/</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -4437,22 +4433,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>KAZAKOV Grand Loft (КАЗАКОВ Гранд Лофт)</t>
+          <t>Дом Chkalov (Чкалов)</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Coldy</t>
+          <t>Ikon Development</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2021–2025</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Москва, Казакова, 7</t>
+          <t>Москва, Курского Вокзала, 1</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4470,7 +4466,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21-22</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4479,20 +4475,20 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>492857</v>
+        <v>796915</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>729064</v>
+        <v>967043</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>839080</v>
+        <v>1500000</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>42–73</t>
+          <t>31–174</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4502,7 +4498,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/324237764/</t>
+          <t>https://www.cian.ru/sale/flat/332033533/</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -4510,22 +4506,18 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Басманный от Гранель</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Гранель</t>
-        </is>
-      </c>
+          <t>Bauman House (Бауман Хаус)</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2024–2025</t>
+          <t>2020–2022</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Москва, Малая Почтовая, 12</t>
+          <t>Москва, Новая Дорога, 9</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4539,11 +4531,11 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>12-21</t>
+          <t>15-16</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -4552,20 +4544,20 @@
         </is>
       </c>
       <c r="J58" s="3" t="n">
-        <v>560484</v>
+        <v>536585</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>718850</v>
+        <v>786687</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>923345</v>
+        <v>812500</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>28–86</t>
+          <t>49–82</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4575,7 +4567,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333613664/</t>
+          <t>https://www.cian.ru/sale/flat/283281477/</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -4583,10 +4575,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Dialog (Диалог)</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr"/>
+          <t>KAZAKOV Grand Loft (КАЗАКОВ Гранд Лофт)</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Coldy</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>2022–2023</t>
@@ -4594,17 +4590,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большая Спасская, 35</t>
+          <t>Москва, Казакова, 7</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Красносельский</t>
+          <t>Басманный</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Красносельский (вне Садового)</t>
+          <t>Басманный (вне Садового)</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
@@ -4612,29 +4608,29 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>22-24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J59" s="3" t="n">
-        <v>754006</v>
+        <v>492857</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>998406</v>
+        <v>729064</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>1187872</v>
+        <v>839080</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>38–121</t>
+          <t>42–73</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4644,7 +4640,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332479143/</t>
+          <t>https://www.cian.ru/sale/flat/324237764/</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
@@ -4652,32 +4648,32 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>RED7 (РЕД7)</t>
+          <t>Басманный от Гранель</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ГК Основа</t>
+          <t>Гранель</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2022–2025</t>
+          <t>2024–2025</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Москва, Академика Сахарова, 7</t>
+          <t>Москва, Малая Почтовая, 12</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Красносельский</t>
+          <t>Басманный</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Красносельский (вне Садового)</t>
+          <t>Басманный (вне Садового)</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
@@ -4685,29 +4681,29 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>19-20</t>
+          <t>12-21</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J60" s="3" t="n">
-        <v>526700</v>
+        <v>560484</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>767285</v>
+        <v>718850</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>1402500</v>
+        <v>923345</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>39–254</t>
+          <t>28–86</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -4717,7 +4713,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/325686030/</t>
+          <t>https://www.cian.ru/sale/flat/333613664/</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
@@ -4725,18 +4721,18 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Волга</t>
+          <t>Dialog (Диалог)</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022–2023</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Москва, Докучаев, 2с3</t>
+          <t>Москва, Большая Спасская, 35</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -4754,29 +4750,29 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22-24</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J61" s="3" t="n">
-        <v>677419</v>
+        <v>754006</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>722271</v>
+        <v>998406</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>767123</v>
+        <v>1187872</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>73–93</t>
+          <t>38–121</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -4786,7 +4782,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333351088/</t>
+          <t>https://www.cian.ru/sale/flat/332479143/</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
@@ -4794,28 +4790,32 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Sole Hill (Соле Хилл)</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr"/>
+          <t>RED7 (РЕД7)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>ГК Основа</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022–2025</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Москва, Олимпийский, 12</t>
+          <t>Москва, Академика Сахарова, 7</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Мещанский</t>
+          <t>Красносельский</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Мещанский (вне Садового)</t>
+          <t>Красносельский (вне Садового)</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19-20</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -4832,20 +4832,20 @@
         </is>
       </c>
       <c r="J62" s="3" t="n">
-        <v>700000</v>
+        <v>526700</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>850000</v>
+        <v>767285</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>950000</v>
+        <v>1402500</v>
       </c>
       <c r="M62" s="3" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>32–180</t>
+          <t>39–254</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333427836/</t>
+          <t>https://www.cian.ru/sale/flat/325686030/</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
@@ -4863,62 +4863,58 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Lucky (Лаки)</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
+          <t>Волга</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Москва, Костикова, 4к2</t>
+          <t>Москва, Докучаев, 2с3</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Красносельский</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Пресненский (вне Садового)</t>
+          <t>Красносельский (вне Садового)</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15-21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J63" s="3" t="n">
-        <v>1296875</v>
+        <v>677419</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>1694915</v>
+        <v>722271</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>2352941</v>
+        <v>767123</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>44–253</t>
+          <t>73–93</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -4928,7 +4924,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333512309/</t>
+          <t>https://www.cian.ru/sale/flat/333351088/</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
@@ -4936,28 +4932,28 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Дом на Тишинке</t>
+          <t>Sole Hill (Соле Хилл)</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Москва, Средний Тишинский, 5</t>
+          <t>Москва, Олимпийский, 12</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Мещанский</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Пресненский (вне Садового)</t>
+          <t>Мещанский (вне Садового)</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
@@ -4965,29 +4961,29 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>7-20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J64" s="3" t="n">
-        <v>1500000</v>
+        <v>700000</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>1614969</v>
+        <v>850000</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>2147239</v>
+        <v>950000</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>84–243</t>
+          <t>32–180</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -4997,7 +4993,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332939786/</t>
+          <t>https://www.cian.ru/sale/flat/333427836/</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
@@ -5005,18 +5001,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Fantastic House (Фантастик Хаус)</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr"/>
+          <t>Lucky (Лаки)</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022–2023</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большой Тишинский, 30</t>
+          <t>Москва, Костикова, 4к2</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -5030,11 +5030,11 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>15-21</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -5043,20 +5043,20 @@
         </is>
       </c>
       <c r="J65" s="3" t="n">
-        <v>1117647</v>
+        <v>1296875</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>1496549</v>
+        <v>1694915</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>1544484</v>
+        <v>2352941</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>140–240</t>
+          <t>44–253</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/325373140/</t>
+          <t>https://www.cian.ru/sale/flat/333512309/</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr"/>
@@ -5074,18 +5074,18 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Edison House (Эдисон Хаус)</t>
+          <t>Дом на Тишинке</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Москва, Электрический, 10</t>
+          <t>Москва, Средний Тишинский, 5</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5103,29 +5103,29 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7-20</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1369863</v>
+        <v>1500000</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1369863</v>
+        <v>1614969</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1369863</v>
+        <v>2147239</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>58–58</t>
+          <t>84–243</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/331518334/</t>
+          <t>https://www.cian.ru/sale/flat/332939786/</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
@@ -5143,7 +5143,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Дизайнерский дом Eleven (11)</t>
+          <t>Fantastic House (Фантастик Хаус)</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Москва, Звенигородское, 11</t>
+          <t>Москва, Большой Тишинский, 30</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16-17</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -5181,20 +5181,20 @@
         </is>
       </c>
       <c r="J67" s="3" t="n">
-        <v>1044868</v>
+        <v>1117647</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>1246251</v>
+        <v>1496549</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>1428571</v>
+        <v>1544484</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>75–191</t>
+          <t>140–240</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332226758/</t>
+          <t>https://www.cian.ru/sale/flat/325373140/</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr"/>
@@ -5212,18 +5212,18 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SkyView</t>
+          <t>Edison House (Эдисон Хаус)</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2023–2025</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Москва, Дружинниковская, 15А</t>
+          <t>Москва, Электрический, 10</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5237,11 +5237,11 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>20-25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -5250,20 +5250,20 @@
         </is>
       </c>
       <c r="J68" s="3" t="n">
-        <v>850000</v>
+        <v>1369863</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>1200000</v>
+        <v>1369863</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>2756939</v>
+        <v>1369863</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>47–847</t>
+          <t>58–58</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332791431/</t>
+          <t>https://www.cian.ru/sale/flat/331518334/</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr"/>
@@ -5281,18 +5281,18 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Sinatra (Синатра)</t>
+          <t>Дизайнерский дом Eleven (11)</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2018–2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большой Тишинский, 38</t>
+          <t>Москва, Звенигородское, 11</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5310,29 +5310,29 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>16-17</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J69" s="3" t="n">
-        <v>839130</v>
+        <v>1044868</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>1052456</v>
+        <v>1246251</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>1388889</v>
+        <v>1428571</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>46–180</t>
+          <t>75–191</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/329740227/</t>
+          <t>https://www.cian.ru/sale/flat/332226758/</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
@@ -5350,22 +5350,18 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Репаблик</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Forma</t>
-        </is>
-      </c>
+          <t>SkyView</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2025–2026</t>
+          <t>2023–2025</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Москва, Пресненский Вал, к2.1</t>
+          <t>Москва, Дружинниковская, 15А</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5379,33 +5375,33 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>26-34</t>
+          <t>20-25</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J70" s="3" t="n">
-        <v>716667</v>
+        <v>850000</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>943141</v>
+        <v>1200000</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>1570228</v>
+        <v>2756939</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>27–140</t>
+          <t>47–847</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5415,7 +5411,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333504607/</t>
+          <t>https://www.cian.ru/sale/flat/332791431/</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr"/>
@@ -5423,22 +5419,18 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Счастье на Пресне</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Группа Эталон</t>
-        </is>
-      </c>
+          <t>Sinatra (Синатра)</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018–2020</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Москва, Красногвардейский, 15С2</t>
+          <t>Москва, Большой Тишинский, 38</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -5456,29 +5448,29 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>19-21</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J71" s="3" t="n">
-        <v>509615</v>
+        <v>839130</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>913838</v>
+        <v>1052456</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1135770</v>
+        <v>1388889</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>38–104</t>
+          <t>46–180</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5488,7 +5480,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/331676309/</t>
+          <t>https://www.cian.ru/sale/flat/329740227/</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
@@ -5496,22 +5488,22 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Пресня Сити</t>
+          <t>Репаблик</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>MR Group</t>
+          <t>Forma</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2025–2026</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Москва, Ходынская, 2</t>
+          <t>Москва, Пресненский Вал, к2.1</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5525,11 +5517,11 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>26-34</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -5538,20 +5530,20 @@
         </is>
       </c>
       <c r="J72" s="3" t="n">
-        <v>647159</v>
+        <v>716667</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>777778</v>
+        <v>943141</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>1426966</v>
+        <v>1570228</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>42–158</t>
+          <t>27–140</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5561,7 +5553,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/326492208/</t>
+          <t>https://www.cian.ru/sale/flat/333504607/</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -5569,18 +5561,22 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Пресненский вал 21</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr"/>
+          <t>Счастье на Пресне</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Группа Эталон</t>
+        </is>
+      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Москва, Пресненский Вал, 21</t>
+          <t>Москва, Красногвардейский, 15С2</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -5598,29 +5594,29 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>19-21</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J73" s="3" t="n">
-        <v>498915</v>
+        <v>509615</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>709877</v>
+        <v>913838</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>1322373</v>
+        <v>1135770</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>23–279</t>
+          <t>38–104</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5630,7 +5626,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332627285/</t>
+          <t>https://www.cian.ru/sale/flat/331676309/</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
@@ -5638,28 +5634,32 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>The Mostman (Мостман)</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr"/>
+          <t>Пресня Сити</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>MR Group</t>
+        </is>
+      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большая Андроньевская, 7</t>
+          <t>Москва, Ходынская, 2</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Таганский (вне Садового)</t>
+          <t>Пресненский (вне Садового)</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -5676,20 +5676,20 @@
         </is>
       </c>
       <c r="J74" s="3" t="n">
-        <v>820158</v>
+        <v>647159</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>837429</v>
+        <v>777778</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>854701</v>
+        <v>1426966</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>101–128</t>
+          <t>42–158</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/317822534/</t>
+          <t>https://www.cian.ru/sale/flat/326492208/</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -5707,36 +5707,36 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Долгоруковская 25</t>
+          <t>Пресненский вал 21</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Москва, Долгоруковская, 25А</t>
+          <t>Москва, Пресненский Вал, 21</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Тверской</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Тверской (вне Садового)</t>
+          <t>Пресненский (вне Садового)</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -5745,20 +5745,20 @@
         </is>
       </c>
       <c r="J75" s="3" t="n">
-        <v>1258268</v>
+        <v>498915</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>1879134</v>
+        <v>709877</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>2500000</v>
+        <v>1322373</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>63–237</t>
+          <t>23–279</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/323749307/</t>
+          <t>https://www.cian.ru/sale/flat/332627285/</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
@@ -5776,28 +5776,28 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Cameo Moscow Villas (Камео Москоу Виллас)</t>
+          <t>The Mostman (Мостман)</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Москва, Долгоруковская, 23А</t>
+          <t>Москва, Большая Андроньевская, 7</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Тверской</t>
+          <t>Таганский</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Тверской (вне Садового)</t>
+          <t>Таганский (вне Садового)</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -5814,20 +5814,20 @@
         </is>
       </c>
       <c r="J76" s="3" t="n">
-        <v>1538462</v>
+        <v>820158</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1538462</v>
+        <v>837429</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>1538462</v>
+        <v>854701</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>390–390</t>
+          <t>101–128</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332372652/</t>
+          <t>https://www.cian.ru/sale/flat/317822534/</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -5845,22 +5845,18 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Веспер Тверская</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
+          <t>Долгоруковская 25</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2020–2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Москва, 1-я Тверская-Ямская, 2А</t>
+          <t>Москва, Долгоруковская, 25А</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -5874,11 +5870,11 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -5887,20 +5883,20 @@
         </is>
       </c>
       <c r="J77" s="3" t="n">
-        <v>1138462</v>
+        <v>1258268</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>1534941</v>
+        <v>1879134</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>2085809</v>
+        <v>2500000</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>36–160</t>
+          <t>63–237</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -5910,7 +5906,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/331960482/</t>
+          <t>https://www.cian.ru/sale/flat/323749307/</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
@@ -5918,18 +5914,18 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Элитный дом Реномэ</t>
+          <t>Cameo Moscow Villas (Камео Москоу Виллас)</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Москва, Новослободская, 24Ас2</t>
+          <t>Москва, Долгоруковская, 23А</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5943,11 +5939,11 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -5956,20 +5952,20 @@
         </is>
       </c>
       <c r="J78" s="3" t="n">
-        <v>887805</v>
+        <v>1538462</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>1532075</v>
+        <v>1538462</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>1825397</v>
+        <v>1538462</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>65–126</t>
+          <t>390–390</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -5979,7 +5975,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333104707/</t>
+          <t>https://www.cian.ru/sale/flat/332372652/</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
@@ -5987,18 +5983,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Клубный дом Maison Rouge (Мезон Руж)</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr"/>
+          <t>Веспер Тверская</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020–2023</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Москва, Палиха, 4</t>
+          <t>Москва, 1-я Тверская-Ямская, 2А</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -6025,20 +6025,20 @@
         </is>
       </c>
       <c r="J79" s="3" t="n">
-        <v>920792</v>
+        <v>1138462</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>1116071</v>
+        <v>1534941</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>1152000</v>
+        <v>2085809</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>101–125</t>
+          <t>36–160</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/329909140/</t>
+          <t>https://www.cian.ru/sale/flat/331960482/</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr"/>
@@ -6056,18 +6056,18 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Резиденция Тверская</t>
+          <t>Элитный дом Реномэ</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2018–2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Москва, 2-я Брестская, 6</t>
+          <t>Москва, Новослободская, 24Ас2</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -6081,33 +6081,33 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J80" s="3" t="n">
-        <v>515556</v>
+        <v>887805</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>772624</v>
+        <v>1532075</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>1700000</v>
+        <v>1825397</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>37–161</t>
+          <t>65–126</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333520220/</t>
+          <t>https://www.cian.ru/sale/flat/333104707/</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -6125,28 +6125,28 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Медный 3.14</t>
+          <t>Клубный дом Maison Rouge (Мезон Руж)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Москва, Донская, 14</t>
+          <t>Москва, Палиха, 4</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Тверской</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Якиманка (вне Садового)</t>
+          <t>Тверской (вне Садового)</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
@@ -6154,29 +6154,29 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>16-21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J81" s="3" t="n">
-        <v>1357143</v>
+        <v>920792</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>1357143</v>
+        <v>1116071</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>1458537</v>
+        <v>1152000</v>
       </c>
       <c r="M81" s="3" t="n">
         <v>3</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>41–42</t>
+          <t>101–125</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332942905/</t>
+          <t>https://www.cian.ru/sale/flat/329909140/</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>
@@ -6194,81 +6194,219 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Sky House (Скай Хаус)</t>
+          <t>Резиденция Тверская</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>2018–2020</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Москва, 2-я Брестская, 6</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Тверской</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Тверской (вне Садового)</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>515556</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>772624</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>37–161</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333520220/</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Медный 3.14</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Москва, Донская, 14</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Якиманка (вне Садового)</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>16-21</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>1357143</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>1357143</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>1458537</v>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>41–42</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332942905/</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Sky House (Скай Хаус)</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
           <t>2020–2022</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Москва, Мытная, 40к3</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Якиманка (вне Садового)</t>
         </is>
       </c>
-      <c r="G82" s="3" t="n">
+      <c r="G84" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>20-30</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J82" s="3" t="n">
+      <c r="J84" s="3" t="n">
         <v>469453</v>
       </c>
-      <c r="K82" s="3" t="n">
-        <v>851938</v>
-      </c>
-      <c r="L82" s="3" t="n">
+      <c r="K84" s="3" t="n">
+        <v>840321</v>
+      </c>
+      <c r="L84" s="3" t="n">
         <v>1035120</v>
       </c>
-      <c r="M82" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="M84" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
         <is>
           <t>54–287</t>
         </is>
       </c>
-      <c r="O82" s="2" t="inlineStr">
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>премиум</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/332350254/</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333352226/</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>Источник: живая выдача Циан 2026-09-07 (api.cian.ru, инструмент tools/cian/cian.js), вторичка с годом дома 2018+ и новостройки по 10 районам ЦАО. Цены — ₽/м² по активным объявлениям. Застройщик и класс — по открытым данным (ручная разметка docs/premium-cao/manual.json).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q82"/>
+  <autoFilter ref="A1:Q84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6279,7 +6417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6427,24 +6565,34 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="K2" s="5" t="n"/>
+        <v>2900000</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>5700000</v>
+      </c>
       <c r="L2" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332838991/</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>по Циан дом сдан</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6491,26 +6639,34 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2873936</v>
+        <v>2818178</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>10816562</v>
+        <v>9287270</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333380220/</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>по Циан дом сдан</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6771,23 +6927,27 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>940000</v>
+        <v>942551</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2400000</v>
+        <v>3159585</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333434926/</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr"/>
@@ -6837,23 +6997,27 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1340000</v>
+        <v>1390000</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>2900000</v>
+        <v>3481000</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>отделка</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332376469/</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7121,23 +7285,27 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1610000</v>
+        <v>1675161</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>3600000</v>
+        <v>4224652</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/328952148/</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr"/>
@@ -7471,7 +7639,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Клубный дом «Резиденции Воронцова»</t>
+          <t>Клубный дом DUO (Дуо)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
@@ -7482,12 +7650,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Москва, Обуха</t>
+          <t>Москва, Софийская, 34С3</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -7496,11 +7664,11 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7509,18 +7677,18 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1656155</v>
+        <v>2408900</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>3549554</v>
+        <v>4300199</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333496265/</t>
+          <t>https://www.cian.ru/sale/flat/329214137/</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -7533,22 +7701,18 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Тессинский V</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Element Development</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> Клубный дом «Резиденции Воронцова»</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Москва, Тессинский, 5С11</t>
+          <t>Москва, Обуха</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -7562,11 +7726,11 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5-12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -7575,18 +7739,18 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1538500</v>
+        <v>1656155</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1750150</v>
+        <v>3549554</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/330017430/</t>
+          <t>https://www.cian.ru/sale/flat/333496265/</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -7594,36 +7758,28 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>старт продаж апрель 2026, котлован</t>
-        </is>
-      </c>
+      <c r="P19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Красный Октябрь»</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Гута Девелопмент</t>
-        </is>
-      </c>
+          <t>Казачий</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3 кв. 2026</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Москва, Берсеневская набережная</t>
+          <t>Москва, 1-й Казачий, 10С1</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Кропоткинская</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7636,7 +7792,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7645,53 +7801,51 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="K20" s="5" t="n"/>
+        <v>1822000</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>2752000</v>
+      </c>
       <c r="L20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333664798/</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>пометка «Изучить»</t>
-        </is>
-      </c>
+          <t>Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Камергер»</t>
+          <t>Тессинский V</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ENGEO Development</t>
+          <t>Element Development</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3 кв. 2026</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Москва, Георгиевский переулок, 1</t>
+          <t>Москва, Тессинский, 5С11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Охотный Ряд</t>
+          <t>Таганский</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -7700,72 +7854,68 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>5-12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1909308</v>
+        <v>1538500</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>4015377</v>
+        <v>1750150</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/322869532/</t>
+          <t>https://www.cian.ru/sale/flat/330017430/</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>пометка «Посмотреть»</t>
+          <t>старт продаж апрель 2026, котлован</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ЖК «PHANTOM»</t>
+          <t>ЖК «Красный Октябрь»</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Sense</t>
+          <t>Гута Девелопмент</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>3 кв. 2027</t>
+          <t>3 кв. 2026</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Москва, Малая Сухаревская площадь</t>
+          <t>Москва, Берсеневская набережная</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Сухаревская</t>
+          <t>Кропоткинская</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -7774,11 +7924,11 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7787,13 +7937,13 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1650000</v>
+        <v>2990000</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>3580000</v>
+        <v>2990000</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -7802,7 +7952,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333236418/</t>
+          <t>https://www.cian.ru/sale/flat/326780795/</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -7810,32 +7960,36 @@
           <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>пометка «Изучить»</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Клубный дом Левенсон»</t>
+          <t>ЖК «Камергер»</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Веспер</t>
+          <t>ENGEO Development</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3 кв. 2027</t>
+          <t>3 кв. 2026</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Москва, Трёхпрудный переулок</t>
+          <t>Москва, Георгиевский переулок, 1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Маяковская</t>
+          <t>Охотный Ряд</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -7844,68 +7998,72 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2800000</v>
+        <v>1909308</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>5500000</v>
+        <v>4015377</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/322869532/</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>пометка «Посмотреть +»</t>
+          <t>пометка «Посмотреть»</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Никитский-6»</t>
+          <t>ЖК «PHANTOM»</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Третий Рим</t>
+          <t>Sense</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4 кв. 2026</t>
+          <t>3 кв. 2027</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Москва, Никитский бульвар, 6/20</t>
+          <t>Москва, Малая Сухаревская площадь</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Арбат</t>
+          <t>Сухаревская</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -7914,11 +8072,11 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -7927,13 +8085,13 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2467500</v>
+        <v>1650000</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>4680000</v>
+        <v>3580000</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -7942,7 +8100,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/324141169/</t>
+          <t>https://www.cian.ru/sale/flat/333236418/</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -7955,27 +8113,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MONO Kami</t>
+          <t>ЖК «Клубный дом Левенсон»</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Tekta Group (ранее ПИК / MONO)</t>
+          <t>Веспер</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4 кв. 2028</t>
+          <t>3 кв. 2027</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Пыжевский переулок</t>
+          <t>Москва, Трёхпрудный переулок</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Маяковская</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -7984,11 +8142,11 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9-14</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -7997,10 +8155,14 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
+        <v>2800000</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
@@ -8014,47 +8176,47 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>пометка «Посмотреть ?»; по данным Движение.ру (май 2026) проект полностью у Tekta Group, ПИК вышел</t>
+          <t>пометка «Посмотреть +»</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Фрунзенская набережная»</t>
+          <t>ЖК «Никитский-6»</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>Третий Рим</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3 кв. 2027</t>
+          <t>4 кв. 2026</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Москва, Фрунзенская набережная, 30</t>
+          <t>Москва, Никитский бульвар, 6/20</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Фрунзенская</t>
+          <t>Арбат</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Хамовники</t>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10-13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -8063,23 +8225,27 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>2400000</v>
+        <v>2467500</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>6500000</v>
+        <v>4680000</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/324141169/</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr"/>
@@ -8087,40 +8253,40 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Коллекция Лужники»</t>
+          <t>MONO Kami</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Absolute Premium</t>
+          <t>Tekta Group (ранее ПИК / MONO)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4 кв. 2027</t>
+          <t>4 кв. 2028</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Москва, Лужнецкая набережная</t>
+          <t>Пыжевский переулок</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Воробьёвы горы</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Хамовники</t>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12-18</t>
+          <t>9-14</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -8129,55 +8295,55 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1400000</v>
+        <v>2050200</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>3170000</v>
+        <v>3322400</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>161</v>
+        <v>14</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332074690/</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>пометка «Изучить»</t>
+          <t>пометка «Посмотреть ?»; по данным Движение.ру (май 2026) проект полностью у Tekta Group, ПИК вышел</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Узоры»</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Capital Group</t>
-        </is>
-      </c>
+          <t>Лё Дом</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>4 кв. 2028</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Москва, 2-й Вражский переулок, 8с2</t>
+          <t>Москва, Соймоновский, 3</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Киевская</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -8190,7 +8356,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -8199,51 +8365,47 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+        <v>2569427</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>10285102</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333564442/</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>пометка «Изучить! +»; по РБК Компании: старт продаж 2026, стройка начата (котлован)</t>
-        </is>
-      </c>
+          <t>Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Погодинская»</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Веспер</t>
-        </is>
-      </c>
+          <t>ДОМ XXII</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4 кв. 2028</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Москва, Погодинская улица</t>
+          <t>Москва, Новодевичий, 6С2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Спортивная</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -8256,7 +8418,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11-12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -8265,56 +8427,52 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+        <v>2479101</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332297994/</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>РНС получено в ноябре 2025, закрытый старт продаж апрель–май 2026</t>
-        </is>
-      </c>
+          <t>Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Дом Дау»</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>1-й КРАСНОГВАРДЕЙСКИЙ</t>
-        </is>
-      </c>
+          <t>Клубные резиденции Лёвшинский, 19</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2 кв. 2027</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Москва, Краснопресненская набережная</t>
+          <t>Москва, Большой Левшинский, 19</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Москва-Сити</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Сити</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
@@ -8322,7 +8480,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -8331,23 +8489,23 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>855000</v>
+        <v>2844930</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>1184000</v>
+        <v>2844930</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/328904518/</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr"/>
@@ -8355,36 +8513,40 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Дом 56</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr"/>
+          <t>ЖК «Фрунзенская набережная»</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>3 кв. 2027</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Москва, Фридриха Энгельса, 56</t>
+          <t>Москва, Фрунзенская набережная, 30</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Фрунзенская</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20-27</t>
+          <t>10-13</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -8393,23 +8555,27 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>609244</v>
+        <v>2180740</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1043429</v>
+        <v>6898288</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333461162/</t>
+          <t>https://www.cian.ru/sale/flat/333537451/</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Циан 2026-09-07</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr"/>
@@ -8417,40 +8583,40 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Новая, 11»</t>
+          <t>ЖК «Коллекция Лужники»</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Element</t>
+          <t>Absolute Premium</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>4 кв. 2027</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Москва, улица Новая Дорога, 11Бс1</t>
+          <t>Москва, Лужнецкая набережная</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Электрозаводская</t>
+          <t>Воробьёвы горы</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9-15</t>
+          <t>12-18</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8459,13 +8625,13 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>664831</v>
+        <v>1218182</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1500000</v>
+        <v>4200000</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -8474,7 +8640,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333531308/</t>
+          <t>https://www.cian.ru/sale/flat/333460103/</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -8482,45 +8648,49 @@
           <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>пометка «Изучить»</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Квартал Life Time»</t>
+          <t>ЖК «Узоры»</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2 кв. 2026</t>
+          <t>4 кв. 2028</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Москва, улица Сергея Макеева</t>
+          <t>Москва, 2-й Вражский переулок, 8с2</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1905 года</t>
+          <t>Киевская</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Пресненский (вне Садового)</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9-23</t>
+          <t>9-10</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -8529,13 +8699,13 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1025225</v>
+        <v>3177900</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1539792</v>
+        <v>4559310</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -8544,7 +8714,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333570956/</t>
+          <t>https://www.cian.ru/sale/flat/333082541/</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -8554,47 +8724,47 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>по Циан дом сдан</t>
+          <t>пометка «Изучить! +»; по РБК Компании: старт продаж 2026, стройка начата (котлован)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Элитный квартал Тишинский бульвар»</t>
+          <t>ЖК «Погодинская»</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>Веспер</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2027–2028</t>
+          <t>4 кв. 2028</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Москва, Электрический переулок</t>
+          <t>Москва, Погодинская улица</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Белорусская</t>
+          <t>Спортивная</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Пресненский (вне Садового)</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3-14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8603,64 +8773,72 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1341000</v>
+        <v>3003600</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>3900000</v>
+        <v>4855100</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>229</v>
+        <v>13</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332519714/</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr"/>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>РНС получено в ноябре 2025, закрытый старт продаж апрель–май 2026</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Начало»</t>
+          <t>ЖК «Дом Дау»</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ДОНСТРОЙ</t>
+          <t>1-й КРАСНОГВАРДЕЙСКИЙ</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2 кв. 2027</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Москва, улица Сергея Макеева, 7</t>
+          <t>Москва, Краснопресненская набережная</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Ул. 1905 года</t>
+          <t>Москва-Сити</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Пресненский (вне Садового)</t>
+          <t>Сити</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11-48</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -8669,13 +8847,13 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>975000</v>
+        <v>855000</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1900000</v>
+        <v>1184000</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -8688,49 +8866,41 @@
           <t>таблица заказчика</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>знак вопроса</t>
-        </is>
-      </c>
+      <c r="P35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Климашкина 7/11»</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>MR Group</t>
-        </is>
-      </c>
+          <t>Дом 56</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>4 кв. 2028</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Москва, улица Климашкина, 7/11</t>
+          <t>Москва, Фридриха Энгельса, 56</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Красная пресня</t>
+          <t>Басманный</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Пресненский (вне Садового)</t>
+          <t>Басманный (вне Садового)</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>20-27</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -8739,23 +8909,23 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1800000</v>
+        <v>609244</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>2550000</v>
+        <v>1043429</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333461162/</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr"/>
@@ -8763,28 +8933,32 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Клубный дом "Магнум Соло"</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr"/>
+          <t>ЖК «Новая, 11»</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Москва, Александра Солженицына, 23Б</t>
+          <t>Москва, улица Новая Дорога, 11Бс1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Электрозаводская</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Таганский (вне Садового)</t>
+          <t>Басманный (вне Садового)</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
@@ -8792,7 +8966,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9-15</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -8801,23 +8975,27 @@
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1625537</v>
+        <v>664831</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>2067015</v>
+        <v>1500000</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/328639275/</t>
+          <t>https://www.cian.ru/sale/flat/333531308/</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Циан 2026-09-07</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr"/>
@@ -8825,114 +9003,102 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Клубный дом Энигмия»</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
+          <t>Vernissage (Апартаменты премиум-класса) (Вернисаж)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>4 кв. 2028</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Москва, Новослободская улица, 19</t>
+          <t>Москва, Щипок, 26С2</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Менделеевская</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Тверской (вне Садового)</t>
+          <t>Замоскворечье (вне Садового)</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>5-8</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>696124</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>962085</v>
+      </c>
+      <c r="L38" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>15-19</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>1138600</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>1766400</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333239761/</t>
+          <t>https://www.cian.ru/sale/flat/326325222/</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>знак вопроса</t>
-        </is>
-      </c>
+          <t>Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Слава»</t>
+          <t>ЖК «Квартал Life Time»</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MR Group</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2 кв. 2027</t>
+          <t>2 кв. 2026</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Москва, Ленинградский проспект, вл8</t>
+          <t>Москва, улица Сергея Макеева</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Белорусская</t>
+          <t>1905 года</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>вне зоны (Беговой, САО)</t>
+          <t>Пресненский (вне Садового)</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>8-37</t>
+          <t>9-23</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -8941,68 +9107,72 @@
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>695000</v>
+        <v>1025225</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1250000</v>
+        <v>1539792</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333570956/</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>пометка «Тише говорят!»</t>
+          <t>по Циан дом сдан</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ЖК «ЛОТ от Аквилон»</t>
+          <t>ЖК «Элитный квартал Тишинский бульвар»</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Аквилон</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>3 кв. 2029</t>
+          <t>2027–2028</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Москва, Жуков проезд, 21</t>
+          <t>Москва, Электрический переулок</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Павелецкая</t>
+          <t>Белорусская</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>вне зоны (Даниловский, ЮАО)</t>
+          <t>Пресненский (вне Садового)</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>3-14</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -9011,13 +9181,13 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>590000</v>
+        <v>1341000</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>860000</v>
+        <v>3900000</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>115</v>
+        <v>229</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -9035,40 +9205,40 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Веспер Кутузовский»</t>
+          <t>ЖК «Начало»</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Веспер</t>
+          <t>ДОНСТРОЙ</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>1 кв. 2028</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Москва, Кутузовский проспект</t>
+          <t>Москва, улица Сергея Макеева, 7</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Дорогомилово</t>
+          <t>Ул. 1905 года</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>вне зоны (Дорогомилово, ЗАО)</t>
+          <t>Пресненский (вне Садового)</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7-17</t>
+          <t>11-48</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -9077,13 +9247,13 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>1350000</v>
+        <v>975000</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>3605000</v>
+        <v>1900000</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -9096,45 +9266,49 @@
           <t>таблица заказчика</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>знак вопроса</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Бадаевский»</t>
+          <t>ЖК «Климашкина 7/11»</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>MR Group</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2026–2027</t>
+          <t>4 кв. 2028</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Москва, Кутузовский проспект</t>
+          <t>Москва, улица Климашкина, 7/11</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Дорогомилово</t>
+          <t>Красная пресня</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>вне зоны (Дорогомилово, ЗАО)</t>
+          <t>Пресненский (вне Садового)</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17-18</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -9143,13 +9317,13 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1150000</v>
+        <v>1800000</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>3100000</v>
+        <v>2550000</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -9167,82 +9341,486 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Клубный дом "Магнум Соло"</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Москва, Александра Солженицына, 23Б</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Таганский</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Таганский (вне Садового)</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>1625537</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>2067015</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/328639275/</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>ЖК «Клубный дом Энигмия»</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>4 кв. 2028</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Москва, Новослободская улица, 19</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Менделеевская</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Тверской (вне Садового)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>15-19</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>1138600</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>1766400</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333239761/</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>знак вопроса</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>ЖК «Слава»</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>MR Group</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2 кв. 2027</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Москва, Ленинградский проспект, вл8</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Белорусская</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>вне зоны (Беговой, САО)</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>8-37</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>695000</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>184</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>таблица заказчика</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>пометка «Тише говорят!»</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ЖК «ЛОТ от Аквилон»</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Аквилон</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>3 кв. 2029</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Москва, Жуков проезд, 21</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Павелецкая</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>вне зоны (Даниловский, ЮАО)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>590000</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>860000</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>таблица заказчика</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>ЖК «Веспер Кутузовский»</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Веспер</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>1 кв. 2028</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Москва, Кутузовский проспект</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Дорогомилово</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>вне зоны (Дорогомилово, ЗАО)</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>7-17</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>3605000</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>таблица заказчика</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ЖК «Бадаевский»</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2026–2027</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Москва, Кутузовский проспект</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Дорогомилово</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>вне зоны (Дорогомилово, ЗАО)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>17-18</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>таблица заказчика</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>ЖК «SHIFT»</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Пионер</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>4 кв. 2028</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Москва, жилой комплекс Шифт</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Ленинский проспект</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>вне зоны (Ленинский проспект)</t>
         </is>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G49" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J43" s="3" t="n">
+      <c r="J49" s="3" t="n">
         <v>826000</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K49" s="3" t="n">
         <v>2100000</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L49" s="3" t="n">
         <v>214</v>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>таблица заказчика</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="P49" s="2" t="inlineStr">
         <is>
           <t>пометка «Посмотреть варианты»</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Строки из таблицы заказчика дополнены живой выдачей Циан там, где ЖК найден в базе (цены и число лотов обновлены). Остальные строки — найдены в выдаче Циан по новостройкам ЦАО.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P43"/>
+  <autoFilter ref="A1:P49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -7141,13 +7141,13 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5980861</v>
+        <v>4318135</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>5980861</v>
+        <v>6843436</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>2800000</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>5500000</v>
+        <v>4189200</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>16</v>
@@ -8168,10 +8168,14 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332401547/</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -8451,36 +8455,40 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Клубные резиденции Лёвшинский, 19</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr"/>
+          <t>ЖК «Фрунзенская набережная»</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>3 кв. 2027</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большой Левшинский, 19</t>
+          <t>Москва, Фрунзенская набережная, 30</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>Фрунзенская</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
       <c r="G30" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10-13</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -8489,23 +8497,27 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2844930</v>
+        <v>2180740</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>2844930</v>
+        <v>6898288</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/328904518/</t>
+          <t>https://www.cian.ru/sale/flat/333537451/</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Циан 2026-09-07</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr"/>
@@ -8513,27 +8525,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Фрунзенская набережная»</t>
+          <t>ЖК «Коллекция Лужники»</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>Absolute Premium</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3 кв. 2027</t>
+          <t>4 кв. 2027</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Москва, Фрунзенская набережная, 30</t>
+          <t>Москва, Лужнецкая набережная</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Фрунзенская</t>
+          <t>Воробьёвы горы</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -8542,11 +8554,11 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10-13</t>
+          <t>12-18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -8555,13 +8567,13 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2180740</v>
+        <v>1218182</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>6898288</v>
+        <v>4200000</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -8570,7 +8582,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333537451/</t>
+          <t>https://www.cian.ru/sale/flat/333460103/</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -8578,32 +8590,36 @@
           <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>пометка «Изучить»</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Коллекция Лужники»</t>
+          <t>ЖК «Узоры»</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Absolute Premium</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>4 кв. 2027</t>
+          <t>4 кв. 2028</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Москва, Лужнецкая набережная</t>
+          <t>Москва, 2-й Вражский переулок, 8с2</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Воробьёвы горы</t>
+          <t>Киевская</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -8612,11 +8628,11 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12-18</t>
+          <t>9-10</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8625,13 +8641,13 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1218182</v>
+        <v>3177900</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>4200000</v>
+        <v>4559310</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -8640,7 +8656,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333460103/</t>
+          <t>https://www.cian.ru/sale/flat/333082541/</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -8650,19 +8666,19 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>пометка «Изучить»</t>
+          <t>пометка «Изучить! +»; по РБК Компании: старт продаж 2026, стройка начата (котлован)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Узоры»</t>
+          <t>ЖК «Погодинская»</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>Веспер</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -8672,12 +8688,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Москва, 2-й Вражский переулок, 8с2</t>
+          <t>Москва, Погодинская улица</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Киевская</t>
+          <t>Спортивная</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -8690,7 +8706,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -8699,13 +8715,13 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>3177900</v>
+        <v>3003600</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4559310</v>
+        <v>4855100</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -8714,7 +8730,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333082541/</t>
+          <t>https://www.cian.ru/sale/flat/332519714/</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -8724,39 +8740,39 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>пометка «Изучить! +»; по РБК Компании: старт продаж 2026, стройка начата (котлован)</t>
+          <t>РНС получено в ноябре 2025, закрытый старт продаж апрель–май 2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Погодинская»</t>
+          <t>ЖК «Дом Дау»</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Веспер</t>
+          <t>1-й Красногвардейский</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>4 кв. 2028</t>
+          <t>2 кв. 2027</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Москва, Погодинская улица</t>
+          <t>Москва, Краснопресненская набережная</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Спортивная</t>
+          <t>Москва-Сити</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Хамовники</t>
+          <t>Сити</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
@@ -8764,7 +8780,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8773,13 +8789,13 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3003600</v>
+        <v>807900</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>4855100</v>
+        <v>1995800</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>13</v>
+        <v>295</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -8788,7 +8804,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332519714/</t>
+          <t>https://www.cian.ru/sale/flat/331233664/</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -8796,49 +8812,41 @@
           <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>РНС получено в ноябре 2025, закрытый старт продаж апрель–май 2026</t>
-        </is>
-      </c>
+      <c r="P34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Дом Дау»</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>1-й КРАСНОГВАРДЕЙСКИЙ</t>
-        </is>
-      </c>
+          <t>Дом 56</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2 кв. 2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Москва, Краснопресненская набережная</t>
+          <t>Москва, Фридриха Энгельса, 56</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Москва-Сити</t>
+          <t>Басманный</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Сити</t>
+          <t>Басманный (вне Садового)</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>20-27</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -8847,23 +8855,23 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>855000</v>
+        <v>609244</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1184000</v>
+        <v>1043429</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333461162/</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr"/>
@@ -8871,23 +8879,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Дом 56</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr"/>
+          <t>ЖК «Новая, 11»</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Москва, Фридриха Энгельса, 56</t>
+          <t>Москва, улица Новая Дорога, 11Бс1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Электрозаводская</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -8896,11 +8908,11 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20-27</t>
+          <t>9-15</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -8909,23 +8921,27 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>609244</v>
+        <v>664831</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1043429</v>
+        <v>1500000</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333461162/</t>
+          <t>https://www.cian.ru/sale/flat/333531308/</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Циан 2026-09-07</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr"/>
@@ -8933,32 +8949,28 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Новая, 11»</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
+          <t>Vernissage (Апартаменты премиум-класса) (Вернисаж)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Москва, улица Новая Дорога, 11Бс1</t>
+          <t>Москва, Щипок, 26С2</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Электрозаводская</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
+          <t>Замоскворечье (вне Садового)</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
@@ -8966,36 +8978,32 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9-15</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>664831</v>
+        <v>696124</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1500000</v>
+        <v>962085</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333531308/</t>
+          <t>https://www.cian.ru/sale/flat/326325222/</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr"/>
@@ -9003,69 +9011,81 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Vernissage (Апартаменты премиум-класса) (Вернисаж)</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr"/>
+          <t>ЖК «Квартал Life Time»</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2 кв. 2026</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Москва, Щипок, 26С2</t>
+          <t>Москва, улица Сергея Макеева</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
+          <t>1905 года</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Замоскворечье (вне Садового)</t>
+          <t>Пресненский (вне Садового)</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>9-23</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>696124</v>
+        <v>1019417</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>962085</v>
+        <v>2290000</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+        <v>232</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/326325222/</t>
+          <t>https://www.cian.ru/sale/flat/333570956/</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr"/>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>по Циан дом сдан</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Квартал Life Time»</t>
+          <t>ЖК «Элитный квартал Тишинский бульвар»</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -9075,17 +9095,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2 кв. 2026</t>
+          <t>2027–2028</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Москва, улица Сергея Макеева</t>
+          <t>Москва, Электрический переулок</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1905 года</t>
+          <t>Белорусская</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -9094,11 +9114,11 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>9-23</t>
+          <t>3-14</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -9107,13 +9127,13 @@
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1025225</v>
+        <v>1239934</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1539792</v>
+        <v>3044646</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>3</v>
+        <v>229</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
@@ -9122,7 +9142,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333570956/</t>
+          <t>https://www.cian.ru/sale/flat/333476988/</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -9130,36 +9150,32 @@
           <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>по Циан дом сдан</t>
-        </is>
-      </c>
+      <c r="P39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Элитный квартал Тишинский бульвар»</t>
+          <t>ЖК «Начало»</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>ДОНСТРОЙ</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2027–2028</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Москва, Электрический переулок</t>
+          <t>Москва, улица Сергея Макеева, 7</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Белорусская</t>
+          <t>Ул. 1905 года</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -9168,11 +9184,11 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3-14</t>
+          <t>11-48</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -9181,36 +9197,44 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1341000</v>
+        <v>925200</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>3900000</v>
+        <v>1352000</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332534047/</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr"/>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>знак вопроса</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ЖК «Начало»</t>
+          <t>Дом Спорта</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ДОНСТРОЙ</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -9220,12 +9244,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Москва, улица Сергея Макеева, 7</t>
+          <t>Москва, Дружинниковская, 18</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Ул. 1905 года</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -9234,11 +9258,11 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11-48</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -9247,28 +9271,28 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>975000</v>
+        <v>2281650</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1900000</v>
+        <v>3174937</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333577651/</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>знак вопроса</t>
+          <t>старт продаж 2026, стройка начата (Ведомости)</t>
         </is>
       </c>
     </row>
@@ -9317,23 +9341,27 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1800000</v>
+        <v>1581360</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>2550000</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/331232083/</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>таблица заказчика</t>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr"/>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -12,7 +12,7 @@
     <sheet name="3. Проектирование" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Построено (вторичка)'!$A$1:$Q$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Построено (вторичка)'!$A$1:$S$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Строится'!$A$1:$P$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Проектирование'!$A$1:$Q$32</definedName>
   </definedNames>
@@ -89,10 +89,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:S86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -476,8 +476,10 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
     <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,10 +560,20 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Квартир в проекте</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Ссылка на Циан</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Сайт проекта / источник</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -633,12 +645,14 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/324077709/</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -646,7 +660,11 @@
           <t>Малая Бронная 15</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ЛидЭстейт</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>2019</t>
@@ -702,12 +720,24 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/313946912/</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>https://malaya-bronnaya15.ru/</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>акт ввода 31.07.2019</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -715,7 +745,11 @@
           <t>Armani/Casa Moscow Residences (Армани/Каса Москоу Резиденсес)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Vos'hod</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>2024</t>
@@ -771,12 +805,22 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/328853365/</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novostroy.ru/buildings/armani-casa-moscow-residences/</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>введён июль 2024; арх. John McAslan + Partners</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -844,12 +888,14 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/325322186/</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -917,12 +963,14 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/320386160/</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -990,12 +1038,14 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/333340431/</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1063,12 +1113,14 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/297109139/</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1136,12 +1188,14 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/331610087/</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1149,7 +1203,11 @@
           <t>Клубный дом TURGENEV (Тургенев)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>НеоСтрой</t>
+        </is>
+      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2023</t>
@@ -1205,12 +1263,24 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P10" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332431882/</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-klubnyy-dom-turgenev-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>5 секций; арх. Squire &amp; Partners</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1218,7 +1288,11 @@
           <t>Дом Бакст на Патриарших</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Инвестстройком</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2020</t>
@@ -1274,12 +1348,22 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/333483562/</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-dom-bakst-na-patriarshih-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>также указывается АСН-Инвест; арх. Павел Андреев</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1287,7 +1371,11 @@
           <t>Клубный дом Фон Дессин</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -1343,14 +1431,22 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/333380198/</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>сдан в 2026, продажи от застройщика</t>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sminex.com/fon-dessin</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>сдан в 2026, продажи от застройщика; реконструкция дома 1915 г.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1456,11 @@
           <t>Золотой, жилой квартал</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>2021–2023</t>
@@ -1416,12 +1516,24 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P13" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/315109130/</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>https://golden-island.moscow/</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>126 квартир + 19 двухуровневых; арх. SPEECH</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1429,7 +1541,11 @@
           <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ГК АфинаСтрой</t>
+        </is>
+      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>2019</t>
@@ -1485,12 +1601,20 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P14" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/313842757/</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>https://homehunter.ru/moscow/complex/zvonarsky-deluxe</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1498,7 +1622,11 @@
           <t>Дом в Газетном</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Актив-Центр</t>
+        </is>
+      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>2021–2022</t>
@@ -1554,12 +1682,22 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332563730/</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>https://homehunter.ru/moscow/complex/dom-v-gazetnom</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>реконструкция</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1567,7 +1705,11 @@
           <t>Малая Ордынка 19</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>2019</t>
@@ -1623,12 +1765,24 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P16" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/325238073/</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>https://mskguru.ru/novostroyki/982-zhk-malaja-ordynka-19</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>завершён сентябрь 2019</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1636,7 +1790,11 @@
           <t>Симфония набережных (Котельническая 21)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>СК-207</t>
+        </is>
+      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>2018–2022</t>
@@ -1692,12 +1850,22 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332034331/</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>https://kotelnicheskaya-21.ru/</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>4 секции</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1705,7 +1873,11 @@
           <t>Cloud Nine (Клауд Найн)</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2021–2022</t>
@@ -1727,7 +1899,7 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1761,12 +1933,20 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P18" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/331425978/</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-cloud-nine-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1774,7 +1954,11 @@
           <t>Рахманинов</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>КМ Девелопмент</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>2020</t>
@@ -1830,12 +2014,24 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P19" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/312672545/</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>https://dom-rahmaninov.ru/</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>реконструкция; также АгроСервисСтрой</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1843,7 +2039,11 @@
           <t>Клубный дом CULT (Клубный дом Культ)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Gravion</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>2025–2026</t>
@@ -1899,12 +2099,22 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/333091841/</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dom-cult.ru/</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>реконструкция гостиницы Варшава; арх. SPEECH</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1912,7 +2122,11 @@
           <t>Абрикосов</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>MR Group</t>
+        </is>
+      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>2022–2023</t>
@@ -1968,12 +2182,24 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P21" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/326531270/</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-abrikosov-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>реставрация усадьбы Абрикосовых</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1981,7 +2207,11 @@
           <t>Artisan (Артисан)</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Valartis Group</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>2020</t>
@@ -2037,12 +2267,22 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332958719/</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>https://artisanhouse.ru/</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>также указывается Era One Holding</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2050,7 +2290,11 @@
           <t>Тессинский, 1</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>INSIGMA</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>2020–2023</t>
@@ -2106,12 +2350,22 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332120866/</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>https://tessin.ru/</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>ввод август 2023</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2119,7 +2373,11 @@
           <t>Резиденция 1864</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Сбербанк Капитал / Midland Development</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>2022</t>
@@ -2175,12 +2433,24 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P24" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/325133439/</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-rezidenciya-1864-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты; бывший Царев сад</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2188,7 +2458,11 @@
           <t>Софийский</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Трансстройинвест</t>
+        </is>
+      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>2018–2019</t>
@@ -2244,12 +2518,22 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/318593959/</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-sofiyskiy-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты; введён январь 2019</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2257,7 +2541,11 @@
           <t>Клубный дом Космо 4/22</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Галс-Девелопмент</t>
+        </is>
+      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>2025</t>
@@ -2313,12 +2601,24 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="P26" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/328309502/</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>https://hals-development.ru/realty/object/kosmodamianskaya</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2326,7 +2626,11 @@
           <t>Дом NV/9</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>INSIGMA / State Development</t>
+        </is>
+      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>2020</t>
@@ -2382,12 +2686,22 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/333345222/</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novostroy-m.ru/baza/jk_nv9_artkvartal_nv9</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>NV/9 ARTKVARTAL; юрлицо Стрелецкая Слобода</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2395,7 +2709,11 @@
           <t>Собрание клубных домов ORDYNKA (Ордынка)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>INSIGMA</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>2020</t>
@@ -2417,7 +2735,7 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2451,12 +2769,20 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P28" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/331685961/</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-sobranie-klubnyh-domov-ordynka-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2464,7 +2790,11 @@
           <t>A.Residence (А Резиденс)</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>O1 Properties (СЗ А-Резиденс)</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>2024–2025</t>
@@ -2486,7 +2816,7 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2520,12 +2850,24 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="P29" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/324615659/</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-aresidence-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>арх. Цимайло Ляшенко и Партнеры</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2533,7 +2875,11 @@
           <t>Клубный дом ЦВЕТ32</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Hutton</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>2019</t>
@@ -2589,12 +2935,24 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P30" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/317801090/</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>https://hutton.ru/</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>введён 28.08.2019; апартаменты</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2602,7 +2960,11 @@
           <t>Титул на Якиманке</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Центр-Инвест</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>2022</t>
@@ -2658,12 +3020,20 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="P31" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/330420858/</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-titul-yakimanka.ru/</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2671,7 +3041,11 @@
           <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Интеко</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>2018</t>
@@ -2727,12 +3101,22 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="P32" s="4" t="n"/>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/320969979/</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novostroy.ru/buildings/balchug-viewpoint/</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2740,7 +3124,11 @@
           <t>Bogenhouse (Богенхаус)</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Lexion Development</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>2020–2021</t>
@@ -2796,12 +3184,24 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="P33" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/323818010/</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>https://bogenhouse.moscow/</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты; также ГК Дельта</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2809,7 +3209,11 @@
           <t>Титул на Серебрянической</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Центр-Инвест</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>2021</t>
@@ -2831,7 +3235,7 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2865,12 +3269,22 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P34" s="4" t="n"/>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/311744163/</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novostroy.ru/buildings/serebryanicheskaya-naberezhnaya-7-11/</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>cian years 2021 (первая очередь)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2878,7 +3292,11 @@
           <t>Полянка/44</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Группа ПСН</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>2019</t>
@@ -2900,7 +3318,7 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2934,12 +3352,22 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332405952/</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>https://44polyanka.com/</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>7 корпусов сданы март 2019; cian: застройщик ТЕЛЕКОМ</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2947,7 +3375,11 @@
           <t>Современник</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>2018</t>
@@ -3003,12 +3435,22 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="P36" s="4" t="n"/>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/330783642/</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-sovremennik-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>реновация здания XIX в.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3016,7 +3458,11 @@
           <t>Уланский, 13</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>РП Проект</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>2020</t>
@@ -3072,12 +3518,24 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="P37" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/328571404/</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>https://ulansky13.ru/</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>реконструкция особняка 1886 г.; апартаменты</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3145,12 +3603,14 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="P38" s="4" t="n"/>
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/328747959/</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3218,12 +3678,14 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
+      <c r="P39" s="4" t="n"/>
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/331607422/</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3231,7 +3693,11 @@
           <t>Меценат</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Москапстрой-ТН</t>
+        </is>
+      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>2019</t>
@@ -3253,7 +3719,7 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -3287,20 +3753,36 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
+      <c r="P40" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332410727/</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>https://mezenat.moscow/</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>24 квартиры + 3 особняка + 9 таунхаусов; юрлицо Торгпродуктсервис; арх. Илья Уткин</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Хамовники 12</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr"/>
+          <t>Саввинская 27</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Level Group</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -3308,7 +3790,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Москва, 1-й Тружеников, 12</t>
+          <t>Москва, Саввинская, 27</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3322,62 +3804,78 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>2800000</v>
+        <v>3060713</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>3151207</v>
+        <v>3095494</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>3502415</v>
+        <v>3130275</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>2</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>104–207</t>
+          <t>81–131</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/317328150/</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr"/>
+          <t>делюкс</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/330582804/</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>https://level.ru/projects/savvinskaya-27/</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Саввинская 27</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr"/>
+          <t>Carré Blanc (Карре Бланк)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 27</t>
+          <t>Москва, Пречистенская, 43</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3395,7 +3893,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -3404,20 +3902,20 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>3060713</v>
+        <v>3000000</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>3095494</v>
+        <v>3000000</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>3130275</v>
+        <v>3000000</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>81–131</t>
+          <t>147–147</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3425,28 +3923,34 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/330582804/</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="P42" s="4" t="n"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/331222940/</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Жизнь на Плющихе</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr"/>
+          <t>Brodsky (Бродский)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Москва, Погодинская, 2</t>
+          <t>Москва, 1-й Тружеников, 16</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3464,7 +3968,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14-16</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3473,53 +3977,55 @@
         </is>
       </c>
       <c r="J43" s="3" t="n">
-        <v>1253669</v>
+        <v>2446043</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>3000000</v>
+        <v>2698752</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>3680336</v>
+        <v>3339278</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>95–254</t>
+          <t>139–224</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/331461063/</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr"/>
+          <t>делюкс</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="n"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/330386808/</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Carré Blanc (Карре Бланк)</t>
+          <t>Villa Grace (Вилла Грейс)</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Vesper</t>
+          <t>ГК Стройтэкс</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020–2023</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Москва, Пречистенская, 43</t>
+          <t>Москва, Пожарский, 3</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3537,29 +4043,29 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>3000000</v>
+        <v>2635581</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>3000000</v>
+        <v>2635659</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>3000000</v>
+        <v>2637704</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>147–147</t>
+          <t>128–129</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3567,32 +4073,44 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/331222940/</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="P44" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/318719181/</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>https://villagrace-zhk.ru/</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>ввод 3 кв. 2020; часть источников 4 кв. 2022</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Brodsky (Бродский)</t>
+          <t>Magnum (Магнум)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Vesper</t>
+          <t>Magnum Development</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020–2022</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Москва, 1-й Тружеников, 16</t>
+          <t>Москва, Усачева, 9</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3610,29 +4128,29 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>14-16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J45" s="3" t="n">
-        <v>2446043</v>
+        <v>1568381</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2698752</v>
+        <v>2490110</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>3339278</v>
+        <v>2738095</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>139–224</t>
+          <t>84–215</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3640,28 +4158,42 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/330386808/</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="P45" s="4" t="n"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332629082/</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>https://magnum-house.ru/</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>арх. бюро VOSTOK</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Villa Grace (Вилла Грейс)</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr"/>
+          <t>Саввинская 17</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Level Group</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2020–2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Москва, Пожарский, 3</t>
+          <t>Москва, Саввинская, 17</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3679,7 +4211,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3688,20 +4220,20 @@
         </is>
       </c>
       <c r="J46" s="3" t="n">
-        <v>2635581</v>
+        <v>2337858</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>2635659</v>
+        <v>2453400</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>2637704</v>
+        <v>2588055</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>128–129</t>
+          <t>65–82</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -3709,28 +4241,44 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/318719181/</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="P46" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/330707597/</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>https://level.ru/projects/savvinskaya-17/</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>потолки 6.4-7 м; арх. AI Studio</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Magnum (Магнум)</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr"/>
+          <t>White Khamovniki (Вайт Хамовники)</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Hutton</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2020–2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Москва, Усачева, 9</t>
+          <t>Москва, Олсуфьевский, 9к1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3748,29 +4296,29 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J47" s="3" t="n">
-        <v>1568381</v>
+        <v>2387268</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>2490110</v>
+        <v>2387268</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>2738095</v>
+        <v>2657480</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>84–215</t>
+          <t>75–152</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -3778,28 +4326,34 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/332629082/</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="P47" s="4" t="n"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/319352551/</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Саввинская 17</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr"/>
+          <t>Пироговская 14</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Elbert Development</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021–2023</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 17</t>
+          <t>Москва, Малая Пироговская, 12</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3817,29 +4371,29 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-9</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2337858</v>
+        <v>1397059</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2453400</v>
+        <v>2033898</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2588055</v>
+        <v>2774566</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>65–82</t>
+          <t>66–254</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -3847,22 +4401,34 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/330707597/</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="P48" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/329965347/</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novostroy.ru/buildings/pirogovskaya-14/</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты; генподрядчик STRABAG</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>White Khamovniki (Вайт Хамовники)</t>
+          <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Hutton</t>
+          <t>Гардтекс</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3872,7 +4438,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Москва, Олсуфьевский, 9к1</t>
+          <t>Москва, Саввинская, 13</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3886,11 +4452,11 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3899,20 +4465,20 @@
         </is>
       </c>
       <c r="J49" s="3" t="n">
-        <v>2387268</v>
+        <v>1869231</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>2387268</v>
+        <v>1884615</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>2657480</v>
+        <v>3751412</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>75–152</t>
+          <t>125–177</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -3920,32 +4486,44 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/319352551/</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="P49" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/324116883/</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.savvin.ru/</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>арх. Цимайло Ляшенко и Партнеры</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Садовые кварталы</t>
+          <t>Хамовники 12</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Интеко</t>
+          <t>Coldy</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2018–2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Москва, Усачева, 15А</t>
+          <t>Москва, 1-й Тружеников, 12</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3959,11 +4537,11 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>5-18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -3972,20 +4550,20 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>1328904</v>
+        <v>2800000</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>2111111</v>
+        <v>3151207</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>3718750</v>
+        <v>3502415</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>54–342</t>
+          <t>104–207</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -3993,32 +4571,44 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/332375457/</t>
-        </is>
+      <c r="P50" s="3" t="n">
+        <v>36</v>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>очереди 2012–2023; в выборку попали корпуса 2018+</t>
+          <t>https://www.cian.ru/sale/flat/317328150/</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>https://khamovniki12.ru/</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>арх. Евгений Герасимов</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Пироговская 14</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr"/>
+          <t>Жизнь на Плющихе</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Донстрой</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2021–2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Москва, Малая Пироговская, 12</t>
+          <t>Москва, Погодинская, 2</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4036,58 +4626,70 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1397059</v>
+        <v>1253669</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>2033898</v>
+        <v>3000000</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>2774566</v>
+        <v>3680336</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>66–254</t>
+          <t>95–254</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/329965347/</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr"/>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/331461063/</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>https://mskguru.ru/novostroyki/1048-zhk-zhizn-na-pljuschihe</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr"/>
+          <t>Садовые кварталы</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Интеко</t>
+        </is>
+      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2018–2023</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 13</t>
+          <t>Москва, Усачева, 15А</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4101,11 +4703,11 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5-18</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -4114,33 +4716,39 @@
         </is>
       </c>
       <c r="J52" s="3" t="n">
-        <v>1869231</v>
+        <v>1328904</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>1884615</v>
+        <v>2111111</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>3751412</v>
+        <v>3718750</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>125–177</t>
+          <t>54–342</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/324116883/</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr"/>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P52" s="4" t="n"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332375457/</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>очереди 2012–2023; в выборку попали корпуса 2018+</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4208,12 +4816,14 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
+      <c r="P53" s="4" t="n"/>
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332883877/</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4281,28 +4891,34 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr">
+      <c r="P54" s="4" t="n"/>
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332938835/</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>City Park (Сити Парк)</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr"/>
+          <t>Дизайнерский дом Eleven (11)</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Холдинг РСТИ</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2019–2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Москва, Мантулинская, 9к4</t>
+          <t>Москва, Звенигородское, 11</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -4316,11 +4932,11 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>6-24</t>
+          <t>16-17</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -4329,20 +4945,20 @@
         </is>
       </c>
       <c r="J55" s="3" t="n">
-        <v>788028</v>
+        <v>1044868</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>1183147</v>
+        <v>1246251</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>2129032</v>
+        <v>1428571</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>34–251</t>
+          <t>75–191</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -4350,32 +4966,44 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/329981804/</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="P55" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332226758/</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>https://dom.eleven.ru/</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>арх. Меганом</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>NEVA TOWERS (Нева Тауэрс)</t>
+          <t>Счастье на Пресне</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Renaissance Development</t>
+          <t>Группа Эталон</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2018–2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Москва, 1-й Красногвардейский, 22с2</t>
+          <t>Москва, Красногвардейский, 15С2</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4389,33 +5017,33 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>63-79</t>
+          <t>19-21</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>615385</v>
+        <v>509615</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>854530</v>
+        <v>913838</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>1968504</v>
+        <v>1135770</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>39–254</t>
+          <t>38–104</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4423,50 +5051,52 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/332591457/</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="P56" s="4" t="n"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/331676309/</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Дом Chkalov (Чкалов)</t>
+          <t>NEVA TOWERS (Нева Тауэрс)</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Ikon Development</t>
+          <t>Renaissance Development</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2021–2025</t>
+          <t>2018–2025</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Москва, Курского Вокзала, 1</t>
+          <t>Москва, 1-й Красногвардейский, 22с2</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
+          <t>Сити</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>63-79</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4475,20 +5105,20 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>796915</v>
+        <v>615385</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>967043</v>
+        <v>854530</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>1500000</v>
+        <v>1968504</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>31–174</t>
+          <t>39–254</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4496,46 +5126,52 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/332033533/</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="P57" s="4" t="n"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332591457/</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Bauman House (Бауман Хаус)</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr"/>
+          <t>City Park (Сити Парк)</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>ГК МонАрх</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2020–2022</t>
+          <t>2019–2023</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Москва, Новая Дорога, 9</t>
+          <t>Москва, Мантулинская, 9к4</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
+          <t>Сити</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15-16</t>
+          <t>6-24</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -4544,53 +5180,61 @@
         </is>
       </c>
       <c r="J58" s="3" t="n">
-        <v>536585</v>
+        <v>788028</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>786687</v>
+        <v>1183147</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>812500</v>
+        <v>2129032</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>49–82</t>
+          <t>34–251</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/283281477/</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr"/>
+          <t>бизнес</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>1213</v>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/329981804/</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>https://citypark.moscow/</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>KAZAKOV Grand Loft (КАЗАКОВ Гранд Лофт)</t>
+          <t>Дом Chkalov (Чкалов)</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Coldy</t>
+          <t>Ikon Development</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2021–2025</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Москва, Казакова, 7</t>
+          <t>Москва, Курского Вокзала, 1</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -4608,7 +5252,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21-22</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -4617,20 +5261,20 @@
         </is>
       </c>
       <c r="J59" s="3" t="n">
-        <v>492857</v>
+        <v>796915</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>729064</v>
+        <v>967043</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>839080</v>
+        <v>1500000</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>42–73</t>
+          <t>31–174</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4638,32 +5282,34 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/324237764/</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="P59" s="4" t="n"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332033533/</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Басманный от Гранель</t>
+          <t>KAZAKOV Grand Loft (КАЗАКОВ Гранд Лофт)</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Гранель</t>
+          <t>Coldy</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2024–2025</t>
+          <t>2022–2023</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Москва, Малая Почтовая, 12</t>
+          <t>Москва, Казакова, 7</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4681,29 +5327,29 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>12-21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J60" s="3" t="n">
-        <v>560484</v>
+        <v>492857</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>718850</v>
+        <v>729064</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>923345</v>
+        <v>839080</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>28–86</t>
+          <t>42–73</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -4711,38 +5357,44 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/333613664/</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="P60" s="4" t="n"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/324237764/</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Dialog (Диалог)</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr"/>
+          <t>Басманный от Гранель</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Гранель</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2024–2025</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большая Спасская, 35</t>
+          <t>Москва, Малая Почтовая, 12</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Красносельский</t>
+          <t>Басманный</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Красносельский (вне Садового)</t>
+          <t>Басманный (вне Садового)</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
@@ -4750,7 +5402,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>22-24</t>
+          <t>12-21</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -4759,20 +5411,20 @@
         </is>
       </c>
       <c r="J61" s="3" t="n">
-        <v>754006</v>
+        <v>560484</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>998406</v>
+        <v>718850</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1187872</v>
+        <v>923345</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>38–121</t>
+          <t>28–86</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -4780,101 +5432,117 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/332479143/</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="P61" s="4" t="n"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333613664/</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RED7 (РЕД7)</t>
+          <t>Bauman House (Бауман Хаус)</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>ГК Основа</t>
+          <t>ГК КОРТРОС</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2022–2025</t>
+          <t>2020–2022</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Москва, Академика Сахарова, 7</t>
+          <t>Москва, Новая Дорога, 9</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Красносельский</t>
+          <t>Басманный</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Красносельский (вне Садового)</t>
+          <t>Басманный (вне Садового)</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>19-20</t>
+          <t>15-16</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J62" s="3" t="n">
-        <v>526700</v>
+        <v>536585</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>767285</v>
+        <v>786687</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>1402500</v>
+        <v>812500</v>
       </c>
       <c r="M62" s="3" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>39–254</t>
+          <t>49–82</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/325686030/</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr"/>
+          <t>бизнес</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="n"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/283281477/</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>https://homehunter.ru/moscow/complex/bauman-house</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>ранее Capital Group (до 2019)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Волга</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr"/>
+          <t>RED7 (РЕД7)</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>ГК Основа</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022–2025</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Москва, Докучаев, 2с3</t>
+          <t>Москва, Академика Сахарова, 7</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -4892,7 +5560,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>19-20</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -4901,20 +5569,20 @@
         </is>
       </c>
       <c r="J63" s="3" t="n">
-        <v>677419</v>
+        <v>526700</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>722271</v>
+        <v>767285</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>767123</v>
+        <v>1402500</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>73–93</t>
+          <t>39–254</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -4922,180 +5590,208 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/333351088/</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="P63" s="4" t="n"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/325686030/</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Sole Hill (Соле Хилл)</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr"/>
+          <t>Dialog (Диалог)</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Центр-Инвест</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022–2023</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Москва, Олимпийский, 12</t>
+          <t>Москва, Большая Спасская, 35</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Мещанский</t>
+          <t>Красносельский</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Мещанский (вне Садового)</t>
+          <t>Красносельский (вне Садового)</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22-24</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J64" s="3" t="n">
-        <v>700000</v>
+        <v>754006</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>850000</v>
+        <v>998406</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>950000</v>
+        <v>1187872</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>32–180</t>
+          <t>38–121</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/333427836/</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr"/>
+          <t>бизнес</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332479143/</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>https://domdialog.com/</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Lucky (Лаки)</t>
+          <t>Волга</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Vesper</t>
+          <t>Волга</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Москва, Костикова, 4к2</t>
+          <t>Москва, Докучаев, 2с3</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Красносельский</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Пресненский (вне Садового)</t>
+          <t>Красносельский (вне Садового)</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>15-21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J65" s="3" t="n">
-        <v>1296875</v>
+        <v>677419</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>1694915</v>
+        <v>722271</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>2352941</v>
+        <v>767123</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>44–253</t>
+          <t>73–93</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/333512309/</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr"/>
+          <t>бизнес</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="n"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333351088/</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novostroy.ru/buildings/dokuchaev-2/</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>апарт-комплекс Докучаев 2; ввод 12.10.2018</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Дом на Тишинке</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr"/>
+          <t>Sole Hill (Соле Хилл)</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Еврофармакол (Sole Group)</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Москва, Средний Тишинский, 5</t>
+          <t>Москва, Олимпийский, 12</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Мещанский</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Пресненский (вне Садового)</t>
+          <t>Мещанский (вне Садового)</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
@@ -5103,29 +5799,29 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>7-20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1500000</v>
+        <v>700000</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1614969</v>
+        <v>850000</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>2147239</v>
+        <v>950000</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>84–243</t>
+          <t>32–180</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -5133,28 +5829,44 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/332939786/</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="P66" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333427836/</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>https://solehills.ru/</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты; арх. Ricardo Bofill</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Fantastic House (Фантастик Хаус)</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr"/>
+          <t>Lucky (Лаки)</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2022–2023</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большой Тишинский, 30</t>
+          <t>Москва, Костикова, 4к2</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -5168,11 +5880,11 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>15-21</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -5181,20 +5893,20 @@
         </is>
       </c>
       <c r="J67" s="3" t="n">
-        <v>1117647</v>
+        <v>1296875</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>1496549</v>
+        <v>1694915</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>1544484</v>
+        <v>2352941</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>140–240</t>
+          <t>44–253</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -5202,28 +5914,34 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/325373140/</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="P67" s="4" t="n"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333512309/</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Edison House (Эдисон Хаус)</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr"/>
+          <t>Дом на Тишинке</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Донстрой</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Москва, Электрический, 10</t>
+          <t>Москва, Средний Тишинский, 5</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5241,29 +5959,29 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7-20</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J68" s="3" t="n">
-        <v>1369863</v>
+        <v>1500000</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>1369863</v>
+        <v>1614969</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>1369863</v>
+        <v>2147239</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>58–58</t>
+          <t>84–243</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -5271,20 +5989,34 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/331518334/</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="P68" s="4" t="n"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332939786/</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-dom-na-tishinke-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>арх. Павел Андреев</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Дизайнерский дом Eleven (11)</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr"/>
+          <t>Fantastic House (Фантастик Хаус)</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>СЗ Полинессо</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>2022</t>
@@ -5292,7 +6024,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Москва, Звенигородское, 11</t>
+          <t>Москва, Большой Тишинский, 30</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5310,7 +6042,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>16-17</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -5319,20 +6051,20 @@
         </is>
       </c>
       <c r="J69" s="3" t="n">
-        <v>1044868</v>
+        <v>1117647</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>1246251</v>
+        <v>1496549</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>1428571</v>
+        <v>1544484</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>75–191</t>
+          <t>140–240</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -5340,28 +6072,44 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/332226758/</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="P69" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/325373140/</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>https://fantastic-house.moscow/</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>21 квартира + 4 резиденции + 3 пентхауса; арх. Цимайло Ляшенко</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SkyView</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr"/>
+          <t>Edison House (Эдисон Хаус)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>ИК Приоритет</t>
+        </is>
+      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2023–2025</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Москва, Дружинниковская, 15А</t>
+          <t>Москва, Электрический, 10</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5375,11 +6123,11 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>20-25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -5388,20 +6136,20 @@
         </is>
       </c>
       <c r="J70" s="3" t="n">
-        <v>850000</v>
+        <v>1369863</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>1200000</v>
+        <v>1369863</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>2756939</v>
+        <v>1369863</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>47–847</t>
+          <t>58–58</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5409,28 +6157,42 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/332791431/</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="P70" s="4" t="n"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/331518334/</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-edison-house-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>cian years 2018; источники: 3 кв. 2019</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Sinatra (Синатра)</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr"/>
+          <t>SkyView</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>СЗ Киноцентр</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2018–2020</t>
+          <t>2023–2025</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Москва, Большой Тишинский, 38</t>
+          <t>Москва, Дружинниковская, 15А</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -5444,11 +6206,11 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>20-25</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -5457,20 +6219,20 @@
         </is>
       </c>
       <c r="J71" s="3" t="n">
-        <v>839130</v>
+        <v>850000</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>1052456</v>
+        <v>1200000</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1388889</v>
+        <v>2756939</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>46–180</t>
+          <t>47–847</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5478,32 +6240,42 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/329740227/</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="P71" s="4" t="n"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/332791431/</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-skyview-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>4 башни на месте Киноцентра</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Репаблик</t>
+          <t>Sinatra (Синатра)</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Forma</t>
+          <t>Glincom</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2025–2026</t>
+          <t>2018–2020</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Москва, Пресненский Вал, к2.1</t>
+          <t>Москва, Большой Тишинский, 38</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5517,33 +6289,33 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>26-34</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J72" s="3" t="n">
-        <v>716667</v>
+        <v>839130</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>943141</v>
+        <v>1052456</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>1570228</v>
+        <v>1388889</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>27–140</t>
+          <t>46–180</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5551,32 +6323,42 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/333504607/</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="P72" s="4" t="n"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/329740227/</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>https://glincom.com/sinatra/</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>реконструкция; cian years 2018/2020</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Счастье на Пресне</t>
+          <t>Репаблик</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Группа Эталон</t>
+          <t>Forma</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025–2026</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Москва, Красногвардейский, 15С2</t>
+          <t>Москва, Пресненский Вал, к2.1</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -5590,11 +6372,11 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>19-21</t>
+          <t>26-34</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -5603,20 +6385,20 @@
         </is>
       </c>
       <c r="J73" s="3" t="n">
-        <v>509615</v>
+        <v>716667</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>913838</v>
+        <v>943141</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>1135770</v>
+        <v>1570228</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>38–104</t>
+          <t>27–140</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5624,12 +6406,14 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cian.ru/sale/flat/331676309/</t>
-        </is>
-      </c>
-      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="P73" s="4" t="n"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cian.ru/sale/flat/333504607/</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5697,12 +6481,14 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr">
+      <c r="P74" s="4" t="n"/>
+      <c r="Q74" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/326492208/</t>
         </is>
       </c>
-      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5710,7 +6496,11 @@
           <t>Пресненский вал 21</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ПИК</t>
+        </is>
+      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>2019</t>
@@ -5763,15 +6553,25 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P75" s="2" t="inlineStr">
+          <t>бизнес</t>
+        </is>
+      </c>
+      <c r="P75" s="4" t="n"/>
+      <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332627285/</t>
         </is>
       </c>
-      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novostroy-m.ru/baza/jk_presnenskiy_val_21</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты; юрлицо Стройпроект</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5779,7 +6579,11 @@
           <t>The Mostman (Мостман)</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Инвест Проект</t>
+        </is>
+      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>2019</t>
@@ -5835,12 +6639,20 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr">
+      <c r="P76" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/317822534/</t>
         </is>
       </c>
-      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>https://themostman.ru/</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5848,7 +6660,11 @@
           <t>Долгоруковская 25</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>БЭЛ Девелопмент</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>2020</t>
@@ -5904,12 +6720,24 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P77" s="2" t="inlineStr">
+      <c r="P77" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/323749307/</t>
         </is>
       </c>
-      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>https://dolgorukovskaya25.ru/</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>корпуса Достижение и Традиция; апартаменты</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5917,7 +6745,11 @@
           <t>Cameo Moscow Villas (Камео Москоу Виллас)</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Stone Hedge</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>2021</t>
@@ -5973,12 +6805,24 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P78" s="2" t="inlineStr">
+      <c r="P78" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332372652/</t>
         </is>
       </c>
-      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>https://zhk-cameo-moscow-villas-i.cian.ru/</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>17 городских вилл; ввод 30.07.2021</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -6046,12 +6890,14 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P79" s="2" t="inlineStr">
+      <c r="P79" s="4" t="n"/>
+      <c r="Q79" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/331960482/</t>
         </is>
       </c>
-      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -6059,7 +6905,11 @@
           <t>Элитный дом Реномэ</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>2019</t>
@@ -6115,12 +6965,22 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P80" s="2" t="inlineStr">
+      <c r="P80" s="4" t="n"/>
+      <c r="Q80" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/333104707/</t>
         </is>
       </c>
-      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>https://mskguru.ru/novostroyki/958-zhk-renome</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>корпуса Nouveau и Heritage; арх. ADM</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -6128,7 +6988,11 @@
           <t>Клубный дом Maison Rouge (Мезон Руж)</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>MR Group</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>2019</t>
@@ -6184,12 +7048,22 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P81" s="2" t="inlineStr">
+      <c r="P81" s="4" t="n"/>
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/329909140/</t>
         </is>
       </c>
-      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>http://www.maisonrouge.moscow/</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6197,7 +7071,11 @@
           <t>Резиденция Тверская</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Kovaks (Ковакс)</t>
+        </is>
+      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>2018–2020</t>
@@ -6253,12 +7131,24 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr">
+      <c r="P82" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/333520220/</t>
         </is>
       </c>
-      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>https://homehunter.ru/moscow/complex/rezidenciya-tverskaya</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>апарт-отель; юрлицо Техноком Трейд</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6266,7 +7156,11 @@
           <t>Медный 3.14</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>2021</t>
@@ -6288,7 +7182,7 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -6322,12 +7216,24 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr">
+      <c r="P83" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/332942905/</t>
         </is>
       </c>
-      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>https://medniy.moscow/</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>арх. Сергей Скуратов</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6335,7 +7241,11 @@
           <t>Sky House (Скай Хаус)</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>2020–2022</t>
@@ -6388,25 +7298,37 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P84" s="2" t="inlineStr">
+          <t>бизнес</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>539</v>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
         <is>
           <t>https://www.cian.ru/sale/flat/333352226/</t>
         </is>
       </c>
-      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>https://info-skyhouse.ru/</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>достройка после банкротства ОЛТЭР</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>Источник: живая выдача Циан 2026-09-07 (api.cian.ru, инструмент tools/cian/cian.js), вторичка с годом дома 2018+ и новостройки по 10 районам ЦАО. Цены — ₽/м² по активным объявлениям. Застройщик и класс — по открытым данным (ручная разметка docs/premium-cao/manual.json).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q84"/>
+  <autoFilter ref="A1:S84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6590,7 +7512,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>по Циан дом сдан</t>
+          <t>по Циан дом сдан; по другим источникам застройщик: Palladio Group</t>
         </is>
       </c>
     </row>
@@ -7308,7 +8230,11 @@
           <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>по другим источникам застройщик: Балчуг Девелопмент (Balchug Estate)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -7316,7 +8242,11 @@
           <t>Kuznetsky Most 12 by Lalique (Кузнецкий Мост 12)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>KR Properties</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -7362,7 +8292,7 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/308892399/</t>
+          <t>https://www.novostroy.ru/buildings/kuznetskiy-most-12/</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -7370,7 +8300,11 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>реконструкция; коллаборация с Lalique</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -7378,7 +8312,11 @@
           <t>ТИТУЛ Империал</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Центр-Инвест</t>
+        </is>
+      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -7424,7 +8362,7 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333303331/</t>
+          <t>https://www.novostroy-m.ru/baza/jk_titul_private_titul</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -7432,7 +8370,11 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>12 лотов 83-131 м², не более 3 квартир на этаже</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -7642,7 +8584,11 @@
           <t>Клубный дом DUO (Дуо)</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Hutton</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2028</t>
@@ -7688,7 +8634,7 @@
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/329214137/</t>
+          <t>https://www.novostroy-m.ru/baza/jk_na_sofiyskoy_naberejnoy</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -7696,7 +8642,11 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>инвестор V2Group; юрлицо СЗ Суплекс Технолоджис; cian: 2028</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -7704,7 +8654,11 @@
           <t xml:space="preserve"> Клубный дом «Резиденции Воронцова»</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ГК Развитие</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>2028</t>
@@ -7726,7 +8680,7 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -7750,7 +8704,7 @@
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333496265/</t>
+          <t>https://xn----8sbfahfbojca2denabul2ii.xn--p1ai/</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -7758,7 +8712,11 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>ранее Sun Development; арх. Blank Architects</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -7766,7 +8724,11 @@
           <t>Казачий</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>MR Group</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>2029</t>
@@ -7812,7 +8774,7 @@
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333664798/</t>
+          <t>https://kazachiy-10.ru/</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -7820,7 +8782,11 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>76 квартир + 4 пентхауса; арх. WALL</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -7962,7 +8928,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>пометка «Изучить»</t>
+          <t>пометка «Изучить»; по другим источникам застройщик: Гута-Девелопмент</t>
         </is>
       </c>
     </row>
@@ -8324,7 +9290,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>пометка «Посмотреть ?»; по данным Движение.ру (май 2026) проект полностью у Tekta Group, ПИК вышел</t>
+          <t>пометка «Посмотреть ?»; по другим источникам застройщик: ТЕКТА Групп; по данным Движение.ру (май 2026) проект полностью у Tekta Group, ПИК вышел</t>
         </is>
       </c>
     </row>
@@ -8334,7 +9300,11 @@
           <t>Лё Дом</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Группа ЛСР</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -8380,7 +9350,7 @@
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333564442/</t>
+          <t>https://ledome.moscow/</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -8388,7 +9358,11 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Le Dôme; СЗ Соймоновский 3; арх. Paris Classical Architecture</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -8396,7 +9370,11 @@
           <t>ДОМ XXII</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Донстрой</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -8442,7 +9420,7 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/332297994/</t>
+          <t>https://donstroy.moscow/objects/house-XXII/</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -8450,7 +9428,11 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>арх. Сергей Киселев и Партнеры</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -8592,7 +9574,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>пометка «Изучить»</t>
+          <t>пометка «Изучить»; по другим источникам застройщик: Абсолют Недвижимость (Absolute Premium)</t>
         </is>
       </c>
     </row>
@@ -8666,7 +9648,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>пометка «Изучить! +»; по РБК Компании: старт продаж 2026, стройка начата (котлован)</t>
+          <t>пометка «Изучить! +»; по другим источникам застройщик: ГК Основа; по РБК Компании: старт продаж 2026, стройка начата (котлован)</t>
         </is>
       </c>
     </row>
@@ -8740,7 +9722,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>РНС получено в ноябре 2025, закрытый старт продаж апрель–май 2026</t>
+          <t>по другим источникам застройщик: Vesper; РНС получено в ноябре 2025, закрытый старт продаж апрель–май 2026</t>
         </is>
       </c>
     </row>
@@ -8820,7 +9802,11 @@
           <t>Дом 56</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Галс-Девелопмент</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -8842,7 +9828,7 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -8866,7 +9852,7 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/333461162/</t>
+          <t>https://hals-development.ru/</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -8874,7 +9860,11 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>арх. Pride</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -8952,7 +9942,11 @@
           <t>Vernissage (Апартаменты премиум-класса) (Вернисаж)</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Ziggurat Development</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -8998,7 +9992,7 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/326325222/</t>
+          <t>https://www.novostroy.ru/buildings/vernissage/</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -9006,7 +10000,11 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>юрлицо СЗ Щипок; апартаменты</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -9372,7 +10370,11 @@
           <t xml:space="preserve"> Клубный дом "Магнум Соло"</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Magnum Development</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>2028</t>
@@ -9418,7 +10420,7 @@
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>https://www.cian.ru/sale/flat/328639275/</t>
+          <t>https://magnumsolo.ru/</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -9426,7 +10428,11 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>юрлицо СЗ КИГ</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -9841,7 +10847,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Строки из таблицы заказчика дополнены живой выдачей Циан там, где ЖК найден в базе (цены и число лотов обновлены). Остальные строки — найдены в выдаче Циан по новостройкам ЦАО.</t>
         </is>
@@ -10079,17 +11085,17 @@
       <c r="G3" s="3" t="n">
         <v>23000</v>
       </c>
-      <c r="H3" s="5" t="n"/>
+      <c r="H3" s="4" t="n"/>
       <c r="I3" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>kvartiravmoskve.ru (также mskdeluxe.ru/start)</t>
@@ -10140,19 +11146,19 @@
       <c r="G4" s="3" t="n">
         <v>17000</v>
       </c>
-      <c r="H4" s="5" t="n"/>
+      <c r="H4" s="4" t="n"/>
       <c r="I4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="5" t="n"/>
+      <c r="J4" s="4" t="n"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>официальный сайт проекта (также whitewill.ru)</t>
@@ -10203,7 +11209,7 @@
       <c r="G5" s="3" t="n">
         <v>9377</v>
       </c>
-      <c r="H5" s="5" t="n"/>
+      <c r="H5" s="4" t="n"/>
       <c r="I5" s="3" t="n">
         <v>9</v>
       </c>
@@ -10215,9 +11221,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>novostroev.ru</t>
@@ -10265,18 +11271,18 @@
           <t>анонсирован, старт продаж ожидается</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2026–2027</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>mskdeluxe.ru</t>
@@ -10327,19 +11333,19 @@
       <c r="G7" s="3" t="n">
         <v>12000</v>
       </c>
-      <c r="H7" s="5" t="n"/>
+      <c r="H7" s="4" t="n"/>
       <c r="I7" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="5" t="n"/>
+      <c r="J7" s="4" t="n"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>sosedi.life (также mskdeluxe.ru/start, anwin.ru)</t>
@@ -10387,12 +11393,12 @@
           <t>проект на согласовании, старт продаж ожидается</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
       <c r="M8" s="3" t="n">
         <v>3000000</v>
       </c>
@@ -10451,7 +11457,7 @@
       <c r="G9" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H9" s="5" t="n"/>
+      <c r="H9" s="4" t="n"/>
       <c r="I9" s="3" t="n">
         <v>6</v>
       </c>
@@ -10463,8 +11469,8 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>2026-04-06</t>
@@ -10520,7 +11526,7 @@
       <c r="G10" s="3" t="n">
         <v>15600</v>
       </c>
-      <c r="H10" s="5" t="n"/>
+      <c r="H10" s="4" t="n"/>
       <c r="I10" s="3" t="n">
         <v>9</v>
       </c>
@@ -10592,8 +11598,8 @@
           <t>старт продаж 2026</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
       <c r="I11" s="3" t="n">
         <v>9</v>
       </c>
@@ -10605,9 +11611,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>официальный сайт проекта (также mskdeluxe.ru/start)</t>
@@ -10655,19 +11661,19 @@
           <t>старт продаж июль–август 2026</t>
         </is>
       </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
       <c r="I12" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J12" s="5" t="n"/>
+      <c r="J12" s="4" t="n"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2026-07</t>
@@ -10732,9 +11738,9 @@
       <c r="J13" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2025-12-12</t>
@@ -10787,13 +11793,13 @@
           <t>участок приобретён (март 2026), проектирование</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2026-03-17</t>
@@ -10849,12 +11855,12 @@
       <c r="G15" s="3" t="n">
         <v>46700</v>
       </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -10910,8 +11916,8 @@
       <c r="G16" s="3" t="n">
         <v>8000</v>
       </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
       <c r="J16" s="3" t="n">
         <v>77</v>
       </c>
@@ -10920,9 +11926,9 @@
           <t>2026–2027</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>kvartiravmoskve.ru (также mskdeluxe.ru/start)</t>
@@ -10973,12 +11979,12 @@
       <c r="G17" s="3" t="n">
         <v>125000</v>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2024-03-12</t>
@@ -11031,16 +12037,16 @@
           <t>анонсирован, старт продаж ожидается</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
       <c r="I18" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>anwin.ru</t>
@@ -11094,11 +12100,11 @@
       <c r="H19" s="3" t="n">
         <v>12400</v>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2025-12-18</t>
@@ -11151,8 +12157,8 @@
           <t>старт бронирования, старт продаж</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
       <c r="I20" s="3" t="n">
         <v>8</v>
       </c>
@@ -11169,8 +12175,8 @@
           <t>2 кв. 2028</t>
         </is>
       </c>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>whitewill.ru (также tehne.com, levshinsky-19.ru)</t>
@@ -11218,20 +12224,20 @@
           <t>ГПЗУ получен (апрель 2021), старт продаж ожидается</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
       <c r="I21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J21" s="5" t="n"/>
+      <c r="J21" s="4" t="n"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
           <t>2026–2027</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t>официальный сайт проекта (также novostroy.ru, mskdeluxe.ru/start)</t>
@@ -11279,17 +12285,17 @@
           <t>проект утверждён (АГР, май 2026), начало строительства 2027</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2027 (стройка)</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2026-05-28</t>
@@ -11348,11 +12354,11 @@
       <c r="H23" s="3" t="n">
         <v>8200</v>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>2026-04-24</t>
@@ -11408,14 +12414,14 @@
       <c r="G24" s="3" t="n">
         <v>2500</v>
       </c>
-      <c r="H24" s="5" t="n"/>
+      <c r="H24" s="4" t="n"/>
       <c r="I24" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>2025-07-09</t>
@@ -11471,19 +12477,19 @@
       <c r="G25" s="3" t="n">
         <v>24600</v>
       </c>
-      <c r="H25" s="5" t="n"/>
+      <c r="H25" s="4" t="n"/>
       <c r="I25" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="J25" s="5" t="n"/>
+      <c r="J25" s="4" t="n"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>novostroev.ru (также usacheva22.ru, sosedi.life)</t>
@@ -11540,15 +12546,15 @@
       <c r="I26" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J26" s="5" t="n"/>
+      <c r="J26" s="4" t="n"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>2026–2027</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>novostroy-m.ru (также mskdeluxe.ru/start)</t>
@@ -11605,7 +12611,7 @@
       <c r="I27" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="J27" s="5" t="n"/>
+      <c r="J27" s="4" t="n"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -11616,7 +12622,7 @@
           <t>2029</t>
         </is>
       </c>
-      <c r="M27" s="5" t="n"/>
+      <c r="M27" s="4" t="n"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>2026-04-07</t>
@@ -11669,20 +12675,20 @@
           <t>анонсирован, старт продаж ожидается</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
       <c r="I28" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J28" s="5" t="n"/>
+      <c r="J28" s="4" t="n"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>mskdeluxe.ru (также smart-lab.ru обзор стартов на Пресне)</t>
@@ -11730,18 +12736,18 @@
           <t>анонсирован, старт продаж ожидается</t>
         </is>
       </c>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t>novostroycity.ru</t>
@@ -11789,9 +12795,9 @@
           <t>проектирование, старт продаж ожидается во II–III кв. 2026 после проектной декларации</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
       <c r="J30" s="3" t="n">
         <v>46</v>
       </c>
@@ -11800,9 +12806,9 @@
           <t>2026 (II–III кв.)</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>официальный сайт проекта (также kvartiravmoskve.ru, whitewill.ru)</t>
@@ -11853,12 +12859,12 @@
       <c r="G31" s="3" t="n">
         <v>3200000</v>
       </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11917,11 +12923,11 @@
       <c r="H32" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
@@ -11944,7 +12950,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Источники: открытые публикации 2025–2026 (stroi.mos.ru, mos.ru, отраслевые СМИ, публичные Telegram-каналы). Закрытый канал t.me/c/3370602239 недоступен без членства — пост №1364 про ЗУ «Большой Тишинский, 8» подтверждён по открытым источникам.</t>
         </is>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -18,9 +18,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Строится'!$A$3:$P$51</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'2. Строится'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'2. Строится'!$A$1:$P$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Проектирование'!$A$3:$Q$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Проектирование'!$A$3:$Q$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'3. Проектирование'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'3. Проектирование'!$A$1:$Q$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'3. Проектирование'!$A$1:$Q$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11252,7 +11252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11455,17 +11455,17 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Берниковская набережная, 12</t>
+          <t>Большая Ордынка, 25</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Берниковская наб., 12</t>
+          <t>ул. Большая Ордынка, 25, стр. 1</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
@@ -11473,33 +11473,35 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>не раскрыт</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>проектирование</t>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Aurix Development (Группа «Эталон»)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>концепция одобрена ГЗК, подготовка к строительству, старт продаж 2026</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
-        <v>23000</v>
+        <v>17000</v>
       </c>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>166</v>
-      </c>
-      <c r="K5" s="5" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="n"/>
       <c r="N5" s="5" t="n"/>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>kvartiravmoskve.ru (также mskdeluxe.ru/start)</t>
+          <t>официальный сайт проекта (также whitewill.ru)</t>
         </is>
       </c>
       <c r="P5" s="8" t="inlineStr">
@@ -11509,24 +11511,24 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>Участок 0,6 га на первой линии Яузы, два корпуса 9–13 этажей, ~23 тыс. м², 166 квартир, «органический неоклассицизм». Делюкс. Застройщик не назван.</t>
+          <t>7 этажей + мансардный уровень, &gt;17 тыс. м², на месте конструктивистской АТС 1927 г. Де-люкс. Одобрение ГЗК упоминает whitewill.ru.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Большая Ордынка, 25</t>
+          <t>Большой Козихинский, 22</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ул. Большая Ордынка, 25, стр. 1</t>
+          <t>Большой Козихинский пер., 22</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="D6" s="28" t="inlineStr">
@@ -11534,24 +11536,26 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Aurix Development (Группа «Эталон»)</t>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>КОЛДИ / Доминанта</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>концепция одобрена ГЗК, подготовка к строительству, старт продаж 2026</t>
+          <t>проект, продажи не начаты</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
-        <v>17000</v>
+        <v>9377</v>
       </c>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" s="5" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>98</v>
+      </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>2026</t>
@@ -11560,9 +11564,9 @@
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="5" t="n"/>
       <c r="N6" s="5" t="n"/>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>официальный сайт проекта (также whitewill.ru)</t>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>novostroev.ru</t>
         </is>
       </c>
       <c r="P6" s="8" t="inlineStr">
@@ -11572,24 +11576,24 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>7 этажей + мансардный уровень, &gt;17 тыс. м², на месте конструктивистской АТС 1927 г. Де-люкс. Одобрение ГЗК упоминает whitewill.ru.</t>
+          <t>Патриаршие пруды. Статус «Проект / продажи не начаты» подтверждён novostroev.ru на 01.09.2026; включён в список перспективных стартов делюкс-класса 2026 (novostroev.ru). Официальный сайт kozihinsky22.ru недоступен (403).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Большой Козихинский, 22</t>
+          <t>Воздвиженка 7/6</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Большой Козихинский пер., 22</t>
+          <t>ул. Воздвиженка, 7/6</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Арбат</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
@@ -11597,29 +11601,23 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>КОЛДИ / Доминанта</t>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>АПРИ (по данным vozdvizhenka7.ru)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>проект, продажи не начаты</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>9377</v>
-      </c>
+          <t>анонсирован, старт продаж ожидается</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
-      <c r="I7" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>98</v>
-      </c>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026–2027</t>
         </is>
       </c>
       <c r="L7" s="5" t="n"/>
@@ -11627,7 +11625,7 @@
       <c r="N7" s="5" t="n"/>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>novostroev.ru</t>
+          <t>mskdeluxe.ru</t>
         </is>
       </c>
       <c r="P7" s="8" t="inlineStr">
@@ -11637,24 +11635,24 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>Патриаршие пруды. Статус «Проект / продажи не начаты» подтверждён novostroev.ru на 01.09.2026; включён в список перспективных стартов делюкс-класса 2026 (novostroev.ru). Официальный сайт kozihinsky22.ru недоступен (403).</t>
+          <t>Указан в базе делюкс-стартов 2026–2027 mskdeluxe.ru. Агрегаторы описывают как бутик-дом на 10–15 квартир; ранее указывалась сдача 1 кв. 2025 — данные противоречивы, официальный сайт vozdvizhenka7.ru недоступен (503). Требует верификации.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Воздвиженка 7/6</t>
+          <t>Клубные дома на Берниковской набережной, 12 (Sminex)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ул. Воздвиженка, 7/6</t>
+          <t>Берниковская набережная, 12, стр. 1 (здание бывшей школы №1685, 1936 г., арх. А. Машинский)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Арбат</t>
+          <t>Таганский</t>
         </is>
       </c>
       <c r="D8" s="28" t="inlineStr">
@@ -11662,31 +11660,41 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>АПРИ (по данным vozdvizhenka7.ru)</t>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>анонсирован, старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>2026–2027</t>
-        </is>
-      </c>
+          <t>проектирование; предварительная архитектурная концепция (бюро 80/88) опубликована в марте 2026</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>23336</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>9–13 (два корпуса; 9-этажный многосекционный вдоль набережной, 13-этажный в глубине со стороны Берникова переулка)</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>166</v>
+      </c>
+      <c r="K8" s="5" t="n"/>
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>mskdeluxe.ru</t>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>Novostroy-M.ru (пресс-релиз Sminex, 18.03.2025); Москвич Mag (17.03.2026)</t>
         </is>
       </c>
       <c r="P8" s="8" t="inlineStr">
@@ -11696,24 +11704,24 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>Указан в базе делюкс-стартов 2026–2027 mskdeluxe.ru. Агрегаторы описывают как бутик-дом на 10–15 квартир; ранее указывалась сдача 1 кв. 2025 — данные противоречивы, официальный сайт vozdvizhenka7.ru недоступен (503). Требует верификации.</t>
+          <t>Участок 0,6 га на первой линии Яузы, два корпуса 9–13 этажей, ~23 тыс. м², 166 квартир, «органический неоклассицизм». Делюкс. Застройщик не назван.; Sminex приобрел площадку в конце 2024 г.; по пресс-релизу — два элитных клубных дома 7–13 этажей, общая площадь 21,4 тыс. м², из них ~13 тыс. м² жилья. По концепции 80/88 (Москвич Mag, https://moskvichmag.ru/gorod/poyavilsya-proekt-mnogosektsionnogo-zhk-na-bernikovskoj-naberezhnoj-na-meste-zakrytoj-shkoly) — 23 336 м², 166 квартир; участок 0,6 га; отмечается, что окончательная реализация именно этого проекта не гарантирована. Агрегатор kvartiravmoskve.ru: стадия «проектирование», монолит-кирпич, подземный паркинг.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Малая Дмитровка, 5/9</t>
+          <t>Клубный дом Duo (Софийская набережная, усадьба Кокорева)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ул. Малая Дмитровка, 5/9</t>
+          <t>Софийская набережная (бывшая усадьба Кокорева), напротив Кремля</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Тверской</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
@@ -11721,35 +11729,37 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Группа «Эталон»</t>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>V2 Group (владелец площадки; fee-девелопер Hutton вышел из проекта в июне 2026)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>анонсирован, старт продаж ожидается в 2026 г.</t>
+          <t>строительство завершается; сдача II кв. 2026, выдача ключей до конца декабря 2026; продано ~27%; ищется новый партнер</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>12000</v>
+        <v>18700</v>
       </c>
       <c r="H9" s="5" t="n"/>
-      <c r="I9" s="7" t="n">
-        <v>9</v>
-      </c>
+      <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>2026 Q2 (ключи — декабрь 2026)</t>
+        </is>
+      </c>
       <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>sosedi.life (также mskdeluxe.ru/start, anwin.ru)</t>
+          <t>Коммерсантъ (17.06.2026)</t>
         </is>
       </c>
       <c r="P9" s="8" t="inlineStr">
@@ -11759,19 +11769,19 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>Участок ~0,4 га у сада «Эрмитаж», 2 корпуса 7–9 этажей, волнообразные фасады, делюкс-класс.</t>
+          <t>Не новая очередь Golden Island, а смена управляющего девелопера на Софийской набережной: Hutton (И. Давыдик, А. Антонов) вышел из проекта; собственник V2 Group (В. Фоминых, В. Грознов) купил площадку у MR Group в 2023 за ~4,5–5 млрд руб. Новых очередей «Золотого острова» (Capital Group, ЖК «Золотой») в 2025–2026 не анонсировано.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Малая Никитская, 27</t>
+          <t>Клубный дом «Большая Никитская, 16» (R4S)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Малая Никитская ул., 27</t>
+          <t>Большая Никитская улица, 16 (реконструкция доходного дома, объект культурного наследия)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -11784,33 +11794,43 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>не раскрыт</t>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>R4S Group (генподрядчик — Спецжилремонт)</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>проект на согласовании, старт продаж ожидается</t>
+          <t>реконструкция; старт продаж I кв. 2026; ввод III кв. 2026</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="7" t="n">
-        <v>3000000</v>
-      </c>
+      <c r="I10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>2026 Q1 (старт продаж)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>2026 Q3</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>sosedi.life (также moskvichmag.ru, 31.03.2024)</t>
+          <t>Novostroev.ru (19.01.2026); sosedi.life</t>
         </is>
       </c>
       <c r="P10" s="8" t="inlineStr">
@@ -11820,24 +11840,24 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом высотой 33 м по проекту бюро WALL на месте двух двухэтажных особняков (бывший отель Club 27). Ориентировочная цена «от ~3 млн руб./м²» — оценка источника, не подтверждена застройщиком. В базе mskdeluxe.ru фигурирует как «Малая Никитская, 29-31».</t>
+          <t>Единственная публичная новинка на Большой Никитской в 2025–2026: 4 квартиры 139,4 / 141,4 / 151 / 234 м². Другие участки на Большой Никитской в открытых анонсах не найдены.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Малая Ордынка, 14/1</t>
+          <t>Клубный дом «Малая Никитская, 27»</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ул. Малая Ордынка, 14/1</t>
+          <t>Малая Никитская улица, 27 (два двухэтажных особняка 1861 г., бывший «Клуб 27»)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
@@ -11845,41 +11865,33 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Гута-Девелопмент</t>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>не раскрыт (по данным форума pronovostroy.ru — Mono/ПИК; официально не подтверждено)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>старт продаж 06.04.2026</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>3000</v>
-      </c>
+          <t>проект на согласовании (высотность 33 м); продажи не открыты</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
-      <c r="I11" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
       <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
+      <c r="M11" s="7" t="n">
+        <v>3000000</v>
+      </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>sosedi.life (также novostroev.ru обзор делюкс-стартов 2026)</t>
+          <t>Москвич Mag (31.03.2024); sosedi.life (07.04.2026); pronovostroy.ru</t>
         </is>
       </c>
       <c r="P11" s="8" t="inlineStr">
@@ -11889,19 +11901,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>Участок 0,1 га, 11 квартир, 14 подземных м/м, архитектура A2M. Делюкс.</t>
+          <t>Клубный дом высотой 33 м по проекту бюро WALL на месте двух двухэтажных особняков (бывший отель Club 27). Ориентировочная цена «от ~3 млн руб./м²» — оценка источника, не подтверждена застройщиком. В базе mskdeluxe.ru фигурирует как «Малая Никитская, 29-31».; Архитектура — бюро WALL (ярусные объемы, черно-белые фасады). Существующие здания ~4 000 м² сносятся. Цена ~3 млн руб./м² — предварительное рыночное ожидание (sosedi.life, https://sosedi.life/news/zhk-malaya-nikitskaya-27/), не оферта. Restate.ru (2025–2026) отмечал неопределенность со стартом: возможна продажа площадки вместо запуска.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Палашёвский 11 (Большой Палашёвский, 11–13/15)</t>
+          <t>Малая Дмитровка, 5/9</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Большой Палашёвский пер., 11–13</t>
+          <t>ул. Малая Дмитровка, 5/9</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -11914,47 +11926,35 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Sminex (СЗ «Смайнэкс Палашёвский 11»)</t>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Группа «Эталон»</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>старт продаж без стройки (закрытый старт 22.04.2026)</t>
+          <t>анонсирован, старт продаж ожидается в 2026 г.</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>15600</v>
+        <v>12000</v>
       </c>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="J12" s="7" t="n">
-        <v>43</v>
-      </c>
+      <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>1 кв. 2030</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>novostroev.ru</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>sosedi.life (также mskdeluxe.ru/start, anwin.ru)</t>
         </is>
       </c>
       <c r="P12" s="8" t="inlineStr">
@@ -11964,24 +11964,24 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>Три корпуса 8–9 этажей с контрастными фасадами у Патриарших. Старт продаж 22.04.2026, лоты от 222,4 млн руб. (nngm.ru), от ~3,5 млн руб./м². Сдача 1 кв. 2030 (novostroev.ru, обзор делюкс-стартов 2026).</t>
+          <t>Участок ~0,4 га у сада «Эрмитаж», 2 корпуса 7–9 этажей, волнообразные фасады, делюкс-класс.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Полянка-3</t>
+          <t>Малая Дмитровка, 5/9 (ожидаемый делюкс-старт)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ул. Малая Полянка, 3</t>
+          <t>Малая Дмитровка, 5/9</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Тверской</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
@@ -11989,35 +11989,27 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Aurix Development (Группа «Эталон»)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>старт продаж 2026</t>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>не раскрыт</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>в списке ожидаемых стартов делюкс-класса 2026 (агрегатор); подробностей нет</t>
         </is>
       </c>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
-      <c r="I13" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>официальный сайт проекта (также mskdeluxe.ru/start)</t>
+          <t>mskdeluxe.ru (список стартов делюкс 2026)</t>
         </is>
       </c>
       <c r="P13" s="8" t="inlineStr">
@@ -12027,24 +12019,24 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>9 этажей, 34 квартиры, паркинг на 36 м/м, проект Etalon Project. Продажи открыты в 2026 г.; стадия строительства в открытых источниках не уточнена.</t>
+          <t>Единственное упоминание новой площадки в зоне Петровка/Дмитровка; по Петровке и Большой Дмитровке в 2025–2026 новых анонсов не найдено (только реализуемые «Советник» (Insigma) и Petrovsky).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Роден (ранее анонсировался как Veil)</t>
+          <t>Малая Никитская, 29–31 (ожидаемый делюкс-старт)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Большой Харитоньевский пер., 13А</t>
+          <t>Малая Никитская улица, 29–31</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="D14" s="28" t="inlineStr">
@@ -12054,35 +12046,25 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>MR Group</t>
+          <t>не раскрыт</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>старт продаж июль–август 2026</t>
+          <t>в списке ожидаемых стартов делюкс-класса 2026 (агрегатор); подробностей нет</t>
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
-      <c r="I14" s="7" t="n">
-        <v>7</v>
-      </c>
+      <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
+      <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
+      <c r="N14" s="5" t="n"/>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>novostroev.ru (также roden.moscow)</t>
+          <t>mskdeluxe.ru (список стартов делюкс 2026)</t>
         </is>
       </c>
       <c r="P14" s="8" t="inlineStr">
@@ -12092,24 +12074,24 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом делюкс-класса у Чистых прудов, 1 монолитный корпус 7 этажей, архитектура WALL. В обзоре делюкс-стартов 2026 novostroev.ru фигурировал как Veil, 9 этажей.</t>
+          <t>В том же списке mskdeluxe.ru: М. Дмитровка 5/9, Льва Толстого 14, Хилков 3, Б. Пироговская 51, Б. Харитоньевский 13, Олсуфьевский 10, Большая Ордынка 25, Воздвиженка 7/6, Малая Полянка 3 — без параметров и девелоперов.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Рождественка 8</t>
+          <t>Малая Ордынка, 14/1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ул. Рождественка / Кузнецкий Мост / Варсонофьевский пер.</t>
+          <t>ул. Малая Ордынка, 14/1</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Мещанский</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="D15" s="28" t="inlineStr">
@@ -12117,39 +12099,41 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Sminex (проект выкуплен у «Галс-Девелопмент»)</t>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Гута-Девелопмент</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>проект приобретён, старт продаж ожидается</t>
+          <t>старт продаж 06.04.2026</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>36400</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>18000</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="H15" s="5" t="n"/>
       <c r="I15" s="7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>115</v>
-      </c>
-      <c r="K15" s="5" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>РИА Недвижимость (также kommersant.ru/doc/8291907, cre.ru)</t>
+          <t>sosedi.life (также novostroev.ru обзор делюкс-стартов 2026)</t>
         </is>
       </c>
       <c r="P15" s="8" t="inlineStr">
@@ -12159,320 +12143,348 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>Семь корпусов 2–10 этажей, 115 квартир 61–426 м², таунхаусы и пентхаусы, двор-парк Scape, реставрация особняка конца XIX в. Сделка 12.12.2025.</t>
+          <t>Участок 0,1 га, 11 квартир, 14 подземных м/м, архитектура A2M. Делюкс.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Палашёвский 11 (Большой Палашёвский, 11–13/15)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Большой Палашёвский пер., 11–13</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Тверской</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Sminex (СЗ «Смайнэкс Палашёвский 11»)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>старт продаж без стройки (закрытый старт 22.04.2026)</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>15600</v>
+      </c>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>1 кв. 2030</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>novostroev.ru</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>Три корпуса 8–9 этажей с контрастными фасадами у Патриарших. Старт продаж 22.04.2026, лоты от 222,4 млн руб. (nngm.ru), от ~3,5 млн руб./м². Сдача 1 кв. 2030 (novostroev.ru, обзор делюкс-стартов 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Полянка-3</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ул. Малая Полянка, 3</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Aurix Development (Группа «Эталон»)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>старт продаж 2026</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>официальный сайт проекта (также mskdeluxe.ru/start)</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>9 этажей, 34 квартиры, паркинг на 36 м/м, проект Etalon Project. Продажи открыты в 2026 г.; стадия строительства в открытых источниках не уточнена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Роден (ранее анонсировался как Veil)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Большой Харитоньевский пер., 13А</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Басманный</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>MR Group</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>старт продаж июль–август 2026</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>novostroev.ru (также roden.moscow)</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом делюкс-класса у Чистых прудов, 1 монолитный корпус 7 этажей, архитектура WALL. В обзоре делюкс-стартов 2026 novostroev.ru фигурировал как Veil, 9 этажей.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Рождественка 8</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ул. Рождественка / Кузнецкий Мост / Варсонофьевский пер.</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Мещанский</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Sminex (проект выкуплен у «Галс-Девелопмент»)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>проект приобретён, старт продаж ожидается</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>36400</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>115</v>
+      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>РИА Недвижимость (также kommersant.ru/doc/8291907, cre.ru)</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>Семь корпусов 2–10 этажей, 115 квартир 61–426 м², таунхаусы и пентхаусы, двор-парк Scape, реставрация особняка конца XIX в. Сделка 12.12.2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>Типография Сытина (Пятницкая, 71/5)</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>ул. Пятницкая, 71/5 (2-й Монетчиковский пер., 5)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Sminex</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>участок приобретён (март 2026), проектирование</t>
         </is>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>РИА Недвижимость (также sminex.com, mperspektiva.ru)</t>
         </is>
       </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>Участок 1,8 га, 8 зданий 38,5 тыс. м², в т.ч. 3 корпуса типографии Сытина (ОКН, арх. Эрихсон/Шухов). Продавец — В. Погребенко, оценка сделки 12–14 млрд руб., инвестиции 25–30 млрд руб. План: реставрация + новые элитные клубные дома. Участок у Садового кольца (Валовая ул.).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Большая Пироговская, 51 (общежития Института красной профессуры)</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>ул. Большая Пироговская, 51</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="D17" s="29" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Vesper (fee-девелопер) / собственник Capital Group</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>анонсирован (fee-development), концепция</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>46700</v>
-      </c>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="10" t="n"/>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="10" t="n"/>
-      <c r="M17" s="10" t="n"/>
-      <c r="N17" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="O17" s="9" t="inlineStr">
-        <is>
-          <t>РИА Недвижимость (также vedomosti.ru 18.06.2026)</t>
-        </is>
-      </c>
-      <c r="P17" s="13" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q17" s="9" t="inlineStr">
-        <is>
-          <t>Участок 1,5 га, ансамбль восьми 6-этажных корпусов 1929–32 гг. (арх. Осипов, Рухлядев; статус памятника утрачен в 2000-х). Планируемая площадь выросла с 39 до 46,7 тыс. м². Vesper — концепция, продукт и управление реализацией. В базе mskdeluxe.ru — «Б.Пироговская, 51».</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Земледельческий, 15</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Земледельческий пер., 15</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="D18" s="29" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>не раскрыт</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>проектирование</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="10" t="n"/>
-      <c r="J18" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>2026–2027</t>
-        </is>
-      </c>
-      <c r="L18" s="10" t="n"/>
-      <c r="M18" s="10" t="n"/>
-      <c r="N18" s="10" t="n"/>
-      <c r="O18" s="9" t="inlineStr">
-        <is>
-          <t>kvartiravmoskve.ru (также mskdeluxe.ru/start)</t>
-        </is>
-      </c>
-      <c r="P18" s="13" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q18" s="9" t="inlineStr">
-        <is>
-          <t>Участок 0,3 га (сейчас административное здание 1975 г., 5 эт., 5,7 тыс. м²), клубный дом ~8 тыс. м², 77 квартир, коммерция, подземный паркинг. Делюкс.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Квартал на Савинской набережной («Московский шёлк»)</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Савинская наб. (территория БЦ «Московский шёлк»)</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="D19" s="29" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Sminex</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>проектирование</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>125000</v>
-      </c>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="10" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="10" t="inlineStr">
-        <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="O19" s="9" t="inlineStr">
-        <is>
-          <t>РИА Недвижимость (стадия подтверждена mperspektiva.ru 18.12.2025)</t>
-        </is>
-      </c>
-      <c r="P19" s="13" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q19" s="9" t="inlineStr">
-        <is>
-          <t>ЖК ~125 тыс. м² на территории делового квартала «Московский шёлк». По данным Sminex на декабрь 2025 г. находится в стадии проектирования (вместе с Лужнецкой).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Курсовой, 15</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Курсовой пер., 15 (Остоженка)</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="D20" s="29" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>не раскрыт (проект бюро Дмитрия Великовского)</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>анонсирован, старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="10" t="n"/>
-      <c r="M20" s="10" t="n"/>
-      <c r="N20" s="10" t="n"/>
-      <c r="O20" s="10" t="inlineStr">
-        <is>
-          <t>anwin.ru</t>
-        </is>
-      </c>
-      <c r="P20" s="13" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q20" s="9" t="inlineStr">
-        <is>
-          <t>«Золотая миля», 6 этажей, камерный клубный дом. Подробные параметры и застройщик в открытых источниках не раскрыты.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Льва Толстого, 14–16 (три клубных дома Sminex)</t>
+          <t>Большая Пироговская, 51 (общежития Института красной профессуры)</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>ул. Льва Толстого, 14</t>
+          <t>ул. Большая Пироговская, 51</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -12485,22 +12497,20 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>Sminex</t>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Vesper (fee-девелопер) / собственник Capital Group</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>участок приобретён (декабрь 2025), концепция в финальной стадии, старт продаж не объявлен</t>
+          <t>анонсирован (fee-development), концепция</t>
         </is>
       </c>
       <c r="G21" s="12" t="n">
-        <v>20300</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>12400</v>
-      </c>
+        <v>46700</v>
+      </c>
+      <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="10" t="n"/>
       <c r="K21" s="10" t="n"/>
@@ -12508,12 +12518,12 @@
       <c r="M21" s="10" t="n"/>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="O21" s="9" t="inlineStr">
         <is>
-          <t>Московская перспектива (также rbc.ru 18.12.2025, sosedi.life 07.04.2026)</t>
+          <t>РИА Недвижимость (также vedomosti.ru 18.06.2026)</t>
         </is>
       </c>
       <c r="P21" s="13" t="inlineStr">
@@ -12523,19 +12533,19 @@
       </c>
       <c r="Q21" s="9" t="inlineStr">
         <is>
-          <t>Участок ~0,6 га у делового квартала «Красная Роза», куплен у структур А. Клячина. Три камерных клубных дома, надземная площадь 20,3 тыс. м², квартиры 12,4 тыс. м². Сохраняется фасад бывшего доходного дома Трындина-Жиро.</t>
+          <t>Участок 1,5 га, ансамбль восьми 6-этажных корпусов 1929–32 гг. (арх. Осипов, Рухлядев; статус памятника утрачен в 2000-х). Планируемая площадь выросла с 39 до 46,7 тыс. м². Vesper — концепция, продукт и управление реализацией. В базе mskdeluxe.ru — «Б.Пироговская, 51».</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Лёвшинский, 19</t>
+          <t>Квартал на Савинской набережной («Московский шёлк»)</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Большой Лёвшинский пер., 19</t>
+          <t>Савинская наб. (территория БЦ «Московский шёлк»)</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -12548,39 +12558,33 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>ТСИ Девелопмент (ГК «Трансстройинвест»)</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>старт бронирования, старт продаж</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="n"/>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>проектирование</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>125000</v>
+      </c>
       <c r="H22" s="10" t="n"/>
-      <c r="I22" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
-        <is>
-          <t>2 кв. 2028</t>
-        </is>
-      </c>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="n"/>
+      <c r="L22" s="10" t="n"/>
       <c r="M22" s="10" t="n"/>
-      <c r="N22" s="10" t="n"/>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
       <c r="O22" s="9" t="inlineStr">
         <is>
-          <t>whitewill.ru (также tehne.com, levshinsky-19.ru)</t>
+          <t>РИА Недвижимость (стадия подтверждена mperspektiva.ru 18.12.2025)</t>
         </is>
       </c>
       <c r="P22" s="13" t="inlineStr">
@@ -12590,19 +12594,19 @@
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
-          <t>Воссоздание фасада доходного дома Духовских (1904, арх. Мейснер), проект HADAA Architects. 16 резиденций 70–239 м², паркинг 18 м/м. Цена от 197,12 млн руб. за лот. Стадия стройки в источниках не подтверждена.</t>
+          <t>ЖК ~125 тыс. м² на территории делового квартала «Московский шёлк». По данным Sminex на декабрь 2025 г. находится в стадии проектирования (вместе с Лужнецкой).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Олсуфьевский 10</t>
+          <t>Клубный дом «Земледельческий, 15»</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Олсуфьевский пер., 10</t>
+          <t>Земледельческий переулок, 15 (на месте административного здания 1975 г., 5 этажей, 5 744 м²)</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -12617,20 +12621,22 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Грандор (Grandor)</t>
+          <t>не раскрыт</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>ГПЗУ получен (апрель 2021), старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="n"/>
+          <t>проектирование (агрегаторы; в списке ожидаемых стартов делюкс-класса 2026 на mskdeluxe.ru)</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>8000</v>
+      </c>
       <c r="H23" s="10" t="n"/>
-      <c r="I23" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="12" t="n">
+        <v>77</v>
+      </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
           <t>2026–2027</t>
@@ -12638,10 +12644,14 @@
       </c>
       <c r="L23" s="10" t="n"/>
       <c r="M23" s="10" t="n"/>
-      <c r="N23" s="10" t="n"/>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
       <c r="O23" s="9" t="inlineStr">
         <is>
-          <t>официальный сайт проекта (также novostroy.ru, mskdeluxe.ru/start)</t>
+          <t>kvartiravmoskve.ru (обновлено 21.06.2026); mskdeluxe.ru/start</t>
         </is>
       </c>
       <c r="P23" s="13" t="inlineStr">
@@ -12651,60 +12661,54 @@
       </c>
       <c r="Q23" s="9" t="inlineStr">
         <is>
-          <t>Участок 0,4 га, семь корпусов 5–8 этажей в индивидуальной архитектуре. В базе делюкс-стартов 2026–2027 mskdeluxe.ru.</t>
+          <t>Участок 0,3 га (сейчас административное здание 1975 г., 5 эт., 5,7 тыс. м²), клубный дом ~8 тыс. м², 77 квартир, коммерция, подземный паркинг. Делюкс.; Участок 0,3 га; делюкс; 77 квартир + коммерческая часть; подземный паркинг; монолит-кирпич; 1 км до м. Смоленская. Сделок по продаже БЦ и решений Москомархитектуры в открытых источниках не найдено.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Премиальный квартал на Лужнецкой набережной, 10А</t>
+          <t>Клубный дом на Курсовом переулке, 15 (проект бюро Дмитрия Великовского)</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Лужнецкая наб., вл. 10А</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
+          <t>Курсовой переулок, 15</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Хамовники (Остоженка)</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D24" s="29" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>Sminex</t>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>не раскрыт (проект бюро Дмитрия Великовского)</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>проект утверждён (АГР, май 2026), начало строительства 2027</t>
+          <t>проект / предстарт; в открытых источниках только страница агрегатора</t>
         </is>
       </c>
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="10" t="n"/>
-      <c r="I24" s="10" t="n"/>
+      <c r="I24" s="12" t="n">
+        <v>6</v>
+      </c>
       <c r="J24" s="10" t="n"/>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>2027 (стройка)</t>
-        </is>
-      </c>
+      <c r="K24" s="10" t="n"/>
       <c r="L24" s="10" t="n"/>
       <c r="M24" s="10" t="n"/>
-      <c r="N24" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
+      <c r="N24" s="10" t="n"/>
       <c r="O24" s="9" t="inlineStr">
         <is>
-          <t>РИА Недвижимость (также anwin.ru)</t>
+          <t>Anwin (агрегатор элитной недвижимости)</t>
         </is>
       </c>
       <c r="P24" s="13" t="inlineStr">
@@ -12714,19 +12718,19 @@
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
-          <t>Два жилых корпуса переменной этажности в неоклассике + эллиптический БЦ 26 тыс. м² («яйцо Фаберже»). Концепция согласована Департаментом градостроительной политики (В. Овчинский). Параметры жилой части не раскрыты.</t>
+          <t>«Золотая миля», 6 этажей, камерный клубный дом. Подробные параметры и застройщик в открытых источниках не раскрыты.; По описанию агрегатора: 6-этажный дом по проекту бюро Дмитрия Великовского, панорамное остекление, локация «Золотой мили» рядом с Зачатьевским монастырем. Сейчас по адресу — детский клуб-студия «Пречистенские ворота». Пресса (Коммерсант, РБК, Ведомости, Москвич Mag) и Москомархитектура публикаций по площадке не имеют; девелопер и параметры не подтверждены.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Тимура Фрунзе, 11 (клубный дом Sminex)</t>
+          <t>Льва Толстого, 14–16 (три клубных дома Sminex)</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>ул. Тимура Фрунзе, 11, стр. 7, 19, 33, 50</t>
+          <t>ул. Льва Толстого, 14</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -12746,14 +12750,14 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>участок приобретён (апрель 2026), проектирование</t>
+          <t>участок приобретён (декабрь 2025), концепция в финальной стадии, старт продаж не объявлен</t>
         </is>
       </c>
       <c r="G25" s="12" t="n">
-        <v>13000</v>
+        <v>20300</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>8200</v>
+        <v>12400</v>
       </c>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="10" t="n"/>
@@ -12762,12 +12766,12 @@
       <c r="M25" s="10" t="n"/>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="O25" s="9" t="inlineStr">
         <is>
-          <t>РИА Недвижимость (также sminex.com, interfax-russia.ru)</t>
+          <t>Московская перспектива (также rbc.ru 18.12.2025, sosedi.life 07.04.2026)</t>
         </is>
       </c>
       <c r="P25" s="13" t="inlineStr">
@@ -12777,19 +12781,19 @@
       </c>
       <c r="Q25" s="9" t="inlineStr">
         <is>
-          <t>Участок 0,5 га (бывшая шёлковая фабрика, 4 здания 5 тыс. м²), продавец KR Properties (А. Клячин), переход прав 23.04.2026. Камерный клубный дом: пентхаусы с видом на Кремль, виллы, двор-сад; фасады по ул. Тимура Фрунзе сохраняются.</t>
+          <t>Участок ~0,6 га у делового квартала «Красная Роза», куплен у структур А. Клячина. Три камерных клубных дома, надземная площадь 20,3 тыс. м², квартиры 12,4 тыс. м². Сохраняется фасад бывшего доходного дома Трындина-Жиро.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Усадьба в Большом Саввинском переулке (клубный дом VSF)</t>
+          <t>Лёвшинский, 19</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Большой Саввинский пер. (усадьба купца Якунина)</t>
+          <t>Большой Лёвшинский пер., 19</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -12804,33 +12808,37 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>ГК «Векторстройфинанс» (VSF)</t>
+          <t>ТСИ Девелопмент (ГК «Трансстройинвест»)</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>анонсирован (приобретение объекта), концепция</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>2500</v>
-      </c>
+          <t>старт бронирования, старт продаж</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="n"/>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J26" s="10" t="n"/>
-      <c r="K26" s="10" t="n"/>
-      <c r="L26" s="10" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>2 кв. 2028</t>
+        </is>
+      </c>
       <c r="M26" s="10" t="n"/>
-      <c r="N26" s="10" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="O26" s="10" t="inlineStr">
-        <is>
-          <t>elitnoe.ru</t>
+      <c r="N26" s="10" t="n"/>
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t>whitewill.ru (также tehne.com, levshinsky-19.ru)</t>
         </is>
       </c>
       <c r="P26" s="13" t="inlineStr">
@@ -12840,19 +12848,19 @@
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
-          <t>Четырёхэтажное здание 1889 г. и двухэтажное до 1812 г., ~2,5 тыс. м². Оценка инвестиций 3,5–4,5 млрд руб., стоимость объекта до 1,3 млрд руб. Планируется перестройка в элитный клубный дом.</t>
+          <t>Воссоздание фасада доходного дома Духовских (1904, арх. Мейснер), проект HADAA Architects. 16 резиденций 70–239 м², паркинг 18 м/м. Цена от 197,12 млн руб. за лот. Стадия стройки в источниках не подтверждена.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Усачёва, 22</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>ул. Усачёва, 22</t>
+          <t>Олсуфьевский 10</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Олсуфьевский пер., 10</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -12865,27 +12873,25 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Regions Development</t>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Грандор (Grandor)</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>проект, продажи не начаты</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>24600</v>
-      </c>
+          <t>ГПЗУ получен (апрель 2021), старт продаж ожидается</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J27" s="10" t="n"/>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026–2027</t>
         </is>
       </c>
       <c r="L27" s="10" t="n"/>
@@ -12893,7 +12899,7 @@
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="9" t="inlineStr">
         <is>
-          <t>novostroev.ru (также usacheva22.ru, sosedi.life)</t>
+          <t>официальный сайт проекта (также novostroy.ru, mskdeluxe.ru/start)</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr">
@@ -12903,19 +12909,19 @@
       </c>
       <c r="Q27" s="9" t="inlineStr">
         <is>
-          <t>Участок ~0,4 га, два корпуса ~14 и 18 этажей, архитектура Arch(e)type, двор без машин. Площадь 24,6 тыс. м² — по обзору делюкс-стартов 2026 novostroev.ru.</t>
+          <t>Участок 0,4 га, семь корпусов 5–8 этажей в индивидуальной архитектуре. В базе делюкс-стартов 2026–2027 mskdeluxe.ru.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Хилков (Хилков переулок, вл. 3)</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Хилков пер., вл. 3</t>
+          <t>Премиальный квартал на Лужнецкой набережной, 10А</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Лужнецкая наб., вл. 10А</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -12930,439 +12936,778 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>Rose Group</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>проектирование (долгосрочный проект), старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>19806</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>8800</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>8</v>
-      </c>
+          <t>проект утверждён (АГР, май 2026), начало строительства 2027</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="10" t="n"/>
       <c r="J28" s="10" t="n"/>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>2026–2027</t>
+          <t>2027 (стройка)</t>
         </is>
       </c>
       <c r="L28" s="10" t="n"/>
       <c r="M28" s="10" t="n"/>
-      <c r="N28" s="10" t="n"/>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
       <c r="O28" s="9" t="inlineStr">
         <is>
+          <t>РИА Недвижимость (также anwin.ru)</t>
+        </is>
+      </c>
+      <c r="P28" s="13" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q28" s="9" t="inlineStr">
+        <is>
+          <t>Два жилых корпуса переменной этажности в неоклассике + эллиптический БЦ 26 тыс. м² («яйцо Фаберже»). Концепция согласована Департаментом градостроительной политики (В. Овчинский). Параметры жилой части не раскрыты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Тимура Фрунзе, 11 (клубный дом Sminex)</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>ул. Тимура Фрунзе, 11, стр. 7, 19, 33, 50</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>участок приобретён (апрель 2026), проектирование</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>13000</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>8200</v>
+      </c>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="10" t="n"/>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="10" t="n"/>
+      <c r="M29" s="10" t="n"/>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t>РИА Недвижимость (также sminex.com, interfax-russia.ru)</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q29" s="9" t="inlineStr">
+        <is>
+          <t>Участок 0,5 га (бывшая шёлковая фабрика, 4 здания 5 тыс. м²), продавец KR Properties (А. Клячин), переход прав 23.04.2026. Камерный клубный дом: пентхаусы с видом на Кремль, виллы, двор-сад; фасады по ул. Тимура Фрунзе сохраняются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Усадьба в Большом Саввинском переулке (клубный дом VSF)</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Большой Саввинский пер. (усадьба купца Якунина)</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>ГК «Векторстройфинанс» (VSF)</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>анонсирован (приобретение объекта), концепция</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="10" t="n"/>
+      <c r="M30" s="10" t="n"/>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>elitnoe.ru</t>
+        </is>
+      </c>
+      <c r="P30" s="13" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q30" s="9" t="inlineStr">
+        <is>
+          <t>Четырёхэтажное здание 1889 г. и двухэтажное до 1812 г., ~2,5 тыс. м². Оценка инвестиций 3,5–4,5 млрд руб., стоимость объекта до 1,3 млрд руб. Планируется перестройка в элитный клубный дом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Усачёва, 22</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>ул. Усачёва, 22</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Regions Development</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>проект, продажи не начаты</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>24600</v>
+      </c>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="n"/>
+      <c r="M31" s="10" t="n"/>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t>novostroev.ru (также usacheva22.ru, sosedi.life)</t>
+        </is>
+      </c>
+      <c r="P31" s="13" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q31" s="9" t="inlineStr">
+        <is>
+          <t>Участок ~0,4 га, два корпуса ~14 и 18 этажей, архитектура Arch(e)type, двор без машин. Площадь 24,6 тыс. м² — по обзору делюкс-стартов 2026 novostroev.ru.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Хилков (Хилков переулок, вл. 3)</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Хилков пер., вл. 3</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="D32" s="29" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Rose Group</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>проектирование (долгосрочный проект), старт продаж ожидается</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>19806</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>8800</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>2026–2027</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="n"/>
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
           <t>novostroy-m.ru (также mskdeluxe.ru/start)</t>
         </is>
       </c>
-      <c r="P28" s="13" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q28" s="9" t="inlineStr">
+      <c r="P32" s="13" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q32" s="9" t="inlineStr">
         <is>
           <t>3–8 этажей, монолит-кирпич, коммерция 1,8 тыс. м², паркинг 170 м/м. Карточка novostroy-m.ru датирована 2016 г.; проект вновь фигурирует в списке делюкс-стартов 2026–2027 на mskdeluxe.ru. Актуальность требует проверки.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Aurus Residences / Страна.Сити</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>2-й Красногвардейский проезд, квартал «Камушки»</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D29" s="30" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>Страна Девелопмент</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>ГПЗУ получен, подготовка к старту продаж</t>
         </is>
       </c>
-      <c r="G29" s="17" t="n">
+      <c r="G33" s="17" t="n">
         <v>280800</v>
       </c>
-      <c r="H29" s="17" t="n">
+      <c r="H33" s="17" t="n">
         <v>231800</v>
       </c>
-      <c r="I29" s="17" t="n">
+      <c r="I33" s="17" t="n">
         <v>97</v>
       </c>
-      <c r="J29" s="15" t="n"/>
-      <c r="K29" s="15" t="inlineStr">
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="15" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L29" s="15" t="inlineStr">
+      <c r="L33" s="15" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="M29" s="15" t="n"/>
-      <c r="N29" s="15" t="inlineStr">
+      <c r="M33" s="15" t="n"/>
+      <c r="N33" s="15" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="O29" s="15" t="inlineStr">
+      <c r="O33" s="15" t="inlineStr">
         <is>
           <t>sosedi.life</t>
         </is>
       </c>
-      <c r="P29" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q29" s="14" t="inlineStr">
+      <c r="P33" s="18" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q33" s="14" t="inlineStr">
         <is>
           <t>Две башни 83 и 97 этажей на шестиярусном стилобате, участок ~1,25 га, архитектура APEX. ГПЗУ получен летом 2024 г., проект проходит согласования. Бизнес/премиум-класс, апартаменты.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>Капранова, 3</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>пер. Капранова, 3 (участки Верхний Предтеченский пер., 11 и Малый Предтеченский пер., 1)</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Жилые башни «Сити-2» (2-й Красногвардейский проезд)</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>2-й Красногвардейский проезд, Пресненский район (площадка 1,255 га у «Москва-Сити»)</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D30" s="30" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>ГК «Страна Девелопмент» (право застройки получено на торгах города; прежний правообладатель — ООО «Моссититстрой»)</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>АГР двух жилых башен утвержден (декабрь 2025); старт продаж не объявлен</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>281000</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>232000</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>две башни, самая высокая — 384 м по утвержденному АГР (ранее заявлялось до 450 м)</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="15" t="n"/>
+      <c r="L34" s="15" t="n"/>
+      <c r="M34" s="15" t="n"/>
+      <c r="N34" s="15" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="O34" s="14" t="inlineStr">
+        <is>
+          <t>72.ru / сеть городских порталов (30.12.2025); IRN.ru (18.04.2024)</t>
+        </is>
+      </c>
+      <c r="P34" s="18" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q34" s="14" t="inlineStr">
+        <is>
+          <t>~232 тыс. м² жилья и 49 тыс. м² нежилых помещений (IRN.ru, https://www.irn.ru/news/156498.html). Самый высокий жилой комплекс России по утвержденной концепции. Отдельно на Novostroy-M числится «Сити-2» Capital Group (квартал 804, Камушки, три башни до 450 м, ~470 тыс. м², ~385 тыс. м² жилья, «скоро старт») — иная площадка в том же районе, не путать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>МФК «На Краснопресненской набережной» (Трёхгорная мануфактура)</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Краснопресненская наб., 10</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>Сити</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>ГК Ташир</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>анонсирован, старт продаж ожидается</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+      <c r="J35" s="15" t="n"/>
+      <c r="K35" s="15" t="n"/>
+      <c r="L35" s="15" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="M35" s="15" t="n"/>
+      <c r="N35" s="15" t="n"/>
+      <c r="O35" s="15" t="inlineStr">
+        <is>
+          <t>novostroycity.ru</t>
+        </is>
+      </c>
+      <c r="P35" s="18" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q35" s="14" t="inlineStr">
+        <is>
+          <t>Участок ~1,7 га с ОКН (фабрика Трёхгорной мануфактуры, будет сохранена/реконструирована). Апартаменты премиум-класса + офисы + wellness, подземный паркинг на 750 м/м. Сроки реализации официально не подтверждены; апартаменты, а не квартиры.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>Клубный дом «Капельский, 5»</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>Капельский переулок, 5</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>Мещанский</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>Мещанский (вне Садового)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>не раскрыт (юрлицо на сайте проекта не указано)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>проектирование / предстарт продаж (официально: открытие продаж планируется во II–III кв. 2026)</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>8–9</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n">
+        <v>46</v>
+      </c>
+      <c r="K36" s="21" t="inlineStr">
+        <is>
+          <t>2026 Q2–Q3 (старт продаж)</t>
+        </is>
+      </c>
+      <c r="L36" s="21" t="inlineStr">
+        <is>
+          <t>2029 Q4 (по данным Whitewill)</t>
+        </is>
+      </c>
+      <c r="M36" s="24" t="n"/>
+      <c r="N36" s="24" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="O36" s="21" t="inlineStr">
+        <is>
+          <t>Официальный сайт kapelsky5.ru; Whitewill; Novostroy-M</t>
+        </is>
+      </c>
+      <c r="P36" s="26" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q36" s="21" t="inlineStr">
+        <is>
+          <t>46 резиденций, переменная этажность, пентхаусы с террасами, приватный сквер, подземный паркинг. ВНИМАНИЕ: локация вне Садового кольца (у м. Проспект Мира, ~1 км севернее), включена по запросу заказчика.; Делюкс/премиум клубный дом; квартиры 54–345 м²; пентхаусы с террасами; двухуровневый паркинг на 56 м/м, 32 кладовые; приватный сад во дворе. Whitewill (https://whitewill.ru/developments/kapelskiy-5) указывает 8 этажей и срок сдачи 4 кв. 2029; Novostroy-M — 9 этажей, «скоро старт». Цены по запросу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>Делюкс-комплекс «Капранова, 3» (проект APEX)</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>переулок Капранова, 3 (БЦ «Премьер Плаза») + Малый Предтеченский пер., 1/2/1, Нововаганьковский пер., 3 стр. 1, Глубокий пер., 7</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>Пресненский (вне Садового)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>не раскрыт</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>анонсирован, старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="J30" s="15" t="n"/>
-      <c r="K30" s="15" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="15" t="n"/>
-      <c r="N30" s="15" t="n"/>
-      <c r="O30" s="14" t="inlineStr">
-        <is>
-          <t>mskdeluxe.ru (также smart-lab.ru обзор стартов на Пресне)</t>
-        </is>
-      </c>
-      <c r="P30" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q30" s="14" t="inlineStr">
-        <is>
-          <t>Делюкс-проект в базе перспективных стартов 2026–2027 (mskdeluxe.ru, цены «от 60 млн руб.»). Обзор smart-lab.ru/blog/1231916.php указывает старт продаж в 2026 г., 12 этажей, двор без машин. Застройщик и параметры в открытых источниках не подтверждены. ~400 м от м. Краснопресненская, вне Садового кольца.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>МФК «На Краснопресненской набережной» (Трёхгорная мануфактура)</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>Краснопресненская наб., 10</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="F37" s="19" t="inlineStr">
+        <is>
+          <t>визуализации направлены на согласование в город (ноябрь 2025); предстарт, старт продаж заявлен на 2026</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="n"/>
+      <c r="H37" s="20" t="n"/>
+      <c r="I37" s="19" t="inlineStr">
+        <is>
+          <t>9–23 (шесть корпусов)</t>
+        </is>
+      </c>
+      <c r="J37" s="22" t="n">
+        <v>255</v>
+      </c>
+      <c r="K37" s="19" t="inlineStr">
+        <is>
+          <t>2026 (старт продаж)</t>
+        </is>
+      </c>
+      <c r="L37" s="20" t="n"/>
+      <c r="M37" s="20" t="n"/>
+      <c r="N37" s="20" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="O37" s="19" t="inlineStr">
+        <is>
+          <t>Москвич Mag (19.11.2025); sosedi.life (07.04.2026)</t>
+        </is>
+      </c>
+      <c r="P37" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q37" s="19" t="inlineStr">
+        <is>
+          <t>Делюкс-проект в базе перспективных стартов 2026–2027 (mskdeluxe.ru, цены «от 60 млн руб.»). Обзор smart-lab.ru/blog/1231916.php указывает старт продаж в 2026 г., 12 этажей, двор без машин. Застройщик и параметры в открытых источниках не подтверждены. ~400 м от м. Краснопресненская, вне Садового кольца.; Единая застройка нескольких участков за Домом Правительства у Пресненского детского парка; башни с «волнообразными» фасадами, снос БЦ «Премьер Плаза», сохранение усадьбы Резанова. По sosedi.life (https://sosedi.life/news/zhk-kapranova-3/): участок &gt;2,5 га, 6 корпусов 9–23 этажа, 255 квартир, двор 7 039,6 м², лобби Balcon, 2–5 квартир на этаже. Указанные в запросе «12 этажей» источниками не подтверждаются. В списке делюкс-стартов mskdeluxe.ru.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>КРТ вдоль Звенигородского шоссе (три участка, 73,62 га)</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>Вдоль Звенигородского шоссе между 3-й Магистральной улицей и ТТК (Пресненский / Хорошёвский районы)</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>Пресненский / Хорошёвский</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>Пресненский (вне Садового)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>не раскрыт (оператор/инвестор не назван; в числе 9 проектов КРТ, утвержденных в августе 2026)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>решение о КРТ принято (август 2026); оператор/торги не объявлены</t>
+        </is>
+      </c>
+      <c r="G38" s="25" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="H38" s="24" t="n"/>
+      <c r="I38" s="24" t="n"/>
+      <c r="J38" s="24" t="n"/>
+      <c r="K38" s="24" t="n"/>
+      <c r="L38" s="24" t="n"/>
+      <c r="M38" s="24" t="n"/>
+      <c r="N38" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="O38" s="21" t="inlineStr">
+        <is>
+          <t>Интерфакс-Россия; Ведомости.Город (02.09.2026)</t>
+        </is>
+      </c>
+      <c r="P38" s="26" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q38" s="21" t="inlineStr">
+        <is>
+          <t>Три участка нежилой застройки общей площадью 73,62 га; &gt;3,2 млн м² недвижимости (жильё + общественно-деловые объекты, школы на 4050 мест, детсады на 1775 мест), 35,5 тыс. рабочих мест. Часть «Большого Сити» (Шелепиха/Магистральные улицы), класс жилья не заявлен — не обязательно премиум.; Три участка нежилой застройки (старые склады, админздания) общей площадью 73,62 га; свыше 3,2 млн м² — жилье, общественно-деловые и социальные объекты; строительство/реконструкция дорог ~6,5 км; здание конечной станции наземного транспорта с отстойно-разворотной площадкой (Ведомости, https://www.vedomosti.ru/gorod/ourcity/articles/gorodskoi-kvartal). Жилая премиальная часть отдельно не выделена; класс жилья не указан. Оператор (Московский фонд реновации / КРТ 21 / инвестор по торгам) не объявлен.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Участок КРТ «Большой Тишинский переулок, 8»</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>Большой Тишинский переулок, 8 (стр. 1, 2)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr">
-        <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>ГК Ташир</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>анонсирован, старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G31" s="15" t="n"/>
-      <c r="H31" s="15" t="n"/>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="n"/>
-      <c r="K31" s="15" t="n"/>
-      <c r="L31" s="15" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="M31" s="15" t="n"/>
-      <c r="N31" s="15" t="n"/>
-      <c r="O31" s="15" t="inlineStr">
-        <is>
-          <t>novostroycity.ru</t>
-        </is>
-      </c>
-      <c r="P31" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q31" s="14" t="inlineStr">
-        <is>
-          <t>Участок ~1,7 га с ОКН (фабрика Трёхгорной мануфактуры, будет сохранена/реконструирована). Апартаменты премиум-класса + офисы + wellness, подземный паркинг на 750 м/м. Сроки реализации официально не подтверждены; апартаменты, а не квартиры.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="21" t="inlineStr">
-        <is>
-          <t>Капельский, 5</t>
-        </is>
-      </c>
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>Капельский пер., 5</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>Мещанский</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>Мещанский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>Пресненский (вне Садового)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>не раскрыт</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
-        <is>
-          <t>проектирование, старт продаж ожидается во II–III кв. 2026 после проектной декларации</t>
-        </is>
-      </c>
-      <c r="G32" s="24" t="n"/>
-      <c r="H32" s="24" t="n"/>
-      <c r="I32" s="24" t="n"/>
-      <c r="J32" s="25" t="n">
-        <v>46</v>
-      </c>
-      <c r="K32" s="24" t="inlineStr">
-        <is>
-          <t>2026 (II–III кв.)</t>
-        </is>
-      </c>
-      <c r="L32" s="24" t="n"/>
-      <c r="M32" s="24" t="n"/>
-      <c r="N32" s="24" t="n"/>
-      <c r="O32" s="21" t="inlineStr">
-        <is>
-          <t>официальный сайт проекта (также kvartiravmoskve.ru, whitewill.ru)</t>
-        </is>
-      </c>
-      <c r="P32" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q32" s="21" t="inlineStr">
-        <is>
-          <t>46 резиденций, переменная этажность, пентхаусы с террасами, приватный сквер, подземный паркинг. ВНИМАНИЕ: локация вне Садового кольца (у м. Проспект Мира, ~1 км севернее), включена по запросу заказчика.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>КРТ вдоль Звенигородского шоссе (Пресненский / Хорошёвский)</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>Звенигородское шоссе, между 3-й Магистральной ул. и ТТК (1-я Магистральная, 25 и др.)</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="inlineStr">
-        <is>
-          <t>не раскрыт</t>
-        </is>
-      </c>
-      <c r="F33" s="20" t="inlineStr">
-        <is>
-          <t>ЗУ/КРТ утверждён</t>
-        </is>
-      </c>
-      <c r="G33" s="22" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="H33" s="20" t="n"/>
-      <c r="I33" s="20" t="n"/>
-      <c r="J33" s="20" t="n"/>
-      <c r="K33" s="20" t="n"/>
-      <c r="L33" s="20" t="n"/>
-      <c r="M33" s="20" t="n"/>
-      <c r="N33" s="20" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="O33" s="20" t="inlineStr">
-        <is>
-          <t>Агентство «Москва»</t>
-        </is>
-      </c>
-      <c r="P33" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q33" s="19" t="inlineStr">
-        <is>
-          <t>Три участка нежилой застройки общей площадью 73,62 га; &gt;3,2 млн м² недвижимости (жильё + общественно-деловые объекты, школы на 4050 мест, детсады на 1775 мест), 35,5 тыс. рабочих мест. Часть «Большого Сити» (Шелепиха/Магистральные улицы), класс жилья не заявлен — не обязательно премиум.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>Участок КРТ «Большой Тишинский переулок, 8»</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>Большой Тишинский пер., 8 (два административных здания 1909–1915 гг.)</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
-        <is>
-          <t>не раскрыт</t>
-        </is>
-      </c>
-      <c r="F34" s="24" t="inlineStr">
-        <is>
-          <t>ЗУ/КРТ утверждён</t>
-        </is>
-      </c>
-      <c r="G34" s="25" t="n">
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>решение о КРТ (по данным заказчика — август 2026); оператор/правообладатель и торги в открытых источниках не найдены</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="n">
         <v>10000</v>
       </c>
-      <c r="H34" s="25" t="n">
+      <c r="H39" s="22" t="n">
         <v>6000</v>
       </c>
-      <c r="I34" s="24" t="n"/>
-      <c r="J34" s="24" t="n"/>
-      <c r="K34" s="24" t="n"/>
-      <c r="L34" s="24" t="n"/>
-      <c r="M34" s="24" t="n"/>
-      <c r="N34" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="O34" s="24" t="inlineStr">
-        <is>
-          <t>АСН-инфо</t>
-        </is>
-      </c>
-      <c r="P34" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q34" s="21" t="inlineStr">
-        <is>
-          <t>Участок ~0,3 га включён в программу КРТ решением властей Москвы. Существующие здания реконструированы в 2004 г., в 2020 г. переоборудованы под хостелы. Оператор/девелопер в публикации не назван; в других открытых источниках на 07.09.2026 не найден. Локация — Пресненский район вне Садового кольца, между Б. Грузинской и Пресненским Валом (условно отнесено к зоне Пресня/Сити).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="I39" s="20" t="n"/>
+      <c r="J39" s="20" t="n"/>
+      <c r="K39" s="20" t="n"/>
+      <c r="L39" s="20" t="n"/>
+      <c r="M39" s="20" t="n"/>
+      <c r="N39" s="20" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="O39" s="19" t="inlineStr">
+        <is>
+          <t>krt.mos.ru (реестр проектов КРТ Москвы)</t>
+        </is>
+      </c>
+      <c r="P39" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q39" s="19" t="inlineStr">
+        <is>
+          <t>Участок ~0,3 га включён в программу КРТ решением властей Москвы. Существующие здания реконструированы в 2004 г., в 2020 г. переоборудованы под хостелы. Оператор/девелопер в публикации не назван; в других открытых источниках на 07.09.2026 не найден. Локация — Пресненский район вне Садового кольца, между Б. Грузинской и Пресненским Валом (условно отнесено к зоне Пресня/Сити).; Поиск по mos.ru, krt.mos.ru, stroi.mos.ru, Ведомости, РБК, Интерфакс, М24, Известия (август–сентябрь 2026) не выявил отдельной публикации по этому участку: новости августа 2026 о КРТ (250 проектов, 63 договора с начала года) даются агрегированно. Ближайший крупный проект — квартал «Тишинский бульвар» Sminex (Электрический пер., 1), связь с участком №8 не подтверждена. Площадь 0,3 га / ~10 000 м² — из исходных данных запроса, независимого подтверждения нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>Источники: открытые публикации 2025–2026 (stroi.mos.ru, mos.ru, отраслевые СМИ, публичные Telegram-каналы). Закрытый канал t.me/c/3370602239 недоступен без членства — пост №1364 про ЗУ «Большой Тишинский, 8» подтверждён по открытым источникам.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q34"/>
+  <autoFilter ref="A3:Q39"/>
   <mergeCells count="3">
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A36:Q36"/>
+    <mergeCell ref="A41:Q41"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId1"/>
@@ -13396,6 +13741,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId36"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -18,9 +18,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Строится'!$A$3:$P$51</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'2. Строится'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'2. Строится'!$A$1:$P$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Проектирование'!$A$3:$Q$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Проектирование'!$A$3:$Q$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'3. Проектирование'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'3. Проектирование'!$A$1:$Q$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'3. Проектирование'!$A$1:$Q$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr"/>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Клубный дом DUO (Дуо)</t>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>инвестор V2Group; юрлицо СЗ Суплекс Технолоджис; cian: 2028</t>
+          <t>Софийская наб., усадьба Кокорева; в июне 2026 fee-девелопер Hutton вышел из проекта, площадка у V2 Group (Коммерсантъ); инвестор V2Group; юрлицо СЗ Суплекс Технолоджис; cian: 2028</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11711,17 +11711,17 @@
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом Duo (Софийская набережная, усадьба Кокорева)</t>
+          <t>Клубный дом «Большая Никитская, 16» (R4S)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Софийская набережная (бывшая усадьба Кокорева), напротив Кремля</t>
+          <t>Большая Никитская улица, 16 (реконструкция доходного дома, объект культурного наследия)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
@@ -11731,35 +11731,41 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>V2 Group (владелец площадки; fee-девелопер Hutton вышел из проекта в июне 2026)</t>
+          <t>R4S Group (генподрядчик — Спецжилремонт)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>строительство завершается; сдача II кв. 2026, выдача ключей до конца декабря 2026; продано ~27%; ищется новый партнер</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>18700</v>
-      </c>
+          <t>реконструкция; старт продаж I кв. 2026; ввод III кв. 2026</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (ключи — декабрь 2026)</t>
+      <c r="I9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>2026 Q1 (старт продаж)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>2026 Q3</t>
         </is>
       </c>
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>Коммерсантъ (17.06.2026)</t>
+          <t>Novostroev.ru (19.01.2026); sosedi.life</t>
         </is>
       </c>
       <c r="P9" s="8" t="inlineStr">
@@ -11769,19 +11775,19 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>Не новая очередь Golden Island, а смена управляющего девелопера на Софийской набережной: Hutton (И. Давыдик, А. Антонов) вышел из проекта; собственник V2 Group (В. Фоминых, В. Грознов) купил площадку у MR Group в 2023 за ~4,5–5 млрд руб. Новых очередей «Золотого острова» (Capital Group, ЖК «Золотой») в 2025–2026 не анонсировано.</t>
+          <t>Единственная публичная новинка на Большой Никитской в 2025–2026: 4 квартиры 139,4 / 141,4 / 151 / 234 м². Другие участки на Большой Никитской в открытых анонсах не найдены.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом «Большая Никитская, 16» (R4S)</t>
+          <t>Клубный дом «Малая Никитская, 27»</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Большая Никитская улица, 16 (реконструкция доходного дома, объект культурного наследия)</t>
+          <t>Малая Никитская улица, 27 (два двухэтажных особняка 1861 г., бывший «Клуб 27»)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -11796,41 +11802,31 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>R4S Group (генподрядчик — Спецжилремонт)</t>
+          <t>не раскрыт (по данным форума pronovostroy.ru — Mono/ПИК; официально не подтверждено)</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>реконструкция; старт продаж I кв. 2026; ввод III кв. 2026</t>
+          <t>проект на согласовании (высотность 33 м); продажи не открыты</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
-      <c r="I10" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q1 (старт продаж)</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>2026 Q3</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="7" t="n">
+        <v>3000000</v>
+      </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>Novostroev.ru (19.01.2026); sosedi.life</t>
+          <t>Москвич Mag (31.03.2024); sosedi.life (07.04.2026); pronovostroy.ru</t>
         </is>
       </c>
       <c r="P10" s="8" t="inlineStr">
@@ -11840,24 +11836,24 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>Единственная публичная новинка на Большой Никитской в 2025–2026: 4 квартиры 139,4 / 141,4 / 151 / 234 м². Другие участки на Большой Никитской в открытых анонсах не найдены.</t>
+          <t>Клубный дом высотой 33 м по проекту бюро WALL на месте двух двухэтажных особняков (бывший отель Club 27). Ориентировочная цена «от ~3 млн руб./м²» — оценка источника, не подтверждена застройщиком. В базе mskdeluxe.ru фигурирует как «Малая Никитская, 29-31».; Архитектура — бюро WALL (ярусные объемы, черно-белые фасады). Существующие здания ~4 000 м² сносятся. Цена ~3 млн руб./м² — предварительное рыночное ожидание (sosedi.life, https://sosedi.life/news/zhk-malaya-nikitskaya-27/), не оферта. Restate.ru (2025–2026) отмечал неопределенность со стартом: возможна продажа площадки вместо запуска.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом «Малая Никитская, 27»</t>
+          <t>Малая Дмитровка, 5/9</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Малая Никитская улица, 27 (два двухэтажных особняка 1861 г., бывший «Клуб 27»)</t>
+          <t>ул. Малая Дмитровка, 5/9</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Тверской</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
@@ -11865,33 +11861,35 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>не раскрыт (по данным форума pronovostroy.ru — Mono/ПИК; официально не подтверждено)</t>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Группа «Эталон»</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>проект на согласовании (высотность 33 м); продажи не открыты</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
+          <t>анонсирован, старт продаж ожидается в 2026 г.</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>12000</v>
+      </c>
       <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
+      <c r="I11" s="7" t="n">
+        <v>9</v>
+      </c>
       <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="L11" s="5" t="n"/>
-      <c r="M11" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>2024-03-31</t>
-        </is>
-      </c>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>Москвич Mag (31.03.2024); sosedi.life (07.04.2026); pronovostroy.ru</t>
+          <t>sosedi.life (также mskdeluxe.ru/start, anwin.ru)</t>
         </is>
       </c>
       <c r="P11" s="8" t="inlineStr">
@@ -11901,24 +11899,24 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом высотой 33 м по проекту бюро WALL на месте двух двухэтажных особняков (бывший отель Club 27). Ориентировочная цена «от ~3 млн руб./м²» — оценка источника, не подтверждена застройщиком. В базе mskdeluxe.ru фигурирует как «Малая Никитская, 29-31».; Архитектура — бюро WALL (ярусные объемы, черно-белые фасады). Существующие здания ~4 000 м² сносятся. Цена ~3 млн руб./м² — предварительное рыночное ожидание (sosedi.life, https://sosedi.life/news/zhk-malaya-nikitskaya-27/), не оферта. Restate.ru (2025–2026) отмечал неопределенность со стартом: возможна продажа площадки вместо запуска.</t>
+          <t>Участок ~0,4 га у сада «Эрмитаж», 2 корпуса 7–9 этажей, волнообразные фасады, делюкс-класс.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Малая Дмитровка, 5/9</t>
+          <t>Малая Никитская, 29–31 (ожидаемый делюкс-старт)</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ул. Малая Дмитровка, 5/9</t>
+          <t>Малая Никитская улица, 29–31</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Тверской</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="D12" s="28" t="inlineStr">
@@ -11928,33 +11926,25 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Группа «Эталон»</t>
+          <t>не раскрыт</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>анонсирован, старт продаж ожидается в 2026 г.</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>12000</v>
-      </c>
+          <t>в списке ожидаемых стартов делюкс-класса 2026 (агрегатор); подробностей нет</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
-      <c r="I12" s="7" t="n">
-        <v>9</v>
-      </c>
+      <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="K12" s="5" t="n"/>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="5" t="n"/>
       <c r="N12" s="5" t="n"/>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>sosedi.life (также mskdeluxe.ru/start, anwin.ru)</t>
+          <t>mskdeluxe.ru (список стартов делюкс 2026)</t>
         </is>
       </c>
       <c r="P12" s="8" t="inlineStr">
@@ -11964,24 +11954,24 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>Участок ~0,4 га у сада «Эрмитаж», 2 корпуса 7–9 этажей, волнообразные фасады, делюкс-класс.</t>
+          <t>В том же списке mskdeluxe.ru: М. Дмитровка 5/9, Льва Толстого 14, Хилков 3, Б. Пироговская 51, Б. Харитоньевский 13, Олсуфьевский 10, Большая Ордынка 25, Воздвиженка 7/6, Малая Полянка 3 — без параметров и девелоперов.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Малая Дмитровка, 5/9 (ожидаемый делюкс-старт)</t>
+          <t>Малая Ордынка, 14/1</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Малая Дмитровка, 5/9</t>
+          <t>ул. Малая Ордынка, 14/1</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Тверской</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
@@ -11991,25 +11981,39 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>не раскрыт</t>
+          <t>Гута-Девелопмент</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>в списке ожидаемых стартов делюкс-класса 2026 (агрегатор); подробностей нет</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n"/>
+          <t>старт продаж 06.04.2026</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>3000</v>
+      </c>
       <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
+      <c r="I13" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>mskdeluxe.ru (список стартов делюкс 2026)</t>
+          <t>sosedi.life (также novostroev.ru обзор делюкс-стартов 2026)</t>
         </is>
       </c>
       <c r="P13" s="8" t="inlineStr">
@@ -12019,24 +12023,24 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>Единственное упоминание новой площадки в зоне Петровка/Дмитровка; по Петровке и Большой Дмитровке в 2025–2026 новых анонсов не найдено (только реализуемые «Советник» (Insigma) и Petrovsky).</t>
+          <t>Участок 0,1 га, 11 квартир, 14 подземных м/м, архитектура A2M. Делюкс.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Малая Никитская, 29–31 (ожидаемый делюкс-старт)</t>
+          <t>Палашёвский 11 (Большой Палашёвский, 11–13/15)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Малая Никитская улица, 29–31</t>
+          <t>Большой Палашёвский пер., 11–13</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Тверской</t>
         </is>
       </c>
       <c r="D14" s="28" t="inlineStr">
@@ -12044,27 +12048,47 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>не раскрыт</t>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Sminex (СЗ «Смайнэкс Палашёвский 11»)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>в списке ожидаемых стартов делюкс-класса 2026 (агрегатор); подробностей нет</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n"/>
+          <t>старт продаж без стройки (закрытый старт 22.04.2026)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>15600</v>
+      </c>
       <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>mskdeluxe.ru (список стартов делюкс 2026)</t>
+      <c r="I14" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>1 кв. 2030</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>novostroev.ru</t>
         </is>
       </c>
       <c r="P14" s="8" t="inlineStr">
@@ -12074,24 +12098,24 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>В том же списке mskdeluxe.ru: М. Дмитровка 5/9, Льва Толстого 14, Хилков 3, Б. Пироговская 51, Б. Харитоньевский 13, Олсуфьевский 10, Большая Ордынка 25, Воздвиженка 7/6, Малая Полянка 3 — без параметров и девелоперов.</t>
+          <t>Три корпуса 8–9 этажей с контрастными фасадами у Патриарших. Старт продаж 22.04.2026, лоты от 222,4 млн руб. (nngm.ru), от ~3,5 млн руб./м². Сдача 1 кв. 2030 (novostroev.ru, обзор делюкс-стартов 2026).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Малая Ордынка, 14/1</t>
+          <t>Полянка-3</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ул. Малая Ордынка, 14/1</t>
+          <t>ул. Малая Полянка, 3</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="D15" s="28" t="inlineStr">
@@ -12099,41 +12123,35 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Гута-Девелопмент</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>старт продаж 06.04.2026</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Aurix Development (Группа «Эталон»)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>старт продаж 2026</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
+      <c r="N15" s="5" t="n"/>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>sosedi.life (также novostroev.ru обзор делюкс-стартов 2026)</t>
+          <t>официальный сайт проекта (также mskdeluxe.ru/start)</t>
         </is>
       </c>
       <c r="P15" s="8" t="inlineStr">
@@ -12143,24 +12161,24 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>Участок 0,1 га, 11 квартир, 14 подземных м/м, архитектура A2M. Делюкс.</t>
+          <t>9 этажей, 34 квартиры, паркинг на 36 м/м, проект Etalon Project. Продажи открыты в 2026 г.; стадия строительства в открытых источниках не уточнена.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Палашёвский 11 (Большой Палашёвский, 11–13/15)</t>
+          <t>Роден (ранее анонсировался как Veil)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Большой Палашёвский пер., 11–13</t>
+          <t>Большой Харитоньевский пер., 13А</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Тверской</t>
+          <t>Басманный</t>
         </is>
       </c>
       <c r="D16" s="28" t="inlineStr">
@@ -12168,47 +12186,37 @@
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Sminex (СЗ «Смайнэкс Палашёвский 11»)</t>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>MR Group</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>старт продаж без стройки (закрытый старт 22.04.2026)</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>15600</v>
-      </c>
+          <t>старт продаж июль–август 2026</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>43</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>1 кв. 2030</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>3500000</v>
-      </c>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>novostroev.ru</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>novostroev.ru (также roden.moscow)</t>
         </is>
       </c>
       <c r="P16" s="8" t="inlineStr">
@@ -12218,24 +12226,24 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>Три корпуса 8–9 этажей с контрастными фасадами у Патриарших. Старт продаж 22.04.2026, лоты от 222,4 млн руб. (nngm.ru), от ~3,5 млн руб./м². Сдача 1 кв. 2030 (novostroev.ru, обзор делюкс-стартов 2026).</t>
+          <t>Клубный дом делюкс-класса у Чистых прудов, 1 монолитный корпус 7 этажей, архитектура WALL. В обзоре делюкс-стартов 2026 novostroev.ru фигурировал как Veil, 9 этажей.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Полянка-3</t>
+          <t>Рождественка 8</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ул. Малая Полянка, 3</t>
+          <t>ул. Рождественка / Кузнецкий Мост / Варсонофьевский пер.</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Мещанский</t>
         </is>
       </c>
       <c r="D17" s="28" t="inlineStr">
@@ -12245,33 +12253,37 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Aurix Development (Группа «Эталон»)</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>старт продаж 2026</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
+          <t>Sminex (проект выкуплен у «Галс-Девелопмент»)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>проект приобретён, старт продаж ожидается</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>36400</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>18000</v>
+      </c>
       <c r="I17" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>официальный сайт проекта (также mskdeluxe.ru/start)</t>
+          <t>РИА Недвижимость (также kommersant.ru/doc/8291907, cre.ru)</t>
         </is>
       </c>
       <c r="P17" s="8" t="inlineStr">
@@ -12281,24 +12293,24 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>9 этажей, 34 квартиры, паркинг на 36 м/м, проект Etalon Project. Продажи открыты в 2026 г.; стадия строительства в открытых источниках не уточнена.</t>
+          <t>Семь корпусов 2–10 этажей, 115 квартир 61–426 м², таунхаусы и пентхаусы, двор-парк Scape, реставрация особняка конца XIX в. Сделка 12.12.2025.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Роден (ранее анонсировался как Veil)</t>
+          <t>Типография Сытина (Пятницкая, 71/5)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Большой Харитоньевский пер., 13А</t>
+          <t>ул. Пятницкая, 71/5 (2-й Монетчиковский пер., 5)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="D18" s="28" t="inlineStr">
@@ -12308,35 +12320,29 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>MR Group</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>старт продаж июль–август 2026</t>
+          <t>участок приобретён (март 2026), проектирование</t>
         </is>
       </c>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
-      <c r="I18" s="7" t="n">
-        <v>7</v>
-      </c>
+      <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
+      <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="5" t="n"/>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>novostroev.ru (также roden.moscow)</t>
+          <t>РИА Недвижимость (также sminex.com, mperspektiva.ru)</t>
         </is>
       </c>
       <c r="P18" s="8" t="inlineStr">
@@ -12346,145 +12352,141 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом делюкс-класса у Чистых прудов, 1 монолитный корпус 7 этажей, архитектура WALL. В обзоре делюкс-стартов 2026 novostroev.ru фигурировал как Veil, 9 этажей.</t>
+          <t>Участок 1,8 га, 8 зданий 38,5 тыс. м², в т.ч. 3 корпуса типографии Сытина (ОКН, арх. Эрихсон/Шухов). Продавец — В. Погребенко, оценка сделки 12–14 млрд руб., инвестиции 25–30 млрд руб. План: реставрация + новые элитные клубные дома. Участок у Садового кольца (Валовая ул.).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Рождественка 8</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>ул. Рождественка / Кузнецкий Мост / Варсонофьевский пер.</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Мещанский</t>
-        </is>
-      </c>
-      <c r="D19" s="28" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Sminex (проект выкуплен у «Галс-Девелопмент»)</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>проект приобретён, старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>36400</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>18000</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>115</v>
-      </c>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>РИА Недвижимость (также kommersant.ru/doc/8291907, cre.ru)</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>Семь корпусов 2–10 этажей, 115 квартир 61–426 м², таунхаусы и пентхаусы, двор-парк Scape, реставрация особняка конца XIX в. Сделка 12.12.2025.</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Большая Пироговская, 51 (общежития Института красной профессуры)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>ул. Большая Пироговская, 51</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Vesper (fee-девелопер) / собственник Capital Group</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>анонсирован (fee-development), концепция</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>46700</v>
+      </c>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>РИА Недвижимость (также vedomosti.ru 18.06.2026)</t>
+        </is>
+      </c>
+      <c r="P19" s="13" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q19" s="9" t="inlineStr">
+        <is>
+          <t>Участок 1,5 га, ансамбль восьми 6-этажных корпусов 1929–32 гг. (арх. Осипов, Рухлядев; статус памятника утрачен в 2000-х). Планируемая площадь выросла с 39 до 46,7 тыс. м². Vesper — концепция, продукт и управление реализацией. В базе mskdeluxe.ru — «Б.Пироговская, 51».</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Типография Сытина (Пятницкая, 71/5)</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>ул. Пятницкая, 71/5 (2-й Монетчиковский пер., 5)</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Замоскворечье</t>
-        </is>
-      </c>
-      <c r="D20" s="28" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Квартал на Савинской набережной («Московский шёлк»)</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Савинская наб. (территория БЦ «Московский шёлк»)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Sminex</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>участок приобретён (март 2026), проектирование</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>РИА Недвижимость (также sminex.com, mperspektiva.ru)</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>Участок 1,8 га, 8 зданий 38,5 тыс. м², в т.ч. 3 корпуса типографии Сытина (ОКН, арх. Эрихсон/Шухов). Продавец — В. Погребенко, оценка сделки 12–14 млрд руб., инвестиции 25–30 млрд руб. План: реставрация + новые элитные клубные дома. Участок у Садового кольца (Валовая ул.).</t>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>проектирование</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>125000</v>
+      </c>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="10" t="n"/>
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>РИА Недвижимость (стадия подтверждена mperspektiva.ru 18.12.2025)</t>
+        </is>
+      </c>
+      <c r="P20" s="13" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>ЖК ~125 тыс. м² на территории делового квартала «Московский шёлк». По данным Sminex на декабрь 2025 г. находится в стадии проектирования (вместе с Лужнецкой).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Большая Пироговская, 51 (общежития Института красной профессуры)</t>
+          <t>Клубный дом «Земледельческий, 15»</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>ул. Большая Пироговская, 51</t>
+          <t>Земледельческий переулок, 15 (на месте административного здания 1975 г., 5 этажей, 5 744 м²)</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -12497,33 +12499,39 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Vesper (fee-девелопер) / собственник Capital Group</t>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>не раскрыт</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>анонсирован (fee-development), концепция</t>
+          <t>проектирование (агрегаторы; в списке ожидаемых стартов делюкс-класса 2026 на mskdeluxe.ru)</t>
         </is>
       </c>
       <c r="G21" s="12" t="n">
-        <v>46700</v>
+        <v>8000</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
+      <c r="J21" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>2026–2027</t>
+        </is>
+      </c>
       <c r="L21" s="10" t="n"/>
       <c r="M21" s="10" t="n"/>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="O21" s="9" t="inlineStr">
         <is>
-          <t>РИА Недвижимость (также vedomosti.ru 18.06.2026)</t>
+          <t>kvartiravmoskve.ru (обновлено 21.06.2026); mskdeluxe.ru/start</t>
         </is>
       </c>
       <c r="P21" s="13" t="inlineStr">
@@ -12533,58 +12541,54 @@
       </c>
       <c r="Q21" s="9" t="inlineStr">
         <is>
-          <t>Участок 1,5 га, ансамбль восьми 6-этажных корпусов 1929–32 гг. (арх. Осипов, Рухлядев; статус памятника утрачен в 2000-х). Планируемая площадь выросла с 39 до 46,7 тыс. м². Vesper — концепция, продукт и управление реализацией. В базе mskdeluxe.ru — «Б.Пироговская, 51».</t>
+          <t>Участок 0,3 га (сейчас административное здание 1975 г., 5 эт., 5,7 тыс. м²), клубный дом ~8 тыс. м², 77 квартир, коммерция, подземный паркинг. Делюкс.; Участок 0,3 га; делюкс; 77 квартир + коммерческая часть; подземный паркинг; монолит-кирпич; 1 км до м. Смоленская. Сделок по продаже БЦ и решений Москомархитектуры в открытых источниках не найдено.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Квартал на Савинской набережной («Московский шёлк»)</t>
+          <t>Клубный дом на Курсовом переулке, 15 (проект бюро Дмитрия Великовского)</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Савинская наб. (территория БЦ «Московский шёлк»)</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
+          <t>Курсовой переулок, 15</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Хамовники (Остоженка)</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>Sminex</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>проектирование</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>125000</v>
-      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>не раскрыт (проект бюро Дмитрия Великовского)</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>проект / предстарт; в открытых источниках только страница агрегатора</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="n"/>
       <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
+      <c r="I22" s="12" t="n">
+        <v>6</v>
+      </c>
       <c r="J22" s="10" t="n"/>
       <c r="K22" s="10" t="n"/>
       <c r="L22" s="10" t="n"/>
       <c r="M22" s="10" t="n"/>
-      <c r="N22" s="10" t="inlineStr">
-        <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
+      <c r="N22" s="10" t="n"/>
       <c r="O22" s="9" t="inlineStr">
         <is>
-          <t>РИА Недвижимость (стадия подтверждена mperspektiva.ru 18.12.2025)</t>
+          <t>Anwin (агрегатор элитной недвижимости)</t>
         </is>
       </c>
       <c r="P22" s="13" t="inlineStr">
@@ -12594,19 +12598,19 @@
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
-          <t>ЖК ~125 тыс. м² на территории делового квартала «Московский шёлк». По данным Sminex на декабрь 2025 г. находится в стадии проектирования (вместе с Лужнецкой).</t>
+          <t>«Золотая миля», 6 этажей, камерный клубный дом. Подробные параметры и застройщик в открытых источниках не раскрыты.; По описанию агрегатора: 6-этажный дом по проекту бюро Дмитрия Великовского, панорамное остекление, локация «Золотой мили» рядом с Зачатьевским монастырем. Сейчас по адресу — детский клуб-студия «Пречистенские ворота». Пресса (Коммерсант, РБК, Ведомости, Москвич Mag) и Москомархитектура публикаций по площадке не имеют; девелопер и параметры не подтверждены.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Клубный дом «Земледельческий, 15»</t>
+          <t>Льва Толстого, 14–16 (три клубных дома Sminex)</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Земледельческий переулок, 15 (на месте административного здания 1975 г., 5 этажей, 5 744 м²)</t>
+          <t>ул. Льва Толстого, 14</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -12621,37 +12625,33 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>не раскрыт</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>проектирование (агрегаторы; в списке ожидаемых стартов делюкс-класса 2026 на mskdeluxe.ru)</t>
+          <t>участок приобретён (декабрь 2025), концепция в финальной стадии, старт продаж не объявлен</t>
         </is>
       </c>
       <c r="G23" s="12" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H23" s="10" t="n"/>
+        <v>20300</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>12400</v>
+      </c>
       <c r="I23" s="10" t="n"/>
-      <c r="J23" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>2026–2027</t>
-        </is>
-      </c>
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="10" t="n"/>
       <c r="L23" s="10" t="n"/>
       <c r="M23" s="10" t="n"/>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="O23" s="9" t="inlineStr">
         <is>
-          <t>kvartiravmoskve.ru (обновлено 21.06.2026); mskdeluxe.ru/start</t>
+          <t>Московская перспектива (также rbc.ru 18.12.2025, sosedi.life 07.04.2026)</t>
         </is>
       </c>
       <c r="P23" s="13" t="inlineStr">
@@ -12661,24 +12661,24 @@
       </c>
       <c r="Q23" s="9" t="inlineStr">
         <is>
-          <t>Участок 0,3 га (сейчас административное здание 1975 г., 5 эт., 5,7 тыс. м²), клубный дом ~8 тыс. м², 77 квартир, коммерция, подземный паркинг. Делюкс.; Участок 0,3 га; делюкс; 77 квартир + коммерческая часть; подземный паркинг; монолит-кирпич; 1 км до м. Смоленская. Сделок по продаже БЦ и решений Москомархитектуры в открытых источниках не найдено.</t>
+          <t>Участок ~0,6 га у делового квартала «Красная Роза», куплен у структур А. Клячина. Три камерных клубных дома, надземная площадь 20,3 тыс. м², квартиры 12,4 тыс. м². Сохраняется фасад бывшего доходного дома Трындина-Жиро.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Клубный дом на Курсовом переулке, 15 (проект бюро Дмитрия Великовского)</t>
+          <t>Лёвшинский, 19</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Курсовой переулок, 15</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Хамовники (Остоженка)</t>
+          <t>Большой Лёвшинский пер., 19</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="D24" s="29" t="inlineStr">
@@ -12688,27 +12688,37 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>не раскрыт (проект бюро Дмитрия Великовского)</t>
+          <t>ТСИ Девелопмент (ГК «Трансстройинвест»)</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>проект / предстарт; в открытых источниках только страница агрегатора</t>
+          <t>старт бронирования, старт продаж</t>
         </is>
       </c>
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" s="10" t="n"/>
-      <c r="K24" s="10" t="n"/>
-      <c r="L24" s="10" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>2 кв. 2028</t>
+        </is>
+      </c>
       <c r="M24" s="10" t="n"/>
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="9" t="inlineStr">
         <is>
-          <t>Anwin (агрегатор элитной недвижимости)</t>
+          <t>whitewill.ru (также tehne.com, levshinsky-19.ru)</t>
         </is>
       </c>
       <c r="P24" s="13" t="inlineStr">
@@ -12718,19 +12728,19 @@
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
-          <t>«Золотая миля», 6 этажей, камерный клубный дом. Подробные параметры и застройщик в открытых источниках не раскрыты.; По описанию агрегатора: 6-этажный дом по проекту бюро Дмитрия Великовского, панорамное остекление, локация «Золотой мили» рядом с Зачатьевским монастырем. Сейчас по адресу — детский клуб-студия «Пречистенские ворота». Пресса (Коммерсант, РБК, Ведомости, Москвич Mag) и Москомархитектура публикаций по площадке не имеют; девелопер и параметры не подтверждены.</t>
+          <t>Воссоздание фасада доходного дома Духовских (1904, арх. Мейснер), проект HADAA Architects. 16 резиденций 70–239 м², паркинг 18 м/м. Цена от 197,12 млн руб. за лот. Стадия стройки в источниках не подтверждена.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Льва Толстого, 14–16 (три клубных дома Sminex)</t>
+          <t>Олсуфьевский 10</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>ул. Льва Толстого, 14</t>
+          <t>Олсуфьевский пер., 10</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -12745,33 +12755,31 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>Грандор (Grandor)</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>участок приобретён (декабрь 2025), концепция в финальной стадии, старт продаж не объявлен</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>20300</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>12400</v>
-      </c>
-      <c r="I25" s="10" t="n"/>
+          <t>ГПЗУ получен (апрель 2021), старт продаж ожидается</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="12" t="n">
+        <v>8</v>
+      </c>
       <c r="J25" s="10" t="n"/>
-      <c r="K25" s="10" t="n"/>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>2026–2027</t>
+        </is>
+      </c>
       <c r="L25" s="10" t="n"/>
       <c r="M25" s="10" t="n"/>
-      <c r="N25" s="10" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
+      <c r="N25" s="10" t="n"/>
       <c r="O25" s="9" t="inlineStr">
         <is>
-          <t>Московская перспектива (также rbc.ru 18.12.2025, sosedi.life 07.04.2026)</t>
+          <t>официальный сайт проекта (также novostroy.ru, mskdeluxe.ru/start)</t>
         </is>
       </c>
       <c r="P25" s="13" t="inlineStr">
@@ -12781,19 +12789,19 @@
       </c>
       <c r="Q25" s="9" t="inlineStr">
         <is>
-          <t>Участок ~0,6 га у делового квартала «Красная Роза», куплен у структур А. Клячина. Три камерных клубных дома, надземная площадь 20,3 тыс. м², квартиры 12,4 тыс. м². Сохраняется фасад бывшего доходного дома Трындина-Жиро.</t>
+          <t>Участок 0,4 га, семь корпусов 5–8 этажей в индивидуальной архитектуре. В базе делюкс-стартов 2026–2027 mskdeluxe.ru.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Лёвшинский, 19</t>
+          <t>Премиальный квартал на Лужнецкой набережной, 10А</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Большой Лёвшинский пер., 19</t>
+          <t>Лужнецкая наб., вл. 10А</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -12806,39 +12814,35 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>ТСИ Девелопмент (ГК «Трансстройинвест»)</t>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>старт бронирования, старт продаж</t>
+          <t>проект утверждён (АГР, май 2026), начало строительства 2027</t>
         </is>
       </c>
       <c r="G26" s="10" t="n"/>
       <c r="H26" s="10" t="n"/>
-      <c r="I26" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>16</v>
-      </c>
+      <c r="I26" s="10" t="n"/>
+      <c r="J26" s="10" t="n"/>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L26" s="10" t="inlineStr">
-        <is>
-          <t>2 кв. 2028</t>
-        </is>
-      </c>
+          <t>2027 (стройка)</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="n"/>
       <c r="M26" s="10" t="n"/>
-      <c r="N26" s="10" t="n"/>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
       <c r="O26" s="9" t="inlineStr">
         <is>
-          <t>whitewill.ru (также tehne.com, levshinsky-19.ru)</t>
+          <t>РИА Недвижимость (также anwin.ru)</t>
         </is>
       </c>
       <c r="P26" s="13" t="inlineStr">
@@ -12848,19 +12852,19 @@
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
-          <t>Воссоздание фасада доходного дома Духовских (1904, арх. Мейснер), проект HADAA Architects. 16 резиденций 70–239 м², паркинг 18 м/м. Цена от 197,12 млн руб. за лот. Стадия стройки в источниках не подтверждена.</t>
+          <t>Два жилых корпуса переменной этажности в неоклассике + эллиптический БЦ 26 тыс. м² («яйцо Фаберже»). Концепция согласована Департаментом градостроительной политики (В. Овчинский). Параметры жилой части не раскрыты.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Олсуфьевский 10</t>
+          <t>Тимура Фрунзе, 11 (клубный дом Sminex)</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Олсуфьевский пер., 10</t>
+          <t>ул. Тимура Фрунзе, 11, стр. 7, 19, 33, 50</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -12875,31 +12879,33 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Грандор (Grandor)</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>ГПЗУ получен (апрель 2021), старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="12" t="n">
-        <v>8</v>
-      </c>
+          <t>участок приобретён (апрель 2026), проектирование</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>13000</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>8200</v>
+      </c>
+      <c r="I27" s="10" t="n"/>
       <c r="J27" s="10" t="n"/>
-      <c r="K27" s="10" t="inlineStr">
-        <is>
-          <t>2026–2027</t>
-        </is>
-      </c>
+      <c r="K27" s="10" t="n"/>
       <c r="L27" s="10" t="n"/>
       <c r="M27" s="10" t="n"/>
-      <c r="N27" s="10" t="n"/>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="O27" s="9" t="inlineStr">
         <is>
-          <t>официальный сайт проекта (также novostroy.ru, mskdeluxe.ru/start)</t>
+          <t>РИА Недвижимость (также sminex.com, interfax-russia.ru)</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr">
@@ -12909,19 +12915,19 @@
       </c>
       <c r="Q27" s="9" t="inlineStr">
         <is>
-          <t>Участок 0,4 га, семь корпусов 5–8 этажей в индивидуальной архитектуре. В базе делюкс-стартов 2026–2027 mskdeluxe.ru.</t>
+          <t>Участок 0,5 га (бывшая шёлковая фабрика, 4 здания 5 тыс. м²), продавец KR Properties (А. Клячин), переход прав 23.04.2026. Камерный клубный дом: пентхаусы с видом на Кремль, виллы, двор-сад; фасады по ул. Тимура Фрунзе сохраняются.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Премиальный квартал на Лужнецкой набережной, 10А</t>
+          <t>Усадьба в Большом Саввинском переулке (клубный дом VSF)</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Лужнецкая наб., вл. 10А</t>
+          <t>Большой Саввинский пер. (усадьба купца Якунина)</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -12934,35 +12940,35 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>Sminex</t>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>ГК «Векторстройфинанс» (VSF)</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>проект утверждён (АГР, май 2026), начало строительства 2027</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="n"/>
+          <t>анонсирован (приобретение объекта), концепция</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>2500</v>
+      </c>
       <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
+      <c r="I28" s="12" t="n">
+        <v>4</v>
+      </c>
       <c r="J28" s="10" t="n"/>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>2027 (стройка)</t>
-        </is>
-      </c>
+      <c r="K28" s="10" t="n"/>
       <c r="L28" s="10" t="n"/>
       <c r="M28" s="10" t="n"/>
       <c r="N28" s="10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="O28" s="9" t="inlineStr">
-        <is>
-          <t>РИА Недвижимость (также anwin.ru)</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="O28" s="10" t="inlineStr">
+        <is>
+          <t>elitnoe.ru</t>
         </is>
       </c>
       <c r="P28" s="13" t="inlineStr">
@@ -12972,19 +12978,19 @@
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
-          <t>Два жилых корпуса переменной этажности в неоклассике + эллиптический БЦ 26 тыс. м² («яйцо Фаберже»). Концепция согласована Департаментом градостроительной политики (В. Овчинский). Параметры жилой части не раскрыты.</t>
+          <t>Четырёхэтажное здание 1889 г. и двухэтажное до 1812 г., ~2,5 тыс. м². Оценка инвестиций 3,5–4,5 млрд руб., стоимость объекта до 1,3 млрд руб. Планируется перестройка в элитный клубный дом.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Тимура Фрунзе, 11 (клубный дом Sminex)</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>ул. Тимура Фрунзе, 11, стр. 7, 19, 33, 50</t>
+          <t>Усачёва, 22</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>ул. Усачёва, 22</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -12997,35 +13003,35 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>Sminex</t>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Regions Development</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>участок приобретён (апрель 2026), проектирование</t>
+          <t>проект, продажи не начаты</t>
         </is>
       </c>
       <c r="G29" s="12" t="n">
-        <v>13000</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>8200</v>
-      </c>
-      <c r="I29" s="10" t="n"/>
+        <v>24600</v>
+      </c>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="12" t="n">
+        <v>18</v>
+      </c>
       <c r="J29" s="10" t="n"/>
-      <c r="K29" s="10" t="n"/>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="L29" s="10" t="n"/>
       <c r="M29" s="10" t="n"/>
-      <c r="N29" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
+      <c r="N29" s="10" t="n"/>
       <c r="O29" s="9" t="inlineStr">
         <is>
-          <t>РИА Недвижимость (также sminex.com, interfax-russia.ru)</t>
+          <t>novostroev.ru (также usacheva22.ru, sosedi.life)</t>
         </is>
       </c>
       <c r="P29" s="13" t="inlineStr">
@@ -13035,19 +13041,19 @@
       </c>
       <c r="Q29" s="9" t="inlineStr">
         <is>
-          <t>Участок 0,5 га (бывшая шёлковая фабрика, 4 здания 5 тыс. м²), продавец KR Properties (А. Клячин), переход прав 23.04.2026. Камерный клубный дом: пентхаусы с видом на Кремль, виллы, двор-сад; фасады по ул. Тимура Фрунзе сохраняются.</t>
+          <t>Участок ~0,4 га, два корпуса ~14 и 18 этажей, архитектура Arch(e)type, двор без машин. Площадь 24,6 тыс. м² — по обзору делюкс-стартов 2026 novostroev.ru.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Усадьба в Большом Саввинском переулке (клубный дом VSF)</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Большой Саввинский пер. (усадьба купца Якунина)</t>
+          <t>Хилков (Хилков переулок, вл. 3)</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Хилков пер., вл. 3</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -13060,35 +13066,37 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>ГК «Векторстройфинанс» (VSF)</t>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Rose Group</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>анонсирован (приобретение объекта), концепция</t>
+          <t>проектирование (долгосрочный проект), старт продаж ожидается</t>
         </is>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2500</v>
-      </c>
-      <c r="H30" s="10" t="n"/>
+        <v>19806</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>8800</v>
+      </c>
       <c r="I30" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J30" s="10" t="n"/>
-      <c r="K30" s="10" t="n"/>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>2026–2027</t>
+        </is>
+      </c>
       <c r="L30" s="10" t="n"/>
       <c r="M30" s="10" t="n"/>
-      <c r="N30" s="10" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="O30" s="10" t="inlineStr">
-        <is>
-          <t>elitnoe.ru</t>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t>novostroy-m.ru (также mskdeluxe.ru/start)</t>
         </is>
       </c>
       <c r="P30" s="13" t="inlineStr">
@@ -13098,397 +13106,395 @@
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
-          <t>Четырёхэтажное здание 1889 г. и двухэтажное до 1812 г., ~2,5 тыс. м². Оценка инвестиций 3,5–4,5 млрд руб., стоимость объекта до 1,3 млрд руб. Планируется перестройка в элитный клубный дом.</t>
+          <t>3–8 этажей, монолит-кирпич, коммерция 1,8 тыс. м², паркинг 170 м/м. Карточка novostroy-m.ru датирована 2016 г.; проект вновь фигурирует в списке делюкс-стартов 2026–2027 на mskdeluxe.ru. Актуальность требует проверки.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Усачёва, 22</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>ул. Усачёва, 22</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="D31" s="29" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Regions Development</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>проект, продажи не начаты</t>
-        </is>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>24600</v>
-      </c>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="10" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Aurus Residences / Страна.Сити</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>2-й Красногвардейский проезд, квартал «Камушки»</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>Сити</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>Страна Девелопмент</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>ГПЗУ получен, подготовка к старту продаж</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>280800</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>231800</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>97</v>
+      </c>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="15" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L31" s="10" t="n"/>
-      <c r="M31" s="10" t="n"/>
-      <c r="N31" s="10" t="n"/>
-      <c r="O31" s="9" t="inlineStr">
-        <is>
-          <t>novostroev.ru (также usacheva22.ru, sosedi.life)</t>
-        </is>
-      </c>
-      <c r="P31" s="13" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q31" s="9" t="inlineStr">
-        <is>
-          <t>Участок ~0,4 га, два корпуса ~14 и 18 этажей, архитектура Arch(e)type, двор без машин. Площадь 24,6 тыс. м² — по обзору делюкс-стартов 2026 novostroev.ru.</t>
+      <c r="L31" s="15" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="M31" s="15" t="n"/>
+      <c r="N31" s="15" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="O31" s="15" t="inlineStr">
+        <is>
+          <t>sosedi.life</t>
+        </is>
+      </c>
+      <c r="P31" s="18" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q31" s="14" t="inlineStr">
+        <is>
+          <t>Две башни 83 и 97 этажей на шестиярусном стилобате, участок ~1,25 га, архитектура APEX. ГПЗУ получен летом 2024 г., проект проходит согласования. Бизнес/премиум-класс, апартаменты.; АГР утверждён в декабре 2025, ~232 тыс. м² жилья (Москомархитектура); https://72.ru/text/gorod/2025/12/30/76197016/</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Хилков (Хилков переулок, вл. 3)</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Хилков пер., вл. 3</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="D32" s="29" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>Rose Group</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>проектирование (долгосрочный проект), старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>19806</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>8800</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="inlineStr">
-        <is>
-          <t>2026–2027</t>
-        </is>
-      </c>
-      <c r="L32" s="10" t="n"/>
-      <c r="M32" s="10" t="n"/>
-      <c r="N32" s="10" t="n"/>
-      <c r="O32" s="9" t="inlineStr">
-        <is>
-          <t>novostroy-m.ru (также mskdeluxe.ru/start)</t>
-        </is>
-      </c>
-      <c r="P32" s="13" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q32" s="9" t="inlineStr">
-        <is>
-          <t>3–8 этажей, монолит-кирпич, коммерция 1,8 тыс. м², паркинг 170 м/м. Карточка novostroy-m.ru датирована 2016 г.; проект вновь фигурирует в списке делюкс-стартов 2026–2027 на mskdeluxe.ru. Актуальность требует проверки.</t>
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>МФК «На Краснопресненской набережной» (Трёхгорная мануфактура)</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Краснопресненская наб., 10</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>Сити</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>ГК Ташир</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>анонсирован, старт продаж ожидается</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="M32" s="15" t="n"/>
+      <c r="N32" s="15" t="n"/>
+      <c r="O32" s="15" t="inlineStr">
+        <is>
+          <t>novostroycity.ru</t>
+        </is>
+      </c>
+      <c r="P32" s="18" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q32" s="14" t="inlineStr">
+        <is>
+          <t>Участок ~1,7 га с ОКН (фабрика Трёхгорной мануфактуры, будет сохранена/реконструирована). Апартаменты премиум-класса + офисы + wellness, подземный паркинг на 750 м/м. Сроки реализации официально не подтверждены; апартаменты, а не квартиры.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>Aurus Residences / Страна.Сити</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>2-й Красногвардейский проезд, квартал «Камушки»</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>Клубный дом «Капельский, 5»</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>Капельский переулок, 5</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>Мещанский</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>Мещанский (вне Садового)</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>не раскрыт (юрлицо на сайте проекта не указано)</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="inlineStr">
+        <is>
+          <t>проектирование / предстарт продаж (официально: открытие продаж планируется во II–III кв. 2026)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="20" t="n"/>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>8–9</t>
+        </is>
+      </c>
+      <c r="J33" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="K33" s="19" t="inlineStr">
+        <is>
+          <t>2026 Q2–Q3 (старт продаж)</t>
+        </is>
+      </c>
+      <c r="L33" s="19" t="inlineStr">
+        <is>
+          <t>2029 Q4 (по данным Whitewill)</t>
+        </is>
+      </c>
+      <c r="M33" s="20" t="n"/>
+      <c r="N33" s="20" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="O33" s="19" t="inlineStr">
+        <is>
+          <t>Официальный сайт kapelsky5.ru; Whitewill; Novostroy-M</t>
+        </is>
+      </c>
+      <c r="P33" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q33" s="19" t="inlineStr">
+        <is>
+          <t>46 резиденций, переменная этажность, пентхаусы с террасами, приватный сквер, подземный паркинг. ВНИМАНИЕ: локация вне Садового кольца (у м. Проспект Мира, ~1 км севернее), включена по запросу заказчика.; Делюкс/премиум клубный дом; квартиры 54–345 м²; пентхаусы с террасами; двухуровневый паркинг на 56 м/м, 32 кладовые; приватный сад во дворе. Whitewill (https://whitewill.ru/developments/kapelskiy-5) указывает 8 этажей и срок сдачи 4 кв. 2029; Novostroy-M — 9 этажей, «скоро старт». Цены по запросу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Делюкс-комплекс «Капранова, 3» (проект APEX)</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>переулок Капранова, 3 (БЦ «Премьер Плаза») + Малый Предтеченский пер., 1/2/1, Нововаганьковский пер., 3 стр. 1, Глубокий пер., 7</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D33" s="30" t="inlineStr">
-        <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>Страна Девелопмент</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>ГПЗУ получен, подготовка к старту продаж</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="n">
-        <v>280800</v>
-      </c>
-      <c r="H33" s="17" t="n">
-        <v>231800</v>
-      </c>
-      <c r="I33" s="17" t="n">
-        <v>97</v>
-      </c>
-      <c r="J33" s="15" t="n"/>
-      <c r="K33" s="15" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L33" s="15" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="M33" s="15" t="n"/>
-      <c r="N33" s="15" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="O33" s="15" t="inlineStr">
-        <is>
-          <t>sosedi.life</t>
-        </is>
-      </c>
-      <c r="P33" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q33" s="14" t="inlineStr">
-        <is>
-          <t>Две башни 83 и 97 этажей на шестиярусном стилобате, участок ~1,25 га, архитектура APEX. ГПЗУ получен летом 2024 г., проект проходит согласования. Бизнес/премиум-класс, апартаменты.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>Жилые башни «Сити-2» (2-й Красногвардейский проезд)</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>2-й Красногвардейский проезд, Пресненский район (площадка 1,255 га у «Москва-Сити»)</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="D34" s="30" t="inlineStr">
-        <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>ГК «Страна Девелопмент» (право застройки получено на торгах города; прежний правообладатель — ООО «Моссититстрой»)</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>АГР двух жилых башен утвержден (декабрь 2025); старт продаж не объявлен</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="n">
-        <v>281000</v>
-      </c>
-      <c r="H34" s="17" t="n">
-        <v>232000</v>
-      </c>
-      <c r="I34" s="14" t="inlineStr">
-        <is>
-          <t>две башни, самая высокая — 384 м по утвержденному АГР (ранее заявлялось до 450 м)</t>
-        </is>
-      </c>
-      <c r="J34" s="15" t="n"/>
-      <c r="K34" s="15" t="n"/>
-      <c r="L34" s="15" t="n"/>
-      <c r="M34" s="15" t="n"/>
-      <c r="N34" s="15" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="O34" s="14" t="inlineStr">
-        <is>
-          <t>72.ru / сеть городских порталов (30.12.2025); IRN.ru (18.04.2024)</t>
-        </is>
-      </c>
-      <c r="P34" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q34" s="14" t="inlineStr">
-        <is>
-          <t>~232 тыс. м² жилья и 49 тыс. м² нежилых помещений (IRN.ru, https://www.irn.ru/news/156498.html). Самый высокий жилой комплекс России по утвержденной концепции. Отдельно на Novostroy-M числится «Сити-2» Capital Group (квартал 804, Камушки, три башни до 450 м, ~470 тыс. м², ~385 тыс. м² жилья, «скоро старт») — иная площадка в том же районе, не путать.</t>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>Пресненский (вне Садового)</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>не раскрыт</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>визуализации направлены на согласование в город (ноябрь 2025); предстарт, старт продаж заявлен на 2026</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="24" t="n"/>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>9–23 (шесть корпусов)</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n">
+        <v>255</v>
+      </c>
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>2026 (старт продаж)</t>
+        </is>
+      </c>
+      <c r="L34" s="24" t="n"/>
+      <c r="M34" s="24" t="n"/>
+      <c r="N34" s="24" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="O34" s="21" t="inlineStr">
+        <is>
+          <t>Москвич Mag (19.11.2025); sosedi.life (07.04.2026)</t>
+        </is>
+      </c>
+      <c r="P34" s="26" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q34" s="21" t="inlineStr">
+        <is>
+          <t>Делюкс-проект в базе перспективных стартов 2026–2027 (mskdeluxe.ru, цены «от 60 млн руб.»). Обзор smart-lab.ru/blog/1231916.php указывает старт продаж в 2026 г., 12 этажей, двор без машин. Застройщик и параметры в открытых источниках не подтверждены. ~400 м от м. Краснопресненская, вне Садового кольца.; Единая застройка нескольких участков за Домом Правительства у Пресненского детского парка; башни с «волнообразными» фасадами, снос БЦ «Премьер Плаза», сохранение усадьбы Резанова. По sosedi.life (https://sosedi.life/news/zhk-kapranova-3/): участок &gt;2,5 га, 6 корпусов 9–23 этажа, 255 квартир, двор 7 039,6 м², лобби Balcon, 2–5 квартир на этаже. Указанные в запросе «12 этажей» источниками не подтверждаются. В списке делюкс-стартов mskdeluxe.ru.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>МФК «На Краснопресненской набережной» (Трёхгорная мануфактура)</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>Краснопресненская наб., 10</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="D35" s="30" t="inlineStr">
-        <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>ГК Ташир</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>анонсирован, старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G35" s="15" t="n"/>
-      <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
-      <c r="K35" s="15" t="n"/>
-      <c r="L35" s="15" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="M35" s="15" t="n"/>
-      <c r="N35" s="15" t="n"/>
-      <c r="O35" s="15" t="inlineStr">
-        <is>
-          <t>novostroycity.ru</t>
-        </is>
-      </c>
-      <c r="P35" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q35" s="14" t="inlineStr">
-        <is>
-          <t>Участок ~1,7 га с ОКН (фабрика Трёхгорной мануфактуры, будет сохранена/реконструирована). Апартаменты премиум-класса + офисы + wellness, подземный паркинг на 750 м/м. Сроки реализации официально не подтверждены; апартаменты, а не квартиры.</t>
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>КРТ вдоль Звенигородского шоссе (три участка, 73,62 га)</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Вдоль Звенигородского шоссе между 3-й Магистральной улицей и ТТК (Пресненский / Хорошёвский районы)</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>Пресненский / Хорошёвский</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>Пресненский (вне Садового)</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>не раскрыт (оператор/инвестор не назван; в числе 9 проектов КРТ, утвержденных в августе 2026)</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>решение о КРТ принято (август 2026); оператор/торги не объявлены</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="H35" s="20" t="n"/>
+      <c r="I35" s="20" t="n"/>
+      <c r="J35" s="20" t="n"/>
+      <c r="K35" s="20" t="n"/>
+      <c r="L35" s="20" t="n"/>
+      <c r="M35" s="20" t="n"/>
+      <c r="N35" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="O35" s="19" t="inlineStr">
+        <is>
+          <t>Интерфакс-Россия; Ведомости.Город (02.09.2026)</t>
+        </is>
+      </c>
+      <c r="P35" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q35" s="19" t="inlineStr">
+        <is>
+          <t>Три участка нежилой застройки общей площадью 73,62 га; &gt;3,2 млн м² недвижимости (жильё + общественно-деловые объекты, школы на 4050 мест, детсады на 1775 мест), 35,5 тыс. рабочих мест. Часть «Большого Сити» (Шелепиха/Магистральные улицы), класс жилья не заявлен — не обязательно премиум.; Три участка нежилой застройки (старые склады, админздания) общей площадью 73,62 га; свыше 3,2 млн м² — жилье, общественно-деловые и социальные объекты; строительство/реконструкция дорог ~6,5 км; здание конечной станции наземного транспорта с отстойно-разворотной площадкой (Ведомости, https://www.vedomosti.ru/gorod/ourcity/articles/gorodskoi-kvartal). Жилая премиальная часть отдельно не выделена; класс жилья не указан. Оператор (Московский фонд реновации / КРТ 21 / инвестор по торгам) не объявлен.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="21" t="inlineStr">
         <is>
-          <t>Клубный дом «Капельский, 5»</t>
+          <t>Участок КРТ «Большой Тишинский переулок, 8»</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>Капельский переулок, 5</t>
+          <t>Большой Тишинский переулок, 8 (стр. 1, 2)</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Мещанский</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>Мещанский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>не раскрыт (юрлицо на сайте проекта не указано)</t>
+          <t>Пресненский (вне Садового)</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>не раскрыт</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t>проектирование / предстарт продаж (официально: открытие продаж планируется во II–III кв. 2026)</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="n"/>
-      <c r="H36" s="24" t="n"/>
-      <c r="I36" s="24" t="inlineStr">
-        <is>
-          <t>8–9</t>
-        </is>
-      </c>
-      <c r="J36" s="25" t="n">
-        <v>46</v>
-      </c>
-      <c r="K36" s="21" t="inlineStr">
-        <is>
-          <t>2026 Q2–Q3 (старт продаж)</t>
-        </is>
-      </c>
-      <c r="L36" s="21" t="inlineStr">
-        <is>
-          <t>2029 Q4 (по данным Whitewill)</t>
-        </is>
-      </c>
+          <t>решение о КРТ (по данным заказчика — август 2026); оператор/правообладатель и торги в открытых источниках не найдены</t>
+        </is>
+      </c>
+      <c r="G36" s="25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H36" s="25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I36" s="24" t="n"/>
+      <c r="J36" s="24" t="n"/>
+      <c r="K36" s="24" t="n"/>
+      <c r="L36" s="24" t="n"/>
       <c r="M36" s="24" t="n"/>
       <c r="N36" s="24" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="O36" s="21" t="inlineStr">
         <is>
-          <t>Официальный сайт kapelsky5.ru; Whitewill; Novostroy-M</t>
+          <t>krt.mos.ru (реестр проектов КРТ Москвы)</t>
         </is>
       </c>
       <c r="P36" s="26" t="inlineStr">
@@ -13498,216 +13504,23 @@
       </c>
       <c r="Q36" s="21" t="inlineStr">
         <is>
-          <t>46 резиденций, переменная этажность, пентхаусы с террасами, приватный сквер, подземный паркинг. ВНИМАНИЕ: локация вне Садового кольца (у м. Проспект Мира, ~1 км севернее), включена по запросу заказчика.; Делюкс/премиум клубный дом; квартиры 54–345 м²; пентхаусы с террасами; двухуровневый паркинг на 56 м/м, 32 кладовые; приватный сад во дворе. Whitewill (https://whitewill.ru/developments/kapelskiy-5) указывает 8 этажей и срок сдачи 4 кв. 2029; Novostroy-M — 9 этажей, «скоро старт». Цены по запросу.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>Делюкс-комплекс «Капранова, 3» (проект APEX)</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>переулок Капранова, 3 (БЦ «Премьер Плаза») + Малый Предтеченский пер., 1/2/1, Нововаганьковский пер., 3 стр. 1, Глубокий пер., 7</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="inlineStr">
-        <is>
-          <t>не раскрыт</t>
-        </is>
-      </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>визуализации направлены на согласование в город (ноябрь 2025); предстарт, старт продаж заявлен на 2026</t>
-        </is>
-      </c>
-      <c r="G37" s="20" t="n"/>
-      <c r="H37" s="20" t="n"/>
-      <c r="I37" s="19" t="inlineStr">
-        <is>
-          <t>9–23 (шесть корпусов)</t>
-        </is>
-      </c>
-      <c r="J37" s="22" t="n">
-        <v>255</v>
-      </c>
-      <c r="K37" s="19" t="inlineStr">
-        <is>
-          <t>2026 (старт продаж)</t>
-        </is>
-      </c>
-      <c r="L37" s="20" t="n"/>
-      <c r="M37" s="20" t="n"/>
-      <c r="N37" s="20" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="O37" s="19" t="inlineStr">
-        <is>
-          <t>Москвич Mag (19.11.2025); sosedi.life (07.04.2026)</t>
-        </is>
-      </c>
-      <c r="P37" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q37" s="19" t="inlineStr">
-        <is>
-          <t>Делюкс-проект в базе перспективных стартов 2026–2027 (mskdeluxe.ru, цены «от 60 млн руб.»). Обзор smart-lab.ru/blog/1231916.php указывает старт продаж в 2026 г., 12 этажей, двор без машин. Застройщик и параметры в открытых источниках не подтверждены. ~400 м от м. Краснопресненская, вне Садового кольца.; Единая застройка нескольких участков за Домом Правительства у Пресненского детского парка; башни с «волнообразными» фасадами, снос БЦ «Премьер Плаза», сохранение усадьбы Резанова. По sosedi.life (https://sosedi.life/news/zhk-kapranova-3/): участок &gt;2,5 га, 6 корпусов 9–23 этажа, 255 квартир, двор 7 039,6 м², лобби Balcon, 2–5 квартир на этаже. Указанные в запросе «12 этажей» источниками не подтверждаются. В списке делюкс-стартов mskdeluxe.ru.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>КРТ вдоль Звенигородского шоссе (три участка, 73,62 га)</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>Вдоль Звенигородского шоссе между 3-й Магистральной улицей и ТТК (Пресненский / Хорошёвский районы)</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский / Хорошёвский</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>не раскрыт (оператор/инвестор не назван; в числе 9 проектов КРТ, утвержденных в августе 2026)</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr">
-        <is>
-          <t>решение о КРТ принято (август 2026); оператор/торги не объявлены</t>
-        </is>
-      </c>
-      <c r="G38" s="25" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="H38" s="24" t="n"/>
-      <c r="I38" s="24" t="n"/>
-      <c r="J38" s="24" t="n"/>
-      <c r="K38" s="24" t="n"/>
-      <c r="L38" s="24" t="n"/>
-      <c r="M38" s="24" t="n"/>
-      <c r="N38" s="24" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="O38" s="21" t="inlineStr">
-        <is>
-          <t>Интерфакс-Россия; Ведомости.Город (02.09.2026)</t>
-        </is>
-      </c>
-      <c r="P38" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q38" s="21" t="inlineStr">
-        <is>
-          <t>Три участка нежилой застройки общей площадью 73,62 га; &gt;3,2 млн м² недвижимости (жильё + общественно-деловые объекты, школы на 4050 мест, детсады на 1775 мест), 35,5 тыс. рабочих мест. Часть «Большого Сити» (Шелепиха/Магистральные улицы), класс жилья не заявлен — не обязательно премиум.; Три участка нежилой застройки (старые склады, админздания) общей площадью 73,62 га; свыше 3,2 млн м² — жилье, общественно-деловые и социальные объекты; строительство/реконструкция дорог ~6,5 км; здание конечной станции наземного транспорта с отстойно-разворотной площадкой (Ведомости, https://www.vedomosti.ru/gorod/ourcity/articles/gorodskoi-kvartal). Жилая премиальная часть отдельно не выделена; класс жилья не указан. Оператор (Московский фонд реновации / КРТ 21 / инвестор по торгам) не объявлен.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>Участок КРТ «Большой Тишинский переулок, 8»</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>Большой Тишинский переулок, 8 (стр. 1, 2)</t>
-        </is>
-      </c>
-      <c r="C39" s="20" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="E39" s="20" t="inlineStr">
-        <is>
-          <t>не раскрыт</t>
-        </is>
-      </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>решение о КРТ (по данным заказчика — август 2026); оператор/правообладатель и торги в открытых источниках не найдены</t>
-        </is>
-      </c>
-      <c r="G39" s="22" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H39" s="22" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I39" s="20" t="n"/>
-      <c r="J39" s="20" t="n"/>
-      <c r="K39" s="20" t="n"/>
-      <c r="L39" s="20" t="n"/>
-      <c r="M39" s="20" t="n"/>
-      <c r="N39" s="20" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="O39" s="19" t="inlineStr">
-        <is>
-          <t>krt.mos.ru (реестр проектов КРТ Москвы)</t>
-        </is>
-      </c>
-      <c r="P39" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q39" s="19" t="inlineStr">
-        <is>
           <t>Участок ~0,3 га включён в программу КРТ решением властей Москвы. Существующие здания реконструированы в 2004 г., в 2020 г. переоборудованы под хостелы. Оператор/девелопер в публикации не назван; в других открытых источниках на 07.09.2026 не найден. Локация — Пресненский район вне Садового кольца, между Б. Грузинской и Пресненским Валом (условно отнесено к зоне Пресня/Сити).; Поиск по mos.ru, krt.mos.ru, stroi.mos.ru, Ведомости, РБК, Интерфакс, М24, Известия (август–сентябрь 2026) не выявил отдельной публикации по этому участку: новости августа 2026 о КРТ (250 проектов, 63 договора с начала года) даются агрегированно. Ближайший крупный проект — квартал «Тишинский бульвар» Sminex (Электрический пер., 1), связь с участком №8 не подтверждена. Площадь 0,3 га / ~10 000 м² — из исходных данных запроса, независимого подтверждения нет.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="27" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>Источники: открытые публикации 2025–2026 (stroi.mos.ru, mos.ru, отраслевые СМИ, публичные Telegram-каналы). Закрытый канал t.me/c/3370602239 недоступен без членства — пост №1364 про ЗУ «Большой Тишинский, 8» подтверждён по открытым источникам.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q39"/>
+  <autoFilter ref="A3:Q36"/>
   <mergeCells count="3">
+    <mergeCell ref="A38:Q38"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A41:Q41"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId1"/>
@@ -13743,9 +13556,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId36"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -12,15 +12,15 @@
     <sheet name="3. Проектирование" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Построено (вторичка)'!$A$3:$S$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Построено (вторичка)'!$A$3:$S$67</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'1. Построено (вторичка)'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1. Построено (вторичка)'!$A$1:$S$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Строится'!$A$3:$P$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1. Построено (вторичка)'!$A$1:$S$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Строится'!$A$3:$P$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'2. Строится'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'2. Строится'!$A$1:$P$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Проектирование'!$A$3:$Q$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2. Строится'!$A$1:$P$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Проектирование'!$A$3:$Q$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'3. Проектирование'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'3. Проектирование'!$A$1:$Q$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'3. Проектирование'!$A$1:$Q$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -71,7 +71,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -100,7 +100,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F6FA"/>
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -144,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -204,8 +209,8 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -213,17 +218,20 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -232,6 +240,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S88"/>
+  <dimension ref="A1:S69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5058,22 +5069,22 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>Дизайнерский дом Eleven (11)</t>
-        </is>
-      </c>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>Холдинг РСТИ</t>
+          <t>NEVA TOWERS (Нева Тауэрс)</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Renaissance Development</t>
         </is>
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018–2025</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
         <is>
-          <t>Москва, Звенигородское, 11</t>
+          <t>Москва, 1-й Красногвардейский, 22с2</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
@@ -5091,29 +5102,29 @@
       </c>
       <c r="H57" s="15" t="inlineStr">
         <is>
-          <t>16-17</t>
+          <t>63-79</t>
         </is>
       </c>
       <c r="I57" s="15" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J57" s="17" t="n">
-        <v>1044868</v>
+        <v>615385</v>
       </c>
       <c r="K57" s="17" t="n">
-        <v>1246251</v>
+        <v>854530</v>
       </c>
       <c r="L57" s="17" t="n">
-        <v>1428571</v>
+        <v>1968504</v>
       </c>
       <c r="M57" s="17" t="n">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="N57" s="15" t="inlineStr">
         <is>
-          <t>75–191</t>
+          <t>39–254</t>
         </is>
       </c>
       <c r="O57" s="15" t="inlineStr">
@@ -5121,44 +5132,34 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P57" s="17" t="n">
-        <v>90</v>
-      </c>
+      <c r="P57" s="15" t="n"/>
       <c r="Q57" s="18" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R57" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S57" s="14" t="inlineStr">
-        <is>
-          <t>арх. Меганом</t>
-        </is>
-      </c>
+      <c r="R57" s="15" t="inlineStr"/>
+      <c r="S57" s="14" t="inlineStr"/>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>Счастье на Пресне</t>
+          <t>City Park (Сити Парк)</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Группа Эталон</t>
+          <t>ГК МонАрх</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019–2023</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>Москва, Красногвардейский, 15С2</t>
+          <t>Москва, Мантулинская, 9к4</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
@@ -5172,234 +5173,242 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>6-24</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J58" s="17" t="n">
+        <v>788028</v>
+      </c>
+      <c r="K58" s="17" t="n">
+        <v>1183147</v>
+      </c>
+      <c r="L58" s="17" t="n">
+        <v>2129032</v>
+      </c>
+      <c r="M58" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="N58" s="15" t="inlineStr">
+        <is>
+          <t>34–251</t>
+        </is>
+      </c>
+      <c r="O58" s="15" t="inlineStr">
+        <is>
+          <t>бизнес</t>
+        </is>
+      </c>
+      <c r="P58" s="17" t="n">
+        <v>1213</v>
+      </c>
+      <c r="Q58" s="18" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R58" s="18" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>Lucky (Лаки)</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>2022–2023</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>Москва, Костикова, 4к2</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H59" s="20" t="inlineStr">
+        <is>
+          <t>15-21</t>
+        </is>
+      </c>
+      <c r="I59" s="20" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J59" s="22" t="n">
+        <v>1296875</v>
+      </c>
+      <c r="K59" s="22" t="n">
+        <v>1694915</v>
+      </c>
+      <c r="L59" s="22" t="n">
+        <v>2352941</v>
+      </c>
+      <c r="M59" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="N59" s="20" t="inlineStr">
+        <is>
+          <t>44–253</t>
+        </is>
+      </c>
+      <c r="O59" s="20" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P59" s="20" t="n"/>
+      <c r="Q59" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R59" s="20" t="inlineStr"/>
+      <c r="S59" s="19" t="inlineStr"/>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>Дом на Тишинке</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>Донстрой</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>Москва, Средний Тишинский, 5</t>
+        </is>
+      </c>
+      <c r="E60" s="20" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="inlineStr">
+        <is>
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="H58" s="15" t="inlineStr">
-        <is>
-          <t>19-21</t>
-        </is>
-      </c>
-      <c r="I58" s="15" t="inlineStr">
+      <c r="H60" s="20" t="inlineStr">
+        <is>
+          <t>7-20</t>
+        </is>
+      </c>
+      <c r="I60" s="20" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J58" s="17" t="n">
-        <v>509615</v>
-      </c>
-      <c r="K58" s="17" t="n">
-        <v>913838</v>
-      </c>
-      <c r="L58" s="17" t="n">
-        <v>1135770</v>
-      </c>
-      <c r="M58" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="N58" s="15" t="inlineStr">
-        <is>
-          <t>38–104</t>
-        </is>
-      </c>
-      <c r="O58" s="15" t="inlineStr">
+      <c r="J60" s="22" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="K60" s="22" t="n">
+        <v>1614969</v>
+      </c>
+      <c r="L60" s="22" t="n">
+        <v>2147239</v>
+      </c>
+      <c r="M60" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
+        <is>
+          <t>84–243</t>
+        </is>
+      </c>
+      <c r="O60" s="20" t="inlineStr">
         <is>
           <t>премиум</t>
         </is>
       </c>
-      <c r="P58" s="15" t="n"/>
-      <c r="Q58" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R58" s="15" t="inlineStr"/>
-      <c r="S58" s="14" t="inlineStr"/>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>NEVA TOWERS (Нева Тауэрс)</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>Renaissance Development</t>
-        </is>
-      </c>
-      <c r="C59" s="15" t="inlineStr">
-        <is>
-          <t>2018–2025</t>
-        </is>
-      </c>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>Москва, 1-й Красногвардейский, 22с2</t>
-        </is>
-      </c>
-      <c r="E59" s="15" t="inlineStr">
+      <c r="P60" s="20" t="n"/>
+      <c r="Q60" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R60" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S60" s="19" t="inlineStr">
+        <is>
+          <t>арх. Павел Андреев</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>Fantastic House (Фантастик Хаус)</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>СЗ Полинессо</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>Москва, Большой Тишинский, 30</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" s="15" t="inlineStr">
-        <is>
-          <t>63-79</t>
-        </is>
-      </c>
-      <c r="I59" s="15" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J59" s="17" t="n">
-        <v>615385</v>
-      </c>
-      <c r="K59" s="17" t="n">
-        <v>854530</v>
-      </c>
-      <c r="L59" s="17" t="n">
-        <v>1968504</v>
-      </c>
-      <c r="M59" s="17" t="n">
-        <v>113</v>
-      </c>
-      <c r="N59" s="15" t="inlineStr">
-        <is>
-          <t>39–254</t>
-        </is>
-      </c>
-      <c r="O59" s="15" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P59" s="15" t="n"/>
-      <c r="Q59" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R59" s="15" t="inlineStr"/>
-      <c r="S59" s="14" t="inlineStr"/>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>City Park (Сити Парк)</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>ГК МонАрх</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>2019–2023</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="inlineStr">
-        <is>
-          <t>Москва, Мантулинская, 9к4</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="G60" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H60" s="15" t="inlineStr">
-        <is>
-          <t>6-24</t>
-        </is>
-      </c>
-      <c r="I60" s="15" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J60" s="17" t="n">
-        <v>788028</v>
-      </c>
-      <c r="K60" s="17" t="n">
-        <v>1183147</v>
-      </c>
-      <c r="L60" s="17" t="n">
-        <v>2129032</v>
-      </c>
-      <c r="M60" s="17" t="n">
-        <v>58</v>
-      </c>
-      <c r="N60" s="15" t="inlineStr">
-        <is>
-          <t>34–251</t>
-        </is>
-      </c>
-      <c r="O60" s="15" t="inlineStr">
-        <is>
-          <t>бизнес</t>
-        </is>
-      </c>
-      <c r="P60" s="17" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q60" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R60" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S60" s="14" t="inlineStr"/>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
-        <is>
-          <t>Дом Chkalov (Чкалов)</t>
-        </is>
-      </c>
-      <c r="B61" s="20" t="inlineStr">
-        <is>
-          <t>Ikon Development</t>
-        </is>
-      </c>
-      <c r="C61" s="20" t="inlineStr">
-        <is>
-          <t>2021–2025</t>
-        </is>
-      </c>
-      <c r="D61" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Курского Вокзала, 1</t>
-        </is>
-      </c>
-      <c r="E61" s="20" t="inlineStr">
-        <is>
-          <t>Басманный</t>
-        </is>
-      </c>
       <c r="F61" s="21" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
+          <t>Пресня</t>
         </is>
       </c>
       <c r="G61" s="22" t="n">
@@ -5407,179 +5416,197 @@
       </c>
       <c r="H61" s="20" t="inlineStr">
         <is>
-          <t>21-22</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J61" s="22" t="n">
+        <v>1117647</v>
+      </c>
+      <c r="K61" s="22" t="n">
+        <v>1496549</v>
+      </c>
+      <c r="L61" s="22" t="n">
+        <v>1544484</v>
+      </c>
+      <c r="M61" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N61" s="20" t="inlineStr">
+        <is>
+          <t>140–240</t>
+        </is>
+      </c>
+      <c r="O61" s="20" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P61" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q61" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R61" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S61" s="19" t="inlineStr">
+        <is>
+          <t>21 квартира + 4 резиденции + 3 пентхауса; арх. Цимайло Ляшенко</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t>Edison House (Эдисон Хаус)</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>ИК Приоритет</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>Москва, Электрический, 10</t>
+        </is>
+      </c>
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F62" s="21" t="inlineStr">
+        <is>
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I62" s="20" t="inlineStr">
+        <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J61" s="22" t="n">
-        <v>796915</v>
-      </c>
-      <c r="K61" s="22" t="n">
-        <v>967043</v>
-      </c>
-      <c r="L61" s="22" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="M61" s="22" t="n">
-        <v>37</v>
-      </c>
-      <c r="N61" s="20" t="inlineStr">
-        <is>
-          <t>31–174</t>
-        </is>
-      </c>
-      <c r="O61" s="20" t="inlineStr">
+      <c r="J62" s="22" t="n">
+        <v>1369863</v>
+      </c>
+      <c r="K62" s="22" t="n">
+        <v>1369863</v>
+      </c>
+      <c r="L62" s="22" t="n">
+        <v>1369863</v>
+      </c>
+      <c r="M62" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="20" t="inlineStr">
+        <is>
+          <t>58–58</t>
+        </is>
+      </c>
+      <c r="O62" s="20" t="inlineStr">
         <is>
           <t>премиум</t>
         </is>
       </c>
-      <c r="P61" s="20" t="n"/>
-      <c r="Q61" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R61" s="20" t="inlineStr"/>
-      <c r="S61" s="19" t="inlineStr"/>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="21" t="inlineStr">
-        <is>
-          <t>KAZAKOV Grand Loft (КАЗАКОВ Гранд Лофт)</t>
-        </is>
-      </c>
-      <c r="B62" s="24" t="inlineStr">
-        <is>
-          <t>Coldy</t>
-        </is>
-      </c>
-      <c r="C62" s="24" t="inlineStr">
-        <is>
-          <t>2022–2023</t>
-        </is>
-      </c>
-      <c r="D62" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Казакова, 7</t>
-        </is>
-      </c>
-      <c r="E62" s="24" t="inlineStr">
-        <is>
-          <t>Басманный</t>
-        </is>
-      </c>
-      <c r="F62" s="21" t="inlineStr">
-        <is>
-          <t>Басманный (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G62" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="24" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I62" s="24" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J62" s="25" t="n">
-        <v>492857</v>
-      </c>
-      <c r="K62" s="25" t="n">
-        <v>729064</v>
-      </c>
-      <c r="L62" s="25" t="n">
-        <v>839080</v>
-      </c>
-      <c r="M62" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="N62" s="24" t="inlineStr">
-        <is>
-          <t>42–73</t>
-        </is>
-      </c>
-      <c r="O62" s="24" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P62" s="24" t="n"/>
-      <c r="Q62" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R62" s="24" t="inlineStr"/>
-      <c r="S62" s="21" t="inlineStr"/>
+      <c r="P62" s="20" t="n"/>
+      <c r="Q62" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R62" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S62" s="19" t="inlineStr">
+        <is>
+          <t>cian years 2018; источники: 3 кв. 2019</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>Басманный от Гранель</t>
+          <t>SkyView</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>Гранель</t>
+          <t>СЗ Киноцентр</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>2024–2025</t>
+          <t>2023–2025</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t>Москва, Малая Почтовая, 12</t>
+          <t>Москва, Дружинниковская, 15А</t>
         </is>
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F63" s="21" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
+          <t>Пресня</t>
         </is>
       </c>
       <c r="G63" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H63" s="20" t="inlineStr">
         <is>
-          <t>12-21</t>
+          <t>20-25</t>
         </is>
       </c>
       <c r="I63" s="20" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J63" s="22" t="n">
-        <v>560484</v>
+        <v>850000</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>718850</v>
+        <v>1200000</v>
       </c>
       <c r="L63" s="22" t="n">
-        <v>923345</v>
+        <v>2756939</v>
       </c>
       <c r="M63" s="22" t="n">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="N63" s="20" t="inlineStr">
         <is>
-          <t>28–86</t>
+          <t>47–847</t>
         </is>
       </c>
       <c r="O63" s="20" t="inlineStr">
@@ -5593,151 +5620,159 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R63" s="20" t="inlineStr"/>
-      <c r="S63" s="19" t="inlineStr"/>
+      <c r="R63" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S63" s="19" t="inlineStr">
+        <is>
+          <t>4 башни на месте Киноцентра</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="21" t="inlineStr">
-        <is>
-          <t>Bauman House (Бауман Хаус)</t>
-        </is>
-      </c>
-      <c r="B64" s="24" t="inlineStr">
-        <is>
-          <t>ГК КОРТРОС</t>
-        </is>
-      </c>
-      <c r="C64" s="24" t="inlineStr">
-        <is>
-          <t>2020–2022</t>
-        </is>
-      </c>
-      <c r="D64" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Новая Дорога, 9</t>
-        </is>
-      </c>
-      <c r="E64" s="24" t="inlineStr">
-        <is>
-          <t>Басманный</t>
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>Sinatra (Синатра)</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>Glincom</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>2018–2020</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>Москва, Большой Тишинский, 38</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F64" s="21" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G64" s="25" t="n">
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="20" t="inlineStr">
+        <is>
+          <t>7-8</t>
+        </is>
+      </c>
+      <c r="I64" s="20" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J64" s="22" t="n">
+        <v>839130</v>
+      </c>
+      <c r="K64" s="22" t="n">
+        <v>1052456</v>
+      </c>
+      <c r="L64" s="22" t="n">
+        <v>1388889</v>
+      </c>
+      <c r="M64" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="24" t="inlineStr">
-        <is>
-          <t>15-16</t>
-        </is>
-      </c>
-      <c r="I64" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J64" s="25" t="n">
-        <v>536585</v>
-      </c>
-      <c r="K64" s="25" t="n">
-        <v>786687</v>
-      </c>
-      <c r="L64" s="25" t="n">
-        <v>812500</v>
-      </c>
-      <c r="M64" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="N64" s="24" t="inlineStr">
-        <is>
-          <t>49–82</t>
-        </is>
-      </c>
-      <c r="O64" s="24" t="inlineStr">
-        <is>
-          <t>бизнес</t>
-        </is>
-      </c>
-      <c r="P64" s="24" t="n"/>
-      <c r="Q64" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R64" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S64" s="21" t="inlineStr">
-        <is>
-          <t>ранее Capital Group (до 2019)</t>
+      <c r="N64" s="20" t="inlineStr">
+        <is>
+          <t>46–180</t>
+        </is>
+      </c>
+      <c r="O64" s="20" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P64" s="20" t="n"/>
+      <c r="Q64" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R64" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S64" s="19" t="inlineStr">
+        <is>
+          <t>реконструкция; cian years 2018/2020</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>RED7 (РЕД7)</t>
+          <t>Репаблик</t>
         </is>
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>ГК Основа</t>
+          <t>Forma</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>2022–2025</t>
+          <t>2025–2026</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>Москва, Академика Сахарова, 7</t>
+          <t>Москва, Пресненский Вал, к2.1</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>Красносельский</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F65" s="21" t="inlineStr">
         <is>
-          <t>Красносельский (вне Садового)</t>
+          <t>Пресня</t>
         </is>
       </c>
       <c r="G65" s="22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H65" s="20" t="inlineStr">
         <is>
-          <t>19-20</t>
+          <t>26-34</t>
         </is>
       </c>
       <c r="I65" s="20" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J65" s="22" t="n">
-        <v>526700</v>
+        <v>716667</v>
       </c>
       <c r="K65" s="22" t="n">
-        <v>767285</v>
+        <v>943141</v>
       </c>
       <c r="L65" s="22" t="n">
-        <v>1402500</v>
+        <v>1570228</v>
       </c>
       <c r="M65" s="22" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="N65" s="20" t="inlineStr">
         <is>
-          <t>39–254</t>
+          <t>27–140</t>
         </is>
       </c>
       <c r="O65" s="20" t="inlineStr">
@@ -5755,115 +5790,109 @@
       <c r="S65" s="19" t="inlineStr"/>
     </row>
     <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="21" t="inlineStr">
-        <is>
-          <t>Dialog (Диалог)</t>
-        </is>
-      </c>
-      <c r="B66" s="24" t="inlineStr">
-        <is>
-          <t>Центр-Инвест</t>
-        </is>
-      </c>
-      <c r="C66" s="24" t="inlineStr">
-        <is>
-          <t>2022–2023</t>
-        </is>
-      </c>
-      <c r="D66" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Большая Спасская, 35</t>
-        </is>
-      </c>
-      <c r="E66" s="24" t="inlineStr">
-        <is>
-          <t>Красносельский</t>
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>Пресня Сити</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>MR Group</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>Москва, Ходынская, 2</t>
+        </is>
+      </c>
+      <c r="E66" s="20" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F66" s="21" t="inlineStr">
         <is>
-          <t>Красносельский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G66" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H66" s="24" t="inlineStr">
-        <is>
-          <t>22-24</t>
-        </is>
-      </c>
-      <c r="I66" s="24" t="inlineStr">
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="20" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I66" s="20" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J66" s="25" t="n">
-        <v>754006</v>
-      </c>
-      <c r="K66" s="25" t="n">
-        <v>998406</v>
-      </c>
-      <c r="L66" s="25" t="n">
-        <v>1187872</v>
-      </c>
-      <c r="M66" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="N66" s="24" t="inlineStr">
-        <is>
-          <t>38–121</t>
-        </is>
-      </c>
-      <c r="O66" s="24" t="inlineStr">
-        <is>
-          <t>бизнес</t>
-        </is>
-      </c>
-      <c r="P66" s="25" t="n">
-        <v>210</v>
-      </c>
-      <c r="Q66" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R66" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S66" s="21" t="inlineStr"/>
+      <c r="J66" s="22" t="n">
+        <v>647159</v>
+      </c>
+      <c r="K66" s="22" t="n">
+        <v>777778</v>
+      </c>
+      <c r="L66" s="22" t="n">
+        <v>1426966</v>
+      </c>
+      <c r="M66" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="N66" s="20" t="inlineStr">
+        <is>
+          <t>42–158</t>
+        </is>
+      </c>
+      <c r="O66" s="20" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P66" s="20" t="n"/>
+      <c r="Q66" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R66" s="20" t="inlineStr"/>
+      <c r="S66" s="19" t="inlineStr"/>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="19" t="inlineStr">
         <is>
-          <t>Волга</t>
+          <t>Резиденция Тверская</t>
         </is>
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>Волга</t>
+          <t>Kovaks (Ковакс)</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018–2020</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t>Москва, Докучаев, 2с3</t>
+          <t>Москва, 2-я Брестская, 6</t>
         </is>
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>Красносельский</t>
+          <t>Тверской</t>
         </is>
       </c>
       <c r="F67" s="21" t="inlineStr">
         <is>
-          <t>Красносельский (вне Садового)</t>
+          <t>Пресня</t>
         </is>
       </c>
       <c r="G67" s="22" t="n">
@@ -5871,7 +5900,7 @@
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="I67" s="20" t="inlineStr">
@@ -5880,28 +5909,30 @@
         </is>
       </c>
       <c r="J67" s="22" t="n">
-        <v>677419</v>
+        <v>515556</v>
       </c>
       <c r="K67" s="22" t="n">
-        <v>722271</v>
+        <v>772624</v>
       </c>
       <c r="L67" s="22" t="n">
-        <v>767123</v>
+        <v>1700000</v>
       </c>
       <c r="M67" s="22" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="N67" s="20" t="inlineStr">
         <is>
-          <t>73–93</t>
+          <t>37–161</t>
         </is>
       </c>
       <c r="O67" s="20" t="inlineStr">
         <is>
-          <t>бизнес</t>
-        </is>
-      </c>
-      <c r="P67" s="20" t="n"/>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P67" s="22" t="n">
+        <v>190</v>
+      </c>
       <c r="Q67" s="23" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -5914,1578 +5945,21 @@
       </c>
       <c r="S67" s="19" t="inlineStr">
         <is>
-          <t>апарт-комплекс Докучаев 2; ввод 12.10.2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="21" t="inlineStr">
-        <is>
-          <t>Sole Hill (Соле Хилл)</t>
-        </is>
-      </c>
-      <c r="B68" s="21" t="inlineStr">
-        <is>
-          <t>Еврофармакол (Sole Group)</t>
-        </is>
-      </c>
-      <c r="C68" s="24" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D68" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Олимпийский, 12</t>
-        </is>
-      </c>
-      <c r="E68" s="24" t="inlineStr">
-        <is>
-          <t>Мещанский</t>
-        </is>
-      </c>
-      <c r="F68" s="21" t="inlineStr">
-        <is>
-          <t>Мещанский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G68" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" s="24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I68" s="24" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J68" s="25" t="n">
-        <v>700000</v>
-      </c>
-      <c r="K68" s="25" t="n">
-        <v>850000</v>
-      </c>
-      <c r="L68" s="25" t="n">
-        <v>950000</v>
-      </c>
-      <c r="M68" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="N68" s="24" t="inlineStr">
-        <is>
-          <t>32–180</t>
-        </is>
-      </c>
-      <c r="O68" s="24" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P68" s="25" t="n">
-        <v>108</v>
-      </c>
-      <c r="Q68" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R68" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S68" s="21" t="inlineStr">
-        <is>
-          <t>апартаменты; арх. Ricardo Bofill</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="19" t="inlineStr">
-        <is>
-          <t>Lucky (Лаки)</t>
-        </is>
-      </c>
-      <c r="B69" s="20" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
-      <c r="C69" s="20" t="inlineStr">
-        <is>
-          <t>2022–2023</t>
-        </is>
-      </c>
-      <c r="D69" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Костикова, 4к2</t>
-        </is>
-      </c>
-      <c r="E69" s="20" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F69" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G69" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="H69" s="20" t="inlineStr">
-        <is>
-          <t>15-21</t>
-        </is>
-      </c>
-      <c r="I69" s="20" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J69" s="22" t="n">
-        <v>1296875</v>
-      </c>
-      <c r="K69" s="22" t="n">
-        <v>1694915</v>
-      </c>
-      <c r="L69" s="22" t="n">
-        <v>2352941</v>
-      </c>
-      <c r="M69" s="22" t="n">
-        <v>23</v>
-      </c>
-      <c r="N69" s="20" t="inlineStr">
-        <is>
-          <t>44–253</t>
-        </is>
-      </c>
-      <c r="O69" s="20" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P69" s="20" t="n"/>
-      <c r="Q69" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R69" s="20" t="inlineStr"/>
-      <c r="S69" s="19" t="inlineStr"/>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="21" t="inlineStr">
-        <is>
-          <t>Дом на Тишинке</t>
-        </is>
-      </c>
-      <c r="B70" s="24" t="inlineStr">
-        <is>
-          <t>Донстрой</t>
-        </is>
-      </c>
-      <c r="C70" s="24" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D70" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Средний Тишинский, 5</t>
-        </is>
-      </c>
-      <c r="E70" s="24" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F70" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G70" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="24" t="inlineStr">
-        <is>
-          <t>7-20</t>
-        </is>
-      </c>
-      <c r="I70" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J70" s="25" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="K70" s="25" t="n">
-        <v>1614969</v>
-      </c>
-      <c r="L70" s="25" t="n">
-        <v>2147239</v>
-      </c>
-      <c r="M70" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="N70" s="24" t="inlineStr">
-        <is>
-          <t>84–243</t>
-        </is>
-      </c>
-      <c r="O70" s="24" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P70" s="24" t="n"/>
-      <c r="Q70" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R70" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S70" s="21" t="inlineStr">
-        <is>
-          <t>арх. Павел Андреев</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>Fantastic House (Фантастик Хаус)</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="inlineStr">
-        <is>
-          <t>СЗ Полинессо</t>
-        </is>
-      </c>
-      <c r="C71" s="20" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Большой Тишинский, 30</t>
-        </is>
-      </c>
-      <c r="E71" s="20" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F71" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G71" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="20" t="inlineStr">
-        <is>
-          <t>5-6</t>
-        </is>
-      </c>
-      <c r="I71" s="20" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J71" s="22" t="n">
-        <v>1117647</v>
-      </c>
-      <c r="K71" s="22" t="n">
-        <v>1496549</v>
-      </c>
-      <c r="L71" s="22" t="n">
-        <v>1544484</v>
-      </c>
-      <c r="M71" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="N71" s="20" t="inlineStr">
-        <is>
-          <t>140–240</t>
-        </is>
-      </c>
-      <c r="O71" s="20" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P71" s="22" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q71" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R71" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S71" s="19" t="inlineStr">
-        <is>
-          <t>21 квартира + 4 резиденции + 3 пентхауса; арх. Цимайло Ляшенко</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="21" t="inlineStr">
-        <is>
-          <t>Edison House (Эдисон Хаус)</t>
-        </is>
-      </c>
-      <c r="B72" s="24" t="inlineStr">
-        <is>
-          <t>ИК Приоритет</t>
-        </is>
-      </c>
-      <c r="C72" s="24" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D72" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Электрический, 10</t>
-        </is>
-      </c>
-      <c r="E72" s="24" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F72" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G72" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I72" s="24" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J72" s="25" t="n">
-        <v>1369863</v>
-      </c>
-      <c r="K72" s="25" t="n">
-        <v>1369863</v>
-      </c>
-      <c r="L72" s="25" t="n">
-        <v>1369863</v>
-      </c>
-      <c r="M72" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N72" s="24" t="inlineStr">
-        <is>
-          <t>58–58</t>
-        </is>
-      </c>
-      <c r="O72" s="24" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P72" s="24" t="n"/>
-      <c r="Q72" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R72" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S72" s="21" t="inlineStr">
-        <is>
-          <t>cian years 2018; источники: 3 кв. 2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="19" t="inlineStr">
-        <is>
-          <t>SkyView</t>
-        </is>
-      </c>
-      <c r="B73" s="20" t="inlineStr">
-        <is>
-          <t>СЗ Киноцентр</t>
-        </is>
-      </c>
-      <c r="C73" s="20" t="inlineStr">
-        <is>
-          <t>2023–2025</t>
-        </is>
-      </c>
-      <c r="D73" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Дружинниковская, 15А</t>
-        </is>
-      </c>
-      <c r="E73" s="20" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F73" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="H73" s="20" t="inlineStr">
-        <is>
-          <t>20-25</t>
-        </is>
-      </c>
-      <c r="I73" s="20" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J73" s="22" t="n">
-        <v>850000</v>
-      </c>
-      <c r="K73" s="22" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="L73" s="22" t="n">
-        <v>2756939</v>
-      </c>
-      <c r="M73" s="22" t="n">
-        <v>61</v>
-      </c>
-      <c r="N73" s="20" t="inlineStr">
-        <is>
-          <t>47–847</t>
-        </is>
-      </c>
-      <c r="O73" s="20" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P73" s="20" t="n"/>
-      <c r="Q73" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R73" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S73" s="19" t="inlineStr">
-        <is>
-          <t>4 башни на месте Киноцентра</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="21" t="inlineStr">
-        <is>
-          <t>Sinatra (Синатра)</t>
-        </is>
-      </c>
-      <c r="B74" s="24" t="inlineStr">
-        <is>
-          <t>Glincom</t>
-        </is>
-      </c>
-      <c r="C74" s="24" t="inlineStr">
-        <is>
-          <t>2018–2020</t>
-        </is>
-      </c>
-      <c r="D74" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Большой Тишинский, 38</t>
-        </is>
-      </c>
-      <c r="E74" s="24" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F74" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G74" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="24" t="inlineStr">
-        <is>
-          <t>7-8</t>
-        </is>
-      </c>
-      <c r="I74" s="24" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J74" s="25" t="n">
-        <v>839130</v>
-      </c>
-      <c r="K74" s="25" t="n">
-        <v>1052456</v>
-      </c>
-      <c r="L74" s="25" t="n">
-        <v>1388889</v>
-      </c>
-      <c r="M74" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="N74" s="24" t="inlineStr">
-        <is>
-          <t>46–180</t>
-        </is>
-      </c>
-      <c r="O74" s="24" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P74" s="24" t="n"/>
-      <c r="Q74" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R74" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S74" s="21" t="inlineStr">
-        <is>
-          <t>реконструкция; cian years 2018/2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="19" t="inlineStr">
-        <is>
-          <t>Репаблик</t>
-        </is>
-      </c>
-      <c r="B75" s="20" t="inlineStr">
-        <is>
-          <t>Forma</t>
-        </is>
-      </c>
-      <c r="C75" s="20" t="inlineStr">
-        <is>
-          <t>2025–2026</t>
-        </is>
-      </c>
-      <c r="D75" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Пресненский Вал, к2.1</t>
-        </is>
-      </c>
-      <c r="E75" s="20" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F75" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G75" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H75" s="20" t="inlineStr">
-        <is>
-          <t>26-34</t>
-        </is>
-      </c>
-      <c r="I75" s="20" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J75" s="22" t="n">
-        <v>716667</v>
-      </c>
-      <c r="K75" s="22" t="n">
-        <v>943141</v>
-      </c>
-      <c r="L75" s="22" t="n">
-        <v>1570228</v>
-      </c>
-      <c r="M75" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="N75" s="20" t="inlineStr">
-        <is>
-          <t>27–140</t>
-        </is>
-      </c>
-      <c r="O75" s="20" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P75" s="20" t="n"/>
-      <c r="Q75" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R75" s="20" t="inlineStr"/>
-      <c r="S75" s="19" t="inlineStr"/>
-    </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="21" t="inlineStr">
-        <is>
-          <t>Пресня Сити</t>
-        </is>
-      </c>
-      <c r="B76" s="24" t="inlineStr">
-        <is>
-          <t>MR Group</t>
-        </is>
-      </c>
-      <c r="C76" s="24" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D76" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Ходынская, 2</t>
-        </is>
-      </c>
-      <c r="E76" s="24" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F76" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G76" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" s="24" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I76" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J76" s="25" t="n">
-        <v>647159</v>
-      </c>
-      <c r="K76" s="25" t="n">
-        <v>777778</v>
-      </c>
-      <c r="L76" s="25" t="n">
-        <v>1426966</v>
-      </c>
-      <c r="M76" s="25" t="n">
-        <v>29</v>
-      </c>
-      <c r="N76" s="24" t="inlineStr">
-        <is>
-          <t>42–158</t>
-        </is>
-      </c>
-      <c r="O76" s="24" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P76" s="24" t="n"/>
-      <c r="Q76" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R76" s="24" t="inlineStr"/>
-      <c r="S76" s="21" t="inlineStr"/>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="19" t="inlineStr">
-        <is>
-          <t>Пресненский вал 21</t>
-        </is>
-      </c>
-      <c r="B77" s="20" t="inlineStr">
-        <is>
-          <t>ПИК</t>
-        </is>
-      </c>
-      <c r="C77" s="20" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D77" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Пресненский Вал, 21</t>
-        </is>
-      </c>
-      <c r="E77" s="20" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F77" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" s="20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I77" s="20" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J77" s="22" t="n">
-        <v>498915</v>
-      </c>
-      <c r="K77" s="22" t="n">
-        <v>709877</v>
-      </c>
-      <c r="L77" s="22" t="n">
-        <v>1322373</v>
-      </c>
-      <c r="M77" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="N77" s="20" t="inlineStr">
-        <is>
-          <t>23–279</t>
-        </is>
-      </c>
-      <c r="O77" s="20" t="inlineStr">
-        <is>
-          <t>бизнес</t>
-        </is>
-      </c>
-      <c r="P77" s="20" t="n"/>
-      <c r="Q77" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R77" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S77" s="19" t="inlineStr">
-        <is>
-          <t>апартаменты; юрлицо Стройпроект</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="21" t="inlineStr">
-        <is>
-          <t>The Mostman (Мостман)</t>
-        </is>
-      </c>
-      <c r="B78" s="24" t="inlineStr">
-        <is>
-          <t>Инвест Проект</t>
-        </is>
-      </c>
-      <c r="C78" s="24" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Большая Андроньевская, 7</t>
-        </is>
-      </c>
-      <c r="E78" s="24" t="inlineStr">
-        <is>
-          <t>Таганский</t>
-        </is>
-      </c>
-      <c r="F78" s="21" t="inlineStr">
-        <is>
-          <t>Таганский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G78" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I78" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J78" s="25" t="n">
-        <v>820158</v>
-      </c>
-      <c r="K78" s="25" t="n">
-        <v>837429</v>
-      </c>
-      <c r="L78" s="25" t="n">
-        <v>854701</v>
-      </c>
-      <c r="M78" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N78" s="24" t="inlineStr">
-        <is>
-          <t>101–128</t>
-        </is>
-      </c>
-      <c r="O78" s="24" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P78" s="25" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q78" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R78" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S78" s="21" t="inlineStr"/>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="19" t="inlineStr">
-        <is>
-          <t>Долгоруковская 25</t>
-        </is>
-      </c>
-      <c r="B79" s="20" t="inlineStr">
-        <is>
-          <t>БЭЛ Девелопмент</t>
-        </is>
-      </c>
-      <c r="C79" s="20" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D79" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Долгоруковская, 25А</t>
-        </is>
-      </c>
-      <c r="E79" s="20" t="inlineStr">
-        <is>
-          <t>Тверской</t>
-        </is>
-      </c>
-      <c r="F79" s="21" t="inlineStr">
-        <is>
-          <t>Тверской (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G79" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H79" s="20" t="inlineStr">
-        <is>
-          <t>5-6</t>
-        </is>
-      </c>
-      <c r="I79" s="20" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J79" s="22" t="n">
-        <v>1258268</v>
-      </c>
-      <c r="K79" s="22" t="n">
-        <v>1879134</v>
-      </c>
-      <c r="L79" s="22" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="M79" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N79" s="20" t="inlineStr">
-        <is>
-          <t>63–237</t>
-        </is>
-      </c>
-      <c r="O79" s="20" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P79" s="22" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q79" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R79" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S79" s="19" t="inlineStr">
-        <is>
-          <t>корпуса Достижение и Традиция; апартаменты</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="21" t="inlineStr">
-        <is>
-          <t>Cameo Moscow Villas (Камео Москоу Виллас)</t>
-        </is>
-      </c>
-      <c r="B80" s="24" t="inlineStr">
-        <is>
-          <t>Stone Hedge</t>
-        </is>
-      </c>
-      <c r="C80" s="24" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Долгоруковская, 23А</t>
-        </is>
-      </c>
-      <c r="E80" s="24" t="inlineStr">
-        <is>
-          <t>Тверской</t>
-        </is>
-      </c>
-      <c r="F80" s="21" t="inlineStr">
-        <is>
-          <t>Тверской (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G80" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I80" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J80" s="25" t="n">
-        <v>1538462</v>
-      </c>
-      <c r="K80" s="25" t="n">
-        <v>1538462</v>
-      </c>
-      <c r="L80" s="25" t="n">
-        <v>1538462</v>
-      </c>
-      <c r="M80" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N80" s="24" t="inlineStr">
-        <is>
-          <t>390–390</t>
-        </is>
-      </c>
-      <c r="O80" s="24" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P80" s="25" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q80" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R80" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S80" s="21" t="inlineStr">
-        <is>
-          <t>17 городских вилл; ввод 30.07.2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="19" t="inlineStr">
-        <is>
-          <t>Веспер Тверская</t>
-        </is>
-      </c>
-      <c r="B81" s="20" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
-      <c r="C81" s="20" t="inlineStr">
-        <is>
-          <t>2020–2023</t>
-        </is>
-      </c>
-      <c r="D81" s="19" t="inlineStr">
-        <is>
-          <t>Москва, 1-я Тверская-Ямская, 2А</t>
-        </is>
-      </c>
-      <c r="E81" s="20" t="inlineStr">
-        <is>
-          <t>Тверской</t>
-        </is>
-      </c>
-      <c r="F81" s="21" t="inlineStr">
-        <is>
-          <t>Тверской (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="20" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I81" s="20" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>1138462</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>1534941</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>2085809</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="N81" s="20" t="inlineStr">
-        <is>
-          <t>36–160</t>
-        </is>
-      </c>
-      <c r="O81" s="20" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P81" s="20" t="n"/>
-      <c r="Q81" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R81" s="20" t="inlineStr"/>
-      <c r="S81" s="19" t="inlineStr"/>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="21" t="inlineStr">
-        <is>
-          <t>Элитный дом Реномэ</t>
-        </is>
-      </c>
-      <c r="B82" s="24" t="inlineStr">
-        <is>
-          <t>Sminex</t>
-        </is>
-      </c>
-      <c r="C82" s="24" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D82" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Новослободская, 24Ас2</t>
-        </is>
-      </c>
-      <c r="E82" s="24" t="inlineStr">
-        <is>
-          <t>Тверской</t>
-        </is>
-      </c>
-      <c r="F82" s="21" t="inlineStr">
-        <is>
-          <t>Тверской (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G82" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H82" s="24" t="inlineStr">
-        <is>
-          <t>5-10</t>
-        </is>
-      </c>
-      <c r="I82" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J82" s="25" t="n">
-        <v>887805</v>
-      </c>
-      <c r="K82" s="25" t="n">
-        <v>1532075</v>
-      </c>
-      <c r="L82" s="25" t="n">
-        <v>1825397</v>
-      </c>
-      <c r="M82" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N82" s="24" t="inlineStr">
-        <is>
-          <t>65–126</t>
-        </is>
-      </c>
-      <c r="O82" s="24" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P82" s="24" t="n"/>
-      <c r="Q82" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R82" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S82" s="21" t="inlineStr">
-        <is>
-          <t>корпуса Nouveau и Heritage; арх. ADM</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="19" t="inlineStr">
-        <is>
-          <t>Клубный дом Maison Rouge (Мезон Руж)</t>
-        </is>
-      </c>
-      <c r="B83" s="20" t="inlineStr">
-        <is>
-          <t>MR Group</t>
-        </is>
-      </c>
-      <c r="C83" s="20" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D83" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Палиха, 4</t>
-        </is>
-      </c>
-      <c r="E83" s="20" t="inlineStr">
-        <is>
-          <t>Тверской</t>
-        </is>
-      </c>
-      <c r="F83" s="21" t="inlineStr">
-        <is>
-          <t>Тверской (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G83" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I83" s="20" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J83" s="22" t="n">
-        <v>920792</v>
-      </c>
-      <c r="K83" s="22" t="n">
-        <v>1116071</v>
-      </c>
-      <c r="L83" s="22" t="n">
-        <v>1152000</v>
-      </c>
-      <c r="M83" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N83" s="20" t="inlineStr">
-        <is>
-          <t>101–125</t>
-        </is>
-      </c>
-      <c r="O83" s="20" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P83" s="20" t="n"/>
-      <c r="Q83" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R83" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S83" s="19" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="21" t="inlineStr">
-        <is>
-          <t>Резиденция Тверская</t>
-        </is>
-      </c>
-      <c r="B84" s="24" t="inlineStr">
-        <is>
-          <t>Kovaks (Ковакс)</t>
-        </is>
-      </c>
-      <c r="C84" s="24" t="inlineStr">
-        <is>
-          <t>2018–2020</t>
-        </is>
-      </c>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>Москва, 2-я Брестская, 6</t>
-        </is>
-      </c>
-      <c r="E84" s="24" t="inlineStr">
-        <is>
-          <t>Тверской</t>
-        </is>
-      </c>
-      <c r="F84" s="21" t="inlineStr">
-        <is>
-          <t>Тверской (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G84" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" s="24" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="I84" s="24" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J84" s="25" t="n">
-        <v>515556</v>
-      </c>
-      <c r="K84" s="25" t="n">
-        <v>772624</v>
-      </c>
-      <c r="L84" s="25" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="M84" s="25" t="n">
-        <v>42</v>
-      </c>
-      <c r="N84" s="24" t="inlineStr">
-        <is>
-          <t>37–161</t>
-        </is>
-      </c>
-      <c r="O84" s="24" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P84" s="25" t="n">
-        <v>190</v>
-      </c>
-      <c r="Q84" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R84" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S84" s="21" t="inlineStr">
-        <is>
           <t>апарт-отель; юрлицо Техноком Трейд</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="19" t="inlineStr">
-        <is>
-          <t>Медный 3.14</t>
-        </is>
-      </c>
-      <c r="B85" s="20" t="inlineStr">
-        <is>
-          <t>Capital Group</t>
-        </is>
-      </c>
-      <c r="C85" s="20" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D85" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Донская, 14</t>
-        </is>
-      </c>
-      <c r="E85" s="20" t="inlineStr">
-        <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F85" s="21" t="inlineStr">
-        <is>
-          <t>Якиманка (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="H85" s="20" t="inlineStr">
-        <is>
-          <t>16-21</t>
-        </is>
-      </c>
-      <c r="I85" s="20" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>1357143</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>1357143</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>1458537</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N85" s="20" t="inlineStr">
-        <is>
-          <t>41–42</t>
-        </is>
-      </c>
-      <c r="O85" s="20" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P85" s="22" t="n">
-        <v>134</v>
-      </c>
-      <c r="Q85" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R85" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S85" s="19" t="inlineStr">
-        <is>
-          <t>арх. Сергей Скуратов</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="21" t="inlineStr">
-        <is>
-          <t>Sky House (Скай Хаус)</t>
-        </is>
-      </c>
-      <c r="B86" s="24" t="inlineStr">
-        <is>
-          <t>Capital Group</t>
-        </is>
-      </c>
-      <c r="C86" s="24" t="inlineStr">
-        <is>
-          <t>2020–2022</t>
-        </is>
-      </c>
-      <c r="D86" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Мытная, 40к3</t>
-        </is>
-      </c>
-      <c r="E86" s="24" t="inlineStr">
-        <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F86" s="21" t="inlineStr">
-        <is>
-          <t>Якиманка (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G86" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H86" s="24" t="inlineStr">
-        <is>
-          <t>20-30</t>
-        </is>
-      </c>
-      <c r="I86" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J86" s="25" t="n">
-        <v>469453</v>
-      </c>
-      <c r="K86" s="25" t="n">
-        <v>840321</v>
-      </c>
-      <c r="L86" s="25" t="n">
-        <v>1035120</v>
-      </c>
-      <c r="M86" s="25" t="n">
-        <v>40</v>
-      </c>
-      <c r="N86" s="24" t="inlineStr">
-        <is>
-          <t>54–287</t>
-        </is>
-      </c>
-      <c r="O86" s="24" t="inlineStr">
-        <is>
-          <t>бизнес</t>
-        </is>
-      </c>
-      <c r="P86" s="25" t="n">
-        <v>539</v>
-      </c>
-      <c r="Q86" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R86" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S86" s="21" t="inlineStr">
-        <is>
-          <t>достройка после банкротства ОЛТЭР</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="27" t="inlineStr">
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="24" t="inlineStr">
         <is>
           <t>Источник: живая выдача Циан 2026-09-07 (api.cian.ru, инструмент tools/cian/cian.js), вторичка с годом дома 2018+ и новостройки по 10 районам ЦАО. Цены — ₽/м² по активным объявлениям. Застройщик и класс — по открытым данным (ручная разметка docs/premium-cao/manual.json).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S86"/>
+  <autoFilter ref="A3:S67"/>
   <mergeCells count="3">
-    <mergeCell ref="A88:S88"/>
+    <mergeCell ref="A69:S69"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
   </mergeCells>
@@ -7583,55 +6057,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R57" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q58" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q58" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R58" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q59" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R60" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R64" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R66" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R67" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R68" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q69" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q70" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R70" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q71" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R71" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q72" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R72" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q73" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R73" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q74" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R74" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q75" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q76" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q77" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R77" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q78" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R78" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R79" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R80" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R82" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q83" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R83" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q84" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R84" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q85" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R85" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q86" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R86" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R61" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R62" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R63" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R64" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R67" r:id="rId110"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -7653,7 +6095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10127,40 +8569,40 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>Дом 56</t>
+          <t>ЖК «Квартал Life Time»</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>Галс-Девелопмент</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2 кв. 2026</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>Москва, Фридриха Энгельса, 56</t>
+          <t>Москва, улица Сергея Макеева</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>1905 года</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
+          <t>Пресня</t>
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H37" s="20" t="inlineStr">
         <is>
-          <t>20-27</t>
+          <t>9-23</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
@@ -10169,1022 +8611,400 @@
         </is>
       </c>
       <c r="J37" s="22" t="n">
-        <v>609244</v>
+        <v>1019417</v>
       </c>
       <c r="K37" s="22" t="n">
-        <v>1043429</v>
+        <v>2290000</v>
       </c>
       <c r="L37" s="22" t="n">
-        <v>61</v>
-      </c>
-      <c r="M37" s="20" t="inlineStr"/>
+        <v>232</v>
+      </c>
+      <c r="M37" s="20" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="N37" s="23" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="O37" s="20" t="inlineStr">
-        <is>
-          <t>Циан 2026-09-07</t>
+      <c r="O37" s="19" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="P37" s="19" t="inlineStr">
         <is>
-          <t>арх. Pride</t>
+          <t>по Циан дом сдан</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>ЖК «Новая, 11»</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>Москва, улица Новая Дорога, 11Бс1</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>Электрозаводская</t>
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>ЖК «Элитный квартал Тишинский бульвар»</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>2027–2028</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Москва, Электрический переулок</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>Белорусская</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>Басманный (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G38" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="24" t="inlineStr">
-        <is>
-          <t>9-15</t>
-        </is>
-      </c>
-      <c r="I38" s="24" t="inlineStr">
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>3-14</t>
+        </is>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J38" s="25" t="n">
-        <v>664831</v>
-      </c>
-      <c r="K38" s="25" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="L38" s="25" t="n">
-        <v>40</v>
-      </c>
-      <c r="M38" s="24" t="inlineStr">
+      <c r="J38" s="22" t="n">
+        <v>1239934</v>
+      </c>
+      <c r="K38" s="22" t="n">
+        <v>3044646</v>
+      </c>
+      <c r="L38" s="22" t="n">
+        <v>229</v>
+      </c>
+      <c r="M38" s="20" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N38" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="O38" s="21" t="inlineStr">
+      <c r="N38" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="O38" s="19" t="inlineStr">
         <is>
           <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P38" s="21" t="inlineStr"/>
+      <c r="P38" s="19" t="inlineStr"/>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>Vernissage (Апартаменты премиум-класса) (Вернисаж)</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>Ziggurat Development</t>
+          <t>ЖК «Начало»</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>ДОНСТРОЙ</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>Москва, Щипок, 26С2</t>
+          <t>Москва, улица Сергея Макеева, 7</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
+          <t>Ул. 1905 года</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
         <is>
-          <t>Замоскворечье (вне Садового)</t>
+          <t>Пресня</t>
         </is>
       </c>
       <c r="G39" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>11-48</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J39" s="22" t="n">
+        <v>925200</v>
+      </c>
+      <c r="K39" s="22" t="n">
+        <v>1352000</v>
+      </c>
+      <c r="L39" s="22" t="n">
+        <v>231</v>
+      </c>
+      <c r="M39" s="20" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="N39" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="O39" s="19" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P39" s="19" t="inlineStr">
+        <is>
+          <t>знак вопроса</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>Дом Спорта</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Москва, Дружинниковская, 18</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="20" t="inlineStr">
-        <is>
-          <t>5-8</t>
-        </is>
-      </c>
-      <c r="I39" s="20" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J39" s="22" t="n">
-        <v>696124</v>
-      </c>
-      <c r="K39" s="22" t="n">
-        <v>962085</v>
-      </c>
-      <c r="L39" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M39" s="20" t="inlineStr"/>
-      <c r="N39" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="O39" s="20" t="inlineStr">
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="n">
+        <v>2281650</v>
+      </c>
+      <c r="K40" s="22" t="n">
+        <v>3174937</v>
+      </c>
+      <c r="L40" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="M40" s="20" t="inlineStr"/>
+      <c r="N40" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="O40" s="20" t="inlineStr">
         <is>
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="P39" s="19" t="inlineStr">
-        <is>
-          <t>юрлицо СЗ Щипок; апартаменты</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>ЖК «Квартал Life Time»</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>Sminex</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>2 кв. 2026</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>Москва, улица Сергея Макеева</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
-        <is>
-          <t>1905 года</t>
-        </is>
-      </c>
-      <c r="F40" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G40" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="H40" s="24" t="inlineStr">
-        <is>
-          <t>9-23</t>
-        </is>
-      </c>
-      <c r="I40" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J40" s="25" t="n">
-        <v>1019417</v>
-      </c>
-      <c r="K40" s="25" t="n">
-        <v>2290000</v>
-      </c>
-      <c r="L40" s="25" t="n">
-        <v>232</v>
-      </c>
-      <c r="M40" s="24" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N40" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="O40" s="21" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="P40" s="21" t="inlineStr">
-        <is>
-          <t>по Циан дом сдан</t>
+      <c r="P40" s="19" t="inlineStr">
+        <is>
+          <t>старт продаж 2026, стройка начата (Ведомости)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>ЖК «Элитный квартал Тишинский бульвар»</t>
+          <t>ЖК «Климашкина 7/11»</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>MR Group</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>2027–2028</t>
+          <t>4 кв. 2028</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>Москва, Электрический переулок</t>
+          <t>Москва, улица Климашкина, 7/11</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
+          <t>Красная пресня</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J41" s="22" t="n">
+        <v>1581360</v>
+      </c>
+      <c r="K41" s="22" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="L41" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="M41" s="20" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="N41" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="O41" s="19" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P41" s="19" t="inlineStr"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>ЖК «Слава»</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>MR Group</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>2 кв. 2027</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="inlineStr">
+        <is>
+          <t>Москва, Ленинградский проспект, вл8</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
+        <is>
           <t>Белорусская</t>
         </is>
       </c>
-      <c r="F41" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G41" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="H41" s="20" t="inlineStr">
-        <is>
-          <t>3-14</t>
-        </is>
-      </c>
-      <c r="I41" s="20" t="inlineStr">
+      <c r="F42" s="27" t="inlineStr">
+        <is>
+          <t>Белорусская</t>
+        </is>
+      </c>
+      <c r="G42" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>8-37</t>
+        </is>
+      </c>
+      <c r="I42" s="26" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J41" s="22" t="n">
-        <v>1239934</v>
-      </c>
-      <c r="K41" s="22" t="n">
-        <v>3044646</v>
-      </c>
-      <c r="L41" s="22" t="n">
-        <v>229</v>
-      </c>
-      <c r="M41" s="20" t="inlineStr">
+      <c r="J42" s="28" t="n">
+        <v>695000</v>
+      </c>
+      <c r="K42" s="28" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="L42" s="28" t="n">
+        <v>184</v>
+      </c>
+      <c r="M42" s="26" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="N41" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="O41" s="19" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="P41" s="19" t="inlineStr"/>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="21" t="inlineStr">
-        <is>
-          <t>ЖК «Начало»</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>ДОНСТРОЙ</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>Москва, улица Сергея Макеева, 7</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>Ул. 1905 года</t>
-        </is>
-      </c>
-      <c r="F42" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="H42" s="24" t="inlineStr">
-        <is>
-          <t>11-48</t>
-        </is>
-      </c>
-      <c r="I42" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J42" s="25" t="n">
-        <v>925200</v>
-      </c>
-      <c r="K42" s="25" t="n">
-        <v>1352000</v>
-      </c>
-      <c r="L42" s="25" t="n">
-        <v>231</v>
-      </c>
-      <c r="M42" s="24" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N42" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="O42" s="21" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="P42" s="21" t="inlineStr">
-        <is>
-          <t>знак вопроса</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t>Дом Спорта</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>Capital Group</t>
-        </is>
-      </c>
-      <c r="C43" s="20" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Дружинниковская, 18</t>
-        </is>
-      </c>
-      <c r="E43" s="20" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F43" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G43" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="20" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I43" s="20" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J43" s="22" t="n">
-        <v>2281650</v>
-      </c>
-      <c r="K43" s="22" t="n">
-        <v>3174937</v>
-      </c>
-      <c r="L43" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="M43" s="20" t="inlineStr"/>
-      <c r="N43" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="O43" s="20" t="inlineStr">
-        <is>
-          <t>Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="P43" s="19" t="inlineStr">
-        <is>
-          <t>старт продаж 2026, стройка начата (Ведомости)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="21" t="inlineStr">
-        <is>
-          <t>ЖК «Климашкина 7/11»</t>
-        </is>
-      </c>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>MR Group</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>4 кв. 2028</t>
-        </is>
-      </c>
-      <c r="D44" s="21" t="inlineStr">
-        <is>
-          <t>Москва, улица Климашкина, 7/11</t>
-        </is>
-      </c>
-      <c r="E44" s="24" t="inlineStr">
-        <is>
-          <t>Красная пресня</t>
-        </is>
-      </c>
-      <c r="F44" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G44" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="24" t="inlineStr">
-        <is>
-          <t>7-9</t>
-        </is>
-      </c>
-      <c r="I44" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J44" s="25" t="n">
-        <v>1581360</v>
-      </c>
-      <c r="K44" s="25" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="L44" s="25" t="n">
-        <v>17</v>
-      </c>
-      <c r="M44" s="24" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N44" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="O44" s="21" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="P44" s="21" t="inlineStr"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Клубный дом "Магнум Соло"</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>Magnum Development</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Александра Солженицына, 23Б</t>
-        </is>
-      </c>
-      <c r="E45" s="20" t="inlineStr">
-        <is>
-          <t>Таганский</t>
-        </is>
-      </c>
-      <c r="F45" s="21" t="inlineStr">
-        <is>
-          <t>Таганский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G45" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I45" s="20" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J45" s="22" t="n">
-        <v>1625537</v>
-      </c>
-      <c r="K45" s="22" t="n">
-        <v>2067015</v>
-      </c>
-      <c r="L45" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="M45" s="20" t="inlineStr"/>
-      <c r="N45" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="O45" s="20" t="inlineStr">
-        <is>
-          <t>Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="P45" s="19" t="inlineStr">
-        <is>
-          <t>юрлицо СЗ КИГ</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="21" t="inlineStr">
-        <is>
-          <t>ЖК «Клубный дом Энигмия»</t>
-        </is>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>Upside</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>4 кв. 2028</t>
-        </is>
-      </c>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Новослободская улица, 19</t>
-        </is>
-      </c>
-      <c r="E46" s="24" t="inlineStr">
-        <is>
-          <t>Менделеевская</t>
-        </is>
-      </c>
-      <c r="F46" s="21" t="inlineStr">
-        <is>
-          <t>Тверской (вне Садового)</t>
-        </is>
-      </c>
-      <c r="G46" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" s="24" t="inlineStr">
-        <is>
-          <t>15-19</t>
-        </is>
-      </c>
-      <c r="I46" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J46" s="25" t="n">
-        <v>1138600</v>
-      </c>
-      <c r="K46" s="25" t="n">
-        <v>1766400</v>
-      </c>
-      <c r="L46" s="25" t="n">
-        <v>50</v>
-      </c>
-      <c r="M46" s="24" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N46" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="O46" s="21" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="P46" s="21" t="inlineStr">
-        <is>
-          <t>знак вопроса</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="19" t="inlineStr">
-        <is>
-          <t>ЖК «Слава»</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>MR Group</t>
-        </is>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
-        <is>
-          <t>2 кв. 2027</t>
-        </is>
-      </c>
-      <c r="D47" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Ленинградский проспект, вл8</t>
-        </is>
-      </c>
-      <c r="E47" s="20" t="inlineStr">
-        <is>
-          <t>Белорусская</t>
-        </is>
-      </c>
-      <c r="F47" s="21" t="inlineStr">
-        <is>
-          <t>вне зоны (Беговой, САО)</t>
-        </is>
-      </c>
-      <c r="G47" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="H47" s="20" t="inlineStr">
-        <is>
-          <t>8-37</t>
-        </is>
-      </c>
-      <c r="I47" s="20" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J47" s="22" t="n">
-        <v>695000</v>
-      </c>
-      <c r="K47" s="22" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="L47" s="22" t="n">
-        <v>184</v>
-      </c>
-      <c r="M47" s="20" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N47" s="20" t="inlineStr"/>
-      <c r="O47" s="20" t="inlineStr">
+      <c r="N42" s="26" t="inlineStr"/>
+      <c r="O42" s="26" t="inlineStr">
         <is>
           <t>таблица заказчика</t>
         </is>
       </c>
-      <c r="P47" s="19" t="inlineStr">
+      <c r="P42" s="25" t="inlineStr">
         <is>
           <t>пометка «Тише говорят!»</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="21" t="inlineStr">
-        <is>
-          <t>ЖК «ЛОТ от Аквилон»</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>Аквилон</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>3 кв. 2029</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Жуков проезд, 21</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>Павелецкая</t>
-        </is>
-      </c>
-      <c r="F48" s="21" t="inlineStr">
-        <is>
-          <t>вне зоны (Даниловский, ЮАО)</t>
-        </is>
-      </c>
-      <c r="G48" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="24" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="I48" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J48" s="25" t="n">
-        <v>590000</v>
-      </c>
-      <c r="K48" s="25" t="n">
-        <v>860000</v>
-      </c>
-      <c r="L48" s="25" t="n">
-        <v>115</v>
-      </c>
-      <c r="M48" s="24" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N48" s="24" t="inlineStr"/>
-      <c r="O48" s="24" t="inlineStr">
-        <is>
-          <t>таблица заказчика</t>
-        </is>
-      </c>
-      <c r="P48" s="21" t="inlineStr"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>ЖК «Веспер Кутузовский»</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>Веспер</t>
-        </is>
-      </c>
-      <c r="C49" s="20" t="inlineStr">
-        <is>
-          <t>1 кв. 2028</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="inlineStr">
-        <is>
-          <t>Москва, Кутузовский проспект</t>
-        </is>
-      </c>
-      <c r="E49" s="20" t="inlineStr">
-        <is>
-          <t>Дорогомилово</t>
-        </is>
-      </c>
-      <c r="F49" s="21" t="inlineStr">
-        <is>
-          <t>вне зоны (Дорогомилово, ЗАО)</t>
-        </is>
-      </c>
-      <c r="G49" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="20" t="inlineStr">
-        <is>
-          <t>7-17</t>
-        </is>
-      </c>
-      <c r="I49" s="20" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J49" s="22" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="K49" s="22" t="n">
-        <v>3605000</v>
-      </c>
-      <c r="L49" s="22" t="n">
-        <v>83</v>
-      </c>
-      <c r="M49" s="20" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N49" s="20" t="inlineStr"/>
-      <c r="O49" s="20" t="inlineStr">
-        <is>
-          <t>таблица заказчика</t>
-        </is>
-      </c>
-      <c r="P49" s="19" t="inlineStr"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>ЖК «Бадаевский»</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>Capital Group</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>2026–2027</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>Москва, Кутузовский проспект</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>Дорогомилово</t>
-        </is>
-      </c>
-      <c r="F50" s="21" t="inlineStr">
-        <is>
-          <t>вне зоны (Дорогомилово, ЗАО)</t>
-        </is>
-      </c>
-      <c r="G50" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="24" t="inlineStr">
-        <is>
-          <t>17-18</t>
-        </is>
-      </c>
-      <c r="I50" s="24" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J50" s="25" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="K50" s="25" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="L50" s="25" t="n">
-        <v>108</v>
-      </c>
-      <c r="M50" s="24" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N50" s="24" t="inlineStr"/>
-      <c r="O50" s="24" t="inlineStr">
-        <is>
-          <t>таблица заказчика</t>
-        </is>
-      </c>
-      <c r="P50" s="21" t="inlineStr"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>ЖК «SHIFT»</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>Пионер</t>
-        </is>
-      </c>
-      <c r="C51" s="20" t="inlineStr">
-        <is>
-          <t>4 кв. 2028</t>
-        </is>
-      </c>
-      <c r="D51" s="19" t="inlineStr">
-        <is>
-          <t>Москва, жилой комплекс Шифт</t>
-        </is>
-      </c>
-      <c r="E51" s="20" t="inlineStr">
-        <is>
-          <t>Ленинский проспект</t>
-        </is>
-      </c>
-      <c r="F51" s="21" t="inlineStr">
-        <is>
-          <t>вне зоны (Ленинский проспект)</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H51" s="20" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I51" s="20" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J51" s="22" t="n">
-        <v>826000</v>
-      </c>
-      <c r="K51" s="22" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="L51" s="22" t="n">
-        <v>214</v>
-      </c>
-      <c r="M51" s="20" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
-      <c r="N51" s="20" t="inlineStr"/>
-      <c r="O51" s="20" t="inlineStr">
-        <is>
-          <t>таблица заказчика</t>
-        </is>
-      </c>
-      <c r="P51" s="19" t="inlineStr">
-        <is>
-          <t>пометка «Посмотреть варианты»</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="27" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>Строки из таблицы заказчика дополнены живой выдачей Циан там, где ЖК найден в базе (цены и число лотов обновлены). Остальные строки — найдены в выдаче Циан по новостройкам ЦАО.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:P51"/>
+  <autoFilter ref="A3:P42"/>
   <mergeCells count="3">
-    <mergeCell ref="A53:P53"/>
+    <mergeCell ref="A44:P44"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
@@ -11226,11 +9046,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId42"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -11252,7 +9067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11391,7 +9206,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -11468,7 +9283,7 @@
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -11531,7 +9346,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -11596,7 +9411,7 @@
           <t>Арбат</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -11655,7 +9470,7 @@
           <t>Таганский</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -11724,7 +9539,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -11795,7 +9610,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -11856,7 +9671,7 @@
           <t>Тверской</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -11919,7 +9734,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -11974,7 +9789,7 @@
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -12043,7 +9858,7 @@
           <t>Тверской</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -12118,7 +9933,7 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -12181,7 +9996,7 @@
           <t>Басманный</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -12246,7 +10061,7 @@
           <t>Мещанский</t>
         </is>
       </c>
-      <c r="D17" s="28" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -12313,7 +10128,7 @@
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -12372,7 +10187,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -12433,7 +10248,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D20" s="29" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -12494,7 +10309,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -12561,7 +10376,7 @@
           <t>Хамовники (Остоженка)</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -12618,7 +10433,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D23" s="29" t="inlineStr">
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -12681,7 +10496,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D24" s="29" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -12748,7 +10563,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D25" s="29" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -12809,7 +10624,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -12872,7 +10687,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -12935,7 +10750,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -12998,7 +10813,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -13061,7 +10876,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -13126,7 +10941,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
@@ -13184,59 +10999,59 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>МФК «На Краснопресненской набережной» (Трёхгорная мануфактура)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>Краснопресненская наб., 10</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D32" s="30" t="inlineStr">
-        <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>ГК Ташир</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>анонсирован, старт продаж ожидается</t>
         </is>
       </c>
-      <c r="G32" s="15" t="n"/>
-      <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="n"/>
-      <c r="K32" s="15" t="n"/>
-      <c r="L32" s="15" t="inlineStr">
+      <c r="G32" s="20" t="n"/>
+      <c r="H32" s="20" t="n"/>
+      <c r="I32" s="20" t="n"/>
+      <c r="J32" s="20" t="n"/>
+      <c r="K32" s="20" t="n"/>
+      <c r="L32" s="20" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="M32" s="15" t="n"/>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="15" t="inlineStr">
+      <c r="M32" s="20" t="n"/>
+      <c r="N32" s="20" t="n"/>
+      <c r="O32" s="20" t="inlineStr">
         <is>
           <t>novostroycity.ru</t>
         </is>
       </c>
-      <c r="P32" s="18" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q32" s="14" t="inlineStr">
+      <c r="P32" s="23" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q32" s="19" t="inlineStr">
         <is>
           <t>Участок ~1,7 га с ОКН (фабрика Трёхгорной мануфактуры, будет сохранена/реконструирована). Апартаменты премиум-класса + офисы + wellness, подземный паркинг на 750 м/м. Сроки реализации официально не подтверждены; апартаменты, а не квартиры.</t>
         </is>
@@ -13245,63 +11060,53 @@
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>Клубный дом «Капельский, 5»</t>
+          <t>Участок КРТ «Большой Тишинский переулок, 8»</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>Капельский переулок, 5</t>
+          <t>Большой Тишинский переулок, 8 (стр. 1, 2)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>Мещанский</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>Мещанский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="E33" s="19" t="inlineStr">
-        <is>
-          <t>не раскрыт (юрлицо на сайте проекта не указано)</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>не раскрыт</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>проектирование / предстарт продаж (официально: открытие продаж планируется во II–III кв. 2026)</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="n"/>
-      <c r="H33" s="20" t="n"/>
-      <c r="I33" s="20" t="inlineStr">
-        <is>
-          <t>8–9</t>
-        </is>
-      </c>
-      <c r="J33" s="22" t="n">
-        <v>46</v>
-      </c>
-      <c r="K33" s="19" t="inlineStr">
-        <is>
-          <t>2026 Q2–Q3 (старт продаж)</t>
-        </is>
-      </c>
-      <c r="L33" s="19" t="inlineStr">
-        <is>
-          <t>2029 Q4 (по данным Whitewill)</t>
-        </is>
-      </c>
+          <t>решение о КРТ (по данным заказчика — август 2026); оператор/правообладатель и торги в открытых источниках не найдены</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H33" s="22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I33" s="20" t="n"/>
+      <c r="J33" s="20" t="n"/>
+      <c r="K33" s="20" t="n"/>
+      <c r="L33" s="20" t="n"/>
       <c r="M33" s="20" t="n"/>
       <c r="N33" s="20" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="O33" s="19" t="inlineStr">
         <is>
-          <t>Официальный сайт kapelsky5.ru; Whitewill; Novostroy-M</t>
+          <t>krt.mos.ru (реестр проектов КРТ Москвы)</t>
         </is>
       </c>
       <c r="P33" s="23" t="inlineStr">
@@ -13311,214 +11116,21 @@
       </c>
       <c r="Q33" s="19" t="inlineStr">
         <is>
-          <t>46 резиденций, переменная этажность, пентхаусы с террасами, приватный сквер, подземный паркинг. ВНИМАНИЕ: локация вне Садового кольца (у м. Проспект Мира, ~1 км севернее), включена по запросу заказчика.; Делюкс/премиум клубный дом; квартиры 54–345 м²; пентхаусы с террасами; двухуровневый паркинг на 56 м/м, 32 кладовые; приватный сад во дворе. Whitewill (https://whitewill.ru/developments/kapelskiy-5) указывает 8 этажей и срок сдачи 4 кв. 2029; Novostroy-M — 9 этажей, «скоро старт». Цены по запросу.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>Делюкс-комплекс «Капранова, 3» (проект APEX)</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>переулок Капранова, 3 (БЦ «Премьер Плаза») + Малый Предтеченский пер., 1/2/1, Нововаганьковский пер., 3 стр. 1, Глубокий пер., 7</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
-        <is>
-          <t>не раскрыт</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
-        <is>
-          <t>визуализации направлены на согласование в город (ноябрь 2025); предстарт, старт продаж заявлен на 2026</t>
-        </is>
-      </c>
-      <c r="G34" s="24" t="n"/>
-      <c r="H34" s="24" t="n"/>
-      <c r="I34" s="21" t="inlineStr">
-        <is>
-          <t>9–23 (шесть корпусов)</t>
-        </is>
-      </c>
-      <c r="J34" s="25" t="n">
-        <v>255</v>
-      </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>2026 (старт продаж)</t>
-        </is>
-      </c>
-      <c r="L34" s="24" t="n"/>
-      <c r="M34" s="24" t="n"/>
-      <c r="N34" s="24" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="O34" s="21" t="inlineStr">
-        <is>
-          <t>Москвич Mag (19.11.2025); sosedi.life (07.04.2026)</t>
-        </is>
-      </c>
-      <c r="P34" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q34" s="21" t="inlineStr">
-        <is>
-          <t>Делюкс-проект в базе перспективных стартов 2026–2027 (mskdeluxe.ru, цены «от 60 млн руб.»). Обзор smart-lab.ru/blog/1231916.php указывает старт продаж в 2026 г., 12 этажей, двор без машин. Застройщик и параметры в открытых источниках не подтверждены. ~400 м от м. Краснопресненская, вне Садового кольца.; Единая застройка нескольких участков за Домом Правительства у Пресненского детского парка; башни с «волнообразными» фасадами, снос БЦ «Премьер Плаза», сохранение усадьбы Резанова. По sosedi.life (https://sosedi.life/news/zhk-kapranova-3/): участок &gt;2,5 га, 6 корпусов 9–23 этажа, 255 квартир, двор 7 039,6 м², лобби Balcon, 2–5 квартир на этаже. Указанные в запросе «12 этажей» источниками не подтверждаются. В списке делюкс-стартов mskdeluxe.ru.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>КРТ вдоль Звенигородского шоссе (три участка, 73,62 га)</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>Вдоль Звенигородского шоссе между 3-й Магистральной улицей и ТТК (Пресненский / Хорошёвский районы)</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>Пресненский / Хорошёвский</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>не раскрыт (оператор/инвестор не назван; в числе 9 проектов КРТ, утвержденных в августе 2026)</t>
-        </is>
-      </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>решение о КРТ принято (август 2026); оператор/торги не объявлены</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="H35" s="20" t="n"/>
-      <c r="I35" s="20" t="n"/>
-      <c r="J35" s="20" t="n"/>
-      <c r="K35" s="20" t="n"/>
-      <c r="L35" s="20" t="n"/>
-      <c r="M35" s="20" t="n"/>
-      <c r="N35" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="O35" s="19" t="inlineStr">
-        <is>
-          <t>Интерфакс-Россия; Ведомости.Город (02.09.2026)</t>
-        </is>
-      </c>
-      <c r="P35" s="23" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q35" s="19" t="inlineStr">
-        <is>
-          <t>Три участка нежилой застройки общей площадью 73,62 га; &gt;3,2 млн м² недвижимости (жильё + общественно-деловые объекты, школы на 4050 мест, детсады на 1775 мест), 35,5 тыс. рабочих мест. Часть «Большого Сити» (Шелепиха/Магистральные улицы), класс жилья не заявлен — не обязательно премиум.; Три участка нежилой застройки (старые склады, админздания) общей площадью 73,62 га; свыше 3,2 млн м² — жилье, общественно-деловые и социальные объекты; строительство/реконструкция дорог ~6,5 км; здание конечной станции наземного транспорта с отстойно-разворотной площадкой (Ведомости, https://www.vedomosti.ru/gorod/ourcity/articles/gorodskoi-kvartal). Жилая премиальная часть отдельно не выделена; класс жилья не указан. Оператор (Московский фонд реновации / КРТ 21 / инвестор по торгам) не объявлен.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>Участок КРТ «Большой Тишинский переулок, 8»</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>Большой Тишинский переулок, 8 (стр. 1, 2)</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>Пресненский (вне Садового)</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
-        <is>
-          <t>не раскрыт</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>решение о КРТ (по данным заказчика — август 2026); оператор/правообладатель и торги в открытых источниках не найдены</t>
-        </is>
-      </c>
-      <c r="G36" s="25" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H36" s="25" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I36" s="24" t="n"/>
-      <c r="J36" s="24" t="n"/>
-      <c r="K36" s="24" t="n"/>
-      <c r="L36" s="24" t="n"/>
-      <c r="M36" s="24" t="n"/>
-      <c r="N36" s="24" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="O36" s="21" t="inlineStr">
-        <is>
-          <t>krt.mos.ru (реестр проектов КРТ Москвы)</t>
-        </is>
-      </c>
-      <c r="P36" s="26" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q36" s="21" t="inlineStr">
-        <is>
           <t>Участок ~0,3 га включён в программу КРТ решением властей Москвы. Существующие здания реконструированы в 2004 г., в 2020 г. переоборудованы под хостелы. Оператор/девелопер в публикации не назван; в других открытых источниках на 07.09.2026 не найден. Локация — Пресненский район вне Садового кольца, между Б. Грузинской и Пресненским Валом (условно отнесено к зоне Пресня/Сити).; Поиск по mos.ru, krt.mos.ru, stroi.mos.ru, Ведомости, РБК, Интерфакс, М24, Известия (август–сентябрь 2026) не выявил отдельной публикации по этому участку: новости августа 2026 о КРТ (250 проектов, 63 договора с начала года) даются агрегированно. Ближайший крупный проект — квартал «Тишинский бульвар» Sminex (Электрический пер., 1), связь с участком №8 не подтверждена. Площадь 0,3 га / ~10 000 м² — из исходных данных запроса, независимого подтверждения нет.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>Источники: открытые публикации 2025–2026 (stroi.mos.ru, mos.ru, отраслевые СМИ, публичные Telegram-каналы). Закрытый канал t.me/c/3370602239 недоступен без членства — пост №1364 про ЗУ «Большой Тишинский, 8» подтверждён по открытым источникам.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q36"/>
+  <autoFilter ref="A3:Q33"/>
   <mergeCells count="3">
-    <mergeCell ref="A38:Q38"/>
+    <mergeCell ref="A35:Q35"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
@@ -13553,9 +11165,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId33"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -729,7 +729,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Резиденция Тверская</t>
@@ -810,7 +810,7 @@
       </c>
       <c r="S4" s="4" t="inlineStr">
         <is>
-          <t>апарт-отель; юрлицо Техноком Трейд</t>
+          <t>апарт-отель; юрлицо Техноком Трейд; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,11 @@
         </is>
       </c>
       <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr"/>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -970,7 +974,7 @@
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t>24 квартиры + 3 особняка + 9 таунхаусов; юрлицо Торгпродуктсервис; арх. Илья Уткин</t>
+          <t>24 квартиры + 3 особняка + 9 таунхаусов; юрлицо Торгпродуктсервис; арх. Илья Уткин; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1051,11 @@
         </is>
       </c>
       <c r="R7" s="11" t="inlineStr"/>
-      <c r="S7" s="10" t="inlineStr"/>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1122,7 +1130,11 @@
         </is>
       </c>
       <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -1197,9 +1209,13 @@
         </is>
       </c>
       <c r="R9" s="11" t="inlineStr"/>
-      <c r="S9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10" ht="15" customHeight="1">
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Sinatra (Синатра)</t>
@@ -1278,7 +1294,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>реконструкция; cian years 2018/2020</t>
+          <t>реконструкция; cian years 2018/2020; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -1355,9 +1371,13 @@
         </is>
       </c>
       <c r="R11" s="11" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12" ht="15" customHeight="1">
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Уланский, 13</t>
@@ -1438,11 +1458,11 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>реконструкция особняка 1886 г.; апартаменты</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
+          <t>реконструкция особняка 1886 г.; апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Современник</t>
@@ -1521,7 +1541,7 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>реновация здания XIX в.</t>
+          <t>реновация здания XIX в.; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -1604,9 +1624,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="S14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>SkyView</t>
@@ -1685,11 +1709,11 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>4 башни на месте Киноцентра</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
+          <t>4 башни на месте Киноцентра; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Полянка/44</t>
@@ -1768,7 +1792,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>7 корпусов сданы март 2019; cian: застройщик ТЕЛЕКОМ</t>
+          <t>7 корпусов сданы март 2019; cian: застройщик ТЕЛЕКОМ; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -1851,11 +1875,11 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>cian years 2021 (первая очередь)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+          <t>cian years 2021 (первая очередь); карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Bogenhouse (Богенхаус)</t>
@@ -1936,11 +1960,11 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>апартаменты; также ГК Дельта</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
+          <t>апартаменты; также ГК Дельта; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
@@ -2019,7 +2043,7 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2120,11 @@
         </is>
       </c>
       <c r="R20" s="5" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -2177,9 +2205,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Клубный дом ЦВЕТ32</t>
@@ -2260,11 +2292,11 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>введён 28.08.2019; апартаменты</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+          <t>введён 28.08.2019; апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
           <t>A.Residence (А Резиденс)</t>
@@ -2345,11 +2377,11 @@
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>арх. Цимайло Ляшенко и Партнеры</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+          <t>арх. Цимайло Ляшенко и Партнеры; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Edison House (Эдисон Хаус)</t>
@@ -2428,7 +2460,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>cian years 2018; источники: 3 кв. 2019</t>
+          <t>cian years 2018; источники: 3 кв. 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2537,11 @@
         </is>
       </c>
       <c r="R25" s="11" t="inlineStr"/>
-      <c r="S25" s="10" t="inlineStr"/>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -2586,9 +2622,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="S26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Дом NV/9</t>
@@ -2667,7 +2707,7 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>NV/9 ARTKVARTAL; юрлицо Стрелецкая Слобода</t>
+          <t>NV/9 ARTKVARTAL; юрлицо Стрелецкая Слобода; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -2752,11 +2792,11 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>21 квартира + 4 резиденции + 3 пентхауса; арх. Цимайло Ляшенко</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
+          <t>21 квартира + 4 резиденции + 3 пентхауса; арх. Цимайло Ляшенко; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Клубный дом Космо 4/22</t>
@@ -2837,11 +2877,11 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Софийский</t>
@@ -2920,11 +2960,11 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>апартаменты; введён январь 2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
+          <t>апартаменты; введён январь 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Дом на Тишинке</t>
@@ -3003,11 +3043,11 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>арх. Павел Андреев</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+          <t>арх. Павел Андреев; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Резиденция 1864</t>
@@ -3088,11 +3128,11 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>апартаменты; бывший Царев сад</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
+          <t>апартаменты; бывший Царев сад; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Тессинский, 1</t>
@@ -3171,7 +3211,7 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>ввод август 2023</t>
+          <t>ввод август 2023; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -3248,9 +3288,13 @@
         </is>
       </c>
       <c r="R34" s="5" t="inlineStr"/>
-      <c r="S34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Artisan (Артисан)</t>
@@ -3329,11 +3373,11 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>также указывается Era One Holding</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
+          <t>также указывается Era One Holding; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Абрикосов</t>
@@ -3414,11 +3458,11 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>реставрация усадьбы Абрикосовых</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
+          <t>реставрация усадьбы Абрикосовых; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Клубный дом CULT (Клубный дом Культ)</t>
@@ -3497,11 +3541,11 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>реконструкция гостиницы Варшава; арх. SPEECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
+          <t>реконструкция гостиницы Варшава; арх. SPEECH; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
@@ -3582,11 +3626,11 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>арх. Цимайло Ляшенко и Партнеры</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
+          <t>арх. Цимайло Ляшенко и Партнеры; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Рахманинов</t>
@@ -3667,11 +3711,11 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>реконструкция; также АгроСервисСтрой</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
+          <t>реконструкция; также АгроСервисСтрой; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Пироговская 14</t>
@@ -3752,7 +3796,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>апартаменты; генподрядчик STRABAG</t>
+          <t>апартаменты; генподрядчик STRABAG; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3879,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr"/>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -3916,11 +3964,11 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>4 секции</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
+          <t>4 секции; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Садовые кварталы</t>
@@ -3995,11 +4043,11 @@
       <c r="R43" s="11" t="inlineStr"/>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>очереди 2012–2023; в выборку попали корпуса 2018+</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
+          <t>очереди 2012–2023; в выборку попали корпуса 2018+; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Малая Ордынка 19</t>
@@ -4080,11 +4128,11 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>завершён сентябрь 2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
+          <t>завершён сентябрь 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
           <t>Дом в Газетном</t>
@@ -4163,7 +4211,7 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>реконструкция</t>
+          <t>реконструкция; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4294,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="S46" s="4" t="inlineStr"/>
+      <c r="S46" s="4" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
@@ -4321,9 +4373,13 @@
         </is>
       </c>
       <c r="R47" s="11" t="inlineStr"/>
-      <c r="S47" s="10" t="inlineStr"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Золотой, жилой квартал</t>
@@ -4404,11 +4460,11 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>126 квартир + 19 двухуровневых; арх. SPEECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1">
+          <t>126 квартир + 19 двухуровневых; арх. SPEECH; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
           <t>Саввинская 17</t>
@@ -4489,7 +4545,7 @@
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>потолки 6.4-7 м; арх. AI Studio</t>
+          <t>потолки 6.4-7 м; арх. AI Studio; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -4574,11 +4630,11 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>сдан в 2026, продажи от застройщика; реконструкция дома 1915 г.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
+          <t>сдан в 2026, продажи от застройщика; реконструкция дома 1915 г.; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
           <t>Magnum (Магнум)</t>
@@ -4657,11 +4713,11 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>арх. бюро VOSTOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
+          <t>арх. бюро VOSTOK; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Дом Бакст на Патриарших</t>
@@ -4740,11 +4796,11 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>также указывается АСН-Инвест; арх. Павел Андреев</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
+          <t>также указывается АСН-Инвест; арх. Павел Андреев; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Клубный дом TURGENEV (Тургенев)</t>
@@ -4825,11 +4881,11 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>5 секций; арх. Squire &amp; Partners</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
+          <t>5 секций; арх. Squire &amp; Partners; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Villa Grace (Вилла Грейс)</t>
@@ -4910,7 +4966,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>ввод 3 кв. 2020; часть источников 4 кв. 2022</t>
+          <t>ввод 3 кв. 2020; часть источников 4 кв. 2022; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -4987,7 +5043,11 @@
         </is>
       </c>
       <c r="R55" s="11" t="inlineStr"/>
-      <c r="S55" s="10" t="inlineStr"/>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
@@ -5068,7 +5128,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="S56" s="4" t="inlineStr"/>
+      <c r="S56" s="4" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
@@ -5143,9 +5207,13 @@
         </is>
       </c>
       <c r="R57" s="11" t="inlineStr"/>
-      <c r="S57" s="10" t="inlineStr"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Саввинская 27</t>
@@ -5226,7 +5294,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -5303,9 +5371,13 @@
         </is>
       </c>
       <c r="R59" s="11" t="inlineStr"/>
-      <c r="S59" s="10" t="inlineStr"/>
-    </row>
-    <row r="60" ht="15" customHeight="1">
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Хамовники 12</t>
@@ -5386,7 +5458,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>арх. Евгений Герасимов</t>
+          <t>арх. Евгений Герасимов; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5535,11 @@
         </is>
       </c>
       <c r="R61" s="11" t="inlineStr"/>
-      <c r="S61" s="10" t="inlineStr"/>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -5538,7 +5614,11 @@
         </is>
       </c>
       <c r="R62" s="5" t="inlineStr"/>
-      <c r="S62" s="4" t="inlineStr"/>
+      <c r="S62" s="4" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
@@ -5613,7 +5693,11 @@
         </is>
       </c>
       <c r="R63" s="11" t="inlineStr"/>
-      <c r="S63" s="10" t="inlineStr"/>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -5688,7 +5772,11 @@
         </is>
       </c>
       <c r="R64" s="5" t="inlineStr"/>
-      <c r="S64" s="4" t="inlineStr"/>
+      <c r="S64" s="4" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
@@ -5769,11 +5857,11 @@
       </c>
       <c r="S65" s="10" t="inlineStr">
         <is>
-          <t>введён июль 2024; арх. John McAslan + Partners</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1">
+          <t>введён июль 2024; арх. John McAslan + Partners; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Малая Бронная 15</t>
@@ -5854,7 +5942,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>акт ввода 31.07.2019</t>
+          <t>акт ввода 31.07.2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -5931,7 +6019,11 @@
         </is>
       </c>
       <c r="R67" s="11" t="inlineStr"/>
-      <c r="S67" s="10" t="inlineStr"/>
+      <c r="S67" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="18" t="inlineStr">
@@ -6664,7 +6756,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Тессинский V</t>
@@ -6733,7 +6825,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>старт продаж апрель 2026, котлован</t>
+          <t>старт продаж апрель 2026, котлован; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -6960,7 +7052,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> Клубный дом «Резиденции Воронцова»</t>
@@ -7029,7 +7121,7 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>ранее Sun Development; арх. Blank Architects</t>
+          <t>ранее Sun Development; арх. Blank Architects; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7425,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Казачий</t>
@@ -7402,7 +7494,7 @@
       </c>
       <c r="Q19" s="10" t="inlineStr">
         <is>
-          <t>76 квартир + 4 пентхауса; арх. WALL</t>
+          <t>76 квартир + 4 пентхауса; арх. WALL; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7715,11 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr"/>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -7692,9 +7788,13 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="Q23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>ТИТУЛ Империал</t>
@@ -7763,7 +7863,7 @@
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>12 лотов 83-131 м², не более 3 квартир на этаже</t>
+          <t>12 лотов 83-131 м², не более 3 квартир на этаже; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -7836,11 +7936,11 @@
       </c>
       <c r="Q25" s="10" t="inlineStr">
         <is>
-          <t>Софийская наб., усадьба Кокорева; в июне 2026 fee-девелопер Hutton вышел из проекта, площадка у V2 Group (Коммерсантъ); инвестор V2Group; юрлицо СЗ Суплекс Технолоджис; cian: 2028</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+          <t>Софийская наб., усадьба Кокорева; в июне 2026 fee-девелопер Hutton вышел из проекта, площадка у V2 Group (Коммерсантъ); инвестор V2Group; юрлицо СЗ Суплекс Технолоджис; cian: 2028; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Дом Спорта</t>
@@ -7909,7 +8009,7 @@
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>старт продаж 2026, стройка начата (Ведомости)</t>
+          <t>старт продаж 2026, стройка начата (Ведомости); карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -8363,7 +8463,7 @@
       </c>
       <c r="Q32" s="4" t="inlineStr"/>
     </row>
-    <row r="33" ht="15" customHeight="1">
+    <row r="33" ht="24" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Kuznetsky Most 12 by Lalique (Кузнецкий Мост 12)</t>
@@ -8432,11 +8532,11 @@
       </c>
       <c r="Q33" s="10" t="inlineStr">
         <is>
-          <t>реконструкция; коллаборация с Lalique</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
+          <t>реконструкция; коллаборация с Lalique; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>ДОМ XXII</t>
@@ -8505,7 +8605,7 @@
       </c>
       <c r="Q34" s="4" t="inlineStr">
         <is>
-          <t>арх. Сергей Киселев и Партнеры</t>
+          <t>арх. Сергей Киселев и Партнеры; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9132,7 @@
       </c>
       <c r="Q41" s="10" t="inlineStr">
         <is>
-          <t>Le Dôme; СЗ Соймоновский 3; арх. Paris Classical Architecture</t>
+          <t>Le Dôme; СЗ Соймоновский 3; арх. Paris Classical Architecture; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -734,12 +734,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Kovaks (Ковакс)</t>
+          <t>Техноком Трейд</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>2018–2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -807,11 +807,11 @@
       </c>
       <c r="S4" s="4" t="inlineStr">
         <is>
-          <t>апарт-отель; юрлицо Техноком Трейд; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
+          <t>апарт-отель; юрлицо Техноком Трейд</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Пресня Сити</t>
@@ -819,7 +819,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>MR Group</t>
+          <t>MR</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -884,11 +884,7 @@
         </is>
       </c>
       <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
+      <c r="S5" s="10" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="inlineStr">

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -12,9 +12,9 @@
     <sheet name="3. Проектирование" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Построено (вторичка)'!$A$3:$S$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Построено (вторичка)'!$A$3:$S$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'1. Построено (вторичка)'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1. Построено (вторичка)'!$A$1:$S$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1. Построено (вторичка)'!$A$1:$S$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Строится'!$A$3:$Q$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'2. Строится'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'2. Строится'!$A$1:$Q$47</definedName>
@@ -95,12 +95,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -187,6 +187,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -194,9 +197,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -211,7 +211,7 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S68"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P4" s="7" t="n">
@@ -811,25 +811,25 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Пресня Сити</t>
+          <t>NEVA TOWERS (Нева Тауэрс)</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>MR</t>
+          <t>СТ Тауэрс</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>4 кв. 2020</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Москва, Ходынская, 2</t>
+          <t>Москва, 1-й Красногвардейский, 22с2</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -837,48 +837,48 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Пресня</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>1</v>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Сити</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>63-79</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>647159</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>777778</v>
-      </c>
-      <c r="L5" s="12" t="n">
-        <v>1426966</v>
-      </c>
-      <c r="M5" s="12" t="n">
-        <v>29</v>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>615385</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>880626</v>
+      </c>
+      <c r="L5" s="13" t="n">
+        <v>2171244</v>
+      </c>
+      <c r="M5" s="13" t="n">
+        <v>123</v>
       </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>42–158</t>
+          <t>39–764</t>
         </is>
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P5" s="11" t="n"/>
-      <c r="Q5" s="14" t="inlineStr">
+      <c r="Q5" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -886,75 +886,73 @@
       <c r="R5" s="11" t="inlineStr"/>
       <c r="S5" s="10" t="inlineStr"/>
     </row>
-    <row r="6" ht="24" customHeight="1">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Меценат</t>
+          <t>Sinatra (Синатра)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Москапстрой-ТН</t>
+          <t>Glincom</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Москва, 2-й Кадашевский, 5с2</t>
+          <t>Москва, Большой Тишинский, 38</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Пресня</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>848033</v>
+        <v>839130</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>848033</v>
+        <v>1052456</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>2988731</v>
+        <v>1388889</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>3</v>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t>204–589</t>
+          <t>46–180</t>
         </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="n">
-        <v>36</v>
-      </c>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -967,47 +965,47 @@
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t>24 квартиры + 3 особняка + 9 таунхаусов; юрлицо Торгпродуктсервис; арх. Илья Уткин; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>реконструкция; cian years 2018/2020</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>NEVA TOWERS (Нева Тауэрс)</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Renaissance Development</t>
+          <t>LUMIN (ЛЮМИН)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>HUTTON</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>2018–2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Москва, 1-й Красногвардейский, 22с2</t>
+          <t>Москва, Славянская, 2/5с1</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Таганский</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>2</v>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>63-79</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
@@ -1015,68 +1013,64 @@
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J7" s="12" t="n">
-        <v>615385</v>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>880626</v>
-      </c>
-      <c r="L7" s="12" t="n">
-        <v>2171244</v>
-      </c>
-      <c r="M7" s="12" t="n">
-        <v>123</v>
+      <c r="J7" s="13" t="n">
+        <v>900901</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>1070076</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>2658908</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>7</v>
       </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>39–764</t>
+          <t>52–213</t>
         </is>
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P7" s="11" t="n"/>
-      <c r="Q7" s="14" t="inlineStr">
+      <c r="Q7" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="R7" s="11" t="inlineStr"/>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+      <c r="S7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>The Book (Бук)</t>
+          <t>Уланский, 13</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>РП Проект</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>2020–2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Москва, Новый Арбат, 15</t>
+          <t>Москва, Уланский, 13С1</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Арбат</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
+          <t>Красносельский</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -1086,7 +1080,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1095,77 +1089,83 @@
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>859729</v>
+        <v>1100000</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>900000</v>
+        <v>1100000</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>953125</v>
+        <v>1100000</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>27–65</t>
+          <t>123–179</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="n"/>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>10</v>
+      </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R8" s="5" t="inlineStr"/>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>реконструкция особняка 1886 г.; апартаменты</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Sinatra (Синатра)</t>
+          <t>Современник</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Glincom</t>
+          <t>VESPER</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>2018–2020</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Москва, Большой Тишинский, 38</t>
+          <t>Москва, Машкова, 13С1</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Пресня</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="n">
+          <t>Басманный</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -1173,268 +1173,268 @@
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J9" s="12" t="n">
-        <v>839130</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>1052456</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>1388889</v>
-      </c>
-      <c r="M9" s="12" t="n">
-        <v>3</v>
+      <c r="J9" s="13" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>1111959</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>1123919</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>46–180</t>
+          <t>34–34</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P9" s="11" t="n"/>
-      <c r="Q9" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R9" s="14" t="inlineStr">
+      <c r="Q9" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R9" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>реконструкция; cian years 2018/2020; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>реновация здания XIX в.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>LUMIN (ЛЮМИН)</t>
+          <t>City Park (Сити Парк)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Hutton</t>
+          <t>МонАрх</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Москва, Славянская, 2/5с1</t>
+          <t>Москва, Мантулинская, 9к4</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Таганский</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Сити</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6-24</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>788028</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>1183147</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>2129032</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>34–251</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>1213</v>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>SkyView</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>СЗ Киноцентр</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>3 кв. 2024</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Дружинниковская, 15А</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>20-25</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J10" s="7" t="n">
-        <v>900901</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>1070076</v>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>2658908</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="N10" s="5" t="inlineStr">
-        <is>
-          <t>52–213</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R10" s="5" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Уланский, 13</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>РП Проект</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Уланский, 13С1</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Красносельский</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>2</v>
+      <c r="J11" s="13" t="n">
+        <v>850000</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>2756939</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>74</v>
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>123–179</t>
+          <t>47–847</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P11" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R11" s="14" t="inlineStr">
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P11" s="11" t="n"/>
+      <c r="Q11" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R11" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>реконструкция особняка 1886 г.; апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>4 башни на месте Киноцентра</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Современник</t>
+          <t>Полянка/44</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Vesper</t>
+          <t>Группа ПСН</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Москва, Машкова, 13С1</t>
+          <t>Москва, Большая Полянка, 44</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Басманный</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1100000</v>
+        <v>1135408</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>1111959</v>
+        <v>1214499</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>1123919</v>
+        <v>2109833</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>34–34</t>
+          <t>117–271</t>
         </is>
       </c>
       <c r="O12" s="5" t="inlineStr">
@@ -1455,298 +1455,294 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>реновация здания XIX в.; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
+          <t>7 корпусов сданы март 2019; cian: застройщик ТЕЛЕКОМ; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>City Park (Сити Парк)</t>
+          <t>Титул на Серебрянической</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>ГК МонАрх</t>
+          <t>Центр-Инвест</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>2019–2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Москва, Мантулинская, 9к4</t>
+          <t>Москва, Серебрянический, 8</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Таганский</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="n">
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>1229434</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>1439394</v>
+      </c>
+      <c r="M13" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>6-24</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>788028</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>1183147</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>2129032</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>58</v>
-      </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>34–251</t>
+          <t>62–276</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>бизнес</t>
-        </is>
-      </c>
-      <c r="P13" s="12" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q13" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R13" s="14" t="inlineStr">
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="n"/>
+      <c r="Q13" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R13" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>cian years 2021 (первая очередь); карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SkyView</t>
+          <t>Bogenhouse (Богенхаус)</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>СЗ Киноцентр</t>
+          <t>Lexion Development</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>2023–2025</t>
+          <t>2020–2021</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Москва, Дружинниковская, 15А</t>
+          <t>Москва, Озерковская, 6</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>Замоскворечье</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>985887</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>1247727</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>43–355</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>апартаменты; также ГК Дельта; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Capital Towers (Капитал Тауэрс)</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>2022–2023</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Краснопресненская, 14Ак3</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Пресня</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>20-25</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>850000</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>2756939</v>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>47–847</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Сити</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>51-72</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>428266</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>1267615</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>28–693</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>премиум</t>
         </is>
       </c>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S14" s="4" t="inlineStr">
-        <is>
-          <t>4 башни на месте Киноцентра; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Полянка/44</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Группа ПСН</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Большая Полянка, 44</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>6-7</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>1135408</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>1214499</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>2109833</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>117–271</t>
-        </is>
-      </c>
-      <c r="O15" s="11" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
       <c r="P15" s="11" t="n"/>
-      <c r="Q15" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R15" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
+      <c r="Q15" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>7 корпусов сданы март 2019; cian: застройщик ТЕЛЕКОМ; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Титул на Серебрянической</t>
+          <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Центр-Инвест</t>
+          <t>Интеко</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Москва, Серебрянический, 8</t>
+          <t>Москва, Садовническая, 7</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Таганский</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="inlineStr">
+          <t>Замоскворечье</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1755,20 +1751,20 @@
         </is>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1200000</v>
+        <v>1094488</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>1229434</v>
+        <v>1268025</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>1439394</v>
+        <v>1927419</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>62–276</t>
+          <t>124–400</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -1789,286 +1785,294 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>cian years 2021 (первая очередь); карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
+          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Bogenhouse (Богенхаус)</t>
+          <t>Титул на Якиманке</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Lexion Development</t>
+          <t>Центр-Инвест</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>2020–2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Москва, Озерковская, 6</t>
+          <t>Москва, 2-й Хвостов, 8</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>1281646</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>1281646</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>1281646</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>63–63</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P17" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q17" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R17" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом ЦВЕТ32</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Hutton</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Цветной, 32А</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Мещанский</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J17" s="12" t="n">
-        <v>985887</v>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>1247727</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="N17" s="11" t="inlineStr">
-        <is>
-          <t>43–355</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="J18" s="7" t="n">
+        <v>1120690</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>1363636</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>1972477</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>37–218</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>премиум</t>
         </is>
       </c>
-      <c r="P17" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q17" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R17" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>апартаменты; также ГК Дельта; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Capital Towers (Капитал Тауэрс)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Capital Group</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>2022–2023</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Краснопресненская, 14Ак3</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>51-72</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>428266</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>1267615</v>
-      </c>
-      <c r="L18" s="7" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="M18" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>28–693</t>
-        </is>
-      </c>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="n"/>
+      <c r="P18" s="7" t="n">
+        <v>47</v>
+      </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R18" s="5" t="inlineStr"/>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>введён 28.08.2019; апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Интеко</t>
+          <t>A.Residence (А Резиденс)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>O1 Properties (СЗ А-Резиденс)</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
+          <t>2024–2025</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Садовническая, 82</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Замоскворечье</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>664234</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>1365000</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>2894000</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>47–210</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P19" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R19" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>арх. Цимайло Ляшенко и Партнеры; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Edison House (Эдисон Хаус)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>ИК Приоритет</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Садовническая, 7</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Замоскворечье</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>5-6</t>
-        </is>
-      </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>1094488</v>
-      </c>
-      <c r="K19" s="13" t="n">
-        <v>1268025</v>
-      </c>
-      <c r="L19" s="12" t="n">
-        <v>1927419</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>124–400</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R19" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Титул на Якиманке</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Центр-Инвест</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Москва, 2-й Хвостов, 8</t>
+          <t>Москва, Электрический, 10</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Пресня</t>
         </is>
       </c>
       <c r="G20" s="7" t="n">
@@ -2076,29 +2080,29 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1281646</v>
+        <v>1369863</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>1281646</v>
+        <v>1369863</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>1281646</v>
+        <v>1369863</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>63–63</t>
+          <t>58–58</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2106,9 +2110,7 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P20" s="7" t="n">
-        <v>18</v>
-      </c>
+      <c r="P20" s="5" t="n"/>
       <c r="Q20" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -2121,163 +2123,157 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
+          <t>cian years 2018; источники: 3 кв. 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Roza Rossa (Роза Росса)</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>KR Properties</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>2020–2023</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Зубовская, 7</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>1408163</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>49–316</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="n"/>
+      <c r="Q21" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R21" s="11" t="inlineStr"/>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
           <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Клубный дом ЦВЕТ32</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Hutton</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Цветной, 32А</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Мещанский</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Собрание клубных домов ORDYNKA (Ордынка)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>INSIGMA</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Большой Ордынский, 4С4</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Замоскворечье</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G22" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>1465909</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>1465909</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>1465909</v>
+      </c>
+      <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>1120690</v>
-      </c>
-      <c r="K21" s="13" t="n">
-        <v>1363636</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>1972477</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>37–218</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>88–88</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>премиум</t>
         </is>
       </c>
-      <c r="P21" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q21" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R21" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>введён 28.08.2019; апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A.Residence (А Резиденс)</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>O1 Properties (СЗ А-Резиденс)</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>2024–2025</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Садовническая, 82</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Замоскворечье</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>5-9</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>664234</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>1365000</v>
-      </c>
-      <c r="L22" s="7" t="n">
-        <v>2894000</v>
-      </c>
-      <c r="M22" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>47–210</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
       <c r="P22" s="7" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
@@ -2291,122 +2287,122 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>арх. Цимайло Ляшенко и Партнеры; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Edison House (Эдисон Хаус)</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>ИК Приоритет</t>
+          <t>Дом NV/9</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>INSIGMA / State Development</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Москва, Электрический, 10</t>
+          <t>Москва, Большой Николоворобинский, 9к1</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
+          <t>Таганский</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>1454693</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>1467116</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>1504854</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>61–118</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P23" s="11" t="n"/>
+      <c r="Q23" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R23" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>NV/9 ARTKVARTAL; юрлицо Стрелецкая Слобода; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Fantastic House (Фантастик Хаус)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>СЗ Полинессо</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Большой Тишинский, 30</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Пресня</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>1369863</v>
-      </c>
-      <c r="K23" s="13" t="n">
-        <v>1369863</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>1369863</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="11" t="inlineStr">
-        <is>
-          <t>58–58</t>
-        </is>
-      </c>
-      <c r="O23" s="11" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P23" s="11" t="n"/>
-      <c r="Q23" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R23" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>cian years 2018; источники: 3 кв. 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Roza Rossa (Роза Росса)</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>KR Properties</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>2020–2023</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Зубовская, 7</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
         </is>
       </c>
       <c r="G24" s="7" t="n">
@@ -2414,193 +2410,199 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>1117647</v>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>1496549</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>1544484</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>140–240</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q24" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>21 квартира + 4 резиденции + 3 пентхауса; арх. Цимайло Ляшенко; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом Космо 4/22</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Галс-Девелопмент</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Космодамианская, 4/22</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Замоскворечье</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>1010101</v>
-      </c>
-      <c r="K24" s="8" t="n">
-        <v>1380000</v>
-      </c>
-      <c r="L24" s="7" t="n">
-        <v>1408163</v>
-      </c>
-      <c r="M24" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>49–316</t>
-        </is>
-      </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>1326531</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>1531532</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>5300745</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>47–174</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="inlineStr">
         <is>
           <t>премиум</t>
         </is>
       </c>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R24" s="5" t="inlineStr"/>
-      <c r="S24" s="4" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Собрание клубных домов ORDYNKA (Ордынка)</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>INSIGMA</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Большой Ордынский, 4С4</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Замоскворечье</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>1465909</v>
-      </c>
-      <c r="K25" s="13" t="n">
-        <v>1465909</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>1465909</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="11" t="inlineStr">
-        <is>
-          <t>88–88</t>
-        </is>
-      </c>
-      <c r="O25" s="11" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P25" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q25" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R25" s="14" t="inlineStr">
+      <c r="P25" s="13" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q25" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R25" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Дом NV/9</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>INSIGMA / State Development</t>
+          <t>Софийский</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Трансстройинвест</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018–2019</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Москва, Большой Николоворобинский, 9к1</t>
+          <t>Москва, Софийская, 34</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Таганский</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1454693</v>
+        <v>1333333</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>1467116</v>
+        <v>1549419</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>1504854</v>
+        <v>2066667</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>61–118</t>
+          <t>53–155</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -2621,29 +2623,29 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>NV/9 ARTKVARTAL; юрлицо Стрелецкая Слобода; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>апартаменты; введён январь 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Fantastic House (Фантастик Хаус)</t>
+          <t>Дом на Тишинке</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>СЗ Полинессо</t>
+          <t>Донстрой</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Москва, Большой Тишинский, 30</t>
+          <t>Москва, Средний Тишинский, 5</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -2656,12 +2658,12 @@
           <t>Пресня</t>
         </is>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="G27" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>7-20</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
@@ -2669,21 +2671,21 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J27" s="12" t="n">
-        <v>1117647</v>
-      </c>
-      <c r="K27" s="13" t="n">
-        <v>1496549</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>1544484</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>4</v>
+      <c r="J27" s="13" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="K27" s="14" t="n">
+        <v>1614969</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>2147239</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>140–240</t>
+          <t>84–243</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
@@ -2691,84 +2693,82 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P27" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q27" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R27" s="14" t="inlineStr">
+      <c r="P27" s="11" t="n"/>
+      <c r="Q27" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R27" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>21 квартира + 4 резиденции + 3 пентхауса; арх. Цимайло Ляшенко; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>арх. Павел Андреев; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом Космо 4/22</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Галс-Девелопмент</t>
+          <t>Резиденция 1864</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Сбербанк Капитал / Midland Development</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Москва, Космодамианская, 4/22</t>
+          <t>Москва, Софийская, 36</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="inlineStr">
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G28" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1326531</v>
+        <v>1510567</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>1531532</v>
+        <v>1617861</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>5300745</v>
+        <v>3213511</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>47–174</t>
+          <t>289–1062</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="P28" s="7" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
@@ -2791,69 +2791,69 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>апартаменты; бывший Царев сад; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Софийский</t>
+          <t>Тессинский, 1</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Трансстройинвест</t>
+          <t>INSIGMA</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>2018–2019</t>
+          <t>2020–2023</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 34</t>
+          <t>Москва, Тессинский, 1</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
+          <t>Таганский</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G29" s="12" t="n">
-        <v>2</v>
+      <c r="G29" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4-9</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>1333333</v>
-      </c>
-      <c r="K29" s="13" t="n">
-        <v>1549419</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>2066667</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>12</v>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>1106420</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>1657000</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>15</v>
       </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>53–155</t>
+          <t>57–458</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
@@ -2862,41 +2862,41 @@
         </is>
       </c>
       <c r="P29" s="11" t="n"/>
-      <c r="Q29" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R29" s="14" t="inlineStr">
+      <c r="Q29" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R29" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>апартаменты; введён январь 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
+          <t>ввод август 2023; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Дом на Тишинке</t>
+          <t>Lucky (Лаки)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Донстрой</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022–2023</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Москва, Средний Тишинский, 5</t>
+          <t>Москва, Костикова, 4к1</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="G30" s="7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>7-20</t>
+          <t>15-21</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2923,20 +2923,20 @@
         </is>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1500000</v>
+        <v>1296875</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>1614969</v>
+        <v>1680791</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>2147239</v>
+        <v>2352941</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>84–243</t>
+          <t>44–434</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
@@ -2950,76 +2950,72 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R30" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
+      <c r="R30" s="5" t="inlineStr"/>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>арх. Павел Андреев; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Резиденция 1864</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Сбербанк Капитал / Midland Development</t>
+          <t>Artisan (Артисан)</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Valartis Group</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 36</t>
+          <t>Москва, Арбат, 39</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
+          <t>Арбат</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="G31" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>1510567</v>
-      </c>
-      <c r="K31" s="13" t="n">
-        <v>1617861</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>3213511</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>7</v>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>1769663</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>1769663</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>1769663</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>289–1062</t>
+          <t>178–178</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
@@ -3027,52 +3023,50 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P31" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q31" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R31" s="14" t="inlineStr">
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R31" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>апартаменты; бывший Царев сад; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>также указывается Era One Holding; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Тессинский, 1</t>
+          <t>Абрикосов</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>INSIGMA</t>
+          <t>MR Group</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>2020–2023</t>
+          <t>2022–2023</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Москва, Тессинский, 1</t>
+          <t>Москва, Потаповский, 6С1</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Таганский</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
+          <t>Басманный</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -3082,7 +3076,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>4-9</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -3091,20 +3085,20 @@
         </is>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1106420</v>
+        <v>1558355</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>1657000</v>
+        <v>1785730</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>1800000</v>
+        <v>2094241</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>57–458</t>
+          <t>67–191</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
@@ -3112,7 +3106,9 @@
           <t>премиум</t>
         </is>
       </c>
-      <c r="P32" s="5" t="n"/>
+      <c r="P32" s="7" t="n">
+        <v>27</v>
+      </c>
       <c r="Q32" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -3125,69 +3121,69 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>ввод август 2023; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
+          <t>реставрация усадьбы Абрикосовых; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Lucky (Лаки)</t>
+          <t>Клубный дом CULT (Клубный дом Культ)</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Vesper</t>
+          <t>Gravion</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2025–2026</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Москва, Костикова, 4к1</t>
+          <t>Москва, Ленинский, 2</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>Пресня</t>
-        </is>
-      </c>
-      <c r="G33" s="12" t="n">
-        <v>9</v>
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>15-21</t>
+          <t>9-16</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>1296875</v>
-      </c>
-      <c r="K33" s="13" t="n">
-        <v>1680791</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>2352941</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>28</v>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>1799500</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>3035672</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>54</v>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>44–434</t>
+          <t>26–336</t>
         </is>
       </c>
       <c r="O33" s="11" t="inlineStr">
@@ -3196,55 +3192,59 @@
         </is>
       </c>
       <c r="P33" s="11" t="n"/>
-      <c r="Q33" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R33" s="11" t="inlineStr"/>
+      <c r="Q33" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R33" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>реконструкция гостиницы Варшава; арх. SPEECH; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Artisan (Артисан)</t>
+          <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Valartis Group</t>
+          <t>Гардтекс</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Москва, Арбат, 39</t>
+          <t>Москва, Саввинская, 13</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Арбат</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G34" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3253,28 +3253,30 @@
         </is>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1769663</v>
+        <v>1869231</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>1769663</v>
+        <v>1884615</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>1769663</v>
+        <v>3751412</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>178–178</t>
+          <t>125–177</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="n"/>
+          <t>делюкс</t>
+        </is>
+      </c>
+      <c r="P34" s="7" t="n">
+        <v>169</v>
+      </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -3287,47 +3289,47 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>также указывается Era One Holding; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>арх. Цимайло Ляшенко и Партнеры; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Абрикосов</t>
+          <t>Рахманинов</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>MR Group</t>
+          <t>КМ Девелопмент</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Москва, Потаповский, 6С1</t>
+          <t>Москва, Малый Кисловский, 3</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Басманный</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr">
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G35" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -3335,76 +3337,76 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J35" s="12" t="n">
-        <v>1558355</v>
-      </c>
-      <c r="K35" s="13" t="n">
-        <v>1785730</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>2094241</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>6</v>
+      <c r="J35" s="13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>67–191</t>
+          <t>145–145</t>
         </is>
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P35" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q35" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R35" s="14" t="inlineStr">
+          <t>делюкс</t>
+        </is>
+      </c>
+      <c r="P35" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q35" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R35" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>реставрация усадьбы Абрикосовых; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>реконструкция; также АгроСервисСтрой; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом CULT (Клубный дом Культ)</t>
+          <t>Пироговская 14</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Gravion</t>
+          <t>Elbert Development</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>2025–2026</t>
+          <t>2021–2023</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Москва, Ленинский, 2</t>
+          <t>Москва, Малая Пироговская, 12</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G36" s="7" t="n">
@@ -3412,7 +3414,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>9-16</t>
+          <t>8-9</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -3421,28 +3423,30 @@
         </is>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1000000</v>
+        <v>1397059</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>1799500</v>
+        <v>2033898</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>3035672</v>
+        <v>2774566</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t>26–336</t>
+          <t>66–254</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P36" s="5" t="n"/>
+          <t>делюкс</t>
+        </is>
+      </c>
+      <c r="P36" s="7" t="n">
+        <v>53</v>
+      </c>
       <c r="Q36" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -3455,69 +3459,69 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>реконструкция гостиницы Варшава; арх. SPEECH; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
+          <t>апартаменты; генподрядчик STRABAG; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
+          <t>Cloud Nine (Клауд Найн)</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Гардтекс</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2021–2022</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 13</t>
+          <t>Москва, Большая Полянка, 9С2</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="n">
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="n">
         <v>4</v>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>1869231</v>
-      </c>
-      <c r="K37" s="13" t="n">
-        <v>1884615</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>3751412</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>7</v>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>квартиры + апартаменты</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="n">
+        <v>1800766</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>2050124</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>2820513</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>125–177</t>
+          <t>195–261</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
@@ -3525,52 +3529,52 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P37" s="12" t="n">
-        <v>169</v>
-      </c>
-      <c r="Q37" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R37" s="14" t="inlineStr">
+      <c r="P37" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q37" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R37" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>арх. Цимайло Ляшенко и Партнеры; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1">
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Рахманинов</t>
+          <t>Симфония набережных (Котельническая 21)</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>КМ Девелопмент</t>
+          <t>СК-207</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018–2022</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Москва, Малый Кисловский, 3</t>
+          <t>Москва, Котельническая, 21</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
+          <t>Таганский</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -3580,29 +3584,29 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>квартиры + апартаменты</t>
         </is>
       </c>
       <c r="J38" s="7" t="n">
-        <v>2000000</v>
+        <v>1174497</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>2000000</v>
+        <v>2067669</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>2000000</v>
+        <v>2070783</v>
       </c>
       <c r="M38" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>145–145</t>
+          <t>149–266</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -3610,9 +3614,7 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P38" s="7" t="n">
-        <v>33</v>
-      </c>
+      <c r="P38" s="5" t="n"/>
       <c r="Q38" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -3625,29 +3627,29 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>реконструкция; также АгроСервисСтрой; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>4 секции; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Пироговская 14</t>
+          <t>Садовые кварталы</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Elbert Development</t>
+          <t>Интеко</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>2021–2023</t>
+          <t>2018–2023</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Москва, Малая Пироговская, 12</t>
+          <t>Москва, Усачева, 15А</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -3660,589 +3662,585 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G39" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>5-18</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="n">
+        <v>1328904</v>
+      </c>
+      <c r="K39" s="14" t="n">
+        <v>2111111</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>3718750</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="N39" s="11" t="inlineStr">
+        <is>
+          <t>54–342</t>
+        </is>
+      </c>
+      <c r="O39" s="11" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P39" s="11" t="n"/>
+      <c r="Q39" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R39" s="11" t="inlineStr"/>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>очереди 2012–2023; в выборку попали корпуса 2018+; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Малая Ордынка 19</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Малая Ордынка, 19</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Замоскворечье</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>8-9</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>квартиры + апартаменты</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>1848152</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <v>2246964</v>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>2246964</v>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>100–148</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>делюкс</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q40" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R40" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>завершён сентябрь 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Дом в Газетном</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Актив-Центр</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>2021–2022</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Газетный, 13с2</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J39" s="12" t="n">
-        <v>1397059</v>
-      </c>
-      <c r="K39" s="13" t="n">
-        <v>2033898</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>2774566</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N39" s="11" t="inlineStr">
-        <is>
-          <t>66–254</t>
-        </is>
-      </c>
-      <c r="O39" s="11" t="inlineStr">
+      <c r="J41" s="13" t="n">
+        <v>1856148</v>
+      </c>
+      <c r="K41" s="14" t="n">
+        <v>2290538</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>4859444</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="N41" s="11" t="inlineStr">
+        <is>
+          <t>65–664</t>
+        </is>
+      </c>
+      <c r="O41" s="11" t="inlineStr">
         <is>
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P39" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q39" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R39" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>апартаменты; генподрядчик STRABAG; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Cloud Nine (Клауд Найн)</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>2021–2022</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Большая Полянка, 9С2</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="P41" s="11" t="n"/>
+      <c r="Q41" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R41" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>реконструкция; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>ГК АфинаСтрой</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Звонарский, 3</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Мещанский</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G40" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>4-7</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>квартиры + апартаменты</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="n">
-        <v>1800766</v>
-      </c>
-      <c r="K40" s="8" t="n">
-        <v>2050124</v>
-      </c>
-      <c r="L40" s="7" t="n">
-        <v>2820513</v>
-      </c>
-      <c r="M40" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>195–261</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="G42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>2321429</v>
+      </c>
+      <c r="K42" s="8" t="n">
+        <v>2321429</v>
+      </c>
+      <c r="L42" s="7" t="n">
+        <v>2321429</v>
+      </c>
+      <c r="M42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>168–168</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P40" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q40" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R40" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S40" s="4" t="inlineStr">
+      <c r="P42" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q42" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R42" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S42" s="4" t="inlineStr">
         <is>
           <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>Симфония набережных (Котельническая 21)</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>СК-207</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>2018–2022</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Котельническая, 21</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>Таганский</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G41" s="12" t="n">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>White Khamovniki (Вайт Хамовники)</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Hutton</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Олсуфьевский, 9к1</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>8-9</t>
-        </is>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>квартиры + апартаменты</t>
-        </is>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>1174497</v>
-      </c>
-      <c r="K41" s="13" t="n">
-        <v>2067669</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>2070783</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N41" s="11" t="inlineStr">
-        <is>
-          <t>149–266</t>
-        </is>
-      </c>
-      <c r="O41" s="11" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>2387268</v>
+      </c>
+      <c r="K43" s="14" t="n">
+        <v>2387268</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>2657480</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N43" s="11" t="inlineStr">
+        <is>
+          <t>75–152</t>
+        </is>
+      </c>
+      <c r="O43" s="11" t="inlineStr">
         <is>
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P41" s="11" t="n"/>
-      <c r="Q41" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R41" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>4 секции; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Садовые кварталы</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Интеко</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>2018–2023</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Усачева, 15А</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>5-18</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="n">
-        <v>1328904</v>
-      </c>
-      <c r="K42" s="8" t="n">
-        <v>2111111</v>
-      </c>
-      <c r="L42" s="7" t="n">
-        <v>3718750</v>
-      </c>
-      <c r="M42" s="7" t="n">
-        <v>83</v>
-      </c>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>54–342</t>
-        </is>
-      </c>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P42" s="5" t="n"/>
-      <c r="Q42" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R42" s="5" t="inlineStr"/>
-      <c r="S42" s="4" t="inlineStr">
-        <is>
-          <t>очереди 2012–2023; в выборку попали корпуса 2018+; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>Малая Ордынка 19</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>Sminex</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Малая Ордынка, 19</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>Замоскворечье</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>квартиры + апартаменты</t>
-        </is>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>1848152</v>
-      </c>
-      <c r="K43" s="13" t="n">
-        <v>2246964</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>2246964</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N43" s="11" t="inlineStr">
-        <is>
-          <t>100–148</t>
-        </is>
-      </c>
-      <c r="O43" s="11" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P43" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q43" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R43" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
+      <c r="P43" s="11" t="n"/>
+      <c r="Q43" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R43" s="11" t="inlineStr"/>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>завершён сентябрь 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Дом в Газетном</t>
+          <t>Золотой, жилой квартал</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Актив-Центр</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>2021–2022</t>
+          <t>2021–2023</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Москва, Газетный, 13с2</t>
+          <t>Москва, Софийская, 18</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="inlineStr">
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G44" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>2-6</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>2083333</v>
+      </c>
+      <c r="K44" s="8" t="n">
+        <v>2448000</v>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>87–269</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>делюкс</t>
+        </is>
+      </c>
+      <c r="P44" s="7" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q44" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R44" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S44" s="4" t="inlineStr">
+        <is>
+          <t>126 квартир + 19 двухуровневых; арх. SPEECH; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Саввинская 17</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Level Group</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Саввинская, 17</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="n">
-        <v>1856148</v>
-      </c>
-      <c r="K44" s="8" t="n">
-        <v>2290538</v>
-      </c>
-      <c r="L44" s="7" t="n">
-        <v>4859444</v>
-      </c>
-      <c r="M44" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="N44" s="5" t="inlineStr">
-        <is>
-          <t>65–664</t>
-        </is>
-      </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>2337858</v>
+      </c>
+      <c r="K45" s="14" t="n">
+        <v>2453400</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>2588055</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N45" s="11" t="inlineStr">
+        <is>
+          <t>65–82</t>
+        </is>
+      </c>
+      <c r="O45" s="11" t="inlineStr">
         <is>
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P44" s="5" t="n"/>
-      <c r="Q44" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R44" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S44" s="4" t="inlineStr">
-        <is>
-          <t>реконструкция; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>ГК АфинаСтрой</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Звонарский, 3</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>Мещанский</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="P45" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q45" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R45" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>потолки 6.4-7 м; арх. AI Studio; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом Фон Дессин</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Потаповский, 5С4</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Басманный</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>2321429</v>
-      </c>
-      <c r="K45" s="13" t="n">
-        <v>2321429</v>
-      </c>
-      <c r="L45" s="12" t="n">
-        <v>2321429</v>
-      </c>
-      <c r="M45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" s="11" t="inlineStr">
-        <is>
-          <t>168–168</t>
-        </is>
-      </c>
-      <c r="O45" s="11" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P45" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q45" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R45" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>White Khamovniki (Вайт Хамовники)</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Hutton</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Олсуфьевский, 9к1</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
         </is>
       </c>
       <c r="G46" s="7" t="n">
@@ -4250,7 +4248,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -4259,20 +4257,20 @@
         </is>
       </c>
       <c r="J46" s="7" t="n">
-        <v>2387268</v>
+        <v>1419298</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>2387268</v>
+        <v>2460514</v>
       </c>
       <c r="L46" s="7" t="n">
-        <v>2657480</v>
+        <v>4191066</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>75–152</t>
+          <t>79–394</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
@@ -4280,78 +4278,84 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P46" s="5" t="n"/>
+      <c r="P46" s="7" t="n">
+        <v>36</v>
+      </c>
       <c r="Q46" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R46" s="5" t="inlineStr"/>
+      <c r="R46" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>сдан в 2026, продажи от застройщика; реконструкция дома 1915 г.; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>Золотой, жилой квартал</t>
+          <t>Magnum (Магнум)</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>Magnum Development</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>2021–2023</t>
+          <t>2020–2022</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 18</t>
+          <t>Москва, Усачева, 9</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="n">
-        <v>2</v>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J47" s="12" t="n">
-        <v>2083333</v>
-      </c>
-      <c r="K47" s="13" t="n">
-        <v>2448000</v>
-      </c>
-      <c r="L47" s="12" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="M47" s="12" t="n">
-        <v>13</v>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>1568381</v>
+      </c>
+      <c r="K47" s="14" t="n">
+        <v>2490110</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>2738095</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>87–269</t>
+          <t>84–215</t>
         </is>
       </c>
       <c r="O47" s="11" t="inlineStr">
@@ -4359,54 +4363,52 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P47" s="12" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q47" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R47" s="14" t="inlineStr">
+      <c r="P47" s="11" t="n"/>
+      <c r="Q47" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R47" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>126 квартир + 19 двухуровневых; арх. SPEECH; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>арх. бюро VOSTOK; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Саввинская 17</t>
+          <t>Дом Бакст на Патриарших</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Level Group</t>
+          <t>Инвестстройком</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 17</t>
+          <t>Москва, Большой Козихинский, 15</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G48" s="7" t="n">
@@ -4414,7 +4416,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -4423,20 +4425,20 @@
         </is>
       </c>
       <c r="J48" s="7" t="n">
-        <v>2337858</v>
+        <v>2488540</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>2453400</v>
+        <v>2500000</v>
       </c>
       <c r="L48" s="7" t="n">
-        <v>2588055</v>
+        <v>3333333</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N48" s="5" t="inlineStr">
         <is>
-          <t>65–82</t>
+          <t>152–498</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
@@ -4444,9 +4446,7 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P48" s="7" t="n">
-        <v>22</v>
-      </c>
+      <c r="P48" s="5" t="n"/>
       <c r="Q48" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -4459,47 +4459,47 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>потолки 6.4-7 м; арх. AI Studio; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>также указывается АСН-Инвест; арх. Павел Андреев; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Клубный дом Фон Дессин</t>
+          <t>Клубный дом TURGENEV (Тургенев)</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>НеоСтрой</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Москва, Потаповский, 5С4</t>
+          <t>Москва, Костянский, 13</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Басманный</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
+          <t>Красносельский</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="G49" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -4507,21 +4507,21 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J49" s="12" t="n">
-        <v>1419298</v>
-      </c>
-      <c r="K49" s="13" t="n">
-        <v>2460514</v>
-      </c>
-      <c r="L49" s="12" t="n">
-        <v>4191066</v>
-      </c>
-      <c r="M49" s="12" t="n">
-        <v>16</v>
+      <c r="J49" s="13" t="n">
+        <v>1902180</v>
+      </c>
+      <c r="K49" s="14" t="n">
+        <v>2523717</v>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>5642162</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>18</v>
       </c>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>79–394</t>
+          <t>70–310</t>
         </is>
       </c>
       <c r="O49" s="11" t="inlineStr">
@@ -4529,44 +4529,44 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P49" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q49" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R49" s="14" t="inlineStr">
+      <c r="P49" s="13" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q49" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R49" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>сдан в 2026, продажи от застройщика; реконструкция дома 1915 г.; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>5 секций; арх. Squire &amp; Partners; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Magnum (Магнум)</t>
+          <t>Villa Grace (Вилла Грейс)</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Magnum Development</t>
+          <t>ГК Стройтэкс</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2020–2022</t>
+          <t>2020–2023</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Москва, Усачева, 9</t>
+          <t>Москва, Пожарский, 3</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -4589,24 +4589,24 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1568381</v>
+        <v>2635581</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>2490110</v>
+        <v>2635659</v>
       </c>
       <c r="L50" s="7" t="n">
-        <v>2738095</v>
+        <v>2637704</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N50" s="5" t="inlineStr">
         <is>
-          <t>84–215</t>
+          <t>128–129</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
@@ -4614,7 +4614,9 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P50" s="5" t="n"/>
+      <c r="P50" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -4627,47 +4629,47 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>арх. бюро VOSTOK; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1">
+          <t>ввод 3 кв. 2020; часть источников 4 кв. 2022; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Дом Бакст на Патриарших</t>
+          <t>Brodsky (Бродский)</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Инвестстройком</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Москва, Большой Козихинский, 15</t>
+          <t>Москва, 1-й Тружеников, 16</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="n">
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>14-16</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -4675,21 +4677,21 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J51" s="12" t="n">
-        <v>2488540</v>
-      </c>
-      <c r="K51" s="13" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>3333333</v>
-      </c>
-      <c r="M51" s="12" t="n">
-        <v>11</v>
+      <c r="J51" s="13" t="n">
+        <v>2446043</v>
+      </c>
+      <c r="K51" s="14" t="n">
+        <v>2698752</v>
+      </c>
+      <c r="L51" s="13" t="n">
+        <v>3339278</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>152–498</t>
+          <t>139–224</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
@@ -4698,51 +4700,47 @@
         </is>
       </c>
       <c r="P51" s="11" t="n"/>
-      <c r="Q51" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R51" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
+      <c r="Q51" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R51" s="11" t="inlineStr"/>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>также указывается АСН-Инвест; арх. Павел Андреев; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="24" customHeight="1">
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом TURGENEV (Тургенев)</t>
+          <t>Жизнь на Плющихе</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>НеоСтрой</t>
+          <t>Донстрой</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Москва, Костянский, 13</t>
+          <t>Москва, Погодинская, 2</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Красносельский</t>
-        </is>
-      </c>
-      <c r="F52" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G52" s="7" t="n">
@@ -4750,7 +4748,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -4759,150 +4757,144 @@
         </is>
       </c>
       <c r="J52" s="7" t="n">
-        <v>1902180</v>
+        <v>1253669</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>2523717</v>
+        <v>3000000</v>
       </c>
       <c r="L52" s="7" t="n">
-        <v>5642162</v>
+        <v>3680336</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="N52" s="5" t="inlineStr">
         <is>
-          <t>70–310</t>
+          <t>95–254</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P52" s="7" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q52" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R52" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S52" s="4" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>Carré Blanc (Карре Бланк)</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Пречистенская, 43</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J53" s="13" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="K53" s="14" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="L53" s="13" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="11" t="inlineStr">
+        <is>
+          <t>147–147</t>
+        </is>
+      </c>
+      <c r="O53" s="11" t="inlineStr">
+        <is>
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P52" s="7" t="n">
-        <v>118</v>
-      </c>
-      <c r="Q52" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R52" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S52" s="4" t="inlineStr">
-        <is>
-          <t>5 секций; арх. Squire &amp; Partners; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>Villa Grace (Вилла Грейс)</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>ГК Стройтэкс</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>2020–2023</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Пожарский, 3</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="G53" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J53" s="12" t="n">
-        <v>2635581</v>
-      </c>
-      <c r="K53" s="13" t="n">
-        <v>2635659</v>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>2637704</v>
-      </c>
-      <c r="M53" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N53" s="11" t="inlineStr">
-        <is>
-          <t>128–129</t>
-        </is>
-      </c>
-      <c r="O53" s="11" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P53" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q53" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R53" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R53" s="11" t="inlineStr"/>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>ввод 3 кв. 2020; часть источников 4 кв. 2022; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Brodsky (Бродский)</t>
+          <t>Саввинская 27</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Vesper</t>
+          <t>Level Group</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Москва, 1-й Тружеников, 16</t>
+          <t>Москва, Саввинская, 27</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -4920,29 +4912,29 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>14-16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J54" s="7" t="n">
-        <v>2446043</v>
+        <v>3060713</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>2698752</v>
+        <v>3095494</v>
       </c>
       <c r="L54" s="7" t="n">
-        <v>3339278</v>
+        <v>3130275</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N54" s="5" t="inlineStr">
         <is>
-          <t>139–224</t>
+          <t>81–131</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
@@ -4950,305 +4942,305 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P54" s="5" t="n"/>
+      <c r="P54" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R54" s="5" t="inlineStr"/>
+      <c r="R54" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Жизнь на Плющихе</t>
+          <t>Дом Лаврушинский</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Донстрой</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
+          <t>2024–2025</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Большой Толмачевский, 5С1</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>3-14</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J55" s="13" t="n">
+        <v>1956522</v>
+      </c>
+      <c r="K55" s="14" t="n">
+        <v>3118040</v>
+      </c>
+      <c r="L55" s="13" t="n">
+        <v>7453392</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="N55" s="11" t="inlineStr">
+        <is>
+          <t>66–980</t>
+        </is>
+      </c>
+      <c r="O55" s="11" t="inlineStr">
+        <is>
+          <t>делюкс</t>
+        </is>
+      </c>
+      <c r="P55" s="11" t="n"/>
+      <c r="Q55" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R55" s="11" t="inlineStr"/>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Хамовники 12</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Coldy</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Москва, 1-й Тружеников, 12</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="K56" s="8" t="n">
+        <v>3151207</v>
+      </c>
+      <c r="L56" s="7" t="n">
+        <v>3502415</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>104–207</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="P56" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q56" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R56" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S56" s="4" t="inlineStr">
+        <is>
+          <t>арх. Евгений Герасимов; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Дом на Хлебном</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Погодинская, 2</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F55" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="G55" s="12" t="n">
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Хлебный, 19</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>Арбат</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>1253669</v>
-      </c>
-      <c r="K55" s="13" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="L55" s="12" t="n">
-        <v>3680336</v>
-      </c>
-      <c r="M55" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="N55" s="11" t="inlineStr">
-        <is>
-          <t>95–254</t>
-        </is>
-      </c>
-      <c r="O55" s="11" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P55" s="12" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q55" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R55" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>квартиры + апартаменты</t>
+        </is>
+      </c>
+      <c r="J57" s="13" t="n">
+        <v>2133333</v>
+      </c>
+      <c r="K57" s="14" t="n">
+        <v>3194462</v>
+      </c>
+      <c r="L57" s="13" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="N57" s="11" t="inlineStr">
+        <is>
+          <t>95–342</t>
+        </is>
+      </c>
+      <c r="O57" s="11" t="inlineStr">
+        <is>
+          <t>делюкс</t>
+        </is>
+      </c>
+      <c r="P57" s="11" t="n"/>
+      <c r="Q57" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R57" s="11" t="inlineStr"/>
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Carré Blanc (Карре Бланк)</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Пречистенская, 43</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="K56" s="8" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="L56" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="M56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" s="5" t="inlineStr">
-        <is>
-          <t>147–147</t>
-        </is>
-      </c>
-      <c r="O56" s="5" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P56" s="5" t="n"/>
-      <c r="Q56" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R56" s="5" t="inlineStr"/>
-      <c r="S56" s="4" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>Саввинская 27</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>Level Group</t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Саввинская, 27</t>
-        </is>
-      </c>
-      <c r="E57" s="11" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F57" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="G57" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I57" s="11" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J57" s="12" t="n">
-        <v>3060713</v>
-      </c>
-      <c r="K57" s="13" t="n">
-        <v>3095494</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>3130275</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N57" s="11" t="inlineStr">
-        <is>
-          <t>81–131</t>
-        </is>
-      </c>
-      <c r="O57" s="11" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P57" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q57" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R57" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Дом Лаврушинский</t>
+          <t>Stoleshnikov 7 (Столешников 7)</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>2024–2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Москва, Большой Толмачевский, 5С1</t>
+          <t>Москва, Столешников, 7С1</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F58" s="15" t="inlineStr">
+          <t>Тверской</t>
+        </is>
+      </c>
+      <c r="F58" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G58" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>3-14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -5257,20 +5249,20 @@
         </is>
       </c>
       <c r="J58" s="7" t="n">
-        <v>1956522</v>
+        <v>2977612</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>3118040</v>
+        <v>3229296</v>
       </c>
       <c r="L58" s="7" t="n">
-        <v>7453392</v>
+        <v>3242801</v>
       </c>
       <c r="M58" s="7" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t>66–980</t>
+          <t>134–158</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
@@ -5294,40 +5286,40 @@
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Хамовники 12</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>Coldy</t>
+          <t>Stella di Mosca Hotel &amp; Residences (Стелла ди Моска Хотел энд Резиденсиз)</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>Bulgari Hotel &amp; Residences</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023–2024</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Москва, 1-й Тружеников, 12</t>
+          <t>Москва, Большая Никитская, 9</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F59" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="G59" s="12" t="n">
-        <v>2</v>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -5335,106 +5327,100 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J59" s="12" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>3151207</v>
-      </c>
-      <c r="L59" s="12" t="n">
-        <v>3502415</v>
-      </c>
-      <c r="M59" s="12" t="n">
-        <v>2</v>
+      <c r="J59" s="13" t="n">
+        <v>3240741</v>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v>3249768</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>5584363</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>104–207</t>
+          <t>107–198</t>
         </is>
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P59" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q59" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R59" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
+          <t>делюкс</t>
+        </is>
+      </c>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R59" s="11" t="inlineStr"/>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>арх. Евгений Герасимов; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Дом на Хлебном</t>
+          <t>Большая Дмитровка IX</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021–2025</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Москва, Хлебный, 19</t>
+          <t>Москва, Большая Дмитровка, 9А</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Арбат</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="inlineStr">
+          <t>Тверской</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G60" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>квартиры + апартаменты</t>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J60" s="7" t="n">
-        <v>2133333</v>
+        <v>2372881</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>3194462</v>
+        <v>3250803</v>
       </c>
       <c r="L60" s="7" t="n">
-        <v>3500000</v>
+        <v>3813559</v>
       </c>
       <c r="M60" s="7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="N60" s="5" t="inlineStr">
         <is>
-          <t>95–342</t>
+          <t>54–192</t>
         </is>
       </c>
       <c r="O60" s="5" t="inlineStr">
@@ -5455,15 +5441,15 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1">
+    <row r="61" ht="24" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Stoleshnikov 7 (Столешников 7)</t>
+          <t>Armani/Casa Moscow Residences (Армани/Каса Москоу Резиденсес)</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Vesper</t>
+          <t>Vos'hod</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -5473,21 +5459,21 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Москва, Столешников, 7С1</t>
+          <t>Москва, Старомонетный, 19/11</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Тверской</t>
-        </is>
-      </c>
-      <c r="F61" s="15" t="inlineStr">
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G61" s="12" t="n">
-        <v>1</v>
+      <c r="G61" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
@@ -5499,21 +5485,21 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J61" s="12" t="n">
-        <v>2977612</v>
-      </c>
-      <c r="K61" s="13" t="n">
-        <v>3229296</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>3242801</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>3</v>
+      <c r="J61" s="13" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="K61" s="14" t="n">
+        <v>3630000</v>
+      </c>
+      <c r="L61" s="13" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>134–158</t>
+          <t>176–421</t>
         </is>
       </c>
       <c r="O61" s="11" t="inlineStr">
@@ -5522,37 +5508,41 @@
         </is>
       </c>
       <c r="P61" s="11" t="n"/>
-      <c r="Q61" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R61" s="11" t="inlineStr"/>
+      <c r="Q61" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R61" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>введён июль 2024; арх. John McAslan + Partners; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Stella di Mosca Hotel &amp; Residences (Стелла ди Моска Хотел энд Резиденсиз)</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Bulgari Hotel &amp; Residences</t>
+          <t>Малая Бронная 15</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>ЛидЭстейт</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>2023–2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Москва, Большая Никитская, 9</t>
+          <t>Москва, Малая Бронная, 15Б</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -5560,7 +5550,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="F62" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -5570,7 +5560,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
@@ -5579,20 +5569,20 @@
         </is>
       </c>
       <c r="J62" s="7" t="n">
-        <v>3240741</v>
+        <v>3792852</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>3249768</v>
+        <v>3795620</v>
       </c>
       <c r="L62" s="7" t="n">
-        <v>5584363</v>
+        <v>6027397</v>
       </c>
       <c r="M62" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N62" s="5" t="inlineStr">
         <is>
-          <t>107–198</t>
+          <t>137–219</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
@@ -5600,78 +5590,84 @@
           <t>делюкс</t>
         </is>
       </c>
-      <c r="P62" s="5" t="n"/>
+      <c r="P62" s="7" t="n">
+        <v>23</v>
+      </c>
       <c r="Q62" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R62" s="5" t="inlineStr"/>
+      <c r="R62" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>акт ввода 31.07.2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Большая Дмитровка IX</t>
+          <t>Barkli Gallery (Баркли Галлери)</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Vesper</t>
+          <t>Barkli</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>2021–2025</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Москва, Большая Дмитровка, 9А</t>
+          <t>Москва, Ордынский, 4А</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Тверской</t>
-        </is>
-      </c>
-      <c r="F63" s="15" t="inlineStr">
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G63" s="12" t="n">
-        <v>3</v>
+      <c r="G63" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J63" s="12" t="n">
-        <v>2372881</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>3250803</v>
-      </c>
-      <c r="L63" s="12" t="n">
-        <v>3813559</v>
-      </c>
-      <c r="M63" s="12" t="n">
-        <v>18</v>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>4694118</v>
+      </c>
+      <c r="K63" s="14" t="n">
+        <v>4694118</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>4694118</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>54–192</t>
+          <t>85–85</t>
         </is>
       </c>
       <c r="O63" s="11" t="inlineStr">
@@ -5680,7 +5676,7 @@
         </is>
       </c>
       <c r="P63" s="11" t="n"/>
-      <c r="Q63" s="14" t="inlineStr">
+      <c r="Q63" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -5692,268 +5688,21 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>Armani/Casa Moscow Residences (Армани/Каса Москоу Резиденсес)</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>Vos'hod</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Старомонетный, 19/11</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F64" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J64" s="7" t="n">
-        <v>2750000</v>
-      </c>
-      <c r="K64" s="8" t="n">
-        <v>3630000</v>
-      </c>
-      <c r="L64" s="7" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="M64" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="N64" s="5" t="inlineStr">
-        <is>
-          <t>176–421</t>
-        </is>
-      </c>
-      <c r="O64" s="5" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P64" s="5" t="n"/>
-      <c r="Q64" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R64" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S64" s="4" t="inlineStr">
-        <is>
-          <t>введён июль 2024; арх. John McAslan + Partners; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>Малая Бронная 15</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>ЛидЭстейт</t>
-        </is>
-      </c>
-      <c r="C65" s="11" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Малая Бронная, 15Б</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G65" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H65" s="11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J65" s="12" t="n">
-        <v>3792852</v>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>3795620</v>
-      </c>
-      <c r="L65" s="12" t="n">
-        <v>6027397</v>
-      </c>
-      <c r="M65" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N65" s="11" t="inlineStr">
-        <is>
-          <t>137–219</t>
-        </is>
-      </c>
-      <c r="O65" s="11" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P65" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q65" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R65" s="14" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S65" s="10" t="inlineStr">
-        <is>
-          <t>акт ввода 31.07.2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>Barkli Gallery (Баркли Галлери)</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>Barkli</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Ордынский, 4А</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F66" s="15" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J66" s="7" t="n">
-        <v>4694118</v>
-      </c>
-      <c r="K66" s="8" t="n">
-        <v>4694118</v>
-      </c>
-      <c r="L66" s="7" t="n">
-        <v>4694118</v>
-      </c>
-      <c r="M66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" s="5" t="inlineStr">
-        <is>
-          <t>85–85</t>
-        </is>
-      </c>
-      <c r="O66" s="5" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P66" s="5" t="n"/>
-      <c r="Q66" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R66" s="5" t="inlineStr"/>
-      <c r="S66" s="4" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="18" t="inlineStr">
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="18" t="inlineStr">
         <is>
           <t>Источник: живая выдача Циан 2026-09-07 (api.cian.ru, инструмент tools/cian/cian.js), вторичка с годом дома 2018+ и новостройки по 10 районам ЦАО. Цены — ₽/м² по активным объявлениям. Застройщик и класс — по открытым данным (ручная разметка docs/premium-cao/manual.json).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S66"/>
+  <autoFilter ref="A3:S63"/>
   <mergeCells count="3">
-    <mergeCell ref="A68:S68"/>
+    <mergeCell ref="A65:S65"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
   </mergeCells>
-  <conditionalFormatting sqref="K4:K66">
+  <conditionalFormatting sqref="K4:K63">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5973,108 +5722,104 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R50" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R51" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R52" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R53" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R50" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R52" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R55" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R54" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R57" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R56" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q58" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q59" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R59" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R61" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R64" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R65" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R62" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId105"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -6318,12 +6063,12 @@
           <t>Москва-Сити</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -6336,16 +6081,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J5" s="13" t="n">
         <v>807900</v>
       </c>
-      <c r="K5" s="13" t="n">
+      <c r="K5" s="14" t="n">
         <v>1032987</v>
       </c>
-      <c r="L5" s="12" t="n">
+      <c r="L5" s="13" t="n">
         <v>1995800</v>
       </c>
-      <c r="M5" s="12" t="n">
+      <c r="M5" s="13" t="n">
         <v>295</v>
       </c>
       <c r="N5" s="11" t="inlineStr">
@@ -6353,7 +6098,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O5" s="14" t="inlineStr">
+      <c r="O5" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -6373,12 +6118,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Forma</t>
+          <t>Страна.Премиум</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>2025–2026</t>
+          <t>3 кв. 2026</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -6432,11 +6177,7 @@
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
+      <c r="Q6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -6469,7 +6210,7 @@
           <t>Пресня</t>
         </is>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <v>8</v>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -6482,16 +6223,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="13" t="n">
         <v>925200</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="14" t="n">
         <v>1172000</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L7" s="13" t="n">
         <v>1884000</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" s="13" t="n">
         <v>231</v>
       </c>
       <c r="N7" s="11" t="inlineStr">
@@ -6499,7 +6240,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O7" s="14" t="inlineStr">
+      <c r="O7" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -6537,7 +6278,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
@@ -6610,7 +6351,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
@@ -6626,20 +6367,20 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="J9" s="13" t="n">
         <v>892920</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="K9" s="14" t="n">
         <v>1237935</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" s="13" t="n">
         <v>1880116</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="M9" s="13" t="n">
         <v>203</v>
       </c>
       <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="14" t="inlineStr">
+      <c r="O9" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -6681,7 +6422,7 @@
           <t>Павелецкая</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -6759,7 +6500,7 @@
           <t>Пресня</t>
         </is>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="13" t="n">
         <v>6</v>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -6772,16 +6513,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="13" t="n">
         <v>1019417</v>
       </c>
-      <c r="K11" s="13" t="n">
+      <c r="K11" s="14" t="n">
         <v>1585417</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="L11" s="13" t="n">
         <v>2290000</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="M11" s="13" t="n">
         <v>232</v>
       </c>
       <c r="N11" s="11" t="inlineStr">
@@ -6789,7 +6530,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O11" s="14" t="inlineStr">
+      <c r="O11" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -6908,12 +6649,12 @@
           <t>Таганский</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="13" t="n">
         <v>3</v>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -6926,20 +6667,20 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J13" s="13" t="n">
         <v>1538500</v>
       </c>
-      <c r="K13" s="13" t="n">
+      <c r="K13" s="14" t="n">
         <v>1610325</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="L13" s="13" t="n">
         <v>1750150</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="M13" s="13" t="n">
         <v>44</v>
       </c>
       <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="14" t="inlineStr">
+      <c r="O13" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -7054,12 +6795,12 @@
           <t>Лубянка</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="13" t="n">
         <v>2</v>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -7072,16 +6813,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="13" t="n">
         <v>1581880</v>
       </c>
-      <c r="K15" s="13" t="n">
+      <c r="K15" s="14" t="n">
         <v>1758200</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="L15" s="13" t="n">
         <v>2165109</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="M15" s="13" t="n">
         <v>9</v>
       </c>
       <c r="N15" s="11" t="inlineStr">
@@ -7089,7 +6830,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O15" s="14" t="inlineStr">
+      <c r="O15" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -7127,7 +6868,7 @@
           <t>Новокузнецкая</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -7204,12 +6945,12 @@
           <t>Таганский</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="13" t="n">
         <v>2</v>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -7222,20 +6963,20 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" s="13" t="n">
         <v>1656155</v>
       </c>
-      <c r="K17" s="13" t="n">
+      <c r="K17" s="14" t="n">
         <v>1808841</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="L17" s="13" t="n">
         <v>3549554</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="M17" s="13" t="n">
         <v>52</v>
       </c>
       <c r="N17" s="11" t="inlineStr"/>
-      <c r="O17" s="14" t="inlineStr">
+      <c r="O17" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -7277,7 +7018,7 @@
           <t>Красные ворота</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -7355,7 +7096,7 @@
           <t>Пресня</t>
         </is>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -7368,16 +7109,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="J19" s="13" t="n">
         <v>1581360</v>
       </c>
-      <c r="K19" s="13" t="n">
+      <c r="K19" s="14" t="n">
         <v>2105000</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="L19" s="13" t="n">
         <v>2550000</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="M19" s="13" t="n">
         <v>17</v>
       </c>
       <c r="N19" s="11" t="inlineStr">
@@ -7385,7 +7126,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O19" s="14" t="inlineStr">
+      <c r="O19" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -7423,7 +7164,7 @@
           <t>Сухаревская</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -7500,12 +7241,12 @@
           <t>Охотный Ряд</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -7518,16 +7259,16 @@
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="J21" s="13" t="n">
         <v>1909308</v>
       </c>
-      <c r="K21" s="13" t="n">
+      <c r="K21" s="14" t="n">
         <v>2171784</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="13" t="n">
         <v>4015377</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="M21" s="13" t="n">
         <v>32</v>
       </c>
       <c r="N21" s="11" t="inlineStr">
@@ -7535,7 +7276,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O21" s="14" t="inlineStr">
+      <c r="O21" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -7577,7 +7318,7 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -7650,12 +7391,12 @@
           <t>Павелецкая</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G23" s="13" t="n">
         <v>4</v>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -7668,16 +7409,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="J23" s="13" t="n">
         <v>1675161</v>
       </c>
-      <c r="K23" s="13" t="n">
+      <c r="K23" s="14" t="n">
         <v>2265083</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="L23" s="13" t="n">
         <v>4224652</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="M23" s="13" t="n">
         <v>36</v>
       </c>
       <c r="N23" s="11" t="inlineStr">
@@ -7685,7 +7426,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O23" s="14" t="inlineStr">
+      <c r="O23" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -7727,7 +7468,7 @@
           <t>Сухаревская</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -7800,12 +7541,12 @@
           <t>Арбат</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G25" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -7818,20 +7559,20 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="J25" s="13" t="n">
         <v>2400000</v>
       </c>
-      <c r="K25" s="13" t="n">
+      <c r="K25" s="14" t="n">
         <v>2650000</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="L25" s="13" t="n">
         <v>6000000</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="M25" s="13" t="n">
         <v>26</v>
       </c>
       <c r="N25" s="11" t="inlineStr"/>
-      <c r="O25" s="14" t="inlineStr">
+      <c r="O25" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -7873,7 +7614,7 @@
           <t>Арбат</t>
         </is>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -7946,12 +7687,12 @@
           <t>Таганский</t>
         </is>
       </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="G27" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -7964,20 +7705,20 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="J27" s="13" t="n">
         <v>2425281</v>
       </c>
-      <c r="K27" s="13" t="n">
+      <c r="K27" s="14" t="n">
         <v>2705884</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="L27" s="13" t="n">
         <v>2914068</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="M27" s="13" t="n">
         <v>9</v>
       </c>
       <c r="N27" s="11" t="inlineStr"/>
-      <c r="O27" s="14" t="inlineStr">
+      <c r="O27" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -8019,7 +7760,7 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8097,7 +7838,7 @@
           <t>Пресня</t>
         </is>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="G29" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="11" t="inlineStr">
@@ -8110,20 +7851,20 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="J29" s="13" t="n">
         <v>2281650</v>
       </c>
-      <c r="K29" s="13" t="n">
+      <c r="K29" s="14" t="n">
         <v>2787488</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="L29" s="13" t="n">
         <v>3174937</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="M29" s="13" t="n">
         <v>13</v>
       </c>
       <c r="N29" s="11" t="inlineStr"/>
-      <c r="O29" s="14" t="inlineStr">
+      <c r="O29" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -8165,7 +7906,7 @@
           <t>Площадь Революции</t>
         </is>
       </c>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8242,12 +7983,12 @@
           <t>Кропоткинская</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="G31" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -8260,16 +8001,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="J31" s="13" t="n">
         <v>2990000</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="14" t="n">
         <v>2990000</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="L31" s="13" t="n">
         <v>2990000</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="M31" s="13" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="11" t="inlineStr">
@@ -8277,7 +8018,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O31" s="14" t="inlineStr">
+      <c r="O31" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -8319,7 +8060,7 @@
           <t>Площадь Революции</t>
         </is>
       </c>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8392,12 +8133,12 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F33" s="15" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="G33" s="13" t="n">
         <v>4</v>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -8410,16 +8151,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="J33" s="13" t="n">
         <v>2050200</v>
       </c>
-      <c r="K33" s="13" t="n">
+      <c r="K33" s="14" t="n">
         <v>3001950</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="L33" s="13" t="n">
         <v>3322400</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="M33" s="13" t="n">
         <v>14</v>
       </c>
       <c r="N33" s="11" t="inlineStr">
@@ -8427,7 +8168,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O33" s="14" t="inlineStr">
+      <c r="O33" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -8469,7 +8210,7 @@
           <t>Арбат</t>
         </is>
       </c>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8547,7 +8288,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G35" s="13" t="n">
         <v>4</v>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -8560,16 +8301,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="J35" s="13" t="n">
         <v>2180740</v>
       </c>
-      <c r="K35" s="13" t="n">
+      <c r="K35" s="14" t="n">
         <v>3083973</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="L35" s="13" t="n">
         <v>6898288</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="M35" s="13" t="n">
         <v>97</v>
       </c>
       <c r="N35" s="11" t="inlineStr">
@@ -8577,7 +8318,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O35" s="14" t="inlineStr">
+      <c r="O35" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -8615,7 +8356,7 @@
           <t>Мещанский</t>
         </is>
       </c>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8693,7 +8434,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="G37" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -8706,20 +8447,20 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="J37" s="13" t="n">
         <v>2479101</v>
       </c>
-      <c r="K37" s="13" t="n">
+      <c r="K37" s="14" t="n">
         <v>3150000</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="L37" s="13" t="n">
         <v>4000000</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="M37" s="13" t="n">
         <v>4</v>
       </c>
       <c r="N37" s="11" t="inlineStr"/>
-      <c r="O37" s="14" t="inlineStr">
+      <c r="O37" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -8761,7 +8502,7 @@
           <t>Чистые пруды</t>
         </is>
       </c>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8835,7 +8576,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G39" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -8848,16 +8589,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="J39" s="13" t="n">
         <v>3177900</v>
       </c>
-      <c r="K39" s="13" t="n">
+      <c r="K39" s="14" t="n">
         <v>3488415</v>
       </c>
-      <c r="L39" s="12" t="n">
+      <c r="L39" s="13" t="n">
         <v>4559310</v>
       </c>
-      <c r="M39" s="12" t="n">
+      <c r="M39" s="13" t="n">
         <v>4</v>
       </c>
       <c r="N39" s="11" t="inlineStr">
@@ -8865,7 +8606,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O39" s="14" t="inlineStr">
+      <c r="O39" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -8907,7 +8648,7 @@
           <t>Кропоткинская</t>
         </is>
       </c>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8984,12 +8725,12 @@
           <t>Маяковская</t>
         </is>
       </c>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="G41" s="13" t="n">
         <v>3</v>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -9002,16 +8743,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="J41" s="13" t="n">
         <v>2800000</v>
       </c>
-      <c r="K41" s="13" t="n">
+      <c r="K41" s="14" t="n">
         <v>3560820</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="L41" s="13" t="n">
         <v>4189200</v>
       </c>
-      <c r="M41" s="12" t="n">
+      <c r="M41" s="13" t="n">
         <v>16</v>
       </c>
       <c r="N41" s="11" t="inlineStr">
@@ -9019,7 +8760,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O41" s="14" t="inlineStr">
+      <c r="O41" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -9138,12 +8879,12 @@
           <t>Кропоткинская</t>
         </is>
       </c>
-      <c r="F43" s="15" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="G43" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="11" t="inlineStr">
@@ -9156,16 +8897,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="J43" s="13" t="n">
         <v>2818178</v>
       </c>
-      <c r="K43" s="13" t="n">
+      <c r="K43" s="14" t="n">
         <v>4239914</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="L43" s="13" t="n">
         <v>9287270</v>
       </c>
-      <c r="M43" s="12" t="n">
+      <c r="M43" s="13" t="n">
         <v>9</v>
       </c>
       <c r="N43" s="11" t="inlineStr">
@@ -9173,7 +8914,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O43" s="14" t="inlineStr">
+      <c r="O43" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -9288,12 +9029,12 @@
           <t>Охотный Ряд</t>
         </is>
       </c>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="G45" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="11" t="inlineStr">
@@ -9306,16 +9047,16 @@
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J45" s="12" t="n">
+      <c r="J45" s="13" t="n">
         <v>4318135</v>
       </c>
-      <c r="K45" s="13" t="n">
+      <c r="K45" s="14" t="n">
         <v>5980861</v>
       </c>
-      <c r="L45" s="12" t="n">
+      <c r="L45" s="13" t="n">
         <v>6843436</v>
       </c>
-      <c r="M45" s="12" t="n">
+      <c r="M45" s="13" t="n">
         <v>7</v>
       </c>
       <c r="N45" s="11" t="inlineStr">
@@ -9323,7 +9064,7 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O45" s="14" t="inlineStr">
+      <c r="O45" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -9642,14 +9383,14 @@
           <t>старт продаж без стройки (закрытый старт 22.04.2026)</t>
         </is>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="13" t="n">
         <v>15600</v>
       </c>
       <c r="H5" s="11" t="n"/>
-      <c r="I5" s="12" t="n">
+      <c r="I5" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J5" s="13" t="n">
         <v>43</v>
       </c>
       <c r="K5" s="11" t="inlineStr">
@@ -9662,7 +9403,7 @@
           <t>1 кв. 2030</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="14" t="n">
         <v>3500000</v>
       </c>
       <c r="N5" s="11" t="inlineStr">
@@ -9675,7 +9416,7 @@
           <t>novostroev.ru</t>
         </is>
       </c>
-      <c r="P5" s="14" t="inlineStr">
+      <c r="P5" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -9794,11 +9535,11 @@
           <t>концепция одобрена ГЗК, подготовка к строительству, старт продаж 2026</t>
         </is>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <v>17000</v>
       </c>
       <c r="H7" s="11" t="n"/>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="13" t="n">
         <v>8</v>
       </c>
       <c r="J7" s="11" t="n"/>
@@ -9815,7 +9556,7 @@
           <t>официальный сайт проекта (также whitewill.ru)</t>
         </is>
       </c>
-      <c r="P7" s="14" t="inlineStr">
+      <c r="P7" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -9918,14 +9659,14 @@
           <t>проект, продажи не начаты</t>
         </is>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="13" t="n">
         <v>9377</v>
       </c>
       <c r="H9" s="11" t="n"/>
-      <c r="I9" s="12" t="n">
+      <c r="I9" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="J9" s="13" t="n">
         <v>98</v>
       </c>
       <c r="K9" s="11" t="inlineStr">
@@ -9941,7 +9682,7 @@
           <t>novostroev.ru</t>
         </is>
       </c>
-      <c r="P9" s="14" t="inlineStr">
+      <c r="P9" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -10042,7 +9783,7 @@
           <t>проектирование</t>
         </is>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="13" t="n">
         <v>125000</v>
       </c>
       <c r="H11" s="11" t="n"/>
@@ -10061,7 +9802,7 @@
           <t>РИА Недвижимость (стадия подтверждена mperspektiva.ru 18.12.2025)</t>
         </is>
       </c>
-      <c r="P11" s="14" t="inlineStr">
+      <c r="P11" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -10174,10 +9915,10 @@
       </c>
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n"/>
-      <c r="I13" s="12" t="n">
+      <c r="I13" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J13" s="13" t="n">
         <v>4</v>
       </c>
       <c r="K13" s="10" t="inlineStr">
@@ -10201,7 +9942,7 @@
           <t>Novostroev.ru (19.01.2026); sosedi.life</t>
         </is>
       </c>
-      <c r="P13" s="14" t="inlineStr">
+      <c r="P13" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -10312,7 +10053,7 @@
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="12" t="n">
+      <c r="I15" s="13" t="n">
         <v>6</v>
       </c>
       <c r="J15" s="11" t="n"/>
@@ -10325,7 +10066,7 @@
           <t>Anwin (агрегатор элитной недвижимости)</t>
         </is>
       </c>
-      <c r="P15" s="14" t="inlineStr">
+      <c r="P15" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -10432,10 +10173,10 @@
       </c>
       <c r="G17" s="11" t="n"/>
       <c r="H17" s="11" t="n"/>
-      <c r="I17" s="12" t="n">
+      <c r="I17" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" s="13" t="n">
         <v>16</v>
       </c>
       <c r="K17" s="11" t="inlineStr">
@@ -10455,7 +10196,7 @@
           <t>whitewill.ru (также tehne.com, levshinsky-19.ru)</t>
         </is>
       </c>
-      <c r="P17" s="14" t="inlineStr">
+      <c r="P17" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -10556,11 +10297,11 @@
           <t>анонсирован, старт продаж ожидается в 2026 г.</t>
         </is>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="13" t="n">
         <v>12000</v>
       </c>
       <c r="H19" s="11" t="n"/>
-      <c r="I19" s="12" t="n">
+      <c r="I19" s="13" t="n">
         <v>9</v>
       </c>
       <c r="J19" s="11" t="n"/>
@@ -10577,7 +10318,7 @@
           <t>sosedi.life (также mskdeluxe.ru/start, anwin.ru)</t>
         </is>
       </c>
-      <c r="P19" s="14" t="inlineStr">
+      <c r="P19" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -10674,14 +10415,14 @@
           <t>старт продаж 06.04.2026</t>
         </is>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="13" t="n">
         <v>3000</v>
       </c>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="12" t="n">
+      <c r="I21" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="J21" s="13" t="n">
         <v>11</v>
       </c>
       <c r="K21" s="11" t="inlineStr">
@@ -10701,7 +10442,7 @@
           <t>sosedi.life (также novostroev.ru обзор делюкс-стартов 2026)</t>
         </is>
       </c>
-      <c r="P21" s="14" t="inlineStr">
+      <c r="P21" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -10806,10 +10547,10 @@
       </c>
       <c r="G23" s="11" t="n"/>
       <c r="H23" s="11" t="n"/>
-      <c r="I23" s="12" t="n">
+      <c r="I23" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="J23" s="13" t="n">
         <v>34</v>
       </c>
       <c r="K23" s="11" t="inlineStr">
@@ -10825,7 +10566,7 @@
           <t>официальный сайт проекта (также mskdeluxe.ru/start)</t>
         </is>
       </c>
-      <c r="P23" s="14" t="inlineStr">
+      <c r="P23" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -10932,7 +10673,7 @@
       </c>
       <c r="G25" s="11" t="n"/>
       <c r="H25" s="11" t="n"/>
-      <c r="I25" s="12" t="n">
+      <c r="I25" s="13" t="n">
         <v>7</v>
       </c>
       <c r="J25" s="11" t="n"/>
@@ -10953,7 +10694,7 @@
           <t>novostroev.ru (также roden.moscow)</t>
         </is>
       </c>
-      <c r="P25" s="14" t="inlineStr">
+      <c r="P25" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -11062,10 +10803,10 @@
           <t>участок приобретён (апрель 2026), проектирование</t>
         </is>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="G27" s="13" t="n">
         <v>13000</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="H27" s="13" t="n">
         <v>8200</v>
       </c>
       <c r="I27" s="11" t="n"/>
@@ -11083,7 +10824,7 @@
           <t>РИА Недвижимость (также sminex.com, interfax-russia.ru)</t>
         </is>
       </c>
-      <c r="P27" s="14" t="inlineStr">
+      <c r="P27" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -11184,11 +10925,11 @@
           <t>анонсирован (приобретение объекта), концепция</t>
         </is>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="G29" s="13" t="n">
         <v>2500</v>
       </c>
       <c r="H29" s="11" t="n"/>
-      <c r="I29" s="12" t="n">
+      <c r="I29" s="13" t="n">
         <v>4</v>
       </c>
       <c r="J29" s="11" t="n"/>
@@ -11205,7 +10946,7 @@
           <t>elitnoe.ru</t>
         </is>
       </c>
-      <c r="P29" s="14" t="inlineStr">
+      <c r="P29" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
@@ -11310,10 +11051,10 @@
           <t>решение о КРТ (по данным заказчика — август 2026); оператор/правообладатель и торги в открытых источниках не найдены</t>
         </is>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="G31" s="13" t="n">
         <v>10000</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="H31" s="13" t="n">
         <v>6000</v>
       </c>
       <c r="I31" s="11" t="n"/>
@@ -11331,7 +11072,7 @@
           <t>krt.mos.ru (реестр проектов КРТ Москвы)</t>
         </is>
       </c>
-      <c r="P31" s="14" t="inlineStr">
+      <c r="P31" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -12,12 +12,12 @@
     <sheet name="3. Проектирование" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Построено (вторичка)'!$A$3:$S$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Построено (вторичка)'!$A$3:$S$54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'1. Построено (вторичка)'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1. Построено (вторичка)'!$A$1:$S$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Строится'!$A$3:$Q$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1. Построено (вторичка)'!$A$1:$S$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Строится'!$A$3:$Q$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'2. Строится'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'2. Строится'!$A$1:$Q$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2. Строится'!$A$1:$Q$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Проектирование'!$A$3:$Q$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'3. Проектирование'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'3. Проектирование'!$A$1:$Q$34</definedName>
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Техноком Трейд</t>
+          <t>Kovaks (Ковакс)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="S4" s="4" t="inlineStr">
         <is>
-          <t>апарт-отель; юрлицо Техноком Трейд</t>
+          <t>в карточке Циан застройщик: Техноком Трейд; апарт-отель; юрлицо Техноком Трейд</t>
         </is>
       </c>
     </row>
@@ -817,9 +817,9 @@
           <t>NEVA TOWERS (Нева Тауэрс)</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>СТ Тауэрс</t>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Renaissance Development</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -884,7 +884,11 @@
         </is>
       </c>
       <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr"/>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>в карточке Циан застройщик: СТ Тауэрс</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -977,7 +981,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>HUTTON</t>
+          <t>Hutton</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>VESPER</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1215,22 +1219,22 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>City Park (Сити Парк)</t>
+          <t>Репаблик</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>МонАрх</t>
+          <t>Forma</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>3 кв. 2026</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Москва, Мантулинская, 9к4</t>
+          <t>Москва, Пресненский Вал, 27к5</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1238,17 +1242,17 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Сити</t>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Пресня</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>6-24</t>
+          <t>18-34</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1257,20 +1261,20 @@
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>788028</v>
+        <v>633319</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>1183147</v>
+        <v>1124794</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>2129032</v>
+        <v>1774262</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>58</v>
+        <v>232</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>34–251</t>
+          <t>26–224</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -1278,168 +1282,164 @@
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P10" s="7" t="n">
-        <v>1213</v>
-      </c>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R10" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S10" s="4" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>в карточке Циан застройщик: Страна.Премиум</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
+          <t>City Park (Сити Парк)</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>ГК МонАрх</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>2019–2021</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Мантулинская, 9к4</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Сити</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>6-24</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>788028</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>1183147</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>2129032</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>34–251</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="n">
+        <v>1213</v>
+      </c>
+      <c r="Q11" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R11" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>SkyView</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>СЗ Киноцентр</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>3 кв. 2024</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Москва, Дружинниковская, 15А</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Пресня</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>20-25</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J11" s="13" t="n">
+      <c r="J12" s="7" t="n">
         <v>850000</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K12" s="8" t="n">
         <v>1200000</v>
       </c>
-      <c r="L11" s="13" t="n">
+      <c r="L12" s="7" t="n">
         <v>2756939</v>
       </c>
-      <c r="M11" s="13" t="n">
+      <c r="M12" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>47–847</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
-        </is>
-      </c>
-      <c r="P11" s="11" t="n"/>
-      <c r="Q11" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R11" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>4 башни на месте Киноцентра</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Полянка/44</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Группа ПСН</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Большая Полянка, 44</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>6-7</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>1135408</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>1214499</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>2109833</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>117–271</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>премиум</t>
         </is>
       </c>
       <c r="P12" s="5" t="n"/>
@@ -1455,34 +1455,34 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>7 корпусов сданы март 2019; cian: застройщик ТЕЛЕКОМ; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>4 башни на месте Киноцентра</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Титул на Серебрянической</t>
+          <t>Полянка/44</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Центр-Инвест</t>
+          <t>Группа ПСН</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1 кв. 2019</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Москва, Серебрянический, 8</t>
+          <t>Москва, Большая Полянка, 44</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -1495,34 +1495,34 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1200000</v>
+        <v>1135408</v>
       </c>
       <c r="K13" s="14" t="n">
-        <v>1229434</v>
+        <v>1214499</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1439394</v>
+        <v>2109833</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>62–276</t>
+          <t>117–271</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P13" s="11" t="n"/>
@@ -1538,238 +1538,242 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>cian years 2021 (первая очередь); карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>в карточке Циан застройщик: ТЕЛЕКОМ; 7 корпусов сданы март 2019; cian: застройщик ТЕЛЕКОМ</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Титул на Серебрянической</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Центр-Инвест</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Серебрянический, 8</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Таганский</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>1229434</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>1439394</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>62–276</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>cian years 2021 (первая очередь); год по объявлениям, в карточке ЖК не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
           <t>Bogenhouse (Богенхаус)</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Lexion Development</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>2020–2021</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Москва, Озерковская, 6</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>5-6</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J15" s="13" t="n">
         <v>985887</v>
       </c>
-      <c r="K14" s="8" t="n">
+      <c r="K15" s="14" t="n">
         <v>1247727</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L15" s="13" t="n">
         <v>2000000</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M15" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>43–355</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="n">
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P15" s="13" t="n">
         <v>43</v>
       </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S14" s="4" t="inlineStr">
-        <is>
-          <t>апартаменты; также ГК Дельта; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Capital Towers (Капитал Тауэрс)</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Capital Group</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>2022–2023</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Краснопресненская, 14Ак3</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>51-72</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>428266</v>
-      </c>
-      <c r="K15" s="14" t="n">
-        <v>1267615</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>110</v>
-      </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>28–693</t>
-        </is>
-      </c>
-      <c r="O15" s="11" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P15" s="11" t="n"/>
       <c r="Q15" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R15" s="11" t="inlineStr"/>
+      <c r="R15" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>в карточке Циан застройщик: Дельта; апартаменты; также ГК Дельта</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
+          <t>Capital Towers (Капитал Тауэрс)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Интеко</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2 кв. 2023</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Москва, Садовническая, 7</t>
+          <t>Москва, Краснопресненская, 14Ак3</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Сити</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>51-72</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1094488</v>
+        <v>428266</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>1268025</v>
+        <v>1267615</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>1927419</v>
+        <v>2500000</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>124–400</t>
+          <t>28–693</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P16" s="5" t="n"/>
@@ -1778,41 +1782,33 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S16" s="4" t="inlineStr">
-        <is>
-          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+      <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Титул на Якиманке</t>
+          <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Центр-Инвест</t>
+          <t>Интеко</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Москва, 2-й Хвостов, 8</t>
+          <t>Москва, Садовническая, 7</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
@@ -1825,39 +1821,37 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J17" s="13" t="n">
-        <v>1281646</v>
+        <v>1094488</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>1281646</v>
+        <v>1268025</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>1281646</v>
+        <v>1927419</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>63–63</t>
+          <t>124–400</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P17" s="13" t="n">
-        <v>18</v>
-      </c>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="n"/>
       <c r="Q17" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -1870,34 +1864,34 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>апартаменты</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом ЦВЕТ32</t>
+          <t>Титул на Якиманке</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Hutton</t>
+          <t>Центр-Инвест</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Москва, Цветной, 32А</t>
+          <t>Москва, 2-й Хвостов, 8</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Мещанский</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
@@ -1910,38 +1904,38 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1120690</v>
+        <v>1281646</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>1363636</v>
+        <v>1281646</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>1972477</v>
+        <v>1281646</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>37–218</t>
+          <t>63–63</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P18" s="7" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
@@ -1953,164 +1947,162 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="S18" s="4" t="inlineStr">
-        <is>
-          <t>введён 28.08.2019; апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
+      <c r="S18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
+          <t>Клубный дом ЦВЕТ32</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Hutton</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Цветной, 32А</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Мещанский</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>1120690</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>1363636</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>1972477</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>37–218</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P19" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q19" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R19" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>введён 28.08.2019; апартаменты</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>A.Residence (А Резиденс)</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>O1 Properties (СЗ А-Резиденс)</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>2024–2025</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>2 кв. 2025</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Москва, Садовническая, 82</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G20" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>5-9</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J19" s="13" t="n">
+      <c r="J20" s="7" t="n">
         <v>664234</v>
       </c>
-      <c r="K19" s="14" t="n">
+      <c r="K20" s="8" t="n">
         <v>1365000</v>
       </c>
-      <c r="L19" s="13" t="n">
+      <c r="L20" s="7" t="n">
         <v>2894000</v>
       </c>
-      <c r="M19" s="13" t="n">
+      <c r="M20" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>47–210</t>
         </is>
       </c>
-      <c r="O19" s="11" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P19" s="13" t="n">
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="Q19" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R19" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>арх. Цимайло Ляшенко и Партнеры; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Edison House (Эдисон Хаус)</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>ИК Приоритет</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Электрический, 10</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Пресня</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>1369863</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>1369863</v>
-      </c>
-      <c r="L20" s="7" t="n">
-        <v>1369863</v>
-      </c>
-      <c r="M20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>58–58</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="n"/>
       <c r="Q20" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -2123,7 +2115,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>cian years 2018; источники: 3 кв. 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>арх. Цимайло Ляшенко и Партнеры</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2132,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>2020–2023</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -2190,7 +2182,7 @@
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P21" s="11" t="n"/>
@@ -2200,13 +2192,9 @@
         </is>
       </c>
       <c r="R21" s="11" t="inlineStr"/>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+      <c r="S21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Собрание клубных домов ORDYNKA (Ордынка)</t>
@@ -2269,7 +2257,7 @@
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P22" s="7" t="n">
@@ -2285,11 +2273,7 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="S22" s="4" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
+      <c r="S22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -2354,7 +2338,7 @@
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P23" s="11" t="n"/>
@@ -2370,7 +2354,7 @@
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>NV/9 ARTKVARTAL; юрлицо Стрелецкая Слобода; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>в карточке Циан застройщик: Стрелецкая Слобода; NV/9 ARTKVARTAL; юрлицо Стрелецкая Слобода</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2421,7 @@
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P24" s="7" t="n">
@@ -2455,7 +2439,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>21 квартира + 4 резиденции + 3 пентхауса; арх. Цимайло Ляшенко; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>21 квартира + 4 резиденции + 3 пентхауса; арх. Цимайло Ляшенко</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2456,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2 кв. 2025</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -2522,7 +2506,7 @@
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P25" s="13" t="n">
@@ -2540,11 +2524,11 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
+          <t>апартаменты</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Софийский</t>
@@ -2557,7 +2541,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>2018–2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2607,7 +2591,7 @@
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P26" s="5" t="n"/>
@@ -2623,7 +2607,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>апартаменты; введён январь 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>апартаменты; введён январь 2019</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2674,7 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P27" s="11" t="n"/>
@@ -2706,34 +2690,34 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>арх. Павел Андреев; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>арх. Павел Андреев</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Резиденция 1864</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Сбербанк Капитал / Midland Development</t>
+          <t>Тессинский, 1</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>INSIGMA</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 36</t>
+          <t>Москва, Тессинский, 1</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Таганский</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
@@ -2746,39 +2730,37 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4-9</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1510567</v>
+        <v>1106420</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>1617861</v>
+        <v>1657000</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>3213511</v>
+        <v>1800000</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>289–1062</t>
+          <t>57–458</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P28" s="7" t="n">
-        <v>68</v>
-      </c>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="n"/>
       <c r="Q28" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -2791,47 +2773,47 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>апартаменты; бывший Царев сад; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
+          <t>в карточке Циан застройщик: Стрелецкая Слобода; ввод август 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Тессинский, 1</t>
+          <t>Lucky (Лаки)</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>INSIGMA</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>2020–2023</t>
+          <t>1 кв. 2023</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Москва, Тессинский, 1</t>
+          <t>Москва, Костикова, 4к1</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Таганский</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Пресня</t>
         </is>
       </c>
       <c r="G29" s="13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>4-9</t>
+          <t>15-21</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -2840,25 +2822,25 @@
         </is>
       </c>
       <c r="J29" s="13" t="n">
-        <v>1106420</v>
+        <v>1296875</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>1657000</v>
+        <v>1680791</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>1800000</v>
+        <v>2352941</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>57–458</t>
+          <t>44–434</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P29" s="11" t="n"/>
@@ -2867,54 +2849,46 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R29" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>ввод август 2023; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+      <c r="R29" s="11" t="inlineStr"/>
+      <c r="S29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Lucky (Лаки)</t>
+          <t>Artisan (Артисан)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Vesper</t>
+          <t>Valartis Group</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Москва, Костикова, 4к1</t>
+          <t>Москва, Арбат, 39</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>Пресня</t>
+          <t>Арбат</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G30" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>15-21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2923,25 +2897,25 @@
         </is>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1296875</v>
+        <v>1769663</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>1680791</v>
+        <v>1769663</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>2352941</v>
+        <v>1769663</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>44–434</t>
+          <t>178–178</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P30" s="5" t="n"/>
@@ -2950,37 +2924,41 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R30" s="5" t="inlineStr"/>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
+          <t>в карточке Циан застройщик: Era One Holding; также указывается Era One Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Artisan (Артисан)</t>
+          <t>Абрикосов</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Valartis Group</t>
+          <t>MR Group</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Москва, Арбат, 39</t>
+          <t>Москва, Потаповский, 6С1</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Арбат</t>
+          <t>Басманный</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -2993,7 +2971,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -3002,28 +2980,30 @@
         </is>
       </c>
       <c r="J31" s="13" t="n">
-        <v>1769663</v>
+        <v>1558355</v>
       </c>
       <c r="K31" s="14" t="n">
-        <v>1769663</v>
+        <v>1785730</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>1769663</v>
+        <v>2094241</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>178–178</t>
+          <t>67–191</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P31" s="11" t="n"/>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P31" s="13" t="n">
+        <v>27</v>
+      </c>
       <c r="Q31" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -3036,34 +3016,34 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>также указывается Era One Holding; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>реставрация усадьбы Абрикосовых</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Абрикосов</t>
+          <t>Клубный дом CULT (Клубный дом Культ)</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>MR Group</t>
+          <t>Gravion</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>2022–2023</t>
+          <t>2025–2026</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Москва, Потаповский, 6С1</t>
+          <t>Москва, Ленинский, 2</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Басманный</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
@@ -3076,39 +3056,37 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>9-16</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1558355</v>
+        <v>1000000</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>1785730</v>
+        <v>1799500</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>2094241</v>
+        <v>3035672</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>67–191</t>
+          <t>26–336</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P32" s="7" t="n">
-        <v>27</v>
-      </c>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="n"/>
       <c r="Q32" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -3121,77 +3099,79 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>реставрация усадьбы Абрикосовых; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>в карточке Циан застройщик: СЗ ВАРШАВА; реконструкция гостиницы Варшава; арх. SPEECH; год по объявлениям, в карточке ЖК не указан</t>
         </is>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Клубный дом CULT (Клубный дом Культ)</t>
+          <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Gravion</t>
+          <t>Гардтекс</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>2025–2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Москва, Ленинский, 2</t>
+          <t>Москва, Саввинская, 13</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G33" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>9-16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J33" s="13" t="n">
-        <v>1000000</v>
+        <v>1869231</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>1799500</v>
+        <v>1884615</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>3035672</v>
+        <v>3751412</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>26–336</t>
+          <t>125–177</t>
         </is>
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P33" s="11" t="n"/>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P33" s="13" t="n">
+        <v>169</v>
+      </c>
       <c r="Q33" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -3204,29 +3184,29 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>реконструкция гостиницы Варшава; арх. SPEECH; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>арх. Цимайло Ляшенко и Партнеры</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
+          <t>Пироговская 14</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Гардтекс</t>
+          <t>Elbert Development</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 13</t>
+          <t>Москва, Малая Пироговская, 12</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -3240,127 +3220,127 @@
         </is>
       </c>
       <c r="G34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>1397059</v>
+      </c>
+      <c r="K34" s="8" t="n">
+        <v>2033898</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>2774566</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>66–254</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>бизнес (Циан)</t>
+        </is>
+      </c>
+      <c r="P34" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q34" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>апартаменты; генподрядчик STRABAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Nine (Клауд Найн)</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Vesper</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Большая Полянка, 9С2</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="n">
-        <v>1869231</v>
-      </c>
-      <c r="K34" s="8" t="n">
-        <v>1884615</v>
-      </c>
-      <c r="L34" s="7" t="n">
-        <v>3751412</v>
-      </c>
-      <c r="M34" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>125–177</t>
-        </is>
-      </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P34" s="7" t="n">
-        <v>169</v>
-      </c>
-      <c r="Q34" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R34" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S34" s="4" t="inlineStr">
-        <is>
-          <t>арх. Цимайло Ляшенко и Партнеры; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Рахманинов</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>КМ Девелопмент</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Малый Кисловский, 3</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>квартиры + апартаменты</t>
         </is>
       </c>
       <c r="J35" s="13" t="n">
-        <v>2000000</v>
+        <v>1800766</v>
       </c>
       <c r="K35" s="14" t="n">
-        <v>2000000</v>
+        <v>2050124</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>2000000</v>
+        <v>2820513</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>145–145</t>
+          <t>195–261</t>
         </is>
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P35" s="13" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q35" s="15" t="inlineStr">
         <is>
@@ -3372,41 +3352,37 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>реконструкция; также АгроСервисСтрой; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
+      <c r="S35" s="10" t="inlineStr"/>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Пироговская 14</t>
+          <t>Симфония набережных (Котельническая 21)</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Elbert Development</t>
+          <t>СК-207</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>2021–2023</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Москва, Малая Пироговская, 12</t>
+          <t>Москва, Котельническая, 21</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Таганский</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G36" s="7" t="n">
@@ -3417,161 +3393,153 @@
           <t>8-9</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>квартиры + апартаменты</t>
         </is>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1397059</v>
+        <v>1174497</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>2033898</v>
+        <v>2067669</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>2774566</v>
+        <v>2070783</v>
       </c>
       <c r="M36" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>149–266</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="n"/>
+      <c r="Q36" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R36" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>4 секции</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Садовые кварталы</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Интеко</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>2014–2022</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Усачева, 15А</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="N36" s="5" t="inlineStr">
-        <is>
-          <t>66–254</t>
-        </is>
-      </c>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P36" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q36" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R36" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S36" s="4" t="inlineStr">
-        <is>
-          <t>апартаменты; генподрядчик STRABAG; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Cloud Nine (Клауд Найн)</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>2021–2022</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Большая Полянка, 9С2</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G37" s="13" t="n">
-        <v>4</v>
-      </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>4-7</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>квартиры + апартаменты</t>
+          <t>5-18</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J37" s="13" t="n">
-        <v>1800766</v>
+        <v>1328904</v>
       </c>
       <c r="K37" s="14" t="n">
-        <v>2050124</v>
+        <v>2111111</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>2820513</v>
+        <v>3718750</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>195–261</t>
+          <t>54–342</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P37" s="13" t="n">
-        <v>45</v>
-      </c>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P37" s="11" t="n"/>
       <c r="Q37" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R37" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
+      <c r="R37" s="11" t="inlineStr"/>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
+          <t>очереди 2012–2023; в выборку попали корпуса 2018+</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Симфония набережных (Котельническая 21)</t>
+          <t>Малая Ордынка 19</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>СК-207</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>2018–2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Москва, Котельническая, 21</t>
+          <t>Москва, Малая Ордынка, 19</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Замоскворечье</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
@@ -3584,7 +3552,7 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -3593,28 +3561,30 @@
         </is>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1174497</v>
+        <v>1848152</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>2067669</v>
+        <v>2246964</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>2070783</v>
+        <v>2246964</v>
       </c>
       <c r="M38" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>149–266</t>
+          <t>100–148</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="n"/>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="n">
+        <v>67</v>
+      </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -3627,74 +3597,74 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>4 секции; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>завершён сентябрь 2019</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Садовые кварталы</t>
+          <t>Дом в Газетном</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Интеко</t>
+          <t>Актив-Центр</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>2018–2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Москва, Усачева, 15А</t>
+          <t>Москва, Газетный, 13с2</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G39" s="13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>5-18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J39" s="13" t="n">
-        <v>1328904</v>
+        <v>1856148</v>
       </c>
       <c r="K39" s="14" t="n">
-        <v>2111111</v>
+        <v>2290538</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>3718750</v>
+        <v>4859444</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>54–342</t>
+          <t>65–664</t>
         </is>
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P39" s="11" t="n"/>
@@ -3703,22 +3673,26 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R39" s="11" t="inlineStr"/>
+      <c r="R39" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>очереди 2012–2023; в выборку попали корпуса 2018+; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>реконструкция</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Малая Ордынка 19</t>
+          <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>ГК АфинаСтрой</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -3728,12 +3702,12 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Москва, Малая Ордынка, 19</t>
+          <t>Москва, Звонарский, 3</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
+          <t>Мещанский</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr">
@@ -3746,38 +3720,38 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>квартиры + апартаменты</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1848152</v>
+        <v>2321429</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>2246964</v>
+        <v>2321429</v>
       </c>
       <c r="L40" s="7" t="n">
-        <v>2246964</v>
+        <v>2321429</v>
       </c>
       <c r="M40" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>100–148</t>
+          <t>168–168</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P40" s="7" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
@@ -3789,41 +3763,37 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="S40" s="4" t="inlineStr">
-        <is>
-          <t>завершён сентябрь 2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
+      <c r="S40" s="4" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Дом в Газетном</t>
+          <t>White Khamovniki (Вайт Хамовники)</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Актив-Центр</t>
+          <t>Hutton</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>2021–2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Москва, Газетный, 13с2</t>
+          <t>Москва, Олсуфьевский, 9к1</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G41" s="13" t="n">
@@ -3831,34 +3801,34 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J41" s="13" t="n">
-        <v>1856148</v>
+        <v>2387268</v>
       </c>
       <c r="K41" s="14" t="n">
-        <v>2290538</v>
+        <v>2387268</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>4859444</v>
+        <v>2657480</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>65–664</t>
+          <t>75–152</t>
         </is>
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>бизнес (Циан)</t>
         </is>
       </c>
       <c r="P41" s="11" t="n"/>
@@ -3867,41 +3837,37 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R41" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
+      <c r="R41" s="11" t="inlineStr"/>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>реконструкция; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
+          <t>в карточке Циан застройщик: Capital Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
+          <t>Золотой, жилой квартал</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>ГК АфинаСтрой</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>4 кв. 2021</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Москва, Звонарский, 3</t>
+          <t>Москва, Софийская, 18</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Мещанский</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F42" s="16" t="inlineStr">
@@ -3910,11 +3876,11 @@
         </is>
       </c>
       <c r="G42" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -3923,29 +3889,29 @@
         </is>
       </c>
       <c r="J42" s="7" t="n">
-        <v>2321429</v>
+        <v>2083333</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>2321429</v>
+        <v>2448000</v>
       </c>
       <c r="L42" s="7" t="n">
-        <v>2321429</v>
+        <v>3200000</v>
       </c>
       <c r="M42" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>168–168</t>
+          <t>87–269</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P42" s="7" t="n">
-        <v>27</v>
+        <v>145</v>
       </c>
       <c r="Q42" s="9" t="inlineStr">
         <is>
@@ -3959,19 +3925,19 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>126 квартир + 19 двухуровневых; арх. SPEECH</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>White Khamovniki (Вайт Хамовники)</t>
+          <t>Magnum (Магнум)</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Hutton</t>
+          <t>Magnum Development</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3981,7 +3947,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Москва, Олсуфьевский, 9к1</t>
+          <t>Москва, Усачева, 9</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -3999,34 +3965,34 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J43" s="13" t="n">
-        <v>2387268</v>
+        <v>1568381</v>
       </c>
       <c r="K43" s="14" t="n">
-        <v>2387268</v>
+        <v>2490110</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>2657480</v>
+        <v>2738095</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>75–152</t>
+          <t>84–215</t>
         </is>
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P43" s="11" t="n"/>
@@ -4035,37 +4001,41 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R43" s="11" t="inlineStr"/>
+      <c r="R43" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>арх. бюро VOSTOK</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Золотой, жилой квартал</t>
+          <t>Дом Бакст на Патриарших</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>Инвестстройком</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>2021–2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 18</t>
+          <t>Москва, Большой Козихинский, 15</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Пресненский</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
@@ -4074,11 +4044,11 @@
         </is>
       </c>
       <c r="G44" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -4087,30 +4057,28 @@
         </is>
       </c>
       <c r="J44" s="7" t="n">
-        <v>2083333</v>
+        <v>2488540</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>2448000</v>
+        <v>2500000</v>
       </c>
       <c r="L44" s="7" t="n">
-        <v>3200000</v>
+        <v>3333333</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
-          <t>87–269</t>
+          <t>152–498</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P44" s="7" t="n">
-        <v>145</v>
-      </c>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="n"/>
       <c r="Q44" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -4123,29 +4091,29 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>126 квартир + 19 двухуровневых; арх. SPEECH; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>в карточке Циан застройщик: Компания Инвестстройком; также указывается АСН-Инвест; арх. Павел Андреев</t>
         </is>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Саввинская 17</t>
+          <t>Villa Grace (Вилла Грейс)</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Level Group</t>
+          <t>ГК Стройтэкс</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 17</t>
+          <t>Москва, Пожарский, 3</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
@@ -4163,7 +4131,7 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -4172,29 +4140,29 @@
         </is>
       </c>
       <c r="J45" s="13" t="n">
-        <v>2337858</v>
+        <v>2635581</v>
       </c>
       <c r="K45" s="14" t="n">
-        <v>2453400</v>
+        <v>2635659</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>2588055</v>
+        <v>2637704</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>65–82</t>
+          <t>128–129</t>
         </is>
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P45" s="13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q45" s="15" t="inlineStr">
         <is>
@@ -4208,39 +4176,39 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>потолки 6.4-7 м; арх. AI Studio; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1">
+          <t>ввод 3 кв. 2020; часть источников 4 кв. 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом Фон Дессин</t>
+          <t>Brodsky (Бродский)</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Москва, Потаповский, 5С4</t>
+          <t>Москва, 1-й Тружеников, 16</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Басманный</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G46" s="7" t="n">
@@ -4248,7 +4216,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14-16</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -4257,65 +4225,55 @@
         </is>
       </c>
       <c r="J46" s="7" t="n">
-        <v>1419298</v>
+        <v>2446043</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>2460514</v>
+        <v>2698752</v>
       </c>
       <c r="L46" s="7" t="n">
-        <v>4191066</v>
+        <v>3339278</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>79–394</t>
+          <t>139–224</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P46" s="7" t="n">
-        <v>36</v>
-      </c>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="n"/>
       <c r="Q46" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R46" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S46" s="4" t="inlineStr">
-        <is>
-          <t>сдан в 2026, продажи от застройщика; реконструкция дома 1915 г.; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
+      <c r="R46" s="5" t="inlineStr"/>
+      <c r="S46" s="4" t="inlineStr"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>Magnum (Магнум)</t>
+          <t>Жизнь на Плющихе</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Magnum Development</t>
+          <t>Донстрой</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>2020–2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Москва, Усачева, 9</t>
+          <t>Москва, Погодинская, 2</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
@@ -4333,37 +4291,39 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J47" s="13" t="n">
-        <v>1568381</v>
+        <v>1253669</v>
       </c>
       <c r="K47" s="14" t="n">
-        <v>2490110</v>
+        <v>3000000</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>2738095</v>
+        <v>3680336</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>84–215</t>
+          <t>95–254</t>
         </is>
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P47" s="11" t="n"/>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P47" s="13" t="n">
+        <v>202</v>
+      </c>
       <c r="Q47" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -4374,41 +4334,37 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>арх. бюро VOSTOK; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
+      <c r="S47" s="10" t="inlineStr"/>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Дом Бакст на Патриарших</t>
+          <t>Carré Blanc (Карре Бланк)</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Инвестстройком</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Москва, Большой Козихинский, 15</t>
+          <t>Москва, Пречистенская, 43</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G48" s="7" t="n">
@@ -4416,34 +4372,34 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J48" s="7" t="n">
-        <v>2488540</v>
+        <v>3000000</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="L48" s="7" t="n">
-        <v>3333333</v>
+        <v>3000000</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N48" s="5" t="inlineStr">
         <is>
-          <t>152–498</t>
+          <t>147–147</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P48" s="5" t="n"/>
@@ -4452,41 +4408,37 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R48" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
+      <c r="R48" s="5" t="inlineStr"/>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>также указывается АСН-Инвест; арх. Павел Андреев; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>в карточке Циан застройщик: Шатер Девелопмент</t>
         </is>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Клубный дом TURGENEV (Тургенев)</t>
+          <t>Дом Лаврушинский</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>НеоСтрой</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1 кв. 2025</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Москва, Костянский, 13</t>
+          <t>Москва, Большой Толмачевский, 5С1</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Красносельский</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F49" s="16" t="inlineStr">
@@ -4495,11 +4447,11 @@
         </is>
       </c>
       <c r="G49" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3-14</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
@@ -4508,65 +4460,55 @@
         </is>
       </c>
       <c r="J49" s="13" t="n">
-        <v>1902180</v>
+        <v>1956522</v>
       </c>
       <c r="K49" s="14" t="n">
-        <v>2523717</v>
+        <v>3118040</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>5642162</v>
+        <v>7453392</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>70–310</t>
+          <t>66–980</t>
         </is>
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P49" s="13" t="n">
-        <v>118</v>
-      </c>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P49" s="11" t="n"/>
       <c r="Q49" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R49" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>5 секций; арх. Squire &amp; Partners; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
+      <c r="R49" s="11" t="inlineStr"/>
+      <c r="S49" s="10" t="inlineStr"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Villa Grace (Вилла Грейс)</t>
+          <t>Хамовники 12</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>ГК Стройтэкс</t>
+          <t>Coldy</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2020–2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Москва, Пожарский, 3</t>
+          <t>Москва, 1-й Тружеников, 12</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -4580,11 +4522,11 @@
         </is>
       </c>
       <c r="G50" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -4593,29 +4535,29 @@
         </is>
       </c>
       <c r="J50" s="7" t="n">
-        <v>2635581</v>
+        <v>2800000</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>2635659</v>
+        <v>3151207</v>
       </c>
       <c r="L50" s="7" t="n">
-        <v>2637704</v>
+        <v>3502415</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N50" s="5" t="inlineStr">
         <is>
-          <t>128–129</t>
+          <t>104–207</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P50" s="7" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
@@ -4629,39 +4571,39 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>ввод 3 кв. 2020; часть источников 4 кв. 2022; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
+          <t>в карточке Циан застройщик: КОЛДИ; арх. Евгений Герасимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Brodsky (Бродский)</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>Vesper</t>
+          <t>Stella di Mosca Hotel &amp; Residences (Стелла ди Моска Хотел энд Резиденсиз)</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Bulgari Hotel &amp; Residences</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Москва, 1-й Тружеников, 16</t>
+          <t>Москва, Большая Никитская, 9</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G51" s="13" t="n">
@@ -4669,7 +4611,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>14-16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -4678,25 +4620,25 @@
         </is>
       </c>
       <c r="J51" s="13" t="n">
-        <v>2446043</v>
+        <v>3240741</v>
       </c>
       <c r="K51" s="14" t="n">
-        <v>2698752</v>
+        <v>3249768</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>3339278</v>
+        <v>5584363</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>139–224</t>
+          <t>107–198</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>делюкс</t>
+          <t>премиум (Циан)</t>
         </is>
       </c>
       <c r="P51" s="11" t="n"/>
@@ -4708,124 +4650,118 @@
       <c r="R51" s="11" t="inlineStr"/>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
+          <t>в карточке Циан застройщик: Intermark Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Жизнь на Плющихе</t>
+          <t>Большая Дмитровка IX</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Донстрой</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
+          <t>1 кв. 2024</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Большая Дмитровка, 9А</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Тверской</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>2372881</v>
+      </c>
+      <c r="K52" s="8" t="n">
+        <v>3250803</v>
+      </c>
+      <c r="L52" s="7" t="n">
+        <v>3813559</v>
+      </c>
+      <c r="M52" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>54–192</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="n"/>
+      <c r="Q52" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="inlineStr"/>
+      <c r="S52" s="4" t="inlineStr">
+        <is>
+          <t>в карточке Циан застройщик: ENGEO Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>Малая Бронная 15</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>ЛидЭстейт</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Погодинская, 2</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="n">
-        <v>1253669</v>
-      </c>
-      <c r="K52" s="8" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="L52" s="7" t="n">
-        <v>3680336</v>
-      </c>
-      <c r="M52" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>95–254</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P52" s="7" t="n">
-        <v>202</v>
-      </c>
-      <c r="Q52" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R52" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S52" s="4" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>Carré Blanc (Карре Бланк)</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Москва, Пречистенская, 43</t>
+          <t>Москва, Малая Бронная, 15Б</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G53" s="13" t="n">
@@ -4833,78 +4769,84 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J53" s="13" t="n">
-        <v>3000000</v>
+        <v>3792852</v>
       </c>
       <c r="K53" s="14" t="n">
-        <v>3000000</v>
+        <v>3795620</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>3000000</v>
+        <v>6027397</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>147–147</t>
+          <t>137–219</t>
         </is>
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P53" s="11" t="n"/>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P53" s="13" t="n">
+        <v>23</v>
+      </c>
       <c r="Q53" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R53" s="11" t="inlineStr"/>
+      <c r="R53" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>в карточке Циан застройщик: R4S GROUP; акт ввода 31.07.2019</t>
         </is>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Саввинская 27</t>
+          <t>Barkli Gallery (Баркли Галлери)</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Level Group</t>
+          <t>Barkli</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 27</t>
+          <t>Москва, Ордынский, 4А</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G54" s="7" t="n">
@@ -4912,797 +4854,64 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J54" s="7" t="n">
-        <v>3060713</v>
+        <v>4694118</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>3095494</v>
+        <v>4694118</v>
       </c>
       <c r="L54" s="7" t="n">
-        <v>3130275</v>
+        <v>4694118</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N54" s="5" t="inlineStr">
         <is>
-          <t>81–131</t>
+          <t>85–85</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P54" s="7" t="n">
-        <v>60</v>
-      </c>
+          <t>премиум (Циан)</t>
+        </is>
+      </c>
+      <c r="P54" s="5" t="n"/>
       <c r="Q54" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="R54" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
+      <c r="R54" s="5" t="inlineStr"/>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>апартаменты; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>Дом Лаврушинский</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>Sminex</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>2024–2025</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Большой Толмачевский, 5С1</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G55" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H55" s="11" t="inlineStr">
-        <is>
-          <t>3-14</t>
-        </is>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J55" s="13" t="n">
-        <v>1956522</v>
-      </c>
-      <c r="K55" s="14" t="n">
-        <v>3118040</v>
-      </c>
-      <c r="L55" s="13" t="n">
-        <v>7453392</v>
-      </c>
-      <c r="M55" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="N55" s="11" t="inlineStr">
-        <is>
-          <t>66–980</t>
-        </is>
-      </c>
-      <c r="O55" s="11" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R55" s="11" t="inlineStr"/>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Хамовники 12</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Coldy</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>Москва, 1-й Тружеников, 12</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="K56" s="8" t="n">
-        <v>3151207</v>
-      </c>
-      <c r="L56" s="7" t="n">
-        <v>3502415</v>
-      </c>
-      <c r="M56" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N56" s="5" t="inlineStr">
-        <is>
-          <t>104–207</t>
-        </is>
-      </c>
-      <c r="O56" s="5" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="P56" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q56" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R56" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S56" s="4" t="inlineStr">
-        <is>
-          <t>арх. Евгений Герасимов; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>Дом на Хлебном</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>Capital Group</t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Хлебный, 19</t>
-        </is>
-      </c>
-      <c r="E57" s="11" t="inlineStr">
-        <is>
-          <t>Арбат</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G57" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" s="11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="inlineStr">
-        <is>
-          <t>квартиры + апартаменты</t>
-        </is>
-      </c>
-      <c r="J57" s="13" t="n">
-        <v>2133333</v>
-      </c>
-      <c r="K57" s="14" t="n">
-        <v>3194462</v>
-      </c>
-      <c r="L57" s="13" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="M57" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="N57" s="11" t="inlineStr">
-        <is>
-          <t>95–342</t>
-        </is>
-      </c>
-      <c r="O57" s="11" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P57" s="11" t="n"/>
-      <c r="Q57" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R57" s="11" t="inlineStr"/>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Stoleshnikov 7 (Столешников 7)</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Столешников, 7С1</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>Тверской</t>
-        </is>
-      </c>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="n">
-        <v>2977612</v>
-      </c>
-      <c r="K58" s="8" t="n">
-        <v>3229296</v>
-      </c>
-      <c r="L58" s="7" t="n">
-        <v>3242801</v>
-      </c>
-      <c r="M58" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N58" s="5" t="inlineStr">
-        <is>
-          <t>134–158</t>
-        </is>
-      </c>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P58" s="5" t="n"/>
-      <c r="Q58" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R58" s="5" t="inlineStr"/>
-      <c r="S58" s="4" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>Stella di Mosca Hotel &amp; Residences (Стелла ди Моска Хотел энд Резиденсиз)</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>Bulgari Hotel &amp; Residences</t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="inlineStr">
-        <is>
-          <t>2023–2024</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Большая Никитская, 9</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G59" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" s="11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I59" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>3240741</v>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v>3249768</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>5584363</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="N59" s="11" t="inlineStr">
-        <is>
-          <t>107–198</t>
-        </is>
-      </c>
-      <c r="O59" s="11" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P59" s="11" t="n"/>
-      <c r="Q59" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R59" s="11" t="inlineStr"/>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Большая Дмитровка IX</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>Vesper</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>2021–2025</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Большая Дмитровка, 9А</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>Тверской</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>5-6</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>апартаменты</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="n">
-        <v>2372881</v>
-      </c>
-      <c r="K60" s="8" t="n">
-        <v>3250803</v>
-      </c>
-      <c r="L60" s="7" t="n">
-        <v>3813559</v>
-      </c>
-      <c r="M60" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="N60" s="5" t="inlineStr">
-        <is>
-          <t>54–192</t>
-        </is>
-      </c>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P60" s="5" t="n"/>
-      <c r="Q60" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R60" s="5" t="inlineStr"/>
-      <c r="S60" s="4" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>Armani/Casa Moscow Residences (Армани/Каса Москоу Резиденсес)</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>Vos'hod</t>
-        </is>
-      </c>
-      <c r="C61" s="11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Старомонетный, 19/11</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G61" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H61" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J61" s="13" t="n">
-        <v>2750000</v>
-      </c>
-      <c r="K61" s="14" t="n">
-        <v>3630000</v>
-      </c>
-      <c r="L61" s="13" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="M61" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="N61" s="11" t="inlineStr">
-        <is>
-          <t>176–421</t>
-        </is>
-      </c>
-      <c r="O61" s="11" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P61" s="11" t="n"/>
-      <c r="Q61" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R61" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>введён июль 2024; арх. John McAslan + Partners; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Малая Бронная 15</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>ЛидЭстейт</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Малая Бронная, 15Б</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="n">
-        <v>3792852</v>
-      </c>
-      <c r="K62" s="8" t="n">
-        <v>3795620</v>
-      </c>
-      <c r="L62" s="7" t="n">
-        <v>6027397</v>
-      </c>
-      <c r="M62" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="N62" s="5" t="inlineStr">
-        <is>
-          <t>137–219</t>
-        </is>
-      </c>
-      <c r="O62" s="5" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P62" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q62" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R62" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="S62" s="4" t="inlineStr">
-        <is>
-          <t>акт ввода 31.07.2019; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>Barkli Gallery (Баркли Галлери)</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>Barkli</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="inlineStr">
-        <is>
-          <t>Москва, Ордынский, 4А</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>Якиманка</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G63" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" s="11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>4694118</v>
-      </c>
-      <c r="K63" s="14" t="n">
-        <v>4694118</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>4694118</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" s="11" t="inlineStr">
-        <is>
-          <t>85–85</t>
-        </is>
-      </c>
-      <c r="O63" s="11" t="inlineStr">
-        <is>
-          <t>делюкс</t>
-        </is>
-      </c>
-      <c r="P63" s="11" t="n"/>
-      <c r="Q63" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="R63" s="11" t="inlineStr"/>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="18" t="inlineStr">
+          <t>в карточке Циан застройщик: Корпорация Баркли</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>Источник: живая выдача Циан 2026-09-07 (api.cian.ru, инструмент tools/cian/cian.js), вторичка с годом дома 2018+ и новостройки по 10 районам ЦАО. Цены — ₽/м² по активным объявлениям. Застройщик и класс — по открытым данным (ручная разметка docs/premium-cao/manual.json).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S63"/>
+  <autoFilter ref="A3:S54"/>
   <mergeCells count="3">
-    <mergeCell ref="A65:S65"/>
+    <mergeCell ref="A56:S56"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
   </mergeCells>
-  <conditionalFormatting sqref="K4:K63">
+  <conditionalFormatting sqref="K4:K54">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5726,100 +4935,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R50" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R52" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R54" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R56" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q58" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q59" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R61" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R62" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R50" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R53" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId88"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -5841,7 +5033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6113,27 +5305,27 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Репаблик</t>
+          <t>ЖК «Начало»</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Страна.Премиум</t>
+          <t>ДОНСТРОЙ</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>3 кв. 2026</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Москва, Пресненский Вал, 27к5</t>
+          <t>Москва, улица Сергея Макеева, 7</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Ул. 1905 года</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -6142,11 +5334,11 @@
         </is>
       </c>
       <c r="G6" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>18-34</t>
+          <t>11-48</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -6155,67 +5347,75 @@
         </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>633319</v>
+        <v>925200</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>1124794</v>
+        <v>1172000</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>1774262</v>
+        <v>1884000</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>232</v>
-      </c>
-      <c r="N6" s="5" t="inlineStr"/>
+        <v>231</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>знак вопроса; срок по карточке Циан: 2029–2030</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>ЖК «Начало»</t>
+          <t>Оне</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>ДОНСТРОЙ</t>
+          <t>MR Group</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2 кв. 2030</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Москва, улица Сергея Макеева, 7</t>
+          <t>Москва, 1-й Красногвардейский, 13</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Ул. 1905 года</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Пресня</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Сити</t>
         </is>
       </c>
       <c r="G7" s="13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>11-48</t>
+          <t>90-95</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
@@ -6224,16 +5424,16 @@
         </is>
       </c>
       <c r="J7" s="13" t="n">
-        <v>925200</v>
+        <v>928571</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>1172000</v>
+        <v>1207700</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1884000</v>
+        <v>1602900</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>231</v>
+        <v>69</v>
       </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
@@ -6245,32 +5445,36 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P7" s="10" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="Q7" s="10" t="inlineStr">
         <is>
-          <t>знак вопроса</t>
+          <t>One Tower, 1-й Красногвардейский пр.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Оне</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr"/>
+          <t>АУРУС Резиденции</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Страна Девелопмент</t>
+        </is>
+      </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>2027–2031</t>
+          <t>4 кв. 2031</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Москва, 1-й Красногвардейский, 13</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -6283,12 +5487,10 @@
           <t>Сити</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>90-95</t>
+          <t>82-101</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -6297,18 +5499,22 @@
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>928571</v>
+        <v>892920</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>1207700</v>
+        <v>1237935</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>1602900</v>
+        <v>1880116</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="N8" s="5" t="inlineStr"/>
+        <v>203</v>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="O8" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -6321,45 +5527,47 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>One Tower, 1-й Красногвардейский пр.; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
+          <t>Aurus Residences / Страна.Сити, 2-й Красногвардейский пр.; продажи открыты, сдача 2031; в карточке Циан застройщик: Страна.Премиум</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>АУРУС Резиденции</t>
+          <t>ЖК «Монблан»</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Страна Девелопмент</t>
+          <t>Галс-Девелопмент</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>1 кв. 2028</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Москва, Шлюзовая набережная</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Сити</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="n"/>
+          <t>Павелецкая</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>6</v>
+      </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>82-101</t>
+          <t>7-27</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -6368,63 +5576,63 @@
         </is>
       </c>
       <c r="J9" s="13" t="n">
-        <v>892920</v>
+        <v>942551</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>1237935</v>
+        <v>1245333</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1880116</v>
+        <v>3159585</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>203</v>
-      </c>
-      <c r="N9" s="11" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr">
-        <is>
-          <t>Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q9" s="10" t="inlineStr">
-        <is>
-          <t>Aurus Residences / Страна.Сити, 2-й Красногвардейский пр.; продажи открыты, сдача 2031; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>ЖК «Монблан»</t>
+          <t>ЖК «Квартал Life Time»</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Галс-Девелопмент</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>1 кв. 2028</t>
+          <t>2 кв. 2026</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Москва, Шлюзовая набережная</t>
+          <t>Москва, улица Сергея Макеева</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Павелецкая</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>1905 года</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Пресня</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
@@ -6432,7 +5640,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>7-27</t>
+          <t>9-23</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -6441,16 +5649,16 @@
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>942551</v>
+        <v>1019417</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>1245333</v>
+        <v>1585417</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>3159585</v>
+        <v>2290000</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>72</v>
+        <v>232</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
@@ -6467,45 +5675,49 @@
           <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>по Циан дом сдан; срок по карточке Циан: 3 кв. 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>ЖК «Квартал Life Time»</t>
+          <t>ЖК «Коллекция Лужники»</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>Absolute Premium</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>2 кв. 2026</t>
+          <t>4 кв. 2027</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Москва, улица Сергея Макеева</t>
+          <t>Москва, Лужнецкая набережная</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>1905 года</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Пресня</t>
+          <t>Воробьёвы горы</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G11" s="13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>9-23</t>
+          <t>12-18</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -6514,16 +5726,16 @@
         </is>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1019417</v>
+        <v>1218182</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>1585417</v>
+        <v>1591320</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>2290000</v>
+        <v>4200000</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>232</v>
+        <v>59</v>
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
@@ -6542,47 +5754,47 @@
       </c>
       <c r="Q11" s="10" t="inlineStr">
         <is>
-          <t>по Циан дом сдан</t>
+          <t>пометка «Изучить»; по другим источникам застройщик: Абсолют Недвижимость (Absolute Premium)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>ЖК «Коллекция Лужники»</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Absolute Premium</t>
+          <t>Тессинский V</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Element Development</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>4 кв. 2027</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Москва, Лужнецкая набережная</t>
+          <t>Москва, Тессинский, 5С11</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Воробьёвы горы</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Таганский</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>12-18</t>
+          <t>5-12</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -6591,16 +5803,16 @@
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1218182</v>
+        <v>1538500</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>1591320</v>
+        <v>1610325</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>4200000</v>
+        <v>1750150</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
@@ -6612,41 +5824,41 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>пометка «Изучить»; по другим источникам застройщик: Абсолют Недвижимость (Absolute Premium)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
+          <t>старт продаж апрель 2026, котлован; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Тессинский V</t>
+          <t>Резиденция 1864</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Element Development</t>
+          <t>Сбербанк Капитал / Midland Development</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>3 кв. 2027</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Москва, Тессинский, 5С11</t>
+          <t>Москва, Софийская, 36</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -6655,31 +5867,35 @@
         </is>
       </c>
       <c r="G13" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>5-12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1538500</v>
+        <v>1510567</v>
       </c>
       <c r="K13" s="14" t="n">
-        <v>1610325</v>
+        <v>1617861</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1750150</v>
+        <v>3213511</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>44</v>
-      </c>
-      <c r="N13" s="11" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -6692,11 +5908,11 @@
       </c>
       <c r="Q13" s="10" t="inlineStr">
         <is>
-          <t>старт продаж апрель 2026, котлован; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
+          <t>апартаменты; бывший Царев сад</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>ЖК «Элитный квартал Тишинский бульвар»</t>
@@ -6769,7 +5985,7 @@
       </c>
       <c r="Q14" s="4" t="inlineStr"/>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>ЖК «Дом Франка»</t>
@@ -6840,9 +6056,13 @@
           <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="Q15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>срок по карточке Циан: 4 кв. 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ЖК «Татарская 35»</t>
@@ -6975,7 +6195,11 @@
       <c r="M17" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="N17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="O17" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -6992,7 +6216,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ЖК «Дом Соболева»</t>
@@ -7065,7 +6289,7 @@
       </c>
       <c r="Q18" s="4" t="inlineStr"/>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>ЖК «Климашкина 7/11»</t>
@@ -7138,7 +6362,7 @@
       </c>
       <c r="Q19" s="10" t="inlineStr"/>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Форум»</t>
@@ -7211,7 +6435,7 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>по Циан дом сдан</t>
+          <t>по Циан дом сдан; срок по карточке Циан: 4 кв. 2027</t>
         </is>
       </c>
     </row>
@@ -7348,7 +6572,11 @@
       <c r="M22" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="N22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="O22" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -7445,40 +6673,40 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>ЖК «PHANTOM»</t>
+          <t>Саввинская 17</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Sense</t>
+          <t>Level Group</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>3 кв. 2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Москва, Малая Сухаревская площадь</t>
+          <t>Москва, Саввинская, 17</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Сухаревская</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G24" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -7487,16 +6715,16 @@
         </is>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1650000</v>
+        <v>2337858</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>2480000</v>
+        <v>2453400</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>3580000</v>
+        <v>2588055</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
@@ -7508,17 +6736,21 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>потолки 6.4-7 м; арх. AI Studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Фамильный дом Люче</t>
+          <t>ЖК «Исторический дом «Чистые Пруды»</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -7528,17 +6760,17 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1 кв. 2026</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Москва, Крестовоздвиженский, 4</t>
+          <t>Москва, Потаповский переулок, 5с4</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Арбат</t>
+          <t>Чистые пруды</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -7551,7 +6783,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>6-7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -7560,131 +6792,135 @@
         </is>
       </c>
       <c r="J25" s="13" t="n">
-        <v>2400000</v>
+        <v>1419298</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>2650000</v>
+        <v>2460514</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>6000000</v>
+        <v>4191066</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>26</v>
-      </c>
-      <c r="N25" s="11" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="O25" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P25" s="11" t="inlineStr">
-        <is>
-          <t>Циан 2026-09-07</t>
+      <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="Q25" s="10" t="inlineStr">
         <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>по Циан дом сдан; на Циан ЖК называется «Дом на Чистых прудах „Фон Дессин“», Потаповский 5</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Кло 17</t>
+          <t>ЖК «PHANTOM»</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>Sense</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
+          <t>3 кв. 2027</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Малая Сухаревская площадь</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Сухаревская</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>7-9</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>2480000</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>3580000</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом TURGENEV (Тургенев)</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>НеоСтрой</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Староваганьковский, 17С4</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Арбат</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="n">
-        <v>2300000</v>
-      </c>
-      <c r="K26" s="8" t="n">
-        <v>2650000</v>
-      </c>
-      <c r="L26" s="7" t="n">
-        <v>3050000</v>
-      </c>
-      <c r="M26" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="inlineStr">
-        <is>
-          <t>Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>ТИТУЛ Империал</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Центр-Инвест</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Москва, Большой Николоворобинский, 12/11</t>
+          <t>Москва, Костянский, 13</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Красносельский</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -7697,7 +6933,7 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
@@ -7706,18 +6942,22 @@
         </is>
       </c>
       <c r="J27" s="13" t="n">
-        <v>2425281</v>
+        <v>1902180</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>2705884</v>
+        <v>2523717</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>2914068</v>
+        <v>5642162</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="N27" s="11" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="O27" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -7730,34 +6970,34 @@
       </c>
       <c r="Q27" s="10" t="inlineStr">
         <is>
-          <t>12 лотов 83-131 м², не более 3 квартир на этаже; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
+          <t>5 секций; арх. Squire &amp; Partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом DUO (Дуо)</t>
+          <t>Фамильный дом Люче</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Hutton</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 34С3</t>
+          <t>Москва, Крестовоздвиженский, 4</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Арбат</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
@@ -7770,7 +7010,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -7779,18 +7019,22 @@
         </is>
       </c>
       <c r="J28" s="7" t="n">
-        <v>2408900</v>
+        <v>2400000</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>2772243</v>
+        <v>2650000</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>4300199</v>
+        <v>6000000</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="N28" s="5" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="O28" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -7803,39 +7047,39 @@
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>Софийская наб., усадьба Кокорева; в июне 2026 fee-девелопер Hutton вышел из проекта, площадка у V2 Group (Коммерсантъ); инвестор V2Group; юрлицо СЗ Суплекс Технолоджис; cian: 2028; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Дом Спорта</t>
+          <t>Кло 17</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Москва, Дружинниковская, 18</t>
+          <t>Москва, Староваганьковский, 17С4</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Пресня</t>
+          <t>Арбат</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G29" s="13" t="n">
@@ -7843,7 +7087,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -7852,18 +7096,22 @@
         </is>
       </c>
       <c r="J29" s="13" t="n">
-        <v>2281650</v>
+        <v>2300000</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>2787488</v>
+        <v>2650000</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>3174937</v>
+        <v>3050000</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="N29" s="11" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="O29" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -7876,34 +7124,34 @@
       </c>
       <c r="Q29" s="10" t="inlineStr">
         <is>
-          <t>старт продаж 2026, стройка начата (Ведомости); карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+          <t>карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>«Ильинка 3/8»</t>
+          <t>ТИТУЛ Империал</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>Центр-Инвест</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>1 кв. 2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Москва, улица Ильинка</t>
+          <t>Москва, Большой Николоворобинский, 12/11</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Площадь Революции</t>
+          <t>Таганский</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
@@ -7912,29 +7160,29 @@
         </is>
       </c>
       <c r="G30" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J30" s="7" t="n">
-        <v>2286753</v>
+        <v>2425281</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>2824061</v>
+        <v>2705884</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>3973321</v>
+        <v>2914068</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
@@ -7946,41 +7194,41 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>по Циан дом сдан</t>
+          <t>12 лотов 83-131 м², не более 3 квартир на этаже; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>ЖК «Красный Октябрь»</t>
+          <t>Клубный дом DUO (Дуо)</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Гута Девелопмент</t>
+          <t>Hutton</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>3 кв. 2026</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Москва, Берсеневская набережная</t>
+          <t>Москва, Софийская, 34С3</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Кропоткинская</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -7993,7 +7241,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -8002,135 +7250,139 @@
         </is>
       </c>
       <c r="J31" s="13" t="n">
-        <v>2990000</v>
+        <v>2408900</v>
       </c>
       <c r="K31" s="14" t="n">
-        <v>2990000</v>
+        <v>2772243</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>2990000</v>
+        <v>4300199</v>
       </c>
       <c r="M31" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="O31" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P31" s="11" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>Софийская наб., усадьба Кокорева; в июне 2026 fee-девелопер Hutton вышел из проекта, площадка у V2 Group (Коммерсантъ); инвестор V2Group; юрлицо СЗ Суплекс Технолоджис; cian: 2028; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Дом Спорта</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Дружинниковская, 18</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Пресня</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="11" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>2281650</v>
+      </c>
+      <c r="K32" s="8" t="n">
+        <v>2787488</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>3174937</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O31" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P31" s="10" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q31" s="10" t="inlineStr">
-        <is>
-          <t>пометка «Изучить»; по другим источникам застройщик: Гута-Девелопмент</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>ЖК «Николь»</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>MR Group</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>2027–2028</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Никольская улица, 8/1с1</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Площадь Революции</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>6-7</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>квартиры</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="n">
-        <v>2325000</v>
-      </c>
-      <c r="K32" s="8" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="L32" s="7" t="n">
-        <v>4950000</v>
-      </c>
-      <c r="M32" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>бетон</t>
-        </is>
-      </c>
       <c r="O32" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>старт продаж 2026, стройка начата (Ведомости); карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>MONO Kami</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Tekta Group (ранее ПИК / MONO)</t>
+          <t>«Ильинка 3/8»</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>4 кв. 2028</t>
+          <t>1 кв. 2026</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Пыжевский переулок</t>
+          <t>Москва, улица Ильинка</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Якиманка</t>
+          <t>Площадь Революции</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
@@ -8139,29 +7391,29 @@
         </is>
       </c>
       <c r="G33" s="13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>9-14</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J33" s="13" t="n">
-        <v>2050200</v>
+        <v>2286753</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>3001950</v>
+        <v>2824061</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>3322400</v>
+        <v>3973321</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
@@ -8180,34 +7432,34 @@
       </c>
       <c r="Q33" s="10" t="inlineStr">
         <is>
-          <t>пометка «Посмотреть ?»; по другим источникам застройщик: ТЕКТА Групп; по данным Движение.ру (май 2026) проект полностью у Tekta Group, ПИК вышел</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
+          <t>по Циан дом сдан; срок по карточке Циан: 3 кв. 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>ЖК «Никитский-6»</t>
+          <t>ЖК «Красный Октябрь»</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Третий Рим</t>
+          <t>Гута Девелопмент</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>4 кв. 2026</t>
+          <t>3 кв. 2026</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Москва, Никитский бульвар, 6/20</t>
+          <t>Москва, Берсеневская набережная</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Арбат</t>
+          <t>Кропоткинская</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
@@ -8220,7 +7472,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -8229,16 +7481,16 @@
         </is>
       </c>
       <c r="J34" s="7" t="n">
-        <v>2467500</v>
+        <v>2990000</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>3037250</v>
+        <v>2990000</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>4680000</v>
+        <v>2990000</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
@@ -8255,45 +7507,49 @@
           <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="inlineStr"/>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>пометка «Изучить»; по другим источникам застройщик: Гута-Девелопмент; в карточке Циан застройщик: ГУТА-ДЕВЕЛОПМЕНТ</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>ЖК «Фрунзенская набережная»</t>
+          <t>ЖК «Николь»</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>MR Group</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>3 кв. 2027</t>
+          <t>2027–2028</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Москва, Фрунзенская набережная, 30</t>
+          <t>Москва, Никольская улица, 8/1с1</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Фрунзенская</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Площадь Революции</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G35" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>10-13</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -8302,16 +7558,16 @@
         </is>
       </c>
       <c r="J35" s="13" t="n">
-        <v>2180740</v>
+        <v>2325000</v>
       </c>
       <c r="K35" s="14" t="n">
-        <v>3083973</v>
+        <v>3000000</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>6898288</v>
+        <v>4950000</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
@@ -8333,27 +7589,27 @@
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Kuznetsky Most 12 by Lalique (Кузнецкий Мост 12)</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>KR Properties</t>
+          <t>MONO Kami</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Tekta Group (ранее ПИК / MONO)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4 кв. 2028</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Москва, Кузнецкий Мост, 12/3С1</t>
+          <t>Пыжевский переулок</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Мещанский</t>
+          <t>Якиманка</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
@@ -8362,76 +7618,80 @@
         </is>
       </c>
       <c r="G36" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>6-7</t>
+          <t>9-14</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>апартаменты</t>
+          <t>квартиры</t>
         </is>
       </c>
       <c r="J36" s="7" t="n">
-        <v>2985075</v>
+        <v>2050200</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>3092773</v>
+        <v>3001950</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>3200472</v>
+        <v>3322400</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N36" s="5" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
       <c r="O36" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P36" s="5" t="inlineStr">
-        <is>
-          <t>Циан 2026-09-07</t>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="Q36" s="4" t="inlineStr">
         <is>
-          <t>реконструкция; коллаборация с Lalique; карточка ЖК на Циан не найдена, год по объявлениям</t>
+          <t>пометка «Посмотреть ?»; по другим источникам застройщик: ТЕКТА Групп; в карточке Циан застройщик: ТЕКТА ГРУПП; срок по карточке Циан: 2 кв. 2029; по данным Движение.ру (май 2026) проект полностью у Tekta Group, ПИК вышел</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>ДОМ XXII</t>
+          <t>ЖК «Никитский-6»</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Донстрой</t>
+          <t>Третий Рим</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4 кв. 2026</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Москва, Новодевичий, 6С2</t>
+          <t>Москва, Никитский бульвар, 6/20</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Арбат</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G37" s="13" t="n">
@@ -8439,7 +7699,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>11-12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -8448,71 +7708,75 @@
         </is>
       </c>
       <c r="J37" s="13" t="n">
-        <v>2479101</v>
+        <v>2467500</v>
       </c>
       <c r="K37" s="14" t="n">
-        <v>3150000</v>
+        <v>3037250</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>4000000</v>
+        <v>4680000</v>
       </c>
       <c r="M37" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="O37" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P37" s="10" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
+          <t>в карточке Циан застройщик: СЗ Третий Рим (Москва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ЖК «Фрунзенская набережная»</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>3 кв. 2027</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Фрунзенская набережная, 30</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Фрунзенская</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="N37" s="11" t="inlineStr"/>
-      <c r="O37" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P37" s="11" t="inlineStr">
-        <is>
-          <t>Циан 2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q37" s="10" t="inlineStr">
-        <is>
-          <t>арх. Сергей Киселев и Партнеры; карточка ЖК на Циан не найдена, год по объявлениям</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>ЖК «Исторический дом «Чистые Пруды»</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Sminex</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>1 кв. 2026</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>Москва, Потаповский переулок, 5с4</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Чистые пруды</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10-13</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -8521,26 +7785,30 @@
         </is>
       </c>
       <c r="J38" s="7" t="n">
-        <v>2284917</v>
+        <v>2180740</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>3412650</v>
+        <v>3083973</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>4540383</v>
+        <v>6898288</v>
       </c>
       <c r="M38" s="7" t="n">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr"/>
-      <c r="P38" s="5" t="inlineStr">
-        <is>
-          <t>таблица заказчика</t>
+      <c r="O38" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
       <c r="Q38" s="4" t="inlineStr"/>
@@ -8548,32 +7816,32 @@
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>ЖК «Узоры»</t>
+          <t>Kuznetsky Most 12 by Lalique (Кузнецкий Мост 12)</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>KR Properties</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>4 кв. 2028</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Москва, 2-й Вражский переулок, 8с2</t>
+          <t>Москва, Кузнецкий Мост, 12/3С1</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Киевская</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Мещанский</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G39" s="13" t="n">
@@ -8581,25 +7849,25 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>квартиры</t>
+          <t>апартаменты</t>
         </is>
       </c>
       <c r="J39" s="13" t="n">
-        <v>3177900</v>
+        <v>2985075</v>
       </c>
       <c r="K39" s="14" t="n">
-        <v>3488415</v>
+        <v>3092773</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>4559310</v>
+        <v>3200472</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
@@ -8611,46 +7879,46 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P39" s="10" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
+      <c r="P39" s="11" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="Q39" s="10" t="inlineStr">
         <is>
-          <t>пометка «Изучить! +»; по другим источникам застройщик: ГК Основа; по РБК Компании: старт продаж 2026, стройка начата (котлован)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1">
+          <t>реконструкция; коллаборация с Lalique; карточка ЖК на Циан не найдена, год по объявлениям</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Annabels</t>
+          <t>Саввинская 27</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>СЗ ЮНИКС</t>
+          <t>Level Group</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>1 кв. 2026</t>
+          <t>2 кв. 2027</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Москва, Курсовой переулок</t>
+          <t>Москва, Саввинская, 27</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Кропоткинская</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G40" s="7" t="n">
@@ -8658,7 +7926,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -8667,16 +7935,16 @@
         </is>
       </c>
       <c r="J40" s="7" t="n">
-        <v>2900000</v>
+        <v>3060713</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>3500141</v>
+        <v>3095494</v>
       </c>
       <c r="L40" s="7" t="n">
-        <v>5700000</v>
+        <v>3130275</v>
       </c>
       <c r="M40" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
@@ -8688,54 +7956,54 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
+      <c r="P40" s="5" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t>по Циан дом сдан; по другим источникам застройщик: Palladio Group</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
+          <t>апартаменты</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>ЖК «Клубный дом Левенсон»</t>
+          <t>ДОМ XXII</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Веспер</t>
+          <t>Донстрой</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>3 кв. 2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Москва, Трёхпрудный переулок</t>
+          <t>Москва, Новодевичий, 6С2</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Маяковская</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G41" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>11-12</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -8744,16 +8012,16 @@
         </is>
       </c>
       <c r="J41" s="13" t="n">
-        <v>2800000</v>
+        <v>2479101</v>
       </c>
       <c r="K41" s="14" t="n">
-        <v>3560820</v>
+        <v>3150000</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>4189200</v>
+        <v>4000000</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
@@ -8765,46 +8033,46 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P41" s="10" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
+      <c r="P41" s="11" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="Q41" s="10" t="inlineStr">
         <is>
-          <t>пометка «Посмотреть +»</t>
+          <t>арх. Сергей Киселев и Партнеры; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>ЖК «Погодинская»</t>
+          <t>Stoleshnikov 7 (Столешников 7)</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Веспер</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>4 кв. 2028</t>
+          <t>3 кв. 2026</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Москва, Погодинская улица</t>
+          <t>Москва, Столешников, 7С1</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Спортивная</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Тверской</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G42" s="7" t="n">
@@ -8812,7 +8080,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -8821,16 +8089,16 @@
         </is>
       </c>
       <c r="J42" s="7" t="n">
-        <v>3003600</v>
+        <v>2977612</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>3977800</v>
+        <v>3229296</v>
       </c>
       <c r="L42" s="7" t="n">
-        <v>4855100</v>
+        <v>3242801</v>
       </c>
       <c r="M42" s="7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
@@ -8842,46 +8110,46 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P42" s="4" t="inlineStr">
-        <is>
-          <t>таблица заказчика + Циан 2026-09-07</t>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
         </is>
       </c>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t>по другим источникам застройщик: Vesper; РНС получено в ноябре 2025, закрытый старт продаж апрель–май 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
+          <t>в карточке Циан застройщик: ВМС Девелопмент</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>ЖК «Клубный дом Обыденский №1»</t>
+          <t>ЖК «Узоры»</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>1 кв. 2026</t>
+          <t>4 кв. 2028</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Москва, 3-й Обыденский переулок, 1</t>
+          <t>Москва, 2-й Вражский переулок, 8с2</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Кропоткинская</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>Садовое кольцо</t>
+          <t>Киевская</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="G43" s="13" t="n">
@@ -8889,7 +8157,7 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9-10</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -8898,16 +8166,16 @@
         </is>
       </c>
       <c r="J43" s="13" t="n">
-        <v>2818178</v>
+        <v>3177900</v>
       </c>
       <c r="K43" s="14" t="n">
-        <v>4239914</v>
+        <v>3488415</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>9287270</v>
+        <v>4559310</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N43" s="11" t="inlineStr">
         <is>
@@ -8926,39 +8194,39 @@
       </c>
       <c r="Q43" s="10" t="inlineStr">
         <is>
-          <t>по Циан дом сдан</t>
+          <t>пометка «Изучить! +»; по другим источникам застройщик: ГК Основа; по РБК Компании: старт продаж 2026, стройка начата (котлован)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Лё Дом</t>
+          <t>Annabels</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Группа ЛСР</t>
+          <t>СЗ ЮНИКС</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1 кв. 2026</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Москва, Соймоновский, 3</t>
+          <t>Москва, Курсовой переулок</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Кропоткинская</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="G44" s="7" t="n">
@@ -8966,135 +8234,524 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>апартаменты</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="K44" s="8" t="n">
+        <v>3500141</v>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="O44" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>по Циан дом сдан; по другим источникам застройщик: Palladio Group; срок по карточке Циан: 4 кв. 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>ЖК «Клубный дом Левенсон»</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Веспер</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>3 кв. 2027</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Трёхпрудный переулок</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Маяковская</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="K45" s="14" t="n">
+        <v>3560820</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>4189200</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="N45" s="11" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="O45" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P45" s="10" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>пометка «Посмотреть +»; в карточке Циан застройщик: VESPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Armani/Casa Moscow Residences (Армани/Каса Москоу Резиденсес)</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Vos'hod</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>4 кв. 2026</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Москва, Старомонетный, 19/11</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Якиманка</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>3630000</v>
+      </c>
+      <c r="L46" s="7" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="M46" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="O46" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr">
+        <is>
+          <t>Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>в карточке Циан застройщик: VOS’HOD; введён июль 2024; арх. John McAslan + Partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>ЖК «Погодинская»</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Веспер</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>4 кв. 2028</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Погодинская улица</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Спортивная</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>3003600</v>
+      </c>
+      <c r="K47" s="14" t="n">
+        <v>3977800</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>4855100</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="N47" s="11" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="O47" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P47" s="10" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q47" s="10" t="inlineStr">
+        <is>
+          <t>по другим источникам застройщик: Vesper; в карточке Циан застройщик: VESPER; РНС получено в ноябре 2025, закрытый старт продаж апрель–май 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ЖК «Клубный дом Обыденский №1»</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Sminex</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>1 кв. 2026</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Москва, 3-й Обыденский переулок, 1</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Кропоткинская</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>квартиры</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>2818178</v>
+      </c>
+      <c r="K48" s="8" t="n">
+        <v>4239914</v>
+      </c>
+      <c r="L48" s="7" t="n">
+        <v>9287270</v>
+      </c>
+      <c r="M48" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="O48" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>таблица заказчика + Циан 2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>по Циан дом сдан; срок по карточке Циан: 1 кв. 2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Лё Дом</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Группа ЛСР</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Москва, Соймоновский, 3</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J44" s="7" t="n">
+      <c r="J49" s="13" t="n">
         <v>2569427</v>
       </c>
-      <c r="K44" s="8" t="n">
+      <c r="K49" s="14" t="n">
         <v>4858198</v>
       </c>
-      <c r="L44" s="7" t="n">
+      <c r="L49" s="13" t="n">
         <v>10285102</v>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M49" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="N44" s="5" t="inlineStr"/>
-      <c r="O44" s="9" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P44" s="5" t="inlineStr">
+      <c r="N49" s="11" t="inlineStr">
+        <is>
+          <t>бетон</t>
+        </is>
+      </c>
+      <c r="O49" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P49" s="11" t="inlineStr">
         <is>
           <t>Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="Q44" s="4" t="inlineStr">
+      <c r="Q49" s="10" t="inlineStr">
         <is>
           <t>Le Dôme; СЗ Соймоновский 3; арх. Paris Classical Architecture; карточка ЖК на Циан не найдена, год по объявлениям</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>ЖК «БРЮСОВ»</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>VOSHOD</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>2 кв. 2026</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Москва, Брюсов переулок, 2/14с10</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Охотный Ряд</t>
         </is>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J45" s="13" t="n">
+      <c r="J50" s="7" t="n">
         <v>4318135</v>
       </c>
-      <c r="K45" s="14" t="n">
+      <c r="K50" s="8" t="n">
         <v>5980861</v>
       </c>
-      <c r="L45" s="13" t="n">
+      <c r="L50" s="7" t="n">
         <v>6843436</v>
       </c>
-      <c r="M45" s="13" t="n">
+      <c r="M50" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="N45" s="11" t="inlineStr">
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O45" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P45" s="10" t="inlineStr">
+      <c r="O50" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr">
         <is>
           <t>таблица заказчика + Циан 2026-09-07</t>
         </is>
       </c>
-      <c r="Q45" s="10" t="inlineStr">
-        <is>
-          <t>по Циан дом сдан</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>по Циан дом сдан; в карточке Циан застройщик: VOS’HOD; срок по карточке Циан: 4 кв. 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>Строки из таблицы заказчика дополнены живой выдачей Циан там, где ЖК найден в базе (цены и число лотов обновлены). Остальные строки — найдены в выдаче Циан по новостройкам ЦАО.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q45"/>
+  <autoFilter ref="A3:Q50"/>
   <mergeCells count="3">
     <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A47:Q47"/>
+    <mergeCell ref="A52:Q52"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="K4:K45">
+  <conditionalFormatting sqref="K4:K50">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -9140,13 +8797,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId46"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,18 +57,23 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="9"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="000563C1"/>
-      <sz val="9"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="9">
@@ -175,7 +180,7 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -193,7 +198,7 @@
     <xf numFmtId="3" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -211,13 +216,13 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6472,7 +6477,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr"/>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31" ht="26" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Клубный дом DUO (Дуо)</t>
@@ -6485,7 +6490,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>1 кв. 2028</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -6533,7 +6538,11 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O31" s="11" t="inlineStr"/>
+      <c r="O31" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="P31" s="10" t="inlineStr"/>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -6549,7 +6558,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>1 кв. 2029</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -6597,7 +6606,11 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr"/>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="P32" s="4" t="inlineStr"/>
     </row>
     <row r="33" ht="26" customHeight="1">
@@ -7865,23 +7878,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId45"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
@@ -7906,22 +7921,22 @@
   <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -787,9 +787,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 12 эт. на 190 апартаментов с отель-сервисом и отделкой, у Белорусской и Маяковской</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>NEVA TOWERS (Нева Тауэрс)</t>
@@ -860,9 +864,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>Две башни 63 и 77 эт. в Сити на общем стилобате, апартаменты, панорамные окна, бассейн на крыше</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Sinatra (Синатра)</t>
@@ -933,9 +941,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 7 эт. на 82 апартамента и пентхауса с потолками до 5,5 м, Тишинка у Белорусской</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>LUMIN (ЛЮМИН)</t>
@@ -1006,9 +1018,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 8 эт. на 58 лотов, стеклянные фасады (ЦЛП), терраса на крыше, 250 м от Зарядья</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Уланский, 13</t>
@@ -1079,9 +1095,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>Реконструкция доходного дома 1886 г., 4 эт., 10 квартир и 2 пентхауса, у Чистых прудов</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Современник</t>
@@ -1152,9 +1172,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10" ht="15" customHeight="1">
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>Реконструкция дома XIX в. с надстройкой, 5 эт., 86 квартир, у Чистых прудов и Красных Ворот</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Репаблик</t>
@@ -1225,9 +1249,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>Квартал из 10 башен 26–33 эт. на месте вагонных мастерских, лобби до 7 м, у Белорусской</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>City Park (Сити Парк)</t>
@@ -1298,9 +1326,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12" ht="15" customHeight="1">
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>Квартал из 6 корпусов 6–20 эт., 1220 квартир, двор-парк, рядом с Сити и парком Красная Пресня</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SkyView</t>
@@ -1371,9 +1403,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13" ht="15" customHeight="1">
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>Четыре 20-эт. башни на 304 апартамента у Белого дома, панорамные виды, парк Пресня рядом</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Полянка/44</t>
@@ -1444,7 +1480,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q13" s="10" t="inlineStr"/>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>Квартал из 8 особняков (3 исторических) по 22–24 квартиры, сад с ручьём, паркинг, у Полянки</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1517,9 +1557,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>Квартал из 8 домов-особняков 7–9 эт., 59 лотов, фасады из юрского мрамора, 1,5 км до Зарядья</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Bogenhouse (Богенхаус)</t>
@@ -1590,9 +1634,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 5 эт. на 43 апартамента и 5 пентхаусов на Озерковской наб., Замоскворечье</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Capital Towers (Капитал Тауэрс)</t>
@@ -1663,9 +1711,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>Три башни 61–65 эт. на стилобате у Сити, 787 квартир, виды на реку и парк Красная Пресня</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
@@ -1736,7 +1788,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q17" s="10" t="inlineStr"/>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>Апарт-комплекс 9 эт. на 116 резиденций на Садовнической наб., панорамные окна, 10 мин до Кремля</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1809,7 +1865,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 6 эт. на 18 квартир с потолками 3,5 м, 2 пентхауса, 200 м от м. Полянка</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -1882,9 +1942,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20" ht="15" customHeight="1">
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 8 эт. на 47 апартаментов, фасады из травертина (ЦЛП), у Цветного бульвара</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>A.Residence (А Резиденс)</t>
@@ -1955,9 +2019,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>Пять корпусов 5–9 эт., 190 апартаментов и пентхаусов, фасады из камня (ЦЛП), Садовническая</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Roza Rossa (Роза Росса)</t>
@@ -2028,7 +2096,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q21" s="10" t="inlineStr"/>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>Дом 6 эт. на 120 апартаментов по проекту Пьеро Лиссони, сервис отеля Метрополь, SPA, бассейн</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -2101,9 +2173,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>Собрание 7 клубных домов, ок. 90 лотов, исторические особняки и новые корпуса, у Третьяковки</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Дом NV/9</t>
@@ -2174,7 +2250,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q23" s="10" t="inlineStr"/>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>Два клубных корпуса 4–9 эт. на 77 квартир, 6 пентхаусов с каминами, патио, у Яузы</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -2247,7 +2327,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="inlineStr"/>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 6 эт. на 28 лотов с фасадом доходного дома 1908 г. (ЦЛП), у Малой Грузинской</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -2320,9 +2404,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>Два клубных корпуса 6 эт. на 73 квартиры, 11 пентхаусов, стиль модерн, Космодамианская наб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Софийский</t>
@@ -2393,9 +2481,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>Апарт-комплекс 8 эт. на Балчуге в 500 м от Кремля, окна в пол с видом на Кремль, отель-сервис</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Дом на Тишинке</t>
@@ -2466,9 +2558,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>Два корпуса 18 эт. на 142 квартиры от 87 м², пентхаусы с патио и каминами, Тишинка</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Тессинский, 1</t>
@@ -2539,9 +2635,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 8 эт. и особняк, 71 лот, пентхаусы с потолками 6,9 м и каминами, у Яузы</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Lucky (Лаки)</t>
@@ -2612,9 +2712,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+      <c r="Q29" s="10" t="inlineStr">
+        <is>
+          <t>Квартал из 8 корпусов 15–21 эт., 619 квартир, дворы без машин, 200 м от м. Улица 1905 года</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Artisan (Артисан)</t>
@@ -2685,9 +2789,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 5 эт. на 32 резиденции, воссозданный ампирный фасад, на Арбате</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Абрикосов</t>
@@ -2758,7 +2866,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q31" s="10" t="inlineStr"/>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>Реконструкция особняка Абрикосовых на палатах XVII в., 5 эт., 26 квартир, у Чистых прудов</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -2831,7 +2943,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q32" s="4" t="inlineStr"/>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>Дом 9 эт. на 91 квартиру с отделкой, 12 пентхаусов, каменные фасады, на месте гостиницы Варшава</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
@@ -2904,9 +3020,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q33" s="10" t="inlineStr"/>
-    </row>
-    <row r="34" ht="15" customHeight="1">
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>Четыре корпуса 4–9 эт. на 169 квартир на Саввинской наб., окна в пол, виды на реку</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Пироговская 14</t>
@@ -2977,9 +3097,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>Клубный апарт-дом 9 эт. на 53 лота, фитнес, библиотека, паркинг на 61 м/м, Хамовники у Усачёва</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Cloud Nine (Клауд Найн)</t>
@@ -3050,7 +3174,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q35" s="10" t="inlineStr"/>
+      <c r="Q35" s="10" t="inlineStr">
+        <is>
+          <t>Реконструкция 4 исторических зданий, 7–9 эт., 45 квартир, паркинг на 70 м/м, 900 м от Кремля</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -3123,9 +3251,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37" ht="15" customHeight="1">
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>Дом 8 эт. в стиле ампир на 53 квартиры, фасады из известняка, виды на Кремль и Зарядье</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Садовые кварталы</t>
@@ -3196,9 +3328,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38" ht="15" customHeight="1">
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
+          <t>Квартал из 33 клубных домов на 11 га с прудом и парком, ок. 920 квартир, у Новодевичьего</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Малая Ордынка 19</t>
@@ -3269,9 +3405,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 6 эт. на 67 квартир, потолки 3,3–3,6 м, паркинг на 124 м/м, у Третьяковской</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Дом в Газетном</t>
@@ -3342,9 +3482,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q39" s="10" t="inlineStr"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 5 эт. на 24 апартамента, пентхаусы и городская вилла, 1 км от Кремля</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
@@ -3415,9 +3559,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q40" s="4" t="inlineStr"/>
-    </row>
-    <row r="41" ht="15" customHeight="1">
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 9 эт. на 27 квартир по 3 на этаже, между Неглинной и Рождественкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
           <t>White Khamovniki (Вайт Хамовники)</t>
@@ -3488,7 +3636,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q41" s="10" t="inlineStr"/>
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
+          <t>Две башни 15 эт. на 76 квартир, архбетон и латунь, паркинг на 120 м/м, у Фрунзенской</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -3561,9 +3713,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43" ht="15" customHeight="1">
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>Квартал 1,7 га на Софийской наб., 162 лота с террасами и садами, виды на Кремль, паркинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Magnum (Магнум)</t>
@@ -3634,7 +3790,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q43" s="10" t="inlineStr"/>
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 6 эт. на 44 квартиры, английский стиль, 4 пентхауса с зимними садами, Усачёва</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -3707,9 +3867,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 3–6 эт. на 18 квартир, панно по Баксту (арх. П. Андреев), у Патриарших</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
           <t>Villa Grace (Вилла Грейс)</t>
@@ -3780,9 +3944,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q45" s="10" t="inlineStr"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 6–7 эт. на 20 квартир от 100 м², потолки 3,5 м, между Пречистенкой и набережной</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Brodsky (Бродский)</t>
@@ -3853,7 +4021,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q46" s="4" t="inlineStr"/>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>Дом 14 эт. на 65 квартир и 2 пентхауса (ЦЛП), детский клуб, wellness, у Новодевичьих прудов</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
@@ -3926,9 +4098,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q47" s="10" t="inlineStr"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
+      <c r="Q47" s="10" t="inlineStr">
+        <is>
+          <t>Дом из 8 секций 7–13 эт. на 202 квартиры, неоклассика, у Плющихи в Хамовниках</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Carré Blanc (Карре Бланк)</t>
@@ -3999,7 +4175,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q48" s="4" t="inlineStr"/>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>Особняк 5 эт. на 46 квартир (Speech), 4 пентхауса, сад 660 м² с фонтаном, у Храма Христа</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
@@ -4072,9 +4252,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q49" s="10" t="inlineStr"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
+      <c r="Q49" s="10" t="inlineStr">
+        <is>
+          <t>Квартал из 3 корпусов 8–14 эт. на 98 квартир, прямые виды на Кремль, у Третьяковки</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Хамовники 12</t>
@@ -4145,7 +4329,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q50" s="4" t="inlineStr"/>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 14 эт. на 51 квартиру от 100 м² (арх. Е. Герасимов), 100 м от Саввинской наб.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
@@ -4218,7 +4406,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q51" s="10" t="inlineStr"/>
+      <c r="Q51" s="10" t="inlineStr">
+        <is>
+          <t>Отель 5* и 14 брендовых резиденций Bulgari, таунхаусы, пентхаус, SPA, на Большой Никитской</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -4291,7 +4483,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q52" s="4" t="inlineStr"/>
+      <c r="Q52" s="4" t="inlineStr">
+        <is>
+          <t>Три корпуса 6 эт.: реконструкция особняка и 2 новых, окна в пол, потолки до 4,6 м, у Большого</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
@@ -4364,9 +4560,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q53" s="10" t="inlineStr"/>
-    </row>
-    <row r="54" ht="15" customHeight="1">
+      <c r="Q53" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 7 эт. на 23 квартиры, потолки от 3,6 м, современная классика, у Патриарших</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Barkli Gallery (Баркли Галлери)</t>
@@ -4437,7 +4637,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q54" s="4" t="inlineStr"/>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>Реконструкция домов 1875 и 1913 гг., 4–7 эт., 43 лота с отделкой, 200 м от Третьяковки</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:Q54"/>
@@ -4647,7 +4851,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ЖК «Слава»</t>
@@ -4709,9 +4913,13 @@
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Квартал из 3 корпусов 6–22 эт. на Ленинградском пр., панорамное остекление, паркинг на 782 м/м</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>ЖК «Дом Дау»</t>
@@ -4777,9 +4985,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>Башня 85 эт., 340 м, 866 квартир на 2-й линии Краснопресненской наб. у Сити, SPA, коворкинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ЖК «Начало»</t>
@@ -4845,9 +5057,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>Квартал из 8 корпусов 12–55 эт. на ул. Сергея Макеева, потолки 3,4–4,1 м, у Пресни</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Оне</t>
@@ -4913,7 +5129,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P7" s="10" t="inlineStr"/>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>Башня 90 эт., 379 м в Москва-Сити, две башни в форме ленты Мёбиуса, Sky Bridge, сад на 338 м</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -4979,9 +5199,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>Две башни 96 и 83 эт., 395 м в Сити-2, 1774 квартиры, парк с бассейнами на 7 эт., APEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t>ЖК «Монблан»</t>
@@ -5047,7 +5271,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P9" s="10" t="inlineStr"/>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>Дом из 6 секций 7–27 эт. на Шлюзовой наб., 341 квартира, вид на реку, у Павелецкой</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -5115,7 +5343,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>Квартал из 6 домов 10–23 эт. на ул. Сергея Макеева, 265 квартир, двор-парк 1,8 га</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -5183,9 +5415,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12" ht="15" customHeight="1">
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>Квартал из 12 домов 12–18 эт. на Лужнецкой наб., парк 8 га, вид на реку и Сити</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Тессинский V</t>
@@ -5251,7 +5487,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>Квартал из 4 клубных домов 5–12 эт., 146 резиденций, у Серебрянической наб., Таганка</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -5319,7 +5559,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P13" s="10" t="inlineStr"/>
+      <c r="P13" s="10" t="inlineStr">
+        <is>
+          <t>Реконструкция Кокоревского подворья 1864 г., 7–8 эт., 68 квартир, потолки 4–7 м, Софийская наб.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -5387,9 +5631,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>Квартал из 10 домов 6–14 эт. на Тишинке, 404 квартиры, парк-бульвар 1,9 га, бассейн</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>ЖК «Дом Франка»</t>
@@ -5455,9 +5703,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
+      <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>Реконструкция торгового дома 1904 г. (Кекушев) и новый корпус в Б. Кисельном пер., у Лубянки</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ЖК «Татарская 35»</t>
@@ -5523,7 +5775,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>Три корпуса 15–24 эт., 472 квартиры, wellness с бассейном, у Озерковской наб., Замоскворечье</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -5591,9 +5847,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+      <c r="P17" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом из 2 корпусов, 75 резиденций, потолки до 5,96 м, каменный фасад, ул. Обуха</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ЖК «Дом Соболева»</t>
@@ -5659,7 +5919,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr"/>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 7–8 эт. на ул. Машкова, 33 резиденции и 2 пентхауса, потолки 3,55 м, Красные Ворота</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -5727,7 +5991,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P19" s="10" t="inlineStr"/>
+      <c r="P19" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 7–9 эт. (арх. Чобан), 46 резиденций, стена доходного дома 1905 г. Нирнзее, Пресня</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -5795,9 +6063,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 13 эт. на Садовом кольце, 48 квартир, бассейн 20 м, SPA, хаммам, у Сухаревской</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>ЖК «Камергер»</t>
@@ -5863,9 +6135,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+      <c r="P21" s="10" t="inlineStr">
+        <is>
+          <t>Комплекс из 5 особняков в 300 м от Кремля, 17 резиденций с террасами, SPA, подземный переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Казачий</t>
@@ -5931,7 +6207,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 9 эт. (бюро WALL) в 1-м Казачьем пер., 76 квартир и 4 пентхауса, потолки до 3,95 м</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -5999,9 +6279,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+      <c r="P23" s="10" t="inlineStr">
+        <is>
+          <t>Клубный квартал из 4 домов 2–10 эт. на Садовнической наб., свой парк 1 га, виллы и пентхаусы</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Саввинская 17</t>
@@ -6067,7 +6351,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 4 эт. на 1-й линии реки в Хамовниках, 22 квартиры, окна в пол, у Девичьего поля</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -6135,9 +6423,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+      <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>Реконструкция доходного дома 1915 г. фон Дессина, 7 эт., 36 квартир, в 50 м от Чистых прудов</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>ЖК «PHANTOM»</t>
@@ -6203,7 +6495,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 7–9 эт. на М. Сухаревской пл., 76 квартир, пентхаусы и дуплексы, у Сухаревской</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -6271,7 +6567,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P27" s="10" t="inlineStr"/>
+      <c r="P27" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 8 эт. в Костянском пер., 118 квартир, каменный фасад, бассейн, SPA, у Чистых прудов</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -6339,9 +6639,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 7 эт. (арх. Казамонти) в Крестовоздвиженском пер., 43 квартиры и 3 пентхауса</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Кло 17</t>
@@ -6407,9 +6711,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+      <c r="P29" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом (бюро PCA) в Староваганьковском пер., 26 квартир и 2 пентхауса, вид на Кремль</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>ТИТУЛ Империал</t>
@@ -6475,7 +6783,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr"/>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом на 12 квартир в Б. Николоворобинском пер., у Яузы, Таганка</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
@@ -6543,9 +6855,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+      <c r="P31" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 6 эт. на Софийской наб. (Кокоревское подворье), 42 квартиры и 5 пентхаусов</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Дом Спорта</t>
@@ -6611,7 +6927,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr"/>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>Три корпуса на Дружинниковской ул. у Дома правительства, спорткластер 20 тыс. м² с катками</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
@@ -6679,7 +6999,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P33" s="10" t="inlineStr"/>
+      <c r="P33" s="10" t="inlineStr">
+        <is>
+          <t>7 особняков 3–5 эт. в неорусском стиле в 160 м от Красной пл., 3 памятника XIX в., двор-сад</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -6747,9 +7071,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 4–5 эт. из 3 корпусов на Берсеневской наб., 21 квартира, у Стрелки</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
           <t>ЖК «Николь»</t>
@@ -6815,9 +7143,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P35" s="10" t="inlineStr"/>
-    </row>
-    <row r="36" ht="15" customHeight="1">
+      <c r="P35" s="10" t="inlineStr">
+        <is>
+          <t>3 здания с реконструкцией исторических домов на Никольской ул. (Heatherwick), у Красной пл.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>MONO Kami</t>
@@ -6883,9 +7215,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37" ht="15" customHeight="1">
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>Комплекс из 4 клубных домов 9–14 эт. в Пыжевском пер., 74 квартиры, 5 мин до Третьяковки</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
           <t>ЖК «Никитский-6»</t>
@@ -6951,7 +7287,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P37" s="10" t="inlineStr"/>
+      <c r="P37" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 8 эт. на Никитском бул., 57 квартир и 4 пентхауса с каминами и террасами</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -7019,9 +7359,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>Квартал из 3 домов 10 эт. и неоклассического корпуса на Фрунзенской наб., 137 квартир, парк</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Kuznetsky Most 12 by Lalique (Кузнецкий Мост 12)</t>
@@ -7034,7 +7378,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4 кв. 2026</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -7082,10 +7426,18 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O39" s="11" t="inlineStr"/>
-      <c r="P39" s="10" t="inlineStr"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
+      <c r="O39" s="15" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P39" s="10" t="inlineStr">
+        <is>
+          <t>Реконструкция здания XIX в. на Кузнецком Мосту, 3–6 эт., 59 квартир, потолки до 5,8 м, wellness</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Саввинская 27</t>
@@ -7151,9 +7503,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr"/>
-    </row>
-    <row r="41" ht="15" customHeight="1">
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 6 эт. (ODA, APEX) на 1-й линии реки, 61 резиденция, 10 пентхаусов, SPA с бассейном</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
           <t>ДОМ XXII</t>
@@ -7166,7 +7522,7 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4 кв. 2026</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -7219,9 +7575,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P41" s="10" t="inlineStr"/>
-    </row>
-    <row r="42" ht="15" customHeight="1">
+      <c r="P41" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом из 2 корпусов 9–12 эт. у Новодевичьего, 109 квартир, потолки 3,5–4,5 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Stoleshnikov 7 (Столешников 7)</t>
@@ -7287,9 +7647,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43" ht="15" customHeight="1">
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>Реконструкция доходного дома 1903 г. (Эрихсон), 5 эт., 12 квартир, камины и террасы</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
           <t>ЖК «Узоры»</t>
@@ -7355,9 +7719,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P43" s="10" t="inlineStr"/>
-    </row>
-    <row r="44" ht="15" customHeight="1">
+      <c r="P43" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом из 2 секций 9–10 эт. на общем стилобате во 2-м Вражском пер., 72 квартиры</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Annabels</t>
@@ -7423,7 +7791,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P44" s="4" t="inlineStr"/>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 7 эт. в Курсовом пер. на Золотой миле, 9 резиденций, пентхаус с террасами</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
@@ -7491,7 +7863,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P45" s="10" t="inlineStr"/>
+      <c r="P45" s="10" t="inlineStr">
+        <is>
+          <t>Реконструкция особняка Шехтеля в Трёхпрудном пер., 2–6 эт., 26 квартир, у Патриарших</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -7559,7 +7935,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P46" s="4" t="inlineStr"/>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 3–6 эт. в Старомонетном пер., 27 резиденций, интерьеры Armani/Casa, у Полянки</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
@@ -7627,7 +8007,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P47" s="10" t="inlineStr"/>
+      <c r="P47" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом из 2 корпусов 11 эт. (GAFA) у Новодевичьего, 64 квартиры, бассейн 25 м</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -7695,9 +8079,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P48" s="4" t="inlineStr"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом в 3-м Обыденском пер., 26 квартир, пентхаусы и виллы, в 150 м от ХХС</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
           <t>Лё Дом</t>
@@ -7763,9 +8151,13 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P49" s="10" t="inlineStr"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
+      <c r="P49" s="10" t="inlineStr">
+        <is>
+          <t>Клубный дом 3–5 эт. в Соймоновском пр., более 70 квартир, вид на Храм Христа Спасителя</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>ЖК «БРЮСОВ»</t>
@@ -7831,7 +8223,11 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P50" s="4" t="inlineStr"/>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>Клубный дом 8 эт. в Брюсовом пер. (1508 London), 20 резиденций и пентхаус, 5 мин до Кремля</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:P50"/>
@@ -7886,17 +8282,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId46"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -213,16 +213,16 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>3 кв. 2026</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -8435,48 +8435,56 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом «Малая Никитская, 27»</t>
+          <t>Лёвшинский, 19</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Малая Никитская улица, 27 (два двухэтажных особняка 1861 г., бывший «Клуб 27»)</t>
+          <t>Большой Лёвшинский пер., 19</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>Садовое кольцо</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>не раскрыт (по данным форума pronovostroy.ru — Mono/ПИК; официально не подтверждено)</t>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>ТСИ Девелопмент</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>проект на согласовании (высотность 33 м); продажи не открыты</t>
+          <t>продажи открыты, котлован/фундамент (novostroy-m.ru, 2026) — вышел из стадии планирования</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
+      <c r="I4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>2 кв. 2028</t>
+        </is>
+      </c>
       <c r="M4" s="8" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>2024-03-31</t>
-        </is>
-      </c>
+        <v>2800000</v>
+      </c>
+      <c r="N4" s="5" t="n"/>
       <c r="O4" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -8484,67 +8492,53 @@
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом высотой 33 м по проекту бюро WALL на месте двух двухэтажных особняков (бывший отель Club 27). Ориентировочная цена «от ~3 млн руб./м²» — оценка источника, не подтверждена застройщиком. В базе mskdeluxe.ru фигурирует как «Малая Никитская, 29-31».; Архитектура — бюро WALL (ярусные объемы, черно-белые фасады). Существующие здания ~4 000 м² сносятся. Цена ~3 млн руб./м² — предварительное рыночное ожидание (sosedi.life, https://sosedi.life/news/zhk-malaya-nikitskaya-27/), не оферта. Restate.ru (2025–2026) отмечал неопределенность со стартом: возможна продажа площадки вместо запуска.</t>
+          <t>Клубный дом 8 эт. на 16 резиденций 70–239 м², воссоздание фасада доходного дома Духовских 1904 г., паркинг 18 м/м, HADAA</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Палашёвский 11 (Большой Палашёвский, 11–13/15)</t>
+          <t>Клубный дом «Малая Никитская, 27»</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Большой Палашёвский пер., 11–13</t>
+          <t>Малая Никитская улица, 27 (два двухэтажных особняка 1861 г., бывший «Клуб 27»)</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Тверской</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>Sminex (СЗ «Смайнэкс Палашёвский 11»)</t>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>не раскрыт</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>старт продаж без стройки (закрытый старт 22.04.2026)</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>15600</v>
-      </c>
+          <t>проектирование (kvartiravmoskve.ru, 02.03.2026); продажи не открыты, старт не анонсирован</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="n"/>
       <c r="H5" s="11" t="n"/>
-      <c r="I5" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>43</v>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>1 кв. 2030</t>
-        </is>
-      </c>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="11" t="n"/>
       <c r="M5" s="14" t="n">
-        <v>3500000</v>
+        <v>3000000</v>
       </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="O5" s="15" t="inlineStr">
@@ -8554,71 +8548,71 @@
       </c>
       <c r="P5" s="10" t="inlineStr">
         <is>
-          <t>Три корпуса 8–9 этажей с контрастными фасадами у Патриарших. Старт продаж 22.04.2026, лоты от 222,4 млн руб. (nngm.ru), от ~3,5 млн руб./м². Сдача 1 кв. 2030 (novostroev.ru, обзор делюкс-стартов 2026).</t>
+          <t>Клубный дом высотой 33 м (бюро WALL) на месте двух особняков 1861 г. у Патриарших; ярусные объёмы, чёрно-белые фасады</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>EDEN Private Residence</t>
+          <t>Палашёвский 11 (Большой Палашёвский, 11–13/15)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Нижний Кисловский пер., 7, стр. 1–2</t>
+          <t>Большой Палашёвский пер., 11–13</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
+          <t>Тверской</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Sense Development (с ГК ПИК и Айсель Трудель)</t>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>старт продаж без стройки (закрытый формат, апрель 2026)</t>
+          <t>продажи открыты (апрель 2026), стадия котлована (проверено 03.09.2026) — вышел из стадии планирования</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
-        <v>17100</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>6200</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>9</v>
+        <v>15600</v>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>8–9</t>
+        </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>1 кв. 2030</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>3 кв. 2029</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -8626,57 +8620,73 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>Ultra luxury, 6–9 этажей, 22 резиденции, участок 0,3 га, архитектура Gregory Tuck Architects. Оценка цены ~5 млн руб./м² (около 1,1 млрд руб. за ~250 м²). Общая площадь в разных источниках 13–17,1 тыс. м².</t>
+          <t>Клубный дом 8–9 эт.: 45 квартир и 7 пентхаусов у Патриарших, три контрастных фасада, двор-сад с прудом, паркинг 88 м/м</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Большая Ордынка, 25</t>
+          <t>EDEN Private Residence</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>ул. Большая Ордынка, 25, стр. 1</t>
+          <t>Нижний Кисловский пер., 7, стр. 1–2</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Замоскворечье</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Aurix Development (Группа «Эталон»)</t>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Sense Development</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>концепция одобрена ГЗК, подготовка к строительству, старт продаж 2026</t>
+          <t>закрытые продажи (апрель 2026), стадия котлована; публичные продажи не открыты (novostroev.ru, 03.09.2026)</t>
         </is>
       </c>
       <c r="G7" s="13" t="n">
-        <v>17000</v>
-      </c>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="11" t="n"/>
+        <v>17100</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>6200</v>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>6–9</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>22</v>
+      </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="11" t="n"/>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>3 кв. 2029</t>
+        </is>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -8684,55 +8694,63 @@
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>7 этажей + мансардный уровень, &gt;17 тыс. м², на месте конструктивистской АТС 1927 г. Де-люкс. Одобрение ГЗК упоминает whitewill.ru.</t>
+          <t>Ultra luxury клубный дом 6–9 эт. на 22 резиденции 107–411 м² у Арбата, участок 0,3 га, Gregory Tuck Architects</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Большая Пироговская, 51 (общежития Института красной профессуры)</t>
+          <t>Большая Ордынка, 25</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ул. Большая Пироговская, 51</t>
+          <t>ул. Большая Ордынка, 25, стр. 1</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Vesper (fee-девелопер) / собственник Capital Group</t>
+          <t>Замоскворечье</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Aurix Development</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>анонсирован (fee-development), концепция</t>
+          <t>концепция одобрена ГЗК, подготовка к строительству; старт продаж заявлен на 2026, цены и планировки не опубликованы</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
-        <v>46700</v>
+        <v>17000</v>
       </c>
       <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>7 + мансарда</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="22" t="n"/>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>4 кв. 2031</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="n"/>
+      <c r="N8" s="5" t="n"/>
       <c r="O8" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -8740,59 +8758,59 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>Участок 1,5 га, ансамбль восьми 6-этажных корпусов 1929–32 гг. (арх. Осипов, Рухлядев; статус памятника утрачен в 2000-х). Планируемая площадь выросла с 39 до 46,7 тыс. м². Vesper — концепция, продукт и управление реализацией. В базе mskdeluxe.ru — «Б.Пироговская, 51».</t>
+          <t>Клубный дом 7 эт. + мансарда, &gt;17 тыс. м², на месте первой АТС Москвы 1927 г. в Замоскворечье; делюкс</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Большой Козихинский, 22</t>
+          <t>Большая Пироговская, 51 (общежития Института красной профессуры)</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Большой Козихинский пер., 22</t>
+          <t>ул. Большая Пироговская, 51</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Пресненский</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>КОЛДИ / Доминанта</t>
+          <t>Vesper</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>проект, продажи не начаты</t>
+          <t>анонсирован (fee-development, июнь 2026), концепция; ГПЗУ получен в начале 2025; реализация не подтверждена</t>
         </is>
       </c>
       <c r="G9" s="13" t="n">
-        <v>9377</v>
+        <v>46700</v>
       </c>
       <c r="H9" s="11" t="n"/>
-      <c r="I9" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>98</v>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>12–13 (концепция Buro 2+2, 8 корпусов)</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n"/>
       <c r="L9" s="11" t="n"/>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="11" t="n"/>
+      <c r="M9" s="22" t="n"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -8800,52 +8818,58 @@
       </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>Патриаршие пруды. Статус «Проект / продажи не начаты» подтверждён novostroev.ru на 01.09.2026; включён в список перспективных стартов делюкс-класса 2026 (novostroev.ru). Официальный сайт kozihinsky22.ru недоступен (403).</t>
+          <t>Застройка 1,5 га бывших общежитий 1929–32 гг.: концепция 8 корпусов 12–13 эт. на стилобате в светлом камне, 46,7 тыс. м²</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Воздвиженка 7/6</t>
+          <t>Большой Козихинский, 22</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ул. Воздвиженка, 7/6</t>
+          <t>Большой Козихинский пер., 22</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Арбат</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>АПРИ (по данным vozdvizhenka7.ru)</t>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>КОЛДИ / Доминанта</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>анонсирован, старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
+          <t>проект, продажи не начаты (novostroev.ru, проверено 03.09.2026)</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>9377</v>
+      </c>
       <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
+      <c r="I10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>98</v>
+      </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>2026–2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="L10" s="5" t="n"/>
-      <c r="M10" s="22" t="n"/>
+      <c r="M10" s="21" t="n"/>
       <c r="N10" s="5" t="n"/>
       <c r="O10" s="9" t="inlineStr">
         <is>
@@ -8854,55 +8878,53 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>Указан в базе делюкс-стартов 2026–2027 mskdeluxe.ru. Агрегаторы описывают как бутик-дом на 10–15 квартир; ранее указывалась сдача 1 кв. 2025 — данные противоречивы, официальный сайт vozdvizhenka7.ru недоступен (503). Требует верификации.</t>
+          <t>Клубный дом 9 эт. на 98 квартир (9,4 тыс. м²) у Патриарших прудов, 5 мин. от м. Пушкинская; делюкс</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Квартал на Савинской набережной («Московский шёлк»)</t>
+          <t>Воздвиженка 7/6</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Савинская наб. (территория БЦ «Московский шёлк»)</t>
+          <t>ул. Воздвиженка, 7/6</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Арбат</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Sminex</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>проектирование</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>125000</v>
-      </c>
+          <t>АПРИ</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>анонсирован; в списке делюкс-стартов 2026–2027 mskdeluxe.ru; параметры не раскрыты, сайт проекта недоступен (08.09.2026)</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="n"/>
       <c r="H11" s="11" t="n"/>
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>2026–2027</t>
+        </is>
+      </c>
       <c r="L11" s="11" t="n"/>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="11" t="n"/>
       <c r="O11" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -8910,29 +8932,29 @@
       </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>ЖК ~125 тыс. м² на территории делового квартала «Московский шёлк». По данным Sminex на декабрь 2025 г. находится в стадии проектирования (вместе с Лужнецкой).</t>
+          <t>Бутик-дом делюкс ориентировочно на 10–15 квартир на Воздвиженке у Александровского сада; параметры не подтверждены</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Клубные дома на Берниковской набережной, 12 (Sminex)</t>
+          <t>Квартал на Савинской набережной («Московский шёлк»)</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Берниковская набережная, 12, стр. 1 (здание бывшей школы №1685, 1936 г., арх. А. Машинский)</t>
+          <t>Савинская наб. (территория БЦ «Московский шёлк»)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Таганский</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>Садовое кольцо</t>
+          <t>Хамовники</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -8942,29 +8964,25 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>проектирование; предварительная архитектурная концепция (бюро 80/88) опубликована в марте 2026</t>
+          <t>проектирование (подтверждено Sminex в декабре 2025); начало реализации планировалось на 2026, старт продаж не объявлен</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>23336</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>13000</v>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>9–13 (два корпуса; 9-этажный многосекционный вдоль набережной, 13-этажный в глубине со стороны Берникова переулка)</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>166</v>
-      </c>
-      <c r="K12" s="5" t="n"/>
+        <v>125000</v>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>2026 (начало реализации, план 2024 г.)</t>
+        </is>
+      </c>
       <c r="L12" s="5" t="n"/>
-      <c r="M12" s="22" t="n"/>
+      <c r="M12" s="21" t="n"/>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="O12" s="9" t="inlineStr">
@@ -8974,63 +8992,61 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>Участок 0,6 га на первой линии Яузы, два корпуса 9–13 этажей, ~23 тыс. м², 166 квартир, «органический неоклассицизм». Делюкс. Застройщик не назван.; Sminex приобрел площадку в конце 2024 г.; по пресс-релизу — два элитных клубных дома 7–13 этажей, общая площадь 21,4 тыс. м², из них ~13 тыс. м² жилья. По концепции 80/88 (Москвич Mag, https://moskvichmag.ru/gorod/poyavilsya-proekt-mnogosektsionnogo-zhk-na-bernikovskoj-naberezhnoj-na-meste-zakrytoj-shkoly) — 23 336 м², 166 квартир; участок 0,6 га; отмечается, что окончательная реализация именно этого проекта не гарантирована. Агрегатор kvartiravmoskve.ru: стадия «проектирование», монолит-кирпич, подземный паркинг.</t>
+          <t>ЖК ~125 тыс. м² на 4,5 га бывшей фабрики «Московский шёлк» на Савинской наб.: новые корпуса и реставрация</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Клубный дом «Большая Никитская, 16» (R4S)</t>
+          <t>Клубные дома на Берниковской набережной, 12 (Sminex)</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Большая Никитская улица, 16 (реконструкция доходного дома, объект культурного наследия)</t>
+          <t>Берниковская набережная, 12, стр. 1 (здание бывшей школы №1685, 1936 г., арх. А. Машинский)</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Пресненский</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
+          <t>Таганский</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>R4S Group (генподрядчик — Спецжилремонт)</t>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>реконструкция; старт продаж I кв. 2026; ввод III кв. 2026</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="13" t="n">
-        <v>4</v>
+          <t>проектирование; площадка подтверждена Sminex 17.03.2026, сроки и старт продаж не объявлены</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>21400</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>7–13 (два корпуса)</t>
+        </is>
       </c>
       <c r="J13" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>2026 Q1 (старт продаж)</t>
-        </is>
-      </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>2026 Q3</t>
-        </is>
-      </c>
-      <c r="M13" s="20" t="n"/>
+        <v>166</v>
+      </c>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="22" t="n"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="O13" s="15" t="inlineStr">
@@ -9040,59 +9056,63 @@
       </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>Единственная публичная новинка на Большой Никитской в 2025–2026: 4 квартиры 139,4 / 141,4 / 151 / 234 м². Другие участки на Большой Никитской в открытых анонсах не найдены.</t>
+          <t>Два клубных дома 7–13 эт., 166 квартир на 0,6 га на первой линии Яузы; двор-парк, пентхаусы с каминами; делюкс</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом «Земледельческий, 15»</t>
+          <t>Клубный дом «Большая Никитская, 16» (R4S)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Земледельческий переулок, 15 (на месте административного здания 1975 г., 5 этажей, 5 744 м²)</t>
+          <t>Большая Никитская улица, 16 (реконструкция доходного дома, объект культурного наследия)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
+          <t>Пресненский</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>Садовое кольцо</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>не раскрыт</t>
+          <t>R4S Group</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>проектирование (агрегаторы; в списке ожидаемых стартов делюкс-класса 2026 на mskdeluxe.ru)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>8000</v>
-      </c>
+          <t>проект/реконструкция; продажи не начаты (novostroev.ru, 02.09.2026); заявленный ввод 3 кв. 2026 не подтверждён</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
+      <c r="I14" s="7" t="n">
+        <v>4</v>
+      </c>
       <c r="J14" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>2026–2027</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="22" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>2026 Q1 (старт продаж, не состоялся на 02.09.2026)</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>2026 Q3</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="n"/>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="O14" s="9" t="inlineStr">
@@ -9102,51 +9122,61 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>Участок 0,3 га (сейчас административное здание 1975 г., 5 эт., 5,7 тыс. м²), клубный дом ~8 тыс. м², 77 квартир, коммерция, подземный паркинг. Делюкс.; Участок 0,3 га; делюкс; 77 квартир + коммерческая часть; подземный паркинг; монолит-кирпич; 1 км до м. Смоленская. Сделок по продаже БЦ и решений Москомархитектуры в открытых источниках не найдено.</t>
+          <t>Реконструкция исторического особняка (ОКН) в клубный дом 4 эт. на 4 квартиры 139–234 м² у Кремля, потолки 3,1–3,7 м</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Клубный дом на Курсовом переулке, 15 (проект бюро Дмитрия Великовского)</t>
+          <t>Клубный дом «Земледельческий, 15»</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Курсовой переулок, 15</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Хамовники (Остоженка)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
+          <t>Земледельческий переулок, 15 (на месте административного здания 1975 г., 5 этажей, 5 744 м²)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>не раскрыт (проект бюро Дмитрия Великовского)</t>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Хамовники</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>не раскрыт</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>проект / предстарт; в открытых источниках только страница агрегатора</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n"/>
+          <t>проектирование (kvartiravmoskve.ru, 21.06.2026); по адресу действует БЦ; сделок и решений МКА не найдено</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>8000</v>
+      </c>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>2026–2027</t>
+        </is>
+      </c>
       <c r="L15" s="11" t="n"/>
-      <c r="M15" s="20" t="n"/>
-      <c r="N15" s="11" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
       <c r="O15" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -9154,57 +9184,51 @@
       </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>«Золотая миля», 6 этажей, камерный клубный дом. Подробные параметры и застройщик в открытых источниках не раскрыты.; По описанию агрегатора: 6-этажный дом по проекту бюро Дмитрия Великовского, панорамное остекление, локация «Золотой мили» рядом с Зачатьевским монастырем. Сейчас по адресу — детский клуб-студия «Пречистенские ворота». Пресса (Коммерсант, РБК, Ведомости, Москвич Mag) и Москомархитектура публикаций по площадке не имеют; девелопер и параметры не подтверждены.</t>
+          <t>Клубный дом ~8 тыс. м² на 77 квартир на 0,3 га на месте БЦ 1975 г. у Плющихи; коммерция, подземный паркинг; делюкс</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Льва Толстого, 14–16 (три клубных дома Sminex)</t>
+          <t>Клубный дом на Курсовом переулке, 15 (проект бюро Дмитрия Великовского)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ул. Льва Толстого, 14</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
+          <t>Курсовой переулок, 15</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Хамовники (Остоженка)</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>Хамовники</t>
-        </is>
-      </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Sminex</t>
+          <t>не раскрыт</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>участок приобретён (декабрь 2025), концепция в финальной стадии, старт продаж не объявлен</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>20300</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>12400</v>
-      </c>
-      <c r="I16" s="5" t="n"/>
+          <t>проект / предстарт; в открытых источниках только страница агрегатора (08.09.2026)</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="7" t="n">
+        <v>6</v>
+      </c>
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="5" t="n"/>
-      <c r="M16" s="22" t="n"/>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
+      <c r="M16" s="21" t="n"/>
+      <c r="N16" s="5" t="n"/>
       <c r="O16" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -9212,19 +9236,19 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>Участок ~0,6 га у делового квартала «Красная Роза», куплен у структур А. Клячина. Три камерных клубных дома, надземная площадь 20,3 тыс. м², квартиры 12,4 тыс. м². Сохраняется фасад бывшего доходного дома Трындина-Жиро.</t>
+          <t>Камерный клубный дом 6 эт. на «Золотой миле» у Зачатьевского монастыря; классика с панорамными окнами, башня с куполом</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Лёвшинский, 19</t>
+          <t>Льва Толстого, 14–16 (три клубных дома Sminex)</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Большой Лёвшинский пер., 19</t>
+          <t>ул. Льва Толстого, 14</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -9232,41 +9256,37 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>ТСИ Девелопмент (ГК «Трансстройинвест»)</t>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>старт бронирования, старт продаж</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="K17" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>2 кв. 2028</t>
-        </is>
-      </c>
-      <c r="M17" s="20" t="n"/>
-      <c r="N17" s="11" t="n"/>
+          <t>участок приобретён (декабрь 2025), проектирование; старт продаж не объявлен (08.09.2026)</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>20300</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>12400</v>
+      </c>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="11" t="n"/>
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="22" t="n"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
       <c r="O17" s="15" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -9274,7 +9294,7 @@
       </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>Воссоздание фасада доходного дома Духовских (1904, арх. Мейснер), проект HADAA Architects. 16 резиденций 70–239 м², паркинг 18 м/м. Цена от 197,12 млн руб. за лот. Стадия стройки в источниках не подтверждена.</t>
+          <t>Три камерных клубных дома у «Красной Розы» на 0,6 га; сохранение фасада дома Трындина-Жиро, виды на Кремль, клубхаус</t>
         </is>
       </c>
     </row>
@@ -9306,10 +9326,12 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>анонсирован, старт продаж ожидается</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="n"/>
+          <t>проект/анонс; сроки реализации и старт продаж не объявлены, предложений нет (сентябрь 2026)</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>90000</v>
+      </c>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
@@ -9319,8 +9341,12 @@
           <t>2030</t>
         </is>
       </c>
-      <c r="M18" s="22" t="n"/>
-      <c r="N18" s="5" t="n"/>
+      <c r="M18" s="21" t="n"/>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>2014-07-17</t>
+        </is>
+      </c>
       <c r="O18" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
@@ -9328,7 +9354,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>Участок ~1,7 га с ОКН (фабрика Трёхгорной мануфактуры, будет сохранена/реконструирована). Апартаменты премиум-класса + офисы + wellness, подземный паркинг на 750 м/м. Сроки реализации официально не подтверждены; апартаменты, а не квартиры.</t>
+          <t>МФК с апартаментами, офисами и wellness на 1,7 га у Трёхгорной мануфактуры (ОКН сохраняется), паркинг 750 м/м</t>
         </is>
       </c>
     </row>
@@ -9348,7 +9374,7 @@
           <t>Тверской</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -9360,15 +9386,17 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>анонсирован, старт продаж ожидается в 2026 г.</t>
+          <t>предстарт; старт продаж ожидается в 2026 г. (на 08.09.2026 не объявлен)</t>
         </is>
       </c>
       <c r="G19" s="13" t="n">
         <v>12000</v>
       </c>
       <c r="H19" s="11" t="n"/>
-      <c r="I19" s="13" t="n">
-        <v>9</v>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>7–9</t>
+        </is>
       </c>
       <c r="J19" s="11" t="n"/>
       <c r="K19" s="11" t="inlineStr">
@@ -9377,7 +9405,7 @@
         </is>
       </c>
       <c r="L19" s="11" t="n"/>
-      <c r="M19" s="20" t="n"/>
+      <c r="M19" s="22" t="n"/>
       <c r="N19" s="11" t="n"/>
       <c r="O19" s="15" t="inlineStr">
         <is>
@@ -9386,7 +9414,7 @@
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>Участок ~0,4 га у сада «Эрмитаж», 2 корпуса 7–9 этажей, волнообразные фасады, делюкс-класс.</t>
+          <t>Два корпуса 7–9 эт. на 0,4 га у сада «Эрмитаж», волнообразные бионические фасады, камерный клубный формат; делюкс</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9434,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -9418,7 +9446,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>в списке ожидаемых стартов делюкс-класса 2026 (агрегатор); подробностей нет</t>
+          <t>в списке ожидаемых стартов делюкс-класса 2026 (mskdeluxe.ru); подробностей нет (08.09.2026)</t>
         </is>
       </c>
       <c r="G20" s="5" t="n"/>
@@ -9427,7 +9455,7 @@
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
-      <c r="M20" s="22" t="n"/>
+      <c r="M20" s="21" t="n"/>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="9" t="inlineStr">
         <is>
@@ -9436,7 +9464,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>В том же списке mskdeluxe.ru: М. Дмитровка 5/9, Льва Толстого 14, Хилков 3, Б. Пироговская 51, Б. Харитоньевский 13, Олсуфьевский 10, Большая Ордынка 25, Воздвиженка 7/6, Малая Полянка 3 — без параметров и девелоперов.</t>
+          <t>Ожидаемый делюкс-старт на Малой Никитской у Красной Пресни; параметры не раскрыты, возможно тот же участок, что и №27</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9484,7 @@
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -9468,13 +9496,15 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>старт продаж 06.04.2026</t>
+          <t>анонс старта продаж 06.04.2026; по novostroev.ru на 03.09.2026 — проект, продажи не начаты</t>
         </is>
       </c>
       <c r="G21" s="13" t="n">
         <v>3000</v>
       </c>
-      <c r="H21" s="11" t="n"/>
+      <c r="H21" s="13" t="n">
+        <v>2360</v>
+      </c>
       <c r="I21" s="13" t="n">
         <v>6</v>
       </c>
@@ -9487,7 +9517,7 @@
         </is>
       </c>
       <c r="L21" s="11" t="n"/>
-      <c r="M21" s="20" t="n"/>
+      <c r="M21" s="22" t="n"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
           <t>2026-04-06</t>
@@ -9500,7 +9530,7 @@
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>Участок 0,1 га, 11 квартир, 14 подземных м/м, архитектура A2M. Делюкс.</t>
+          <t>Клубный дом 6 эт. на 11 квартир на участке 0,1 га в Замоскворечье, 14 м/м, архитектура A2M; делюкс</t>
         </is>
       </c>
     </row>
@@ -9520,25 +9550,27 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Грандор (Grandor)</t>
+          <t>Грандор</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>ГПЗУ получен (апрель 2021), старт продаж ожидается</t>
+          <t>проект (ГПЗУ апрель 2021); продажи не начаты, «скоро в продаже» (08.09.2026)</t>
         </is>
       </c>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
-      <c r="I22" s="7" t="n">
-        <v>8</v>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>5–8</t>
+        </is>
       </c>
       <c r="J22" s="5" t="n"/>
       <c r="K22" s="5" t="inlineStr">
@@ -9547,7 +9579,7 @@
         </is>
       </c>
       <c r="L22" s="5" t="n"/>
-      <c r="M22" s="22" t="n"/>
+      <c r="M22" s="21" t="n"/>
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="9" t="inlineStr">
         <is>
@@ -9556,7 +9588,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>Участок 0,4 га, семь корпусов 5–8 этажей в индивидуальной архитектуре. В базе делюкс-стартов 2026–2027 mskdeluxe.ru.</t>
+          <t>Семь корпусов 5–8 эт. на 0,4 га в Хамовниках у м. Фрунзенская, индивидуальная архитектура; делюкс</t>
         </is>
       </c>
     </row>
@@ -9576,19 +9608,19 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>Aurix Development (Группа «Эталон»)</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>старт продаж 2026</t>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Aurix Development</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>старт продаж 2026 (по сайту проекта); строительство не начато, цены не опубликованы (08.09.2026)</t>
         </is>
       </c>
       <c r="G23" s="11" t="n"/>
@@ -9605,7 +9637,7 @@
         </is>
       </c>
       <c r="L23" s="11" t="n"/>
-      <c r="M23" s="20" t="n"/>
+      <c r="M23" s="22" t="n"/>
       <c r="N23" s="11" t="n"/>
       <c r="O23" s="15" t="inlineStr">
         <is>
@@ -9614,7 +9646,7 @@
       </c>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>9 этажей, 34 квартиры, паркинг на 36 м/м, проект Etalon Project. Продажи открыты в 2026 г.; стадия строительства в открытых источниках не уточнена.</t>
+          <t>Клубный дом 9 эт. на 34 резиденции у Третьяковской галереи, паркинг 36 м/м, отделка премиум, мотивы русского фольклора</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9666,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -9646,20 +9678,24 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>проект утверждён (АГР, май 2026), начало строительства 2027</t>
+          <t>проект утверждён (АГР, май 2026); начало строительства 2027, старт продаж ожидается в 2027</t>
         </is>
       </c>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>8–24 (жилые корпуса переменной этажности)</t>
+        </is>
+      </c>
       <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>2027 (стройка)</t>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>2027 (стройка и старт продаж)</t>
         </is>
       </c>
       <c r="L24" s="5" t="n"/>
-      <c r="M24" s="22" t="n"/>
+      <c r="M24" s="21" t="n"/>
       <c r="N24" s="5" t="inlineStr">
         <is>
           <t>2026-05-28</t>
@@ -9672,7 +9708,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>Два жилых корпуса переменной этажности в неоклассике + эллиптический БЦ 26 тыс. м² («яйцо Фаберже»). Концепция согласована Департаментом градостроительной политики (В. Овчинский). Параметры жилой части не раскрыты.</t>
+          <t>Квартал на 5,27 га у Лужников: два жилых корпуса 8–24 эт. в неоклассике + эллиптический БЦ «яйцо Фаберже» 26 тыс. м²</t>
         </is>
       </c>
     </row>
@@ -9692,7 +9728,7 @@
           <t>Басманный</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -9704,7 +9740,7 @@
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>старт продаж июль–август 2026</t>
+          <t>проектирование (kvartiravmoskve.ru, 15.07.2026); старт продаж заявлен на июль–август 2026, цены не опубликованы</t>
         </is>
       </c>
       <c r="G25" s="11" t="n"/>
@@ -9719,7 +9755,7 @@
         </is>
       </c>
       <c r="L25" s="11" t="n"/>
-      <c r="M25" s="20" t="n"/>
+      <c r="M25" s="22" t="n"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
           <t>2026-07</t>
@@ -9732,7 +9768,7 @@
       </c>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>Клубный дом делюкс-класса у Чистых прудов, 1 монолитный корпус 7 этажей, архитектура WALL. В обзоре делюкс-стартов 2026 novostroev.ru фигурировал как Veil, 9 этажей.</t>
+          <t>Камерный клубный дом 7 эт. у Чистых прудов, монолит-кирпич, двор без машин, архитектура WALL; делюкс</t>
         </is>
       </c>
     </row>
@@ -9752,23 +9788,23 @@
           <t>Мещанский</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Sminex (проект выкуплен у «Галс-Девелопмент»)</t>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Sminex</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>проект приобретён, старт продаж ожидается</t>
+          <t>проект дорабатывается под стандарты Sminex; по gdeetotdom.ru — возведение стен; продажи по запросу, старт не объявлен</t>
         </is>
       </c>
       <c r="G26" s="7" t="n">
-        <v>36400</v>
+        <v>31000</v>
       </c>
       <c r="H26" s="7" t="n">
         <v>18000</v>
@@ -9780,8 +9816,12 @@
         <v>115</v>
       </c>
       <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="22" t="n"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>2 кв. 2030</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="n"/>
       <c r="N26" s="5" t="inlineStr">
         <is>
           <t>2025-12-12</t>
@@ -9794,7 +9834,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>Семь корпусов 2–10 этажей, 115 квартир 61–426 м², таунхаусы и пентхаусы, двор-парк Scape, реставрация особняка конца XIX в. Сделка 12.12.2025.</t>
+          <t>Семь клубных домов 2–10 эт., 115 квартир 61–426 м² у Кузнецкого Моста, двор-парк, реставрация особняка XIX в.</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9854,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -9826,7 +9866,7 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>участок приобретён (апрель 2026), проектирование</t>
+          <t>участок приобретён (апрель 2026), проектирование; сроки не объявлены (08.09.2026)</t>
         </is>
       </c>
       <c r="G27" s="13" t="n">
@@ -9839,7 +9879,7 @@
       <c r="J27" s="11" t="n"/>
       <c r="K27" s="11" t="n"/>
       <c r="L27" s="11" t="n"/>
-      <c r="M27" s="20" t="n"/>
+      <c r="M27" s="22" t="n"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
           <t>2026-04-24</t>
@@ -9852,7 +9892,7 @@
       </c>
       <c r="P27" s="10" t="inlineStr">
         <is>
-          <t>Участок 0,5 га (бывшая шёлковая фабрика, 4 здания 5 тыс. м²), продавец KR Properties (А. Клячин), переход прав 23.04.2026. Камерный клубный дом: пентхаусы с видом на Кремль, виллы, двор-сад; фасады по ул. Тимура Фрунзе сохраняются.</t>
+          <t>Камерный клубный дом на 0,5 га бывшей шёлковой фабрики: пентхаусы с видом на Кремль, виллы, двор-сад среди ОКН</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9912,7 @@
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -9884,7 +9924,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>участок приобретён (март 2026), проектирование</t>
+          <t>участок приобретён (март 2026), проектирование; параметры и сроки не раскрыты (08.09.2026)</t>
         </is>
       </c>
       <c r="G28" s="5" t="n"/>
@@ -9893,7 +9933,7 @@
       <c r="J28" s="5" t="n"/>
       <c r="K28" s="5" t="n"/>
       <c r="L28" s="5" t="n"/>
-      <c r="M28" s="22" t="n"/>
+      <c r="M28" s="21" t="n"/>
       <c r="N28" s="5" t="inlineStr">
         <is>
           <t>2026-03-17</t>
@@ -9906,7 +9946,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>Участок 1,8 га, 8 зданий 38,5 тыс. м², в т.ч. 3 корпуса типографии Сытина (ОКН, арх. Эрихсон/Шухов). Продавец — В. Погребенко, оценка сделки 12–14 млрд руб., инвестиции 25–30 млрд руб. План: реставрация + новые элитные клубные дома. Участок у Садового кольца (Валовая ул.).</t>
+          <t>Реставрация типографии Сытина (ОКН) и новые клубные дома на 1,8 га в Замоскворечье; двор-парк, виды на Кремль</t>
         </is>
       </c>
     </row>
@@ -9926,32 +9966,36 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>ГК «Векторстройфинанс» (VSF)</t>
+          <t>ГК «Векторстройфинанс»</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>анонсирован (приобретение объекта), концепция</t>
+          <t>концепция бюро МЛА+ опубликована (январь 2026); сроки строительства не объявлены, реализация именно этой концепции не подтверждена</t>
         </is>
       </c>
       <c r="G29" s="13" t="n">
         <v>2500</v>
       </c>
       <c r="H29" s="11" t="n"/>
-      <c r="I29" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J29" s="11" t="n"/>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>4–10 (башня 10 эт. + клубный корпус 4 эт.)</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>27</v>
+      </c>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="11" t="n"/>
-      <c r="M29" s="20" t="n"/>
+      <c r="M29" s="22" t="n"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
           <t>2025-07-09</t>
@@ -9964,7 +10008,7 @@
       </c>
       <c r="P29" s="10" t="inlineStr">
         <is>
-          <t>Четырёхэтажное здание 1889 г. и двухэтажное до 1812 г., ~2,5 тыс. м². Оценка инвестиций 3,5–4,5 млрд руб., стоимость объекта до 1,3 млрд руб. Планируется перестройка в элитный клубный дом.</t>
+          <t>Клубный дом на месте усадьбы Якунина: башня «Шёлк» 10 эт. и корпус «Кашемир» 4 эт., 27 квартир, вход-«игольное ушко»</t>
         </is>
       </c>
     </row>
@@ -9984,7 +10028,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -9996,7 +10040,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>проект, продажи не начаты</t>
+          <t>проект, продажи не начаты (novostroev.ru, 03.09.2026); старт продаж заявлен на 2026</t>
         </is>
       </c>
       <c r="G30" s="7" t="n">
@@ -10012,8 +10056,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="22" t="n"/>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="M30" s="21" t="n"/>
       <c r="N30" s="5" t="n"/>
       <c r="O30" s="9" t="inlineStr">
         <is>
@@ -10022,7 +10070,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>Участок ~0,4 га, два корпуса ~14 и 18 этажей, архитектура Arch(e)type, двор без машин. Площадь 24,6 тыс. м² — по обзору делюкс-стартов 2026 novostroev.ru.</t>
+          <t>Два корпуса 14–18 эт. на 0,4 га у м. Спортивная, Arch(e)type, двор без машин, SPA с бассейном; делюкс</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10102,7 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>решение о КРТ (по данным заказчика — август 2026); оператор/правообладатель и торги в открытых источниках не найдены</t>
+          <t>решение о КРТ (август 2026); оператор/правообладатель и торги в открытых источниках не найдены (проверка 08.09.2026)</t>
         </is>
       </c>
       <c r="G31" s="13" t="n">
@@ -10067,7 +10115,7 @@
       <c r="J31" s="11" t="n"/>
       <c r="K31" s="11" t="n"/>
       <c r="L31" s="11" t="n"/>
-      <c r="M31" s="20" t="n"/>
+      <c r="M31" s="22" t="n"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -10080,7 +10128,7 @@
       </c>
       <c r="P31" s="10" t="inlineStr">
         <is>
-          <t>Участок ~0,3 га включён в программу КРТ решением властей Москвы. Существующие здания реконструированы в 2004 г., в 2020 г. переоборудованы под хостелы. Оператор/девелопер в публикации не назван; в других открытых источниках на 07.09.2026 не найден. Локация — Пресненский район вне Садового кольца, между Б. Грузинской и Пресненским Валом (условно отнесено к зоне Пресня/Сити).; Поиск по mos.ru, krt.mos.ru, stroi.mos.ru, Ведомости, РБК, Интерфакс, М24, Известия (август–сентябрь 2026) не выявил отдельной публикации по этому участку: новости августа 2026 о КРТ (250 проектов, 63 договора с начала года) даются агрегированно. Ближайший крупный проект — квартал «Тишинский бульвар» Sminex (Электрический пер., 1), связь с участком №8 не подтверждена. Площадь 0,3 га / ~10 000 м² — из исходных данных запроса, независимого подтверждения нет.</t>
+          <t>Участок КРТ 0,3 га с двумя зданиями (хостелы) на Пресне между Б. Грузинской и Пресненским Валом; параметры не раскрыты</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10148,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -10112,7 +10160,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>проектирование (долгосрочный проект), старт продаж ожидается</t>
+          <t>статус противоречив: novostroy-m.ru — проект 2016 г. «скоро старт»; novostroev.ru (03.09.2026) — «строительство/продажи завершены»; mskdeluxe.ru — старт 2026–2027</t>
         </is>
       </c>
       <c r="G32" s="7" t="n">
@@ -10121,8 +10169,10 @@
       <c r="H32" s="7" t="n">
         <v>8800</v>
       </c>
-      <c r="I32" s="7" t="n">
-        <v>8</v>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>3–8</t>
+        </is>
       </c>
       <c r="J32" s="5" t="n"/>
       <c r="K32" s="5" t="inlineStr">
@@ -10131,7 +10181,7 @@
         </is>
       </c>
       <c r="L32" s="5" t="n"/>
-      <c r="M32" s="22" t="n"/>
+      <c r="M32" s="21" t="n"/>
       <c r="N32" s="5" t="n"/>
       <c r="O32" s="9" t="inlineStr">
         <is>
@@ -10140,7 +10190,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>3–8 этажей, монолит-кирпич, коммерция 1,8 тыс. м², паркинг 170 м/м. Карточка novostroy-m.ru датирована 2016 г.; проект вновь фигурирует в списке делюкс-стартов 2026–2027 на mskdeluxe.ru. Актуальность требует проверки.</t>
+          <t>Клубный дом 3–8 эт. на «Золотой миле», 19,8 тыс. м², жильё 8,8 тыс. м², коммерция 1,8 тыс. м², паркинг 170 м/м</t>
         </is>
       </c>
     </row>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,6 +69,10 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -159,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -180,11 +184,14 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -198,11 +205,14 @@
     <xf numFmtId="3" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -219,10 +229,10 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -596,15 +606,15 @@
   <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -612,7 +622,7 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="7" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="74" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -716,7 +726,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Резиденция Тверская</t>
@@ -787,90 +797,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q4" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 12 эт. на 190 апартаментов с отель-сервисом и отделкой, у Белорусской и Маяковской</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>NEVA TOWERS (Нева Тауэрс)</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Renaissance Development</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>4 кв. 2020</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Москва, 1-й Красногвардейский, 22с2</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>63-79</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <v>615385</v>
       </c>
-      <c r="K5" s="14" t="n">
+      <c r="K5" s="15" t="n">
         <v>880626</v>
       </c>
-      <c r="L5" s="13" t="n">
+      <c r="L5" s="14" t="n">
         <v>2171244</v>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="14" t="n">
         <v>123</v>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>39–764</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P5" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q5" s="17" t="inlineStr">
         <is>
           <t>Две башни 63 и 77 эт. в Сити на общем стилобате, апартаменты, панорамные окна, бассейн на крыше</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="26" customHeight="1">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Sinatra (Синатра)</t>
@@ -941,90 +951,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="Q6" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 7 эт. на 82 апартамента и пентхауса с потолками до 5,5 м, Тишинка у Белорусской</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>LUMIN (ЛЮМИН)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Hutton</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Москва, Славянская, 2/5с1</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Таганский</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <v>900901</v>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="K7" s="15" t="n">
         <v>1070076</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="14" t="n">
         <v>2658908</v>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t>52–213</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O7" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P7" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q7" s="10" t="inlineStr">
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q7" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 8 эт. на 58 лотов, стеклянные фасады (ЦЛП), терраса на крыше, 250 м от Зарядья</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Уланский, 13</t>
@@ -1050,7 +1060,7 @@
           <t>Красносельский</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -1095,90 +1105,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="Q8" s="10" t="inlineStr">
         <is>
           <t>Реконструкция доходного дома 1886 г., 4 эт., 10 квартир и 2 пентхауса, у Чистых прудов</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Современник</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Vesper</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Москва, Машкова, 13С1</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Басманный</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="14" t="n">
         <v>1100000</v>
       </c>
-      <c r="K9" s="14" t="n">
+      <c r="K9" s="15" t="n">
         <v>1111959</v>
       </c>
-      <c r="L9" s="13" t="n">
+      <c r="L9" s="14" t="n">
         <v>1123919</v>
       </c>
-      <c r="M9" s="13" t="n">
+      <c r="M9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t>34–34</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P9" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q9" s="17" t="inlineStr">
         <is>
           <t>Реконструкция дома XIX в. с надстройкой, 5 эт., 86 квартир, у Чистых прудов и Красных Ворот</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Репаблик</t>
@@ -1249,90 +1259,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="Q10" s="10" t="inlineStr">
         <is>
           <t>Квартал из 10 башен 26–33 эт. на месте вагонных мастерских, лобби до 7 м, у Белорусской</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>City Park (Сити Парк)</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>ГК МонАрх</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>2019–2021</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Москва, Мантулинская, 9к4</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>6-24</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J11" s="13" t="n">
+      <c r="J11" s="14" t="n">
         <v>788028</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="15" t="n">
         <v>1183147</v>
       </c>
-      <c r="L11" s="13" t="n">
+      <c r="L11" s="14" t="n">
         <v>2129032</v>
       </c>
-      <c r="M11" s="13" t="n">
+      <c r="M11" s="14" t="n">
         <v>58</v>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N11" s="12" t="inlineStr">
         <is>
           <t>34–251</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O11" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P11" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="P11" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q11" s="17" t="inlineStr">
         <is>
           <t>Квартал из 6 корпусов 6–20 эт., 1220 квартир, двор-парк, рядом с Сити и парком Красная Пресня</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SkyView</t>
@@ -1403,90 +1413,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="Q12" s="10" t="inlineStr">
         <is>
           <t>Четыре 20-эт. башни на 304 апартамента у Белого дома, панорамные виды, парк Пресня рядом</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Полянка/44</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Группа ПСН</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>1 кв. 2019</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Москва, Большая Полянка, 44</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>6-7</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="J13" s="14" t="n">
         <v>1135408</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="15" t="n">
         <v>1214499</v>
       </c>
-      <c r="L13" s="13" t="n">
+      <c r="L13" s="14" t="n">
         <v>2109833</v>
       </c>
-      <c r="M13" s="13" t="n">
+      <c r="M13" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t>117–271</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O13" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P13" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q13" s="10" t="inlineStr">
+      <c r="P13" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q13" s="17" t="inlineStr">
         <is>
           <t>Квартал из 8 особняков (3 исторических) по 22–24 квартиры, сад с ручьём, паркинг, у Полянки</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Титул на Серебрянической</t>
@@ -1512,7 +1522,7 @@
           <t>Таганский</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -1557,90 +1567,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Квартал из 8 домов-особняков 7–9 эт., 59 лотов, фасады из юрского мрамора, 1,5 км до Зарядья</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Bogenhouse (Богенхаус)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Lexion Development</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Москва, Озерковская, 6</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>5-6</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J15" s="13" t="n">
+      <c r="J15" s="14" t="n">
         <v>985887</v>
       </c>
-      <c r="K15" s="14" t="n">
+      <c r="K15" s="15" t="n">
         <v>1247727</v>
       </c>
-      <c r="L15" s="13" t="n">
+      <c r="L15" s="14" t="n">
         <v>2000000</v>
       </c>
-      <c r="M15" s="13" t="n">
+      <c r="M15" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="12" t="inlineStr">
         <is>
           <t>43–355</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P15" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
+      <c r="P15" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q15" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 5 эт. на 43 апартамента и 5 пентхаусов на Озерковской наб., Замоскворечье</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Capital Towers (Капитал Тауэрс)</t>
@@ -1666,7 +1676,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
@@ -1711,90 +1721,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="Q16" s="10" t="inlineStr">
         <is>
           <t>Три башни 61–65 эт. на стилобате у Сити, 787 квартир, виды на реку и парк Красная Пресня</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Интеко</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Москва, Садовническая, 7</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>5-6</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J17" s="13" t="n">
+      <c r="J17" s="14" t="n">
         <v>1094488</v>
       </c>
-      <c r="K17" s="14" t="n">
+      <c r="K17" s="15" t="n">
         <v>1268025</v>
       </c>
-      <c r="L17" s="13" t="n">
+      <c r="L17" s="14" t="n">
         <v>1927419</v>
       </c>
-      <c r="M17" s="13" t="n">
+      <c r="M17" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="N17" s="12" t="inlineStr">
         <is>
           <t>124–400</t>
         </is>
       </c>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="O17" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P17" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q17" s="10" t="inlineStr">
+      <c r="P17" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q17" s="17" t="inlineStr">
         <is>
           <t>Апарт-комплекс 9 эт. на 116 резиденций на Садовнической наб., панорамные окна, 10 мин до Кремля</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Титул на Якиманке</t>
@@ -1820,7 +1830,7 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -1865,90 +1875,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="Q18" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 6 эт. на 18 квартир с потолками 3,5 м, 2 пентхауса, 200 м от м. Полянка</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Клубный дом ЦВЕТ32</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Hutton</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Москва, Цветной, 32А</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Мещанский</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J19" s="13" t="n">
+      <c r="J19" s="14" t="n">
         <v>1120690</v>
       </c>
-      <c r="K19" s="14" t="n">
+      <c r="K19" s="15" t="n">
         <v>1363636</v>
       </c>
-      <c r="L19" s="13" t="n">
+      <c r="L19" s="14" t="n">
         <v>1972477</v>
       </c>
-      <c r="M19" s="13" t="n">
+      <c r="M19" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="N19" s="12" t="inlineStr">
         <is>
           <t>37–218</t>
         </is>
       </c>
-      <c r="O19" s="11" t="inlineStr">
+      <c r="O19" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P19" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q19" s="10" t="inlineStr">
+      <c r="P19" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q19" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 8 эт. на 47 апартаментов, фасады из травертина (ЦЛП), у Цветного бульвара</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>A.Residence (А Резиденс)</t>
@@ -1974,7 +1984,7 @@
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -2019,90 +2029,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="Q20" s="10" t="inlineStr">
         <is>
           <t>Пять корпусов 5–9 эт., 190 апартаментов и пентхаусов, фасады из камня (ЦЛП), Садовническая</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Roza Rossa (Роза Росса)</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>KR Properties</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Москва, Зубовская, 7</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J21" s="13" t="n">
+      <c r="J21" s="14" t="n">
         <v>1010101</v>
       </c>
-      <c r="K21" s="14" t="n">
+      <c r="K21" s="15" t="n">
         <v>1380000</v>
       </c>
-      <c r="L21" s="13" t="n">
+      <c r="L21" s="14" t="n">
         <v>1408163</v>
       </c>
-      <c r="M21" s="13" t="n">
+      <c r="M21" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="N21" s="11" t="inlineStr">
+      <c r="N21" s="12" t="inlineStr">
         <is>
           <t>49–316</t>
         </is>
       </c>
-      <c r="O21" s="11" t="inlineStr">
+      <c r="O21" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P21" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q21" s="10" t="inlineStr">
+      <c r="P21" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q21" s="17" t="inlineStr">
         <is>
           <t>Дом 6 эт. на 120 апартаментов по проекту Пьеро Лиссони, сервис отеля Метрополь, SPA, бассейн</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Собрание клубных домов ORDYNKA (Ордынка)</t>
@@ -2128,7 +2138,7 @@
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -2173,90 +2183,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr">
+      <c r="Q22" s="10" t="inlineStr">
         <is>
           <t>Собрание 7 клубных домов, ок. 90 лотов, исторические особняки и новые корпуса, у Третьяковки</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Дом NV/9</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>INSIGMA / State Development</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Москва, Большой Николоворобинский, 9к1</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Таганский</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J23" s="13" t="n">
+      <c r="J23" s="14" t="n">
         <v>1454693</v>
       </c>
-      <c r="K23" s="14" t="n">
+      <c r="K23" s="15" t="n">
         <v>1467116</v>
       </c>
-      <c r="L23" s="13" t="n">
+      <c r="L23" s="14" t="n">
         <v>1504854</v>
       </c>
-      <c r="M23" s="13" t="n">
+      <c r="M23" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="N23" s="11" t="inlineStr">
+      <c r="N23" s="12" t="inlineStr">
         <is>
           <t>61–118</t>
         </is>
       </c>
-      <c r="O23" s="11" t="inlineStr">
+      <c r="O23" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P23" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q23" s="10" t="inlineStr">
+      <c r="P23" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q23" s="17" t="inlineStr">
         <is>
           <t>Два клубных корпуса 4–9 эт. на 77 квартир, 6 пентхаусов с каминами, патио, у Яузы</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1">
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Fantastic House (Фантастик Хаус)</t>
@@ -2327,90 +2337,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="inlineStr">
+      <c r="Q24" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 6 эт. на 28 лотов с фасадом доходного дома 1908 г. (ЦЛП), у Малой Грузинской</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Клубный дом Космо 4/22</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Галс-Девелопмент</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>2 кв. 2025</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Москва, Космодамианская, 4/22</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J25" s="13" t="n">
+      <c r="J25" s="14" t="n">
         <v>1326531</v>
       </c>
-      <c r="K25" s="14" t="n">
+      <c r="K25" s="15" t="n">
         <v>1531532</v>
       </c>
-      <c r="L25" s="13" t="n">
+      <c r="L25" s="14" t="n">
         <v>5300745</v>
       </c>
-      <c r="M25" s="13" t="n">
+      <c r="M25" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="N25" s="11" t="inlineStr">
+      <c r="N25" s="12" t="inlineStr">
         <is>
           <t>47–174</t>
         </is>
       </c>
-      <c r="O25" s="11" t="inlineStr">
+      <c r="O25" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P25" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q25" s="10" t="inlineStr">
+      <c r="P25" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q25" s="17" t="inlineStr">
         <is>
           <t>Два клубных корпуса 6 эт. на 73 квартиры, 11 пентхаусов, стиль модерн, Космодамианская наб.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
+    <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Софийский</t>
@@ -2436,7 +2446,7 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -2481,34 +2491,34 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q26" s="4" t="inlineStr">
+      <c r="Q26" s="10" t="inlineStr">
         <is>
           <t>Апарт-комплекс 8 эт. на Балчуге в 500 м от Кремля, окна в пол с видом на Кремль, отель-сервис</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Дом на Тишинке</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Донстрой</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Москва, Средний Тишинский, 5</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
@@ -2518,53 +2528,53 @@
           <t>Пресня</t>
         </is>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>7-20</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J27" s="13" t="n">
+      <c r="J27" s="14" t="n">
         <v>1500000</v>
       </c>
-      <c r="K27" s="14" t="n">
+      <c r="K27" s="15" t="n">
         <v>1614969</v>
       </c>
-      <c r="L27" s="13" t="n">
+      <c r="L27" s="14" t="n">
         <v>2147239</v>
       </c>
-      <c r="M27" s="13" t="n">
+      <c r="M27" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="N27" s="11" t="inlineStr">
+      <c r="N27" s="12" t="inlineStr">
         <is>
           <t>84–243</t>
         </is>
       </c>
-      <c r="O27" s="11" t="inlineStr">
+      <c r="O27" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P27" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q27" s="10" t="inlineStr">
+      <c r="P27" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q27" s="17" t="inlineStr">
         <is>
           <t>Два корпуса 18 эт. на 142 квартиры от 87 м², пентхаусы с патио и каминами, Тишинка</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="26" customHeight="1">
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Тессинский, 1</t>
@@ -2590,7 +2600,7 @@
           <t>Таганский</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -2635,34 +2645,34 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q28" s="4" t="inlineStr">
+      <c r="Q28" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 8 эт. и особняк, 71 лот, пентхаусы с потолками 6,9 м и каминами, у Яузы</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Lucky (Лаки)</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Vesper</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>1 кв. 2023</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Москва, Костикова, 4к1</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
@@ -2672,53 +2682,53 @@
           <t>Пресня</t>
         </is>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>15-21</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J29" s="13" t="n">
+      <c r="J29" s="14" t="n">
         <v>1296875</v>
       </c>
-      <c r="K29" s="14" t="n">
+      <c r="K29" s="15" t="n">
         <v>1680791</v>
       </c>
-      <c r="L29" s="13" t="n">
+      <c r="L29" s="14" t="n">
         <v>2352941</v>
       </c>
-      <c r="M29" s="13" t="n">
+      <c r="M29" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="N29" s="11" t="inlineStr">
+      <c r="N29" s="12" t="inlineStr">
         <is>
           <t>44–434</t>
         </is>
       </c>
-      <c r="O29" s="11" t="inlineStr">
+      <c r="O29" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P29" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q29" s="10" t="inlineStr">
+      <c r="P29" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q29" s="17" t="inlineStr">
         <is>
           <t>Квартал из 8 корпусов 15–21 эт., 619 квартир, дворы без машин, 200 м от м. Улица 1905 года</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Artisan (Артисан)</t>
@@ -2744,7 +2754,7 @@
           <t>Арбат</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -2789,90 +2799,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="inlineStr">
+      <c r="Q30" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 5 эт. на 32 резиденции, воссозданный ампирный фасад, на Арбате</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Абрикосов</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>MR Group</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Москва, Потаповский, 6С1</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Басманный</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>5-6</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J31" s="13" t="n">
+      <c r="J31" s="14" t="n">
         <v>1558355</v>
       </c>
-      <c r="K31" s="14" t="n">
+      <c r="K31" s="15" t="n">
         <v>1785730</v>
       </c>
-      <c r="L31" s="13" t="n">
+      <c r="L31" s="14" t="n">
         <v>2094241</v>
       </c>
-      <c r="M31" s="13" t="n">
+      <c r="M31" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="N31" s="11" t="inlineStr">
+      <c r="N31" s="12" t="inlineStr">
         <is>
           <t>67–191</t>
         </is>
       </c>
-      <c r="O31" s="11" t="inlineStr">
+      <c r="O31" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P31" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q31" s="10" t="inlineStr">
+      <c r="P31" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q31" s="17" t="inlineStr">
         <is>
           <t>Реконструкция особняка Абрикосовых на палатах XVII в., 5 эт., 26 квартир, у Чистых прудов</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="26" customHeight="1">
+    <row r="32" ht="24" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Клубный дом CULT (Клубный дом Культ)</t>
@@ -2898,7 +2908,7 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -2943,90 +2953,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q32" s="4" t="inlineStr">
+      <c r="Q32" s="10" t="inlineStr">
         <is>
           <t>Дом 9 эт. на 91 квартиру с отделкой, 12 пентхаусов, каменные фасады, на месте гостиницы Варшава</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Гардтекс</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Москва, Саввинская, 13</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J33" s="13" t="n">
+      <c r="J33" s="14" t="n">
         <v>1869231</v>
       </c>
-      <c r="K33" s="14" t="n">
+      <c r="K33" s="15" t="n">
         <v>1884615</v>
       </c>
-      <c r="L33" s="13" t="n">
+      <c r="L33" s="14" t="n">
         <v>3751412</v>
       </c>
-      <c r="M33" s="13" t="n">
+      <c r="M33" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="N33" s="11" t="inlineStr">
+      <c r="N33" s="12" t="inlineStr">
         <is>
           <t>125–177</t>
         </is>
       </c>
-      <c r="O33" s="11" t="inlineStr">
+      <c r="O33" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P33" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q33" s="10" t="inlineStr">
+      <c r="P33" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q33" s="17" t="inlineStr">
         <is>
           <t>Четыре корпуса 4–9 эт. на 169 квартир на Саввинской наб., окна в пол, виды на реку</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="26" customHeight="1">
+    <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Пироговская 14</t>
@@ -3052,7 +3062,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -3097,90 +3107,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="Q34" s="10" t="inlineStr">
         <is>
           <t>Клубный апарт-дом 9 эт. на 53 лота, фитнес, библиотека, паркинг на 61 м/м, Хамовники у Усачёва</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Cloud Nine (Клауд Найн)</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Vesper</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Москва, Большая Полянка, 9С2</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F35" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="G35" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>4-7</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>квартиры + апартаменты</t>
         </is>
       </c>
-      <c r="J35" s="13" t="n">
+      <c r="J35" s="14" t="n">
         <v>1800766</v>
       </c>
-      <c r="K35" s="14" t="n">
+      <c r="K35" s="15" t="n">
         <v>2050124</v>
       </c>
-      <c r="L35" s="13" t="n">
+      <c r="L35" s="14" t="n">
         <v>2820513</v>
       </c>
-      <c r="M35" s="13" t="n">
+      <c r="M35" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="11" t="inlineStr">
+      <c r="N35" s="12" t="inlineStr">
         <is>
           <t>195–261</t>
         </is>
       </c>
-      <c r="O35" s="11" t="inlineStr">
+      <c r="O35" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P35" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q35" s="10" t="inlineStr">
+      <c r="P35" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q35" s="17" t="inlineStr">
         <is>
           <t>Реконструкция 4 исторических зданий, 7–9 эт., 45 квартир, паркинг на 70 м/м, 900 м от Кремля</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="26" customHeight="1">
+    <row r="36" ht="15" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Симфония набережных (Котельническая 21)</t>
@@ -3206,7 +3216,7 @@
           <t>Таганский</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -3251,90 +3261,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q36" s="4" t="inlineStr">
+      <c r="Q36" s="10" t="inlineStr">
         <is>
           <t>Дом 8 эт. в стиле ампир на 53 квартиры, фасады из известняка, виды на Кремль и Зарядье</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Садовые кварталы</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Интеко</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>2014–2022</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Москва, Усачева, 15А</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="F37" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>5-18</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J37" s="13" t="n">
+      <c r="J37" s="14" t="n">
         <v>1328904</v>
       </c>
-      <c r="K37" s="14" t="n">
+      <c r="K37" s="15" t="n">
         <v>2111111</v>
       </c>
-      <c r="L37" s="13" t="n">
+      <c r="L37" s="14" t="n">
         <v>3718750</v>
       </c>
-      <c r="M37" s="13" t="n">
+      <c r="M37" s="14" t="n">
         <v>83</v>
       </c>
-      <c r="N37" s="11" t="inlineStr">
+      <c r="N37" s="12" t="inlineStr">
         <is>
           <t>54–342</t>
         </is>
       </c>
-      <c r="O37" s="11" t="inlineStr">
+      <c r="O37" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P37" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q37" s="10" t="inlineStr">
+      <c r="P37" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q37" s="17" t="inlineStr">
         <is>
           <t>Квартал из 33 клубных домов на 11 га с прудом и парком, ок. 920 квартир, у Новодевичьего</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="26" customHeight="1">
+    <row r="38" ht="15" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Малая Ордынка 19</t>
@@ -3360,7 +3370,7 @@
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F38" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -3405,90 +3415,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q38" s="4" t="inlineStr">
+      <c r="Q38" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 6 эт. на 67 квартир, потолки 3,3–3,6 м, паркинг на 124 м/м, у Третьяковской</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Дом в Газетном</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Актив-Центр</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Москва, Газетный, 13с2</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F39" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="G39" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="I39" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J39" s="13" t="n">
+      <c r="J39" s="14" t="n">
         <v>1856148</v>
       </c>
-      <c r="K39" s="14" t="n">
+      <c r="K39" s="15" t="n">
         <v>2290538</v>
       </c>
-      <c r="L39" s="13" t="n">
+      <c r="L39" s="14" t="n">
         <v>4859444</v>
       </c>
-      <c r="M39" s="13" t="n">
+      <c r="M39" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="N39" s="11" t="inlineStr">
+      <c r="N39" s="12" t="inlineStr">
         <is>
           <t>65–664</t>
         </is>
       </c>
-      <c r="O39" s="11" t="inlineStr">
+      <c r="O39" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P39" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q39" s="10" t="inlineStr">
+      <c r="P39" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q39" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 5 эт. на 24 апартамента, пентхаусы и городская вилла, 1 км от Кремля</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="26" customHeight="1">
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
@@ -3514,7 +3524,7 @@
           <t>Мещанский</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F40" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -3559,90 +3569,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q40" s="4" t="inlineStr">
+      <c r="Q40" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 9 эт. на 27 квартир по 3 на этаже, между Неглинной и Рождественкой</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>White Khamovniki (Вайт Хамовники)</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>Hutton</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>Москва, Олсуфьевский, 9к1</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F41" s="17" t="inlineStr">
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="I41" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J41" s="13" t="n">
+      <c r="J41" s="14" t="n">
         <v>2387268</v>
       </c>
-      <c r="K41" s="14" t="n">
+      <c r="K41" s="15" t="n">
         <v>2387268</v>
       </c>
-      <c r="L41" s="13" t="n">
+      <c r="L41" s="14" t="n">
         <v>2657480</v>
       </c>
-      <c r="M41" s="13" t="n">
+      <c r="M41" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="N41" s="11" t="inlineStr">
+      <c r="N41" s="12" t="inlineStr">
         <is>
           <t>75–152</t>
         </is>
       </c>
-      <c r="O41" s="11" t="inlineStr">
+      <c r="O41" s="12" t="inlineStr">
         <is>
           <t>бизнес (Циан)</t>
         </is>
       </c>
-      <c r="P41" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q41" s="10" t="inlineStr">
+      <c r="P41" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q41" s="17" t="inlineStr">
         <is>
           <t>Две башни 15 эт. на 76 квартир, архбетон и латунь, паркинг на 120 м/м, у Фрунзенской</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1">
+    <row r="42" ht="15" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Золотой, жилой квартал</t>
@@ -3668,7 +3678,7 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="F42" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -3713,90 +3723,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q42" s="4" t="inlineStr">
+      <c r="Q42" s="10" t="inlineStr">
         <is>
           <t>Квартал 1,7 га на Софийской наб., 162 лота с террасами и садами, виды на Кремль, паркинг</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Magnum (Магнум)</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>Magnum Development</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>Москва, Усачева, 9</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F43" s="17" t="inlineStr">
+      <c r="F43" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="G43" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J43" s="13" t="n">
+      <c r="J43" s="14" t="n">
         <v>1568381</v>
       </c>
-      <c r="K43" s="14" t="n">
+      <c r="K43" s="15" t="n">
         <v>2490110</v>
       </c>
-      <c r="L43" s="13" t="n">
+      <c r="L43" s="14" t="n">
         <v>2738095</v>
       </c>
-      <c r="M43" s="13" t="n">
+      <c r="M43" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="N43" s="11" t="inlineStr">
+      <c r="N43" s="12" t="inlineStr">
         <is>
           <t>84–215</t>
         </is>
       </c>
-      <c r="O43" s="11" t="inlineStr">
+      <c r="O43" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P43" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q43" s="10" t="inlineStr">
+      <c r="P43" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q43" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 6 эт. на 44 квартиры, английский стиль, 4 пентхауса с зимними садами, Усачёва</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="26" customHeight="1">
+    <row r="44" ht="15" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Дом Бакст на Патриарших</t>
@@ -3822,7 +3832,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="F44" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -3867,90 +3877,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q44" s="4" t="inlineStr">
+      <c r="Q44" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 3–6 эт. на 18 квартир, панно по Баксту (арх. П. Андреев), у Патриарших</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Villa Grace (Вилла Грейс)</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>ГК Стройтэкс</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>Москва, Пожарский, 3</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F45" s="17" t="inlineStr">
+      <c r="F45" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="G45" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J45" s="13" t="n">
+      <c r="J45" s="14" t="n">
         <v>2635581</v>
       </c>
-      <c r="K45" s="14" t="n">
+      <c r="K45" s="15" t="n">
         <v>2635659</v>
       </c>
-      <c r="L45" s="13" t="n">
+      <c r="L45" s="14" t="n">
         <v>2637704</v>
       </c>
-      <c r="M45" s="13" t="n">
+      <c r="M45" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="N45" s="11" t="inlineStr">
+      <c r="N45" s="12" t="inlineStr">
         <is>
           <t>128–129</t>
         </is>
       </c>
-      <c r="O45" s="11" t="inlineStr">
+      <c r="O45" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P45" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q45" s="10" t="inlineStr">
+      <c r="P45" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q45" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 6–7 эт. на 20 квартир от 100 м², потолки 3,5 м, между Пречистенкой и набережной</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="26" customHeight="1">
+    <row r="46" ht="15" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Brodsky (Бродский)</t>
@@ -3976,7 +3986,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -4021,90 +4031,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q46" s="4" t="inlineStr">
+      <c r="Q46" s="10" t="inlineStr">
         <is>
           <t>Дом 14 эт. на 65 квартир и 2 пентхауса (ЦЛП), детский клуб, wellness, у Новодевичьих прудов</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Жизнь на Плющихе</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Донстрой</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>Москва, Погодинская, 2</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="G47" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
+      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J47" s="13" t="n">
+      <c r="J47" s="14" t="n">
         <v>1253669</v>
       </c>
-      <c r="K47" s="14" t="n">
+      <c r="K47" s="15" t="n">
         <v>3000000</v>
       </c>
-      <c r="L47" s="13" t="n">
+      <c r="L47" s="14" t="n">
         <v>3680336</v>
       </c>
-      <c r="M47" s="13" t="n">
+      <c r="M47" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N47" s="11" t="inlineStr">
+      <c r="N47" s="12" t="inlineStr">
         <is>
           <t>95–254</t>
         </is>
       </c>
-      <c r="O47" s="11" t="inlineStr">
+      <c r="O47" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P47" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q47" s="10" t="inlineStr">
+      <c r="P47" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q47" s="17" t="inlineStr">
         <is>
           <t>Дом из 8 секций 7–13 эт. на 202 квартиры, неоклассика, у Плющихи в Хамовниках</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="26" customHeight="1">
+    <row r="48" ht="15" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Carré Blanc (Карре Бланк)</t>
@@ -4130,7 +4140,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -4175,90 +4185,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q48" s="4" t="inlineStr">
+      <c r="Q48" s="10" t="inlineStr">
         <is>
           <t>Особняк 5 эт. на 46 квартир (Speech), 4 пентхауса, сад 660 м² с фонтаном, у Храма Христа</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Дом Лаврушинский</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Sminex</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>1 кв. 2025</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>Москва, Большой Толмачевский, 5С1</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F49" s="16" t="inlineStr">
+      <c r="F49" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="G49" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="H49" s="12" t="inlineStr">
         <is>
           <t>3-14</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr">
+      <c r="I49" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J49" s="13" t="n">
+      <c r="J49" s="14" t="n">
         <v>1956522</v>
       </c>
-      <c r="K49" s="14" t="n">
+      <c r="K49" s="15" t="n">
         <v>3118040</v>
       </c>
-      <c r="L49" s="13" t="n">
+      <c r="L49" s="14" t="n">
         <v>7453392</v>
       </c>
-      <c r="M49" s="13" t="n">
+      <c r="M49" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="N49" s="11" t="inlineStr">
+      <c r="N49" s="12" t="inlineStr">
         <is>
           <t>66–980</t>
         </is>
       </c>
-      <c r="O49" s="11" t="inlineStr">
+      <c r="O49" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P49" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q49" s="10" t="inlineStr">
+      <c r="P49" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q49" s="17" t="inlineStr">
         <is>
           <t>Квартал из 3 корпусов 8–14 эт. на 98 квартир, прямые виды на Кремль, у Третьяковки</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="26" customHeight="1">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Хамовники 12</t>
@@ -4284,7 +4294,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F50" s="17" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -4329,90 +4339,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q50" s="4" t="inlineStr">
+      <c r="Q50" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 14 эт. на 51 квартиру от 100 м² (арх. Е. Герасимов), 100 м от Саввинской наб.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Stella di Mosca Hotel &amp; Residences (Стелла ди Моска Хотел энд Резиденсиз)</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>Bulgari Hotel &amp; Residences</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>Москва, Большая Никитская, 9</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F51" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="G51" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="H51" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr">
+      <c r="I51" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J51" s="13" t="n">
+      <c r="J51" s="14" t="n">
         <v>3240741</v>
       </c>
-      <c r="K51" s="14" t="n">
+      <c r="K51" s="15" t="n">
         <v>3249768</v>
       </c>
-      <c r="L51" s="13" t="n">
+      <c r="L51" s="14" t="n">
         <v>5584363</v>
       </c>
-      <c r="M51" s="13" t="n">
+      <c r="M51" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="N51" s="11" t="inlineStr">
+      <c r="N51" s="12" t="inlineStr">
         <is>
           <t>107–198</t>
         </is>
       </c>
-      <c r="O51" s="11" t="inlineStr">
+      <c r="O51" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P51" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q51" s="10" t="inlineStr">
+      <c r="P51" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q51" s="17" t="inlineStr">
         <is>
           <t>Отель 5* и 14 брендовых резиденций Bulgari, таунхаусы, пентхаус, SPA, на Большой Никитской</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="26" customHeight="1">
+    <row r="52" ht="24" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Большая Дмитровка IX</t>
@@ -4438,7 +4448,7 @@
           <t>Тверской</t>
         </is>
       </c>
-      <c r="F52" s="16" t="inlineStr">
+      <c r="F52" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -4483,90 +4493,90 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q52" s="4" t="inlineStr">
+      <c r="Q52" s="10" t="inlineStr">
         <is>
           <t>Три корпуса 6 эт.: реконструкция особняка и 2 новых, окна в пол, потолки до 4,6 м, у Большого</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="26" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Малая Бронная 15</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>ЛидЭстейт</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>Москва, Малая Бронная, 15Б</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F53" s="16" t="inlineStr">
+      <c r="F53" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="G53" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="H53" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr">
+      <c r="I53" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J53" s="13" t="n">
+      <c r="J53" s="14" t="n">
         <v>3792852</v>
       </c>
-      <c r="K53" s="14" t="n">
+      <c r="K53" s="15" t="n">
         <v>3795620</v>
       </c>
-      <c r="L53" s="13" t="n">
+      <c r="L53" s="14" t="n">
         <v>6027397</v>
       </c>
-      <c r="M53" s="13" t="n">
+      <c r="M53" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="N53" s="11" t="inlineStr">
+      <c r="N53" s="12" t="inlineStr">
         <is>
           <t>137–219</t>
         </is>
       </c>
-      <c r="O53" s="11" t="inlineStr">
+      <c r="O53" s="12" t="inlineStr">
         <is>
           <t>премиум (Циан)</t>
         </is>
       </c>
-      <c r="P53" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="Q53" s="10" t="inlineStr">
+      <c r="P53" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="Q53" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 7 эт. на 23 квартиры, потолки от 3,6 м, современная классика, у Патриарших</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="26" customHeight="1">
+    <row r="54" ht="15" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Barkli Gallery (Баркли Галлери)</t>
@@ -4592,7 +4602,7 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F54" s="16" t="inlineStr">
+      <c r="F54" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -4637,7 +4647,7 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="Q54" s="4" t="inlineStr">
+      <c r="Q54" s="10" t="inlineStr">
         <is>
           <t>Реконструкция домов 1875 и 1913 гг., 4–7 эт., 43 лота с отделкой, 200 м от Третьяковки</t>
         </is>
@@ -4737,22 +4747,22 @@
   <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="74" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4851,7 +4861,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ЖК «Слава»</t>
@@ -4877,7 +4887,7 @@
           <t>Белорусская</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Белорусская</t>
         </is>
@@ -4913,85 +4923,85 @@
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="10" t="inlineStr">
         <is>
           <t>Квартал из 3 корпусов 6–22 эт. на Ленинградском пр., панорамное остекление, паркинг на 782 м/м</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>ЖК «Дом Дау»</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1-й Красногвардейский</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>2 кв. 2027</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Москва, Краснопресненская набережная</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Москва-Сити</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <v>807900</v>
       </c>
-      <c r="K5" s="14" t="n">
+      <c r="K5" s="15" t="n">
         <v>1032987</v>
       </c>
-      <c r="L5" s="13" t="n">
+      <c r="L5" s="14" t="n">
         <v>1995800</v>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="14" t="n">
         <v>295</v>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O5" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P5" s="10" t="inlineStr">
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P5" s="17" t="inlineStr">
         <is>
           <t>Башня 85 эт., 340 м, 866 квартир на 2-й линии Краснопресненской наб. у Сити, SPA, коворкинг</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="26" customHeight="1">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ЖК «Начало»</t>
@@ -5057,85 +5067,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="P6" s="10" t="inlineStr">
         <is>
           <t>Квартал из 8 корпусов 12–55 эт. на ул. Сергея Макеева, потолки 3,4–4,1 м, у Пресни</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Оне</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>MR Group</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>2 кв. 2030</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Москва, 1-й Красногвардейский, 13</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>90-95</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <v>928571</v>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="K7" s="15" t="n">
         <v>1207700</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="14" t="n">
         <v>1602900</v>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="14" t="n">
         <v>69</v>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O7" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P7" s="10" t="inlineStr">
+      <c r="O7" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P7" s="17" t="inlineStr">
         <is>
           <t>Башня 90 эт., 379 м в Москва-Сити, две башни в форме ленты Мёбиуса, Sky Bridge, сад на 338 м</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>АУРУС Резиденции</t>
@@ -5161,7 +5171,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>Сити</t>
         </is>
@@ -5199,85 +5209,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="P8" s="10" t="inlineStr">
         <is>
           <t>Две башни 96 и 83 эт., 395 м в Сити-2, 1774 квартиры, парк с бассейнами на 7 эт., APEX</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>ЖК «Монблан»</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Галс-Девелопмент</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>1 кв. 2028</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Москва, Шлюзовая набережная</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Павелецкая</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>7-27</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="14" t="n">
         <v>942551</v>
       </c>
-      <c r="K9" s="14" t="n">
+      <c r="K9" s="15" t="n">
         <v>1245333</v>
       </c>
-      <c r="L9" s="13" t="n">
+      <c r="L9" s="14" t="n">
         <v>3159585</v>
       </c>
-      <c r="M9" s="13" t="n">
+      <c r="M9" s="14" t="n">
         <v>72</v>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O9" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P9" s="10" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P9" s="17" t="inlineStr">
         <is>
           <t>Дом из 6 секций 7–27 эт. на Шлюзовой наб., 341 квартира, вид на реку, у Павелецкой</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ЖК «Квартал Life Time»</t>
@@ -5343,85 +5353,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="P10" s="10" t="inlineStr">
         <is>
           <t>Квартал из 6 домов 10–23 эт. на ул. Сергея Макеева, 265 квартир, двор-парк 1,8 га</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>ЖК «Коллекция Лужники»</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Absolute Premium</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>4 кв. 2027</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Москва, Лужнецкая набережная</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Воробьёвы горы</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>12-18</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J11" s="13" t="n">
+      <c r="J11" s="14" t="n">
         <v>1218182</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="15" t="n">
         <v>1591320</v>
       </c>
-      <c r="L11" s="13" t="n">
+      <c r="L11" s="14" t="n">
         <v>4200000</v>
       </c>
-      <c r="M11" s="13" t="n">
+      <c r="M11" s="14" t="n">
         <v>59</v>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N11" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O11" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="inlineStr">
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t>Квартал из 12 домов 12–18 эт. на Лужнецкой наб., парк 8 га, вид на реку и Сити</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Тессинский V</t>
@@ -5447,7 +5457,7 @@
           <t>Таганский</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -5487,85 +5497,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="P12" s="10" t="inlineStr">
         <is>
           <t>Квартал из 4 клубных домов 5–12 эт., 146 резиденций, у Серебрянической наб., Таганка</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Резиденция 1864</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Сбербанк Капитал / Midland Development</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>3 кв. 2027</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Москва, Софийская, 36</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="J13" s="14" t="n">
         <v>1510567</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="15" t="n">
         <v>1617861</v>
       </c>
-      <c r="L13" s="13" t="n">
+      <c r="L13" s="14" t="n">
         <v>3213511</v>
       </c>
-      <c r="M13" s="13" t="n">
+      <c r="M13" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O13" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P13" s="10" t="inlineStr">
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P13" s="17" t="inlineStr">
         <is>
           <t>Реконструкция Кокоревского подворья 1864 г., 7–8 эт., 68 квартир, потолки 4–7 м, Софийская наб.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>ЖК «Элитный квартал Тишинский бульвар»</t>
@@ -5631,85 +5641,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Квартал из 10 домов 6–14 эт. на Тишинке, 404 квартиры, парк-бульвар 1,9 га, бассейн</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>ЖК «Дом Франка»</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Трансстройинвест</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>2 кв. 2026 (Циан: 4 кв. 2026)</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Москва, Большой Кисельный переулок, 11</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Лубянка</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>5-8</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J15" s="13" t="n">
+      <c r="J15" s="14" t="n">
         <v>1581880</v>
       </c>
-      <c r="K15" s="14" t="n">
+      <c r="K15" s="15" t="n">
         <v>1758200</v>
       </c>
-      <c r="L15" s="13" t="n">
+      <c r="L15" s="14" t="n">
         <v>2165109</v>
       </c>
-      <c r="M15" s="13" t="n">
+      <c r="M15" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O15" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P15" s="17" t="inlineStr">
         <is>
           <t>Реконструкция торгового дома 1904 г. (Кекушев) и новый корпус в Б. Кисельном пер., у Лубянки</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ЖК «Татарская 35»</t>
@@ -5735,7 +5745,7 @@
           <t>Новокузнецкая</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -5775,85 +5785,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="P16" s="10" t="inlineStr">
         <is>
           <t>Три корпуса 15–24 эт., 472 квартиры, wellness с бассейном, у Озерковской наб., Замоскворечье</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve"> Клубный дом «Резиденции Воронцова»</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>ГК Развитие</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>2 кв. 2028</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Москва, Обуха</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Таганский</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J17" s="13" t="n">
+      <c r="J17" s="14" t="n">
         <v>1656155</v>
       </c>
-      <c r="K17" s="14" t="n">
+      <c r="K17" s="15" t="n">
         <v>1808841</v>
       </c>
-      <c r="L17" s="13" t="n">
+      <c r="L17" s="14" t="n">
         <v>3549554</v>
       </c>
-      <c r="M17" s="13" t="n">
+      <c r="M17" s="14" t="n">
         <v>52</v>
       </c>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="N17" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O17" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P17" s="10" t="inlineStr">
+      <c r="O17" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P17" s="17" t="inlineStr">
         <is>
           <t>Клубный дом из 2 корпусов, 75 резиденций, потолки до 5,96 м, каменный фасад, ул. Обуха</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ЖК «Дом Соболева»</t>
@@ -5879,7 +5889,7 @@
           <t>Красные ворота</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -5919,34 +5929,34 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="P18" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 7–8 эт. на ул. Машкова, 33 резиденции и 2 пентхауса, потолки 3,55 м, Красные Ворота</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>ЖК «Климашкина 7/11»</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>MR Group</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>4 кв. 2028</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Москва, улица Климашкина, 7/11</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Красная пресня</t>
         </is>
@@ -5956,48 +5966,48 @@
           <t>Пресня</t>
         </is>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>7-9</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J19" s="13" t="n">
+      <c r="J19" s="14" t="n">
         <v>1581360</v>
       </c>
-      <c r="K19" s="14" t="n">
+      <c r="K19" s="15" t="n">
         <v>2105000</v>
       </c>
-      <c r="L19" s="13" t="n">
+      <c r="L19" s="14" t="n">
         <v>2550000</v>
       </c>
-      <c r="M19" s="13" t="n">
+      <c r="M19" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="N19" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O19" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P19" s="10" t="inlineStr">
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P19" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 7–9 эт. (арх. Чобан), 46 резиденций, стена доходного дома 1905 г. Нирнзее, Пресня</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Форум»</t>
@@ -6023,7 +6033,7 @@
           <t>Сухаревская</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -6063,85 +6073,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr">
+      <c r="P20" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 13 эт. на Садовом кольце, 48 квартир, бассейн 20 м, SPA, хаммам, у Сухаревской</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>ЖК «Камергер»</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>ENGEO Development</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>3 кв. 2026</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Москва, Георгиевский переулок, 1</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Охотный Ряд</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>3-6</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J21" s="13" t="n">
+      <c r="J21" s="14" t="n">
         <v>1909308</v>
       </c>
-      <c r="K21" s="14" t="n">
+      <c r="K21" s="15" t="n">
         <v>2171784</v>
       </c>
-      <c r="L21" s="13" t="n">
+      <c r="L21" s="14" t="n">
         <v>4015377</v>
       </c>
-      <c r="M21" s="13" t="n">
+      <c r="M21" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="N21" s="11" t="inlineStr">
+      <c r="N21" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O21" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P21" s="10" t="inlineStr">
+      <c r="O21" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P21" s="17" t="inlineStr">
         <is>
           <t>Комплекс из 5 особняков в 300 м от Кремля, 17 резиденций с террасами, SPA, подземный переход</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
+    <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Казачий</t>
@@ -6167,7 +6177,7 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -6207,85 +6217,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="P22" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 9 эт. (бюро WALL) в 1-м Казачьем пер., 76 квартир и 4 пентхауса, потолки до 3,95 м</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>ЖК «Садовническая 69»</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>ГК БАЛЧУГ ДЕВЕЛОПМЕНТ</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>2 кв. 2028</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Москва, Садовническая улица</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Павелецкая</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>1-10</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J23" s="13" t="n">
+      <c r="J23" s="14" t="n">
         <v>1675161</v>
       </c>
-      <c r="K23" s="14" t="n">
+      <c r="K23" s="15" t="n">
         <v>2265083</v>
       </c>
-      <c r="L23" s="13" t="n">
+      <c r="L23" s="14" t="n">
         <v>4224652</v>
       </c>
-      <c r="M23" s="13" t="n">
+      <c r="M23" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="N23" s="11" t="inlineStr">
+      <c r="N23" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O23" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P23" s="10" t="inlineStr">
+      <c r="O23" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P23" s="17" t="inlineStr">
         <is>
           <t>Клубный квартал из 4 домов 2–10 эт. на Садовнической наб., свой парк 1 га, виллы и пентхаусы</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1">
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Саввинская 17</t>
@@ -6311,7 +6321,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -6351,85 +6361,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr">
+      <c r="P24" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 4 эт. на 1-й линии реки в Хамовниках, 22 квартиры, окна в пол, у Девичьего поля</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>ЖК «Исторический дом «Чистые Пруды»</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Sminex</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>1 кв. 2026</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Москва, Потаповский переулок, 5с4</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Чистые пруды</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J25" s="13" t="n">
+      <c r="J25" s="14" t="n">
         <v>1419298</v>
       </c>
-      <c r="K25" s="14" t="n">
+      <c r="K25" s="15" t="n">
         <v>2460514</v>
       </c>
-      <c r="L25" s="13" t="n">
+      <c r="L25" s="14" t="n">
         <v>4191066</v>
       </c>
-      <c r="M25" s="13" t="n">
+      <c r="M25" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="N25" s="11" t="inlineStr">
+      <c r="N25" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O25" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P25" s="10" t="inlineStr">
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P25" s="17" t="inlineStr">
         <is>
           <t>Реконструкция доходного дома 1915 г. фон Дессина, 7 эт., 36 квартир, в 50 м от Чистых прудов</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>ЖК «PHANTOM»</t>
@@ -6455,7 +6465,7 @@
           <t>Сухаревская</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -6495,85 +6505,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr">
+      <c r="P26" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 7–9 эт. на М. Сухаревской пл., 76 квартир, пентхаусы и дуплексы, у Сухаревской</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Клубный дом TURGENEV (Тургенев)</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>НеоСтрой</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Москва, Костянский, 13</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Красносельский</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J27" s="13" t="n">
+      <c r="J27" s="14" t="n">
         <v>1902180</v>
       </c>
-      <c r="K27" s="14" t="n">
+      <c r="K27" s="15" t="n">
         <v>2523717</v>
       </c>
-      <c r="L27" s="13" t="n">
+      <c r="L27" s="14" t="n">
         <v>5642162</v>
       </c>
-      <c r="M27" s="13" t="n">
+      <c r="M27" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="N27" s="11" t="inlineStr">
+      <c r="N27" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O27" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P27" s="10" t="inlineStr">
+      <c r="O27" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P27" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 8 эт. в Костянском пер., 118 квартир, каменный фасад, бассейн, SPA, у Чистых прудов</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="26" customHeight="1">
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Фамильный дом Люче</t>
@@ -6599,7 +6609,7 @@
           <t>Арбат</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -6639,85 +6649,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P28" s="4" t="inlineStr">
+      <c r="P28" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 7 эт. (арх. Казамонти) в Крестовоздвиженском пер., 43 квартиры и 3 пентхауса</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Кло 17</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Sminex</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>3 кв. 2026</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Москва, Староваганьковский, 17С4</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>Арбат</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F29" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J29" s="13" t="n">
+      <c r="J29" s="14" t="n">
         <v>2300000</v>
       </c>
-      <c r="K29" s="14" t="n">
+      <c r="K29" s="15" t="n">
         <v>2650000</v>
       </c>
-      <c r="L29" s="13" t="n">
+      <c r="L29" s="14" t="n">
         <v>3050000</v>
       </c>
-      <c r="M29" s="13" t="n">
+      <c r="M29" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="N29" s="11" t="inlineStr">
+      <c r="N29" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O29" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P29" s="10" t="inlineStr">
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P29" s="17" t="inlineStr">
         <is>
           <t>Клубный дом (бюро PCA) в Староваганьковском пер., 26 квартир и 2 пентхауса, вид на Кремль</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>ТИТУЛ Империал</t>
@@ -6743,7 +6753,7 @@
           <t>Таганский</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -6783,85 +6793,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="P30" s="10" t="inlineStr">
         <is>
           <t>Клубный дом на 12 квартир в Б. Николоворобинском пер., у Яузы, Таганка</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Клубный дом DUO (Дуо)</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Hutton</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>1 кв. 2028</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Москва, Софийская, 34С3</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J31" s="13" t="n">
+      <c r="J31" s="14" t="n">
         <v>2408900</v>
       </c>
-      <c r="K31" s="14" t="n">
+      <c r="K31" s="15" t="n">
         <v>2772243</v>
       </c>
-      <c r="L31" s="13" t="n">
+      <c r="L31" s="14" t="n">
         <v>4300199</v>
       </c>
-      <c r="M31" s="13" t="n">
+      <c r="M31" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="N31" s="11" t="inlineStr">
+      <c r="N31" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O31" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P31" s="10" t="inlineStr">
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P31" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 6 эт. на Софийской наб. (Кокоревское подворье), 42 квартиры и 5 пентхаусов</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="26" customHeight="1">
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Дом Спорта</t>
@@ -6927,85 +6937,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="P32" s="10" t="inlineStr">
         <is>
           <t>Три корпуса на Дружинниковской ул. у Дома правительства, спорткластер 20 тыс. м² с катками</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>«Ильинка 3/8»</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Sminex</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>1 кв. 2026 (Циан: 3 кв. 2025)</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Москва, улица Ильинка</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Площадь Революции</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F33" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>3-5</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J33" s="13" t="n">
+      <c r="J33" s="14" t="n">
         <v>2286753</v>
       </c>
-      <c r="K33" s="14" t="n">
+      <c r="K33" s="15" t="n">
         <v>2824061</v>
       </c>
-      <c r="L33" s="13" t="n">
+      <c r="L33" s="14" t="n">
         <v>3973321</v>
       </c>
-      <c r="M33" s="13" t="n">
+      <c r="M33" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="N33" s="11" t="inlineStr">
+      <c r="N33" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O33" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P33" s="10" t="inlineStr">
+      <c r="O33" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P33" s="17" t="inlineStr">
         <is>
           <t>7 особняков 3–5 эт. в неорусском стиле в 160 м от Красной пл., 3 памятника XIX в., двор-сад</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="26" customHeight="1">
+    <row r="34" ht="15" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>ЖК «Красный Октябрь»</t>
@@ -7031,7 +7041,7 @@
           <t>Кропоткинская</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F34" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -7071,85 +7081,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr">
+      <c r="P34" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 4–5 эт. из 3 корпусов на Берсеневской наб., 21 квартира, у Стрелки</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>ЖК «Николь»</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>MR Group</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>2027–2028</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Москва, Никольская улица, 8/1с1</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Площадь Революции</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F35" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="G35" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>6-7</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J35" s="13" t="n">
+      <c r="J35" s="14" t="n">
         <v>2325000</v>
       </c>
-      <c r="K35" s="14" t="n">
+      <c r="K35" s="15" t="n">
         <v>3000000</v>
       </c>
-      <c r="L35" s="13" t="n">
+      <c r="L35" s="14" t="n">
         <v>4950000</v>
       </c>
-      <c r="M35" s="13" t="n">
+      <c r="M35" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="N35" s="11" t="inlineStr">
+      <c r="N35" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O35" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P35" s="10" t="inlineStr">
+      <c r="O35" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P35" s="17" t="inlineStr">
         <is>
           <t>3 здания с реконструкцией исторических домов на Никольской ул. (Heatherwick), у Красной пл.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="26" customHeight="1">
+    <row r="36" ht="15" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>MONO Kami</t>
@@ -7175,7 +7185,7 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -7215,85 +7225,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P36" s="4" t="inlineStr">
+      <c r="P36" s="10" t="inlineStr">
         <is>
           <t>Комплекс из 4 клубных домов 9–14 эт. в Пыжевском пер., 74 квартиры, 5 мин до Третьяковки</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>ЖК «Никитский-6»</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Третий Рим</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>4 кв. 2026</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Москва, Никитский бульвар, 6/20</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Арбат</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J37" s="13" t="n">
+      <c r="J37" s="14" t="n">
         <v>2467500</v>
       </c>
-      <c r="K37" s="14" t="n">
+      <c r="K37" s="15" t="n">
         <v>3037250</v>
       </c>
-      <c r="L37" s="13" t="n">
+      <c r="L37" s="14" t="n">
         <v>4680000</v>
       </c>
-      <c r="M37" s="13" t="n">
+      <c r="M37" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="N37" s="11" t="inlineStr">
+      <c r="N37" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O37" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P37" s="10" t="inlineStr">
+      <c r="O37" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P37" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 8 эт. на Никитском бул., 57 квартир и 4 пентхауса с каминами и террасами</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="26" customHeight="1">
+    <row r="38" ht="15" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>ЖК «Фрунзенская набережная»</t>
@@ -7319,7 +7329,7 @@
           <t>Фрунзенская</t>
         </is>
       </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -7359,85 +7369,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P38" s="4" t="inlineStr">
+      <c r="P38" s="10" t="inlineStr">
         <is>
           <t>Квартал из 3 домов 10 эт. и неоклассического корпуса на Фрунзенской наб., 137 квартир, парк</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Kuznetsky Most 12 by Lalique (Кузнецкий Мост 12)</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>KR Properties</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>4 кв. 2026</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Москва, Кузнецкий Мост, 12/3С1</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Мещанский</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F39" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="G39" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>6-7</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="I39" s="12" t="inlineStr">
         <is>
           <t>апартаменты</t>
         </is>
       </c>
-      <c r="J39" s="13" t="n">
+      <c r="J39" s="14" t="n">
         <v>2985075</v>
       </c>
-      <c r="K39" s="14" t="n">
+      <c r="K39" s="15" t="n">
         <v>3092773</v>
       </c>
-      <c r="L39" s="13" t="n">
+      <c r="L39" s="14" t="n">
         <v>3200472</v>
       </c>
-      <c r="M39" s="13" t="n">
+      <c r="M39" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="N39" s="11" t="inlineStr">
+      <c r="N39" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O39" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P39" s="10" t="inlineStr">
+      <c r="O39" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P39" s="17" t="inlineStr">
         <is>
           <t>Реконструкция здания XIX в. на Кузнецком Мосту, 3–6 эт., 59 квартир, потолки до 5,8 м, wellness</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="26" customHeight="1">
+    <row r="40" ht="24" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Саввинская 27</t>
@@ -7463,7 +7473,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F40" s="17" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -7503,85 +7513,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr">
+      <c r="P40" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 6 эт. (ODA, APEX) на 1-й линии реки, 61 резиденция, 10 пентхаусов, SPA с бассейном</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>ДОМ XXII</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>Донстрой</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>4 кв. 2026</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>Москва, Новодевичий, 6С2</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F41" s="17" t="inlineStr">
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>11-12</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="I41" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J41" s="13" t="n">
+      <c r="J41" s="14" t="n">
         <v>2479101</v>
       </c>
-      <c r="K41" s="14" t="n">
+      <c r="K41" s="15" t="n">
         <v>3150000</v>
       </c>
-      <c r="L41" s="13" t="n">
+      <c r="L41" s="14" t="n">
         <v>4000000</v>
       </c>
-      <c r="M41" s="13" t="n">
+      <c r="M41" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="N41" s="11" t="inlineStr">
+      <c r="N41" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O41" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P41" s="10" t="inlineStr">
+      <c r="O41" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P41" s="17" t="inlineStr">
         <is>
           <t>Клубный дом из 2 корпусов 9–12 эт. у Новодевичьего, 109 квартир, потолки 3,5–4,5 м</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1">
+    <row r="42" ht="15" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Stoleshnikov 7 (Столешников 7)</t>
@@ -7607,7 +7617,7 @@
           <t>Тверской</t>
         </is>
       </c>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="F42" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -7647,85 +7657,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P42" s="4" t="inlineStr">
+      <c r="P42" s="10" t="inlineStr">
         <is>
           <t>Реконструкция доходного дома 1903 г. (Эрихсон), 5 эт., 12 квартир, камины и террасы</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>ЖК «Узоры»</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>Capital Group</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>4 кв. 2028</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>Москва, 2-й Вражский переулок, 8с2</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Киевская</t>
         </is>
       </c>
-      <c r="F43" s="17" t="inlineStr">
+      <c r="F43" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="G43" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>9-10</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J43" s="13" t="n">
+      <c r="J43" s="14" t="n">
         <v>3177900</v>
       </c>
-      <c r="K43" s="14" t="n">
+      <c r="K43" s="15" t="n">
         <v>3488415</v>
       </c>
-      <c r="L43" s="13" t="n">
+      <c r="L43" s="14" t="n">
         <v>4559310</v>
       </c>
-      <c r="M43" s="13" t="n">
+      <c r="M43" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="N43" s="11" t="inlineStr">
+      <c r="N43" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O43" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P43" s="10" t="inlineStr">
+      <c r="O43" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P43" s="17" t="inlineStr">
         <is>
           <t>Клубный дом из 2 секций 9–10 эт. на общем стилобате во 2-м Вражском пер., 72 квартиры</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="26" customHeight="1">
+    <row r="44" ht="15" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Annabels</t>
@@ -7751,7 +7761,7 @@
           <t>Кропоткинская</t>
         </is>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="F44" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -7791,85 +7801,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P44" s="4" t="inlineStr">
+      <c r="P44" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 7 эт. в Курсовом пер. на Золотой миле, 9 резиденций, пентхаус с террасами</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Левенсон»</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>Веспер</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>3 кв. 2027</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>Москва, Трёхпрудный переулок</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Маяковская</t>
         </is>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="F45" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="G45" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>4-6</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J45" s="13" t="n">
+      <c r="J45" s="14" t="n">
         <v>2800000</v>
       </c>
-      <c r="K45" s="14" t="n">
+      <c r="K45" s="15" t="n">
         <v>3560820</v>
       </c>
-      <c r="L45" s="13" t="n">
+      <c r="L45" s="14" t="n">
         <v>4189200</v>
       </c>
-      <c r="M45" s="13" t="n">
+      <c r="M45" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="N45" s="11" t="inlineStr">
+      <c r="N45" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O45" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P45" s="10" t="inlineStr">
+      <c r="O45" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P45" s="17" t="inlineStr">
         <is>
           <t>Реконструкция особняка Шехтеля в Трёхпрудном пер., 2–6 эт., 26 квартир, у Патриарших</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="26" customHeight="1">
+    <row r="46" ht="15" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Armani/Casa Moscow Residences (Армани/Каса Москоу Резиденсес)</t>
@@ -7895,7 +7905,7 @@
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="F46" s="16" t="inlineStr">
+      <c r="F46" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -7935,85 +7945,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P46" s="4" t="inlineStr">
+      <c r="P46" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 3–6 эт. в Старомонетном пер., 27 резиденций, интерьеры Armani/Casa, у Полянки</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>ЖК «Погодинская»</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Веспер</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>4 кв. 2028</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>Москва, Погодинская улица</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Спортивная</t>
         </is>
       </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="G47" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
+      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J47" s="13" t="n">
+      <c r="J47" s="14" t="n">
         <v>3003600</v>
       </c>
-      <c r="K47" s="14" t="n">
+      <c r="K47" s="15" t="n">
         <v>3977800</v>
       </c>
-      <c r="L47" s="13" t="n">
+      <c r="L47" s="14" t="n">
         <v>4855100</v>
       </c>
-      <c r="M47" s="13" t="n">
+      <c r="M47" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="N47" s="11" t="inlineStr">
+      <c r="N47" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O47" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P47" s="10" t="inlineStr">
+      <c r="O47" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P47" s="17" t="inlineStr">
         <is>
           <t>Клубный дом из 2 корпусов 11 эт. (GAFA) у Новодевичьего, 64 квартиры, бассейн 25 м</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="26" customHeight="1">
+    <row r="48" ht="15" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Обыденский №1»</t>
@@ -8039,7 +8049,7 @@
           <t>Кропоткинская</t>
         </is>
       </c>
-      <c r="F48" s="16" t="inlineStr">
+      <c r="F48" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8079,85 +8089,85 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P48" s="4" t="inlineStr">
+      <c r="P48" s="10" t="inlineStr">
         <is>
           <t>Клубный дом в 3-м Обыденском пер., 26 квартир, пентхаусы и виллы, в 150 м от ХХС</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Лё Дом</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Группа ЛСР</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>3 кв. 2026</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>Москва, Соймоновский, 3</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="F49" s="17" t="inlineStr">
+      <c r="F49" s="19" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="G49" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="H49" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr">
+      <c r="I49" s="12" t="inlineStr">
         <is>
           <t>квартиры</t>
         </is>
       </c>
-      <c r="J49" s="13" t="n">
+      <c r="J49" s="14" t="n">
         <v>2569427</v>
       </c>
-      <c r="K49" s="14" t="n">
+      <c r="K49" s="15" t="n">
         <v>4858198</v>
       </c>
-      <c r="L49" s="13" t="n">
+      <c r="L49" s="14" t="n">
         <v>10285102</v>
       </c>
-      <c r="M49" s="13" t="n">
+      <c r="M49" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="N49" s="11" t="inlineStr">
+      <c r="N49" s="12" t="inlineStr">
         <is>
           <t>бетон</t>
         </is>
       </c>
-      <c r="O49" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P49" s="10" t="inlineStr">
+      <c r="O49" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P49" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 3–5 эт. в Соймоновском пр., более 70 квартир, вид на Храм Христа Спасителя</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="26" customHeight="1">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>ЖК «БРЮСОВ»</t>
@@ -8183,7 +8193,7 @@
           <t>Охотный Ряд</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F50" s="18" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8223,7 +8233,7 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P50" s="4" t="inlineStr">
+      <c r="P50" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 8 эт. в Брюсовом пер. (1508 London), 20 резиденций и пентхаус, 5 мин до Кремля</t>
         </is>
@@ -8318,12 +8328,12 @@
   <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
@@ -8333,7 +8343,7 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="52" customWidth="1" min="16" max="16"/>
+    <col width="74" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -8432,7 +8442,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Лёвшинский, 19</t>
@@ -8448,7 +8458,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -8490,69 +8500,69 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 8 эт. на 16 резиденций 70–239 м², воссоздание фасада доходного дома Духовских 1904 г., паркинг 18 м/м, HADAA</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Клубный дом «Малая Никитская, 27»</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Малая Никитская улица, 27 (два двухэтажных особняка 1861 г., бывший «Клуб 27»)</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>не раскрыт</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>проектирование (kvartiravmoskve.ru, 02.03.2026); продажи не открыты, старт не анонсирован</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="11" t="n"/>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="14" t="n">
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="15" t="n">
         <v>3000000</v>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>2024-03-31</t>
         </is>
       </c>
-      <c r="O5" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P5" s="10" t="inlineStr">
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P5" s="17" t="inlineStr">
         <is>
           <t>Клубный дом высотой 33 м (бюро WALL) на месте двух особняков 1861 г. у Патриарших; ярусные объёмы, чёрно-белые фасады</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="26" customHeight="1">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Палашёвский 11 (Большой Палашёвский, 11–13/15)</t>
@@ -8568,7 +8578,7 @@
           <t>Тверской</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8618,87 +8628,87 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="P6" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 8–9 эт.: 45 квартир и 7 пентхаусов у Патриарших, три контрастных фасада, двор-сад с прудом, паркинг 88 м/м</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>EDEN Private Residence</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Нижний Кисловский пер., 7, стр. 1–2</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Sense Development</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>закрытые продажи (апрель 2026), стадия котлована; публичные продажи не открыты (novostroev.ru, 03.09.2026)</t>
         </is>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="14" t="n">
         <v>17100</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="14" t="n">
         <v>6200</v>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>6–9</t>
         </is>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t>3 кв. 2029</t>
         </is>
       </c>
-      <c r="M7" s="14" t="n">
+      <c r="M7" s="15" t="n">
         <v>5000000</v>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="O7" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P7" s="10" t="inlineStr">
+      <c r="O7" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P7" s="17" t="inlineStr">
         <is>
           <t>Ultra luxury клубный дом 6–9 эт. на 22 резиденции 107–411 м² у Арбата, участок 0,3 га, Gregory Tuck Architects</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Большая Ордынка, 25</t>
@@ -8714,7 +8724,7 @@
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8749,80 +8759,80 @@
           <t>4 кв. 2031</t>
         </is>
       </c>
-      <c r="M8" s="21" t="n"/>
+      <c r="M8" s="23" t="n"/>
       <c r="N8" s="5" t="n"/>
       <c r="O8" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="P8" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 7 эт. + мансарда, &gt;17 тыс. м², на месте первой АТС Москвы 1927 г. в Замоскворечье; делюкс</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Большая Пироговская, 51 (общежития Института красной профессуры)</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>ул. Большая Пироговская, 51</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Vesper</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>анонсирован (fee-development, июнь 2026), концепция; ГПЗУ получен в начале 2025; реализация не подтверждена</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="14" t="n">
         <v>46700</v>
       </c>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>12–13 (концепция Buro 2+2, 8 корпусов)</t>
         </is>
       </c>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="22" t="n"/>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="O9" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P9" s="10" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P9" s="17" t="inlineStr">
         <is>
           <t>Застройка 1,5 га бывших общежитий 1929–32 гг.: концепция 8 корпусов 12–13 эт. на стилобате в светлом камне, 46,7 тыс. м²</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Большой Козихинский, 22</t>
@@ -8838,7 +8848,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -8869,74 +8879,74 @@
         </is>
       </c>
       <c r="L10" s="5" t="n"/>
-      <c r="M10" s="21" t="n"/>
+      <c r="M10" s="23" t="n"/>
       <c r="N10" s="5" t="n"/>
       <c r="O10" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="P10" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 9 эт. на 98 квартир (9,4 тыс. м²) у Патриарших прудов, 5 мин. от м. Пушкинская; делюкс</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Воздвиженка 7/6</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>ул. Воздвиженка, 7/6</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Арбат</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>АПРИ</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>анонсирован; в списке делюкс-стартов 2026–2027 mskdeluxe.ru; параметры не раскрыты, сайт проекта недоступен (08.09.2026)</t>
         </is>
       </c>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>2026–2027</t>
         </is>
       </c>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="22" t="n"/>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="inlineStr">
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t>Бутик-дом делюкс ориентировочно на 10–15 квартир на Воздвиженке у Александровского сада; параметры не подтверждены</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Квартал на Савинской набережной («Московский шёлк»)</t>
@@ -8952,7 +8962,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -8979,7 +8989,7 @@
         </is>
       </c>
       <c r="L12" s="5" t="n"/>
-      <c r="M12" s="21" t="n"/>
+      <c r="M12" s="23" t="n"/>
       <c r="N12" s="5" t="inlineStr">
         <is>
           <t>2024-03-12</t>
@@ -8990,77 +9000,77 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="P12" s="10" t="inlineStr">
         <is>
           <t>ЖК ~125 тыс. м² на 4,5 га бывшей фабрики «Московский шёлк» на Савинской наб.: новые корпуса и реставрация</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Клубные дома на Берниковской набережной, 12 (Sminex)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Берниковская набережная, 12, стр. 1 (здание бывшей школы №1685, 1936 г., арх. А. Машинский)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Таганский</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Sminex</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>проектирование; площадка подтверждена Sminex 17.03.2026, сроки и старт продаж не объявлены</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="14" t="n">
         <v>21400</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="14" t="n">
         <v>13000</v>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>7–13 (два корпуса)</t>
         </is>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="J13" s="14" t="n">
         <v>166</v>
       </c>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="22" t="n"/>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="24" t="n"/>
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="O13" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P13" s="10" t="inlineStr">
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P13" s="17" t="inlineStr">
         <is>
           <t>Два клубных дома 7–13 эт., 166 квартир на 0,6 га на первой линии Яузы; двор-парк, пентхаусы с каминами; делюкс</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Клубный дом «Большая Никитская, 16» (R4S)</t>
@@ -9076,7 +9086,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -9109,7 +9119,7 @@
           <t>2026 Q3</t>
         </is>
       </c>
-      <c r="M14" s="21" t="n"/>
+      <c r="M14" s="23" t="n"/>
       <c r="N14" s="5" t="inlineStr">
         <is>
           <t>2026-01-19</t>
@@ -9120,75 +9130,75 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Реконструкция исторического особняка (ОКН) в клубный дом 4 эт. на 4 квартиры 139–234 м² у Кремля, потолки 3,1–3,7 м</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Клубный дом «Земледельческий, 15»</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Земледельческий переулок, 15 (на месте административного здания 1975 г., 5 этажей, 5 744 м²)</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>не раскрыт</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>проектирование (kvartiravmoskve.ru, 21.06.2026); по адресу действует БЦ; сделок и решений МКА не найдено</t>
         </is>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="14" t="n">
         <v>8000</v>
       </c>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="13" t="n">
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="14" t="n">
         <v>77</v>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="K15" s="12" t="inlineStr">
         <is>
           <t>2026–2027</t>
         </is>
       </c>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="22" t="n"/>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="24" t="n"/>
+      <c r="N15" s="12" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="O15" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P15" s="17" t="inlineStr">
         <is>
           <t>Клубный дом ~8 тыс. м² на 77 квартир на 0,3 га на месте БЦ 1975 г. у Плющихи; коммерция, подземный паркинг; делюкс</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Клубный дом на Курсовом переулке, 15 (проект бюро Дмитрия Великовского)</t>
@@ -9204,7 +9214,7 @@
           <t>Хамовники (Остоженка)</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -9227,78 +9237,78 @@
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="5" t="n"/>
-      <c r="M16" s="21" t="n"/>
+      <c r="M16" s="23" t="n"/>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="P16" s="10" t="inlineStr">
         <is>
           <t>Камерный клубный дом 6 эт. на «Золотой миле» у Зачатьевского монастыря; классика с панорамными окнами, башня с куполом</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Льва Толстого, 14–16 (три клубных дома Sminex)</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>ул. Льва Толстого, 14</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Sminex</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>участок приобретён (декабрь 2025), проектирование; старт продаж не объявлен (08.09.2026)</t>
         </is>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="14" t="n">
         <v>20300</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="14" t="n">
         <v>12400</v>
       </c>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="11" t="n"/>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="22" t="n"/>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="12" t="inlineStr">
         <is>
           <t>2025-12-18</t>
         </is>
       </c>
-      <c r="O17" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P17" s="10" t="inlineStr">
+      <c r="O17" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P17" s="17" t="inlineStr">
         <is>
           <t>Три камерных клубных дома у «Красной Розы» на 0,6 га; сохранение фасада дома Трындина-Жиро, виды на Кремль, клубхаус</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>МФК «На Краснопресненской набережной» (Трёхгорная мануфактура)</t>
@@ -9314,7 +9324,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>Пресня</t>
         </is>
@@ -9341,7 +9351,7 @@
           <t>2030</t>
         </is>
       </c>
-      <c r="M18" s="21" t="n"/>
+      <c r="M18" s="23" t="n"/>
       <c r="N18" s="5" t="inlineStr">
         <is>
           <t>2014-07-17</t>
@@ -9352,73 +9362,73 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="P18" s="10" t="inlineStr">
         <is>
           <t>МФК с апартаментами, офисами и wellness на 1,7 га у Трёхгорной мануфактуры (ОКН сохраняется), паркинг 750 м/м</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Малая Дмитровка, 5/9</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>ул. Малая Дмитровка, 5/9</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Тверской</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Группа «Эталон»</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>предстарт; старт продаж ожидается в 2026 г. (на 08.09.2026 не объявлен)</t>
         </is>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="14" t="n">
         <v>12000</v>
       </c>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>7–9</t>
         </is>
       </c>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="22" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P19" s="10" t="inlineStr">
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P19" s="17" t="inlineStr">
         <is>
           <t>Два корпуса 7–9 эт. на 0,4 га у сада «Эрмитаж», волнообразные бионические фасады, камерный клубный формат; делюкс</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Малая Никитская, 29–31 (ожидаемый делюкс-старт)</t>
@@ -9434,7 +9444,7 @@
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -9455,86 +9465,86 @@
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
-      <c r="M20" s="21" t="n"/>
+      <c r="M20" s="23" t="n"/>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr">
+      <c r="P20" s="10" t="inlineStr">
         <is>
           <t>Ожидаемый делюкс-старт на Малой Никитской у Красной Пресни; параметры не раскрыты, возможно тот же участок, что и №27</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Малая Ордынка, 14/1</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>ул. Малая Ордынка, 14/1</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Гута-Девелопмент</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>анонс старта продаж 06.04.2026; по novostroev.ru на 03.09.2026 — проект, продажи не начаты</t>
         </is>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="14" t="n">
         <v>2360</v>
       </c>
-      <c r="I21" s="13" t="n">
+      <c r="I21" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="J21" s="13" t="n">
+      <c r="J21" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="K21" s="12" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="22" t="n"/>
-      <c r="N21" s="11" t="inlineStr">
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="24" t="n"/>
+      <c r="N21" s="12" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="O21" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P21" s="10" t="inlineStr">
+      <c r="O21" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P21" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 6 эт. на 11 квартир на участке 0,1 га в Замоскворечье, 14 м/м, архитектура A2M; делюкс</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
+    <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Олсуфьевский 10</t>
@@ -9550,7 +9560,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -9579,78 +9589,78 @@
         </is>
       </c>
       <c r="L22" s="5" t="n"/>
-      <c r="M22" s="21" t="n"/>
+      <c r="M22" s="23" t="n"/>
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="P22" s="10" t="inlineStr">
         <is>
           <t>Семь корпусов 5–8 эт. на 0,4 га в Хамовниках у м. Фрунзенская, индивидуальная архитектура; делюкс</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Полянка-3</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>ул. Малая Полянка, 3</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Якиманка</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Aurix Development</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>старт продаж 2026 (по сайту проекта); строительство не начато, цены не опубликованы (08.09.2026)</t>
         </is>
       </c>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="13" t="n">
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="J23" s="13" t="n">
+      <c r="J23" s="14" t="n">
         <v>34</v>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="22" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P23" s="10" t="inlineStr">
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="24" t="n"/>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P23" s="17" t="inlineStr">
         <is>
           <t>Клубный дом 9 эт. на 34 резиденции у Третьяковской галереи, паркинг 36 м/м, отделка премиум, мотивы русского фольклора</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1">
+    <row r="24" ht="24" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Премиальный квартал на Лужнецкой набережной, 10А</t>
@@ -9666,7 +9676,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -9695,7 +9705,7 @@
         </is>
       </c>
       <c r="L24" s="5" t="n"/>
-      <c r="M24" s="21" t="n"/>
+      <c r="M24" s="23" t="n"/>
       <c r="N24" s="5" t="inlineStr">
         <is>
           <t>2026-05-28</t>
@@ -9706,73 +9716,73 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr">
+      <c r="P24" s="10" t="inlineStr">
         <is>
           <t>Квартал на 5,27 га у Лужников: два жилых корпуса 8–24 эт. в неоклассике + эллиптический БЦ «яйцо Фаберже» 26 тыс. м²</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Роден (ранее анонсировался как Veil)</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Большой Харитоньевский пер., 13А</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>Басманный</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>MR Group</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>проектирование (kvartiravmoskve.ru, 15.07.2026); старт продаж заявлен на июль–август 2026, цены не опубликованы</t>
         </is>
       </c>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="13" t="n">
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="J25" s="11" t="n"/>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="22" t="n"/>
-      <c r="N25" s="11" t="inlineStr">
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="24" t="n"/>
+      <c r="N25" s="12" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="O25" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P25" s="10" t="inlineStr">
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P25" s="17" t="inlineStr">
         <is>
           <t>Камерный клубный дом 7 эт. у Чистых прудов, монолит-кирпич, двор без машин, архитектура WALL; делюкс</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
+    <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Рождественка 8</t>
@@ -9788,7 +9798,7 @@
           <t>Мещанский</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -9821,7 +9831,7 @@
           <t>2 кв. 2030</t>
         </is>
       </c>
-      <c r="M26" s="21" t="n"/>
+      <c r="M26" s="23" t="n"/>
       <c r="N26" s="5" t="inlineStr">
         <is>
           <t>2025-12-12</t>
@@ -9832,71 +9842,71 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr">
+      <c r="P26" s="10" t="inlineStr">
         <is>
           <t>Семь клубных домов 2–10 эт., 115 квартир 61–426 м² у Кузнецкого Моста, двор-парк, реставрация особняка XIX в.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Тимура Фрунзе, 11 (клубный дом Sminex)</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>ул. Тимура Фрунзе, 11, стр. 7, 19, 33, 50</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Sminex</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>участок приобретён (апрель 2026), проектирование; сроки не объявлены (08.09.2026)</t>
         </is>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="14" t="n">
         <v>13000</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="14" t="n">
         <v>8200</v>
       </c>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="11" t="n"/>
-      <c r="K27" s="11" t="n"/>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="22" t="n"/>
-      <c r="N27" s="11" t="inlineStr">
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="24" t="n"/>
+      <c r="N27" s="12" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="O27" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P27" s="10" t="inlineStr">
+      <c r="O27" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P27" s="17" t="inlineStr">
         <is>
           <t>Камерный клубный дом на 0,5 га бывшей шёлковой фабрики: пентхаусы с видом на Кремль, виллы, двор-сад среди ОКН</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="26" customHeight="1">
+    <row r="28" ht="24" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Типография Сытина (Пятницкая, 71/5)</t>
@@ -9912,7 +9922,7 @@
           <t>Замоскворечье</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>Садовое кольцо</t>
         </is>
@@ -9933,7 +9943,7 @@
       <c r="J28" s="5" t="n"/>
       <c r="K28" s="5" t="n"/>
       <c r="L28" s="5" t="n"/>
-      <c r="M28" s="21" t="n"/>
+      <c r="M28" s="23" t="n"/>
       <c r="N28" s="5" t="inlineStr">
         <is>
           <t>2026-03-17</t>
@@ -9944,75 +9954,75 @@
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P28" s="4" t="inlineStr">
+      <c r="P28" s="10" t="inlineStr">
         <is>
           <t>Реставрация типографии Сытина (ОКН) и новые клубные дома на 1,8 га в Замоскворечье; двор-парк, виды на Кремль</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Усадьба в Большом Саввинском переулке (клубный дом VSF)</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Большой Саввинский пер. (усадьба купца Якунина)</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>ГК «Векторстройфинанс»</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>концепция бюро МЛА+ опубликована (январь 2026); сроки строительства не объявлены, реализация именно этой концепции не подтверждена</t>
         </is>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>4–10 (башня 10 эт. + клубный корпус 4 эт.)</t>
         </is>
       </c>
-      <c r="J29" s="13" t="n">
+      <c r="J29" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="22" t="n"/>
-      <c r="N29" s="11" t="inlineStr">
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="24" t="n"/>
+      <c r="N29" s="12" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="O29" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P29" s="10" t="inlineStr">
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P29" s="17" t="inlineStr">
         <is>
           <t>Клубный дом на месте усадьбы Якунина: башня «Шёлк» 10 эт. и корпус «Кашемир» 4 эт., 27 квартир, вход-«игольное ушко»</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
+    <row r="30" ht="24" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Усачёва, 22</t>
@@ -10028,7 +10038,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D30" s="19" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -10061,78 +10071,78 @@
           <t>2030</t>
         </is>
       </c>
-      <c r="M30" s="21" t="n"/>
+      <c r="M30" s="23" t="n"/>
       <c r="N30" s="5" t="n"/>
       <c r="O30" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="P30" s="10" t="inlineStr">
         <is>
           <t>Два корпуса 14–18 эт. на 0,4 га у м. Спортивная, Arch(e)type, двор без машин, SPA с бассейном; делюкс</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Участок КРТ «Большой Тишинский переулок, 8»</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Большой Тишинский переулок, 8 (стр. 1, 2)</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>Пресненский</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="25" t="inlineStr">
         <is>
           <t>Пресня</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>не раскрыт</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>решение о КРТ (август 2026); оператор/правообладатель и торги в открытых источниках не найдены (проверка 08.09.2026)</t>
         </is>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="14" t="n">
         <v>10000</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="14" t="n">
         <v>6000</v>
       </c>
-      <c r="I31" s="11" t="n"/>
-      <c r="J31" s="11" t="n"/>
-      <c r="K31" s="11" t="n"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="22" t="n"/>
-      <c r="N31" s="11" t="inlineStr">
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="24" t="n"/>
+      <c r="N31" s="12" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="O31" s="15" t="inlineStr">
-        <is>
-          <t>ссылка</t>
-        </is>
-      </c>
-      <c r="P31" s="10" t="inlineStr">
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
+      <c r="P31" s="17" t="inlineStr">
         <is>
           <t>Участок КРТ 0,3 га с двумя зданиями (хостелы) на Пресне между Б. Грузинской и Пресненским Валом; параметры не раскрыты</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="26" customHeight="1">
+    <row r="32" ht="24" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Хилков (Хилков переулок, вл. 3)</t>
@@ -10148,7 +10158,7 @@
           <t>Хамовники</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>Хамовники</t>
         </is>
@@ -10181,14 +10191,14 @@
         </is>
       </c>
       <c r="L32" s="5" t="n"/>
-      <c r="M32" s="21" t="n"/>
+      <c r="M32" s="23" t="n"/>
       <c r="N32" s="5" t="n"/>
       <c r="O32" s="9" t="inlineStr">
         <is>
           <t>ссылка</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="P32" s="10" t="inlineStr">
         <is>
           <t>Клубный дом 3–8 эт. на «Золотой миле», 19,8 тыс. м², жильё 8,8 тыс. м², коммерция 1,8 тыс. м², паркинг 170 м/м</t>
         </is>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -4922,7 +4922,11 @@
           <t>бетон</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr"/>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>ссылка</t>
+        </is>
+      </c>
       <c r="P4" s="10" t="inlineStr">
         <is>
           <t>Квартал из 3 корпусов 6–22 эт. на Ленинградском пр., панорамное остекление, паркинг на 782 м/м</t>
@@ -8258,52 +8262,53 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId47"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -606,15 +606,15 @@
   <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -622,7 +622,7 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="7" customWidth="1" min="16" max="16"/>
-    <col width="74" customWidth="1" min="17" max="17"/>
+    <col width="70" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -635,7 +635,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ЦАО, дома 2018+, активные объявления Циан на 2026-09-07; зоны: Садовое кольцо / Хамовники / Сити / Пресня / Белорусская. Сортировка по медиане ₽/м², цвет — от дешёвых (зелёный) к дорогим (красный)</t>
+          <t>ЦАО, дома 2018+, активные объявления Циан на 2026-09-07; зоны: Садовое кольцо / Хамовники / Сити / Пресня / Белорусская. Сортировка по медиане ₽/м², цвет — от дешёвых (зелёный) к дорогим (красный). Класс — по карточке ЖК на Циан</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="140.5" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Резиденция Тверская</t>
@@ -789,7 +789,7 @@
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P4" s="9" t="inlineStr">
@@ -803,7 +803,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
+    <row r="5" ht="115.5" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>NEVA TOWERS (Нева Тауэрс)</t>
@@ -866,7 +866,7 @@
       </c>
       <c r="O5" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P5" s="16" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="115.5" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Sinatra (Синатра)</t>
@@ -943,7 +943,7 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P6" s="9" t="inlineStr">
@@ -957,7 +957,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="115.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>LUMIN (ЛЮМИН)</t>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P7" s="16" t="inlineStr">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8" ht="115.5" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Уланский, 13</t>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P8" s="9" t="inlineStr">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9" ht="115.5" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Современник</t>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P9" s="16" t="inlineStr">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="115.5" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Репаблик</t>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr">
@@ -1265,7 +1265,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
+    <row r="11" ht="115.5" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>City Park (Сити Парк)</t>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P11" s="16" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12" ht="115.5" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SkyView</t>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P12" s="9" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" ht="115.5" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Полянка/44</t>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P13" s="16" t="inlineStr">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="140.5" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Титул на Серебрянической</t>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P14" s="9" t="inlineStr">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="115.5" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Bogenhouse (Богенхаус)</t>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P15" s="16" t="inlineStr">
@@ -1650,7 +1650,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="128" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Capital Towers (Капитал Тауэрс)</t>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P16" s="9" t="inlineStr">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
+    <row r="17" ht="128" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P17" s="16" t="inlineStr">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="128" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Титул на Якиманке</t>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P18" s="9" t="inlineStr">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="128" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Клубный дом ЦВЕТ32</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P19" s="16" t="inlineStr">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="115.5" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>A.Residence (А Резиденс)</t>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P20" s="9" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="115.5" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Roza Rossa (Роза Росса)</t>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P21" s="16" t="inlineStr">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
+    <row r="22" ht="153" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Собрание клубных домов ORDYNKA (Ордынка)</t>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P22" s="9" t="inlineStr">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23" ht="115.5" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Дом NV/9</t>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P23" s="16" t="inlineStr">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
+    <row r="24" ht="128" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Fantastic House (Фантастик Хаус)</t>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P24" s="9" t="inlineStr">
@@ -2343,7 +2343,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" ht="140.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Клубный дом Космо 4/22</t>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P25" s="16" t="inlineStr">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
+    <row r="26" ht="115.5" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Софийский</t>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P26" s="9" t="inlineStr">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" ht="128" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Дом на Тишинке</t>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P27" s="16" t="inlineStr">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
+    <row r="28" ht="128" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Тессинский, 1</t>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P28" s="9" t="inlineStr">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="103" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Lucky (Лаки)</t>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P29" s="16" t="inlineStr">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
+    <row r="30" ht="115.5" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Artisan (Артисан)</t>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P30" s="9" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31" ht="115.5" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Абрикосов</t>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P31" s="16" t="inlineStr">
@@ -2882,7 +2882,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1">
+    <row r="32" ht="128" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Клубный дом CULT (Клубный дом Культ)</t>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P32" s="9" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
+    <row r="33" ht="140.5" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P33" s="16" t="inlineStr">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
+    <row r="34" ht="128" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Пироговская 14</t>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>бизнес (Циан)</t>
+          <t>бизнес</t>
         </is>
       </c>
       <c r="P34" s="9" t="inlineStr">
@@ -3113,7 +3113,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
+    <row r="35" ht="115.5" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Cloud Nine (Клауд Найн)</t>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P35" s="16" t="inlineStr">
@@ -3190,7 +3190,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
+    <row r="36" ht="140.5" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Симфония набережных (Котельническая 21)</t>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P36" s="9" t="inlineStr">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
+    <row r="37" ht="128" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Садовые кварталы</t>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P37" s="16" t="inlineStr">
@@ -3344,7 +3344,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
+    <row r="38" ht="128" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Малая Ордынка 19</t>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P38" s="9" t="inlineStr">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
+    <row r="39" ht="128" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Дом в Газетном</t>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P39" s="16" t="inlineStr">
@@ -3498,7 +3498,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
+    <row r="40" ht="128" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P40" s="9" t="inlineStr">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
+    <row r="41" ht="128" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
           <t>White Khamovniki (Вайт Хамовники)</t>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>бизнес (Циан)</t>
+          <t>бизнес</t>
         </is>
       </c>
       <c r="P41" s="16" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1">
+    <row r="42" ht="140.5" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Золотой, жилой квартал</t>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P42" s="9" t="inlineStr">
@@ -3729,7 +3729,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
+    <row r="43" ht="103" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Magnum (Магнум)</t>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P43" s="16" t="inlineStr">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
+    <row r="44" ht="140.5" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Дом Бакст на Патриарших</t>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P44" s="9" t="inlineStr">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
+    <row r="45" ht="115.5" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Villa Grace (Вилла Грейс)</t>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P45" s="16" t="inlineStr">
@@ -3960,7 +3960,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1">
+    <row r="46" ht="115.5" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Brodsky (Бродский)</t>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P46" s="9" t="inlineStr">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
+    <row r="47" ht="128" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Жизнь на Плющихе</t>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P47" s="16" t="inlineStr">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1">
+    <row r="48" ht="115.5" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Carré Blanc (Карре Бланк)</t>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P48" s="9" t="inlineStr">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1">
+    <row r="49" ht="128" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Дом Лаврушинский</t>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P49" s="16" t="inlineStr">
@@ -4268,7 +4268,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1">
+    <row r="50" ht="128" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Хамовники 12</t>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P50" s="9" t="inlineStr">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1">
+    <row r="51" ht="153" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Stella di Mosca Hotel &amp; Residences (Стелла ди Моска Хотел энд Резиденсиз)</t>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P51" s="16" t="inlineStr">
@@ -4422,7 +4422,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="24" customHeight="1">
+    <row r="52" ht="140.5" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Большая Дмитровка IX</t>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P52" s="9" t="inlineStr">
@@ -4499,7 +4499,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1">
+    <row r="53" ht="128" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Малая Бронная 15</t>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P53" s="16" t="inlineStr">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1">
+    <row r="54" ht="128" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Barkli Gallery (Баркли Галлери)</t>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>премиум (Циан)</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="P54" s="9" t="inlineStr">
@@ -4747,22 +4747,22 @@
   <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="74" customWidth="1" min="16" max="16"/>
+    <col width="70" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4861,7 +4861,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="103" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ЖК «Слава»</t>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" ht="115.5" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>ЖК «Дом Дау»</t>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="115.5" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ЖК «Начало»</t>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="103" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Оне</t>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8" ht="128" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>АУРУС Резиденции</t>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9" ht="115.5" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>ЖК «Монблан»</t>
@@ -5291,7 +5291,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="128" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ЖК «Квартал Life Time»</t>
@@ -5363,7 +5363,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11" ht="140.5" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>ЖК «Коллекция Лужники»</t>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12" ht="128" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Тессинский V</t>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
+    <row r="13" ht="128" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Резиденция 1864</t>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="165.5" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>ЖК «Элитный квартал Тишинский бульвар»</t>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="115.5" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>ЖК «Дом Франка»</t>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="128" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ЖК «Татарская 35»</t>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" ht="153" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve"> Клубный дом «Резиденции Воронцова»</t>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
+    <row r="18" ht="128" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ЖК «Дом Соболева»</t>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
+    <row r="19" ht="128" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>ЖК «Климашкина 7/11»</t>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="128" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Форум»</t>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="115.5" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>ЖК «Камергер»</t>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
+    <row r="22" ht="115.5" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Казачий</t>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23" ht="128" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>ЖК «Садовническая 69»</t>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
+    <row r="24" ht="128" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Саввинская 17</t>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" ht="140.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>ЖК «Исторический дом «Чистые Пруды»</t>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26" ht="115.5" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>ЖК «PHANTOM»</t>
@@ -6515,7 +6515,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
+    <row r="27" ht="140.5" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Клубный дом TURGENEV (Тургенев)</t>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
+    <row r="28" ht="140.5" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Фамильный дом Люче</t>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="115.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Кло 17</t>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
+    <row r="30" ht="128" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>ТИТУЛ Империал</t>
@@ -6803,7 +6803,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31" ht="128" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Клубный дом DUO (Дуо)</t>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
+    <row r="32" ht="115.5" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Дом Спорта</t>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
+    <row r="33" ht="165.5" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>«Ильинка 3/8»</t>
@@ -7019,7 +7019,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
+    <row r="34" ht="128" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>ЖК «Красный Октябрь»</t>
@@ -7091,7 +7091,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
+    <row r="35" ht="115.5" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>ЖК «Николь»</t>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
+    <row r="36" ht="115.5" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>MONO Kami</t>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
+    <row r="37" ht="115.5" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t>ЖК «Никитский-6»</t>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
+    <row r="38" ht="153" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>ЖК «Фрунзенская набережная»</t>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1">
+    <row r="39" ht="153" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Kuznetsky Most 12 by Lalique (Кузнецкий Мост 12)</t>
@@ -7451,7 +7451,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
+    <row r="40" ht="128" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Саввинская 27</t>
@@ -7523,7 +7523,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
+    <row r="41" ht="115.5" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
           <t>ДОМ XXII</t>
@@ -7595,7 +7595,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1">
+    <row r="42" ht="128" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Stoleshnikov 7 (Столешников 7)</t>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
+    <row r="43" ht="115.5" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
           <t>ЖК «Узоры»</t>
@@ -7739,7 +7739,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
+    <row r="44" ht="115.5" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Annabels</t>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
+    <row r="45" ht="140.5" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Левенсон»</t>
@@ -7883,7 +7883,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1">
+    <row r="46" ht="153" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Armani/Casa Moscow Residences (Армани/Каса Москоу Резиденсес)</t>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
+    <row r="47" ht="140.5" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t>ЖК «Погодинская»</t>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1">
+    <row r="48" ht="140.5" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Обыденский №1»</t>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1">
+    <row r="49" ht="115.5" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Лё Дом</t>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1">
+    <row r="50" ht="115.5" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>ЖК «БРЮСОВ»</t>
@@ -8333,22 +8333,22 @@
   <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="74" customWidth="1" min="16" max="16"/>
+    <col width="70" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="90.5" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Лёвшинский, 19</t>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
+    <row r="5" ht="215.5" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Клубный дом «Малая Никитская, 27»</t>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
+    <row r="6" ht="128" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Палашёвский 11 (Большой Палашёвский, 11–13/15)</t>
@@ -8639,7 +8639,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
+    <row r="7" ht="115.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>EDEN Private Residence</t>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="103" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Большая Ордынка, 25</t>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
+    <row r="9" ht="103" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Большая Пироговская, 51 (общежития Института красной профессуры)</t>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
+    <row r="10" ht="153" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Большой Козихинский, 22</t>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
+    <row r="11" ht="65.5" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Воздвиженка 7/6</t>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1">
+    <row r="12" ht="103" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Квартал на Савинской набережной («Московский шёлк»)</t>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
+    <row r="13" ht="178" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Клубные дома на Берниковской набережной, 12 (Sminex)</t>
@@ -9075,7 +9075,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
+    <row r="14" ht="153" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Клубный дом «Большая Никитская, 16» (R4S)</t>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
+    <row r="15" ht="115.5" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Клубный дом «Земледельческий, 15»</t>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
+    <row r="16" ht="78" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Клубный дом на Курсовом переулке, 15 (проект бюро Дмитрия Великовского)</t>
@@ -9255,7 +9255,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
+    <row r="17" ht="228" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Льва Толстого, 14–16 (три клубных дома Sminex)</t>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
+    <row r="18" ht="140.5" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>МФК «На Краснопресненской набережной» (Трёхгорная мануфактура)</t>
@@ -9373,7 +9373,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
+    <row r="19" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Малая Дмитровка, 5/9</t>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
+    <row r="20" ht="53" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Малая Никитская, 29–31 (ожидаемый делюкс-старт)</t>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
+    <row r="21" ht="140.5" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Малая Ордынка, 14/1</t>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
+    <row r="22" ht="53" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Олсуфьевский 10</t>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
+    <row r="23" ht="53" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Полянка-3</t>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
+    <row r="24" ht="103" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Премиальный квартал на Лужнецкой набережной, 10А</t>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
+    <row r="25" ht="165.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Роден (ранее анонсировался как Veil)</t>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
+    <row r="26" ht="228" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Рождественка 8</t>
@@ -9853,7 +9853,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
+    <row r="27" ht="103" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Тимура Фрунзе, 11 (клубный дом Sminex)</t>
@@ -9911,7 +9911,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
+    <row r="28" ht="115.5" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Типография Сытина (Пятницкая, 71/5)</t>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1">
+    <row r="29" ht="240.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Усадьба в Большом Саввинском переулке (клубный дом VSF)</t>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1">
+    <row r="30" ht="128" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Усачёва, 22</t>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1">
+    <row r="31" ht="65.5" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Участок КРТ «Большой Тишинский переулок, 8»</t>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1">
+    <row r="32" ht="90.5" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Хилков (Хилков переулок, вл. 3)</t>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="140.5" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Резиденция Тверская</t>
@@ -803,7 +803,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="115.5" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>NEVA TOWERS (Нева Тауэрс)</t>
@@ -880,7 +880,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="115.5" customHeight="1">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Sinatra (Синатра)</t>
@@ -957,7 +957,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="115.5" customHeight="1">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>LUMIN (ЛЮМИН)</t>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="115.5" customHeight="1">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Уланский, 13</t>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="115.5" customHeight="1">
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Современник</t>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="115.5" customHeight="1">
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Репаблик</t>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="115.5" customHeight="1">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>City Park (Сити Парк)</t>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="115.5" customHeight="1">
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SkyView</t>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="115.5" customHeight="1">
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Полянка/44</t>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="140.5" customHeight="1">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Титул на Серебрянической</t>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="115.5" customHeight="1">
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Bogenhouse (Богенхаус)</t>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="128" customHeight="1">
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Capital Towers (Капитал Тауэрс)</t>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="128" customHeight="1">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="128" customHeight="1">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Титул на Якиманке</t>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="128" customHeight="1">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Клубный дом ЦВЕТ32</t>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="115.5" customHeight="1">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>A.Residence (А Резиденс)</t>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="115.5" customHeight="1">
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Roza Rossa (Роза Росса)</t>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="153" customHeight="1">
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Собрание клубных домов ORDYNKA (Ордынка)</t>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="115.5" customHeight="1">
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Дом NV/9</t>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="128" customHeight="1">
+    <row r="24" ht="28" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Fantastic House (Фантастик Хаус)</t>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="140.5" customHeight="1">
+    <row r="25" ht="28" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Клубный дом Космо 4/22</t>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="115.5" customHeight="1">
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Софийский</t>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="128" customHeight="1">
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Дом на Тишинке</t>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="128" customHeight="1">
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Тессинский, 1</t>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="103" customHeight="1">
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Lucky (Лаки)</t>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="115.5" customHeight="1">
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Artisan (Артисан)</t>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="115.5" customHeight="1">
+    <row r="31" ht="28" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Абрикосов</t>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="128" customHeight="1">
+    <row r="32" ht="28" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Клубный дом CULT (Клубный дом Культ)</t>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="140.5" customHeight="1">
+    <row r="33" ht="28" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="128" customHeight="1">
+    <row r="34" ht="28" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Пироговская 14</t>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="115.5" customHeight="1">
+    <row r="35" ht="28" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Cloud Nine (Клауд Найн)</t>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="140.5" customHeight="1">
+    <row r="36" ht="28" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Симфония набережных (Котельническая 21)</t>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="128" customHeight="1">
+    <row r="37" ht="28" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Садовые кварталы</t>
@@ -3344,7 +3344,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="128" customHeight="1">
+    <row r="38" ht="28" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Малая Ордынка 19</t>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="128" customHeight="1">
+    <row r="39" ht="15" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Дом в Газетном</t>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="128" customHeight="1">
+    <row r="40" ht="28" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="128" customHeight="1">
+    <row r="41" ht="28" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
           <t>White Khamovniki (Вайт Хамовники)</t>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="140.5" customHeight="1">
+    <row r="42" ht="28" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Золотой, жилой квартал</t>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="103" customHeight="1">
+    <row r="43" ht="28" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Magnum (Магнум)</t>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="140.5" customHeight="1">
+    <row r="44" ht="28" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Дом Бакст на Патриарших</t>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="115.5" customHeight="1">
+    <row r="45" ht="28" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Villa Grace (Вилла Грейс)</t>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="115.5" customHeight="1">
+    <row r="46" ht="28" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Brodsky (Бродский)</t>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="128" customHeight="1">
+    <row r="47" ht="15" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Жизнь на Плющихе</t>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="115.5" customHeight="1">
+    <row r="48" ht="28" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Carré Blanc (Карре Бланк)</t>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="128" customHeight="1">
+    <row r="49" ht="28" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Дом Лаврушинский</t>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="128" customHeight="1">
+    <row r="50" ht="28" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Хамовники 12</t>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="153" customHeight="1">
+    <row r="51" ht="40.5" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Stella di Mosca Hotel &amp; Residences (Стелла ди Моска Хотел энд Резиденсиз)</t>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="140.5" customHeight="1">
+    <row r="52" ht="28" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Большая Дмитровка IX</t>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="128" customHeight="1">
+    <row r="53" ht="15" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Малая Бронная 15</t>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="128" customHeight="1">
+    <row r="54" ht="28" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Barkli Gallery (Баркли Галлери)</t>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="103" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ЖК «Слава»</t>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="115.5" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>ЖК «Дом Дау»</t>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="115.5" customHeight="1">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ЖК «Начало»</t>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="103" customHeight="1">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Оне</t>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="128" customHeight="1">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>АУРУС Резиденции</t>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="115.5" customHeight="1">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>ЖК «Монблан»</t>
@@ -5291,7 +5291,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="128" customHeight="1">
+    <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ЖК «Квартал Life Time»</t>
@@ -5363,7 +5363,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="140.5" customHeight="1">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>ЖК «Коллекция Лужники»</t>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="128" customHeight="1">
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Тессинский V</t>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="128" customHeight="1">
+    <row r="13" ht="40.5" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Резиденция 1864</t>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="165.5" customHeight="1">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>ЖК «Элитный квартал Тишинский бульвар»</t>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="115.5" customHeight="1">
+    <row r="15" ht="40.5" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>ЖК «Дом Франка»</t>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="128" customHeight="1">
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ЖК «Татарская 35»</t>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="153" customHeight="1">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve"> Клубный дом «Резиденции Воронцова»</t>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="128" customHeight="1">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ЖК «Дом Соболева»</t>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="128" customHeight="1">
+    <row r="19" ht="28" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>ЖК «Климашкина 7/11»</t>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="128" customHeight="1">
+    <row r="20" ht="40.5" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Форум»</t>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="115.5" customHeight="1">
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>ЖК «Камергер»</t>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="115.5" customHeight="1">
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Казачий</t>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="128" customHeight="1">
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>ЖК «Садовническая 69»</t>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="128" customHeight="1">
+    <row r="24" ht="28" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Саввинская 17</t>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="140.5" customHeight="1">
+    <row r="25" ht="28" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>ЖК «Исторический дом «Чистые Пруды»</t>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="115.5" customHeight="1">
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>ЖК «PHANTOM»</t>
@@ -6515,7 +6515,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="140.5" customHeight="1">
+    <row r="27" ht="28" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Клубный дом TURGENEV (Тургенев)</t>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="140.5" customHeight="1">
+    <row r="28" ht="28" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Фамильный дом Люче</t>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="115.5" customHeight="1">
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Кло 17</t>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="128" customHeight="1">
+    <row r="30" ht="28" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>ТИТУЛ Империал</t>
@@ -6803,7 +6803,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="128" customHeight="1">
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Клубный дом DUO (Дуо)</t>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="115.5" customHeight="1">
+    <row r="32" ht="28" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Дом Спорта</t>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="165.5" customHeight="1">
+    <row r="33" ht="40.5" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>«Ильинка 3/8»</t>
@@ -7019,7 +7019,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="128" customHeight="1">
+    <row r="34" ht="28" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>ЖК «Красный Октябрь»</t>
@@ -7091,7 +7091,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="115.5" customHeight="1">
+    <row r="35" ht="28" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>ЖК «Николь»</t>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="115.5" customHeight="1">
+    <row r="36" ht="40.5" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>MONO Kami</t>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="115.5" customHeight="1">
+    <row r="37" ht="28" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t>ЖК «Никитский-6»</t>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="153" customHeight="1">
+    <row r="38" ht="28" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>ЖК «Фрунзенская набережная»</t>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="153" customHeight="1">
+    <row r="39" ht="28" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Kuznetsky Most 12 by Lalique (Кузнецкий Мост 12)</t>
@@ -7451,7 +7451,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="128" customHeight="1">
+    <row r="40" ht="28" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Саввинская 27</t>
@@ -7523,7 +7523,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="115.5" customHeight="1">
+    <row r="41" ht="15" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
           <t>ДОМ XXII</t>
@@ -7595,7 +7595,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="128" customHeight="1">
+    <row r="42" ht="28" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Stoleshnikov 7 (Столешников 7)</t>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="115.5" customHeight="1">
+    <row r="43" ht="28" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
           <t>ЖК «Узоры»</t>
@@ -7739,7 +7739,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="115.5" customHeight="1">
+    <row r="44" ht="40.5" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Annabels</t>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="140.5" customHeight="1">
+    <row r="45" ht="15" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Левенсон»</t>
@@ -7883,7 +7883,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="153" customHeight="1">
+    <row r="46" ht="40.5" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Armani/Casa Moscow Residences (Армани/Каса Москоу Резиденсес)</t>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="140.5" customHeight="1">
+    <row r="47" ht="15" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t>ЖК «Погодинская»</t>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="140.5" customHeight="1">
+    <row r="48" ht="40.5" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Обыденский №1»</t>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="115.5" customHeight="1">
+    <row r="49" ht="15" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Лё Дом</t>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="115.5" customHeight="1">
+    <row r="50" ht="40.5" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>ЖК «БРЮСОВ»</t>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="90.5" customHeight="1">
+    <row r="4" ht="53" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Лёвшинский, 19</t>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="215.5" customHeight="1">
+    <row r="5" ht="53" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Клубный дом «Малая Никитская, 27»</t>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="128" customHeight="1">
+    <row r="6" ht="65.5" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Палашёвский 11 (Большой Палашёвский, 11–13/15)</t>
@@ -8639,7 +8639,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="115.5" customHeight="1">
+    <row r="7" ht="65.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>EDEN Private Residence</t>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="103" customHeight="1">
+    <row r="8" ht="65.5" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Большая Ордынка, 25</t>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="103" customHeight="1">
+    <row r="9" ht="65.5" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Большая Пироговская, 51 (общежития Института красной профессуры)</t>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="153" customHeight="1">
+    <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Большой Козихинский, 22</t>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="103" customHeight="1">
+    <row r="12" ht="65.5" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Квартал на Савинской набережной («Московский шёлк»)</t>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="178" customHeight="1">
+    <row r="13" ht="53" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Клубные дома на Берниковской набережной, 12 (Sminex)</t>
@@ -9075,7 +9075,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="153" customHeight="1">
+    <row r="14" ht="65.5" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Клубный дом «Большая Никитская, 16» (R4S)</t>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="115.5" customHeight="1">
+    <row r="15" ht="65.5" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Клубный дом «Земледельческий, 15»</t>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="78" customHeight="1">
+    <row r="16" ht="53" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Клубный дом на Курсовом переулке, 15 (проект бюро Дмитрия Великовского)</t>
@@ -9255,7 +9255,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="228" customHeight="1">
+    <row r="17" ht="53" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Льва Толстого, 14–16 (три клубных дома Sminex)</t>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="140.5" customHeight="1">
+    <row r="18" ht="53" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>МФК «На Краснопресненской набережной» (Трёхгорная мануфактура)</t>
@@ -9373,7 +9373,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="115.5" customHeight="1">
+    <row r="19" ht="40.5" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Малая Дмитровка, 5/9</t>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="140.5" customHeight="1">
+    <row r="21" ht="53" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Малая Ордынка, 14/1</t>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="103" customHeight="1">
+    <row r="24" ht="78" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Премиальный квартал на Лужнецкой набережной, 10А</t>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="165.5" customHeight="1">
+    <row r="25" ht="65.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Роден (ранее анонсировался как Veil)</t>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="228" customHeight="1">
+    <row r="26" ht="65.5" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Рождественка 8</t>
@@ -9853,7 +9853,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="103" customHeight="1">
+    <row r="27" ht="53" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Тимура Фрунзе, 11 (клубный дом Sminex)</t>
@@ -9911,7 +9911,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="115.5" customHeight="1">
+    <row r="28" ht="53" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Типография Сытина (Пятницкая, 71/5)</t>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="240.5" customHeight="1">
+    <row r="29" ht="78" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Усадьба в Большом Саввинском переулке (клубный дом VSF)</t>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="128" customHeight="1">
+    <row r="30" ht="53" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Усачёва, 22</t>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -606,10 +606,10 @@
   <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
@@ -622,7 +622,7 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="7" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
+    <col width="84" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Резиденция Тверская</t>
@@ -734,7 +734,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Kovaks (Ковакс)</t>
+          <t>Kovaks</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Москва, 2-я Брестская, 6</t>
+          <t>2-я Брестская, 6</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>NEVA TOWERS (Нева Тауэрс)</t>
+          <t>NEVA TOWERS</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Москва, 1-й Красногвардейский, 22с2</t>
+          <t>1-й Красногвардейский, 22с2</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -880,10 +880,10 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Sinatra (Синатра)</t>
+          <t>Sinatra</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Москва, Большой Тишинский, 38</t>
+          <t>Большой Тишинский, 38</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>LUMIN (ЛЮМИН)</t>
+          <t>LUMIN</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Москва, Славянская, 2/5с1</t>
+          <t>Славянская, 2/5с1</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Москва, Уланский, 13С1</t>
+          <t>Уланский, 13С1</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Современник</t>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Москва, Машкова, 13С1</t>
+          <t>Машкова, 13С1</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Репаблик</t>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Москва, Пресненский Вал, 27к5</t>
+          <t>Пресненский Вал, 27к5</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1265,10 +1265,10 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>City Park (Сити Парк)</t>
+          <t>City Park</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Москва, Мантулинская, 9к4</t>
+          <t>Мантулинская, 9к4</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SkyView</t>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Москва, Дружинниковская, 15А</t>
+          <t>Дружинниковская, 15А</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Полянка/44</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Москва, Большая Полянка, 44</t>
+          <t>Большая Полянка, 44</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Титул на Серебрянической</t>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Москва, Серебрянический, 8</t>
+          <t>Серебрянический, 8</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Bogenhouse (Богенхаус)</t>
+          <t>Bogenhouse</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Москва, Озерковская, 6</t>
+          <t>Озерковская, 6</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -1650,10 +1650,10 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Capital Towers (Капитал Тауэрс)</t>
+          <t>Capital Towers</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Москва, Краснопресненская, 14Ак3</t>
+          <t>Краснопресненская, 14Ак3</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>BALCHUG VIEWPOINT (Балчуг Вьюпоинт)</t>
+          <t>BALCHUG VIEWPOINT</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Москва, Садовническая, 7</t>
+          <t>Садовническая, 7</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Москва, 2-й Хвостов, 8</t>
+          <t>2-й Хвостов, 8</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Москва, Цветной, 32А</t>
+          <t>Цветной, 32А</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -1958,15 +1958,15 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A.Residence (А Резиденс)</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>O1 Properties (СЗ А-Резиденс)</t>
+          <t>A.Residence</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>O1 Properties</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Москва, Садовническая, 82</t>
+          <t>Садовническая, 82</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2035,10 +2035,10 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Roza Rossa (Роза Росса)</t>
+          <t>Roza Rossa</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Москва, Зубовская, 7</t>
+          <t>Зубовская, 7</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Собрание клубных домов ORDYNKA (Ордынка)</t>
+          <t>Собрание клубных домов ORDYNKA</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Москва, Большой Ордынский, 4С4</t>
+          <t>Большой Ордынский, 4С4</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Москва, Большой Николоворобинский, 9к1</t>
+          <t>Большой Николоворобинский, 9к1</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -2266,10 +2266,10 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Fantastic House (Фантастик Хаус)</t>
+          <t>Fantastic House</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Москва, Большой Тишинский, 30</t>
+          <t>Большой Тишинский, 30</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2343,7 +2343,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Клубный дом Космо 4/22</t>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Москва, Космодамианская, 4/22</t>
+          <t>Космодамианская, 4/22</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Софийский</t>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 34</t>
+          <t>Софийская, 34</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Москва, Средний Тишинский, 5</t>
+          <t>Средний Тишинский, 5</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Москва, Тессинский, 1</t>
+          <t>Тессинский, 1</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2651,10 +2651,10 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Lucky (Лаки)</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Москва, Костикова, 4к1</t>
+          <t>Костикова, 4к1</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -2731,7 +2731,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Artisan (Артисан)</t>
+          <t>Artisan</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Москва, Арбат, 39</t>
+          <t>Арбат, 39</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Абрикосов</t>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Москва, Потаповский, 6С1</t>
+          <t>Потаповский, 6С1</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -2882,10 +2882,10 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом CULT (Клубный дом Культ)</t>
+          <t>Клубный дом CULT</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Москва, Ленинский, 2</t>
+          <t>Ленинский, 2</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
+    <row r="33" ht="15" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>SAVVIN RIVER RESIDENCE (Саввин Ривер Резиденс)</t>
+          <t>SAVVIN RIVER RESIDENCE</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 13</t>
+          <t>Саввинская, 13</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Москва, Малая Пироговская, 12</t>
+          <t>Малая Пироговская, 12</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -3116,7 +3116,7 @@
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>Cloud Nine (Клауд Найн)</t>
+          <t>Cloud Nine</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Москва, Большая Полянка, 9С2</t>
+          <t>Большая Полянка, 9С2</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Москва, Котельническая, 21</t>
+          <t>Котельническая, 21</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
+    <row r="37" ht="15" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Садовые кварталы</t>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Москва, Усачева, 15А</t>
+          <t>Усачева, 15А</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Москва, Малая Ордынка, 19</t>
+          <t>Малая Ордынка, 19</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Москва, Газетный, 13с2</t>
+          <t>Газетный, 13с2</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
@@ -3498,10 +3498,10 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Zvonarsky Deluxe (Звонарский Делюкс)</t>
+          <t>Zvonarsky Deluxe</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Москва, Звонарский, 3</t>
+          <t>Звонарский, 3</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3575,10 +3575,10 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="28" customHeight="1">
+    <row r="41" ht="15" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>White Khamovniki (Вайт Хамовники)</t>
+          <t>White Khamovniki</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Москва, Олсуфьевский, 9к1</t>
+          <t>Олсуфьевский, 9к1</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="28" customHeight="1">
+    <row r="42" ht="15" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Золотой, жилой квартал</t>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 18</t>
+          <t>Софийская, 18</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>Magnum (Магнум)</t>
+          <t>Magnum</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Москва, Усачева, 9</t>
+          <t>Усачева, 9</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="28" customHeight="1">
+    <row r="44" ht="15" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Дом Бакст на Патриарших</t>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Москва, Большой Козихинский, 15</t>
+          <t>Большой Козихинский, 15</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -3883,10 +3883,10 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="28" customHeight="1">
+    <row r="45" ht="15" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>Villa Grace (Вилла Грейс)</t>
+          <t>Villa Grace</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Москва, Пожарский, 3</t>
+          <t>Пожарский, 3</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
@@ -3960,10 +3960,10 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="28" customHeight="1">
+    <row r="46" ht="15" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Brodsky (Бродский)</t>
+          <t>Brodsky</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Москва, 1-й Тружеников, 16</t>
+          <t>1-й Тружеников, 16</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Москва, Погодинская, 2</t>
+          <t>Погодинская, 2</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="28" customHeight="1">
+    <row r="48" ht="15" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Carré Blanc (Карре Бланк)</t>
+          <t>Carré Blanc</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Москва, Пречистенская, 43</t>
+          <t>Пречистенская, 43</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="28" customHeight="1">
+    <row r="49" ht="15" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Дом Лаврушинский</t>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Москва, Большой Толмачевский, 5С1</t>
+          <t>Большой Толмачевский, 5С1</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
@@ -4268,7 +4268,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="28" customHeight="1">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Хамовники 12</t>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Москва, 1-й Тружеников, 12</t>
+          <t>1-й Тружеников, 12</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="40.5" customHeight="1">
+    <row r="51" ht="28" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>Stella di Mosca Hotel &amp; Residences (Стелла ди Моска Хотел энд Резиденсиз)</t>
+          <t>Stella di Mosca Hotel &amp; Residences</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Москва, Большая Никитская, 9</t>
+          <t>Большая Никитская, 9</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
@@ -4422,7 +4422,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="28" customHeight="1">
+    <row r="52" ht="15" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Большая Дмитровка IX</t>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Москва, Большая Дмитровка, 9А</t>
+          <t>Большая Дмитровка, 9А</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Москва, Малая Бронная, 15Б</t>
+          <t>Малая Бронная, 15Б</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
@@ -4576,10 +4576,10 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="28" customHeight="1">
+    <row r="54" ht="15" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Barkli Gallery (Баркли Галлери)</t>
+          <t>Barkli Gallery</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Москва, Ордынский, 4А</t>
+          <t>Ордынский, 4А</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -4747,10 +4747,10 @@
   <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
@@ -4762,7 +4762,7 @@
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
+    <col width="84" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Москва, Ленинградский проспект, вл8</t>
+          <t>Ленинградский проспект, вл8</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Москва, Краснопресненская набережная</t>
+          <t>Краснопресненская набережная</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ЖК «Начало»</t>
@@ -5016,14 +5016,14 @@
           <t>ДОНСТРОЙ</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>2029 (Циан: 2029–2030)</t>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2029–2030</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Москва, улица Сергея Макеева, 7</t>
+          <t>улица Сергея Макеева, 7</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -5077,7 +5077,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Оне</t>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Москва, 1-й Красногвардейский, 13</t>
+          <t>1-й Красногвардейский, 13</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>АУРУС Резиденции</t>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Москва, Шлюзовая набережная</t>
+          <t>Шлюзовая набережная</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -5291,7 +5291,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="40.5" customHeight="1">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ЖК «Квартал Life Time»</t>
@@ -5302,14 +5302,14 @@
           <t>Sminex</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>2 кв. 2026 (Циан: 3 кв. 2026)</t>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>3 кв. 2026</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Москва, улица Сергея Макеева</t>
+          <t>улица Сергея Макеева</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Москва, Лужнецкая набережная</t>
+          <t>Лужнецкая набережная</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Москва, Тессинский, 5С11</t>
+          <t>Тессинский, 5С11</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 36</t>
+          <t>Софийская, 36</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Москва, Электрический переулок</t>
+          <t>Электрический переулок</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -5651,7 +5651,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="40.5" customHeight="1">
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>ЖК «Дом Франка»</t>
@@ -5662,14 +5662,14 @@
           <t>Трансстройинвест</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>2 кв. 2026 (Циан: 4 кв. 2026)</t>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>4 кв. 2026</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Москва, Большой Кисельный переулок, 11</t>
+          <t>Большой Кисельный переулок, 11</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -5723,7 +5723,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ЖК «Татарская 35»</t>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Москва, Большая Татарская улица</t>
+          <t>Большая Татарская улица</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -5798,7 +5798,7 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Клубный дом «Резиденции Воронцова»</t>
+          <t>Клубный дом «Резиденции Воронцова»</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Москва, Обуха</t>
+          <t>Обуха</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Москва, Машкова улица, 18</t>
+          <t>Машкова улица, 18</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -5939,7 +5939,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>ЖК «Климашкина 7/11»</t>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Москва, улица Климашкина, 7/11</t>
+          <t>улица Климашкина, 7/11</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -6011,7 +6011,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="40.5" customHeight="1">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Форум»</t>
@@ -6022,14 +6022,14 @@
           <t>MR Group</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>1 кв. 2026 (Циан: 4 кв. 2027)</t>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>4 кв. 2027</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Москва, Садовая-Сухаревская улица, 14</t>
+          <t>Садовая-Сухаревская улица, 14</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -6083,7 +6083,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>ЖК «Камергер»</t>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Москва, Георгиевский переулок, 1</t>
+          <t>Георгиевский переулок, 1</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Казачий</t>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Москва, 1-й Казачий, 10С1</t>
+          <t>1-й Казачий, 10С1</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Москва, Садовническая улица</t>
+          <t>Садовническая улица</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -6299,7 +6299,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Саввинская 17</t>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 17</t>
+          <t>Саввинская, 17</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Москва, Потаповский переулок, 5с4</t>
+          <t>Потаповский переулок, 5с4</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -6443,7 +6443,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>ЖК «PHANTOM»</t>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Москва, Малая Сухаревская площадь</t>
+          <t>Малая Сухаревская площадь</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Клубный дом TURGENEV (Тургенев)</t>
+          <t>Клубный дом TURGENEV</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Москва, Костянский, 13</t>
+          <t>Костянский, 13</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Фамильный дом Люче</t>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Москва, Крестовоздвиженский, 4</t>
+          <t>Крестовоздвиженский, 4</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Кло 17</t>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Москва, Староваганьковский, 17С4</t>
+          <t>Староваганьковский, 17С4</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Москва, Большой Николоворобинский, 12/11</t>
+          <t>Большой Николоворобинский, 12/11</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -6806,7 +6806,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Клубный дом DUO (Дуо)</t>
+          <t>Клубный дом DUO</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Москва, Софийская, 34С3</t>
+          <t>Софийская, 34С3</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -6875,7 +6875,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Дом Спорта</t>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Москва, Дружинниковская, 18</t>
+          <t>Дружинниковская, 18</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -6947,7 +6947,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="40.5" customHeight="1">
+    <row r="33" ht="28" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>«Ильинка 3/8»</t>
@@ -6958,14 +6958,14 @@
           <t>Sminex</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>1 кв. 2026 (Циан: 3 кв. 2025)</t>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>3 кв. 2025</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Москва, улица Ильинка</t>
+          <t>улица Ильинка</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -7019,7 +7019,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
+    <row r="34" ht="15" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>ЖК «Красный Октябрь»</t>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Москва, Берсеневская набережная</t>
+          <t>Берсеневская набережная</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Москва, Никольская улица, 8/1с1</t>
+          <t>Никольская улица, 8/1с1</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -7163,20 +7163,20 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="40.5" customHeight="1">
+    <row r="36" ht="15" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>MONO Kami</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Tekta Group (ранее ПИК / MONO)</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>4 кв. 2028 (Циан: 2 кв. 2029)</t>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Tekta Group</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>2 кв. 2029</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -7235,7 +7235,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
+    <row r="37" ht="15" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t>ЖК «Никитский-6»</t>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Москва, Никитский бульвар, 6/20</t>
+          <t>Никитский бульвар, 6/20</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -7307,7 +7307,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1">
+    <row r="38" ht="15" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>ЖК «Фрунзенская набережная»</t>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Москва, Фрунзенская набережная, 30</t>
+          <t>Фрунзенская набережная, 30</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -7379,10 +7379,10 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="28" customHeight="1">
+    <row r="39" ht="15" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>Kuznetsky Most 12 by Lalique (Кузнецкий Мост 12)</t>
+          <t>Kuznetsky Most 12 by Lalique</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Москва, Кузнецкий Мост, 12/3С1</t>
+          <t>Кузнецкий Мост, 12/3С1</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
@@ -7451,7 +7451,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Саввинская 27</t>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Москва, Саввинская, 27</t>
+          <t>Саввинская, 27</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Москва, Новодевичий, 6С2</t>
+          <t>Новодевичий, 6С2</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
@@ -7595,10 +7595,10 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="28" customHeight="1">
+    <row r="42" ht="15" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Stoleshnikov 7 (Столешников 7)</t>
+          <t>Stoleshnikov 7</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Москва, Столешников, 7С1</t>
+          <t>Столешников, 7С1</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -7667,7 +7667,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="28" customHeight="1">
+    <row r="43" ht="15" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
           <t>ЖК «Узоры»</t>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Москва, 2-й Вражский переулок, 8с2</t>
+          <t>2-й Вражский переулок, 8с2</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
@@ -7739,7 +7739,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="40.5" customHeight="1">
+    <row r="44" ht="15" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Annabels</t>
@@ -7750,14 +7750,14 @@
           <t>СЗ ЮНИКС</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>1 кв. 2026 (Циан: 4 кв. 2026)</t>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>4 кв. 2026</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Москва, Курсовой переулок</t>
+          <t>Курсовой переулок</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Москва, Трёхпрудный переулок</t>
+          <t>Трёхпрудный переулок</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
@@ -7883,10 +7883,10 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="40.5" customHeight="1">
+    <row r="46" ht="28" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Armani/Casa Moscow Residences (Армани/Каса Москоу Резиденсес)</t>
+          <t>Armani/Casa Moscow Residences</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Москва, Старомонетный, 19/11</t>
+          <t>Старомонетный, 19/11</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Москва, Погодинская улица</t>
+          <t>Погодинская улица</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
@@ -8027,7 +8027,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="40.5" customHeight="1">
+    <row r="48" ht="28" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Обыденский №1»</t>
@@ -8038,14 +8038,14 @@
           <t>Sminex</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>1 кв. 2026 (Циан: 1 кв. 2030)</t>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>1 кв. 2030</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Москва, 3-й Обыденский переулок, 1</t>
+          <t>3-й Обыденский переулок, 1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Москва, Соймоновский, 3</t>
+          <t>Соймоновский, 3</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
@@ -8171,7 +8171,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="40.5" customHeight="1">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>ЖК «БРЮСОВ»</t>
@@ -8182,14 +8182,14 @@
           <t>VOSHOD</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>2 кв. 2026 (Циан: 4 кв. 2026)</t>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>4 кв. 2026</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Москва, Брюсов переулок, 2/14с10</t>
+          <t>Брюсов переулок, 2/14с10</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -8333,22 +8333,22 @@
   <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
+    <col width="84" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="53" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Лёвшинский, 19</t>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>продажи открыты, котлован/фундамент (novostroy-m.ru, 2026) — вышел из стадии планирования</t>
+          <t>продажи открыты, котлован/фундамент</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="53" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Клубный дом «Малая Никитская, 27»</t>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Малая Никитская улица, 27 (два двухэтажных особняка 1861 г., бывший «Клуб 27»)</t>
+          <t>Малая Никитская улица, 27</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -8537,9 +8537,9 @@
           <t>не раскрыт</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>проектирование (kvartiravmoskve.ru, 02.03.2026); продажи не открыты, старт не анонсирован</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>проектирование</t>
         </is>
       </c>
       <c r="G5" s="12" t="n"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="65.5" customHeight="1">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Палашёвский 11 (Большой Палашёвский, 11–13/15)</t>
+          <t>Палашёвский 11</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>продажи открыты (апрель 2026), стадия котлована (проверено 03.09.2026) — вышел из стадии планирования</t>
+          <t>продажи открыты, стадия котлована</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -8639,7 +8639,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65.5" customHeight="1">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>EDEN Private Residence</t>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>закрытые продажи (апрель 2026), стадия котлована; публичные продажи не открыты (novostroev.ru, 03.09.2026)</t>
+          <t>закрытые продажи, стадия котлована</t>
         </is>
       </c>
       <c r="G7" s="14" t="n">
@@ -8713,7 +8713,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65.5" customHeight="1">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Большая Ордынка, 25</t>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>концепция одобрена ГЗК, подготовка к строительству; старт продаж заявлен на 2026, цены и планировки не опубликованы</t>
+          <t>концепция одобрена ГЗК, подготовка к строительст</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -8780,7 +8780,7 @@
     <row r="9" ht="65.5" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Большая Пироговская, 51 (общежития Института красной профессуры)</t>
+          <t>Большая Пироговская, 51</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>анонсирован (fee-development, июнь 2026), концепция; ГПЗУ получен в начале 2025; реализация не подтверждена</t>
+          <t>анонсирован, концепция</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -8837,7 +8837,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="40.5" customHeight="1">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Большой Козихинский, 22</t>
@@ -8865,7 +8865,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>проект, продажи не начаты (novostroev.ru, проверено 03.09.2026)</t>
+          <t>проект, продажи не начаты</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
@@ -8897,7 +8897,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65.5" customHeight="1">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Воздвиженка 7/6</t>
@@ -8923,9 +8923,9 @@
           <t>АПРИ</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>анонсирован; в списке делюкс-стартов 2026–2027 mskdeluxe.ru; параметры не раскрыты, сайт проекта недоступен (08.09.2026)</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>анонсирован</t>
         </is>
       </c>
       <c r="G11" s="12" t="n"/>
@@ -8951,15 +8951,15 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65.5" customHeight="1">
+    <row r="12" ht="40.5" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Квартал на Савинской набережной («Московский шёлк»)</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Савинская наб. (территория БЦ «Московский шёлк»)</t>
+          <t>Квартал на Савинской набережной</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Савинская наб.</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -8977,9 +8977,9 @@
           <t>Sminex</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>проектирование (подтверждено Sminex в декабре 2025); начало реализации планировалось на 2026, старт продаж не объявлен</t>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>проектирование</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
@@ -9011,15 +9011,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="53" customHeight="1">
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Клубные дома на Берниковской набережной, 12 (Sminex)</t>
+          <t>Клубные дома на Берниковской набережной, 12</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Берниковская набережная, 12, стр. 1 (здание бывшей школы №1685, 1936 г., арх. А. Машинский)</t>
+          <t>Берниковская набережная, 12, стр. 1</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -9037,9 +9037,9 @@
           <t>Sminex</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>проектирование; площадка подтверждена Sminex 17.03.2026, сроки и старт продаж не объявлены</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>проектирование</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -9075,15 +9075,15 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65.5" customHeight="1">
+    <row r="14" ht="53" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом «Большая Никитская, 16» (R4S)</t>
+          <t>Клубный дом «Большая Никитская, 16»</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Большая Никитская улица, 16 (реконструкция доходного дома, объект культурного наследия)</t>
+          <t>Большая Никитская улица, 16</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>проект/реконструкция; продажи не начаты (novostroev.ru, 02.09.2026); заявленный ввод 3 кв. 2026 не подтверждён</t>
+          <t>проект/реконструкция</t>
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65.5" customHeight="1">
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Клубный дом «Земледельческий, 15»</t>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Земледельческий переулок, 15 (на месте административного здания 1975 г., 5 этажей, 5 744 м²)</t>
+          <t>Земледельческий переулок, 15</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -9167,9 +9167,9 @@
           <t>не раскрыт</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>проектирование (kvartiravmoskve.ru, 21.06.2026); по адресу действует БЦ; сделок и решений МКА не найдено</t>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>проектирование</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -9203,10 +9203,10 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="53" customHeight="1">
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Клубный дом на Курсовом переулке, 15 (проект бюро Дмитрия Великовского)</t>
+          <t>Клубный дом на Курсовом переулке, 15</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -9229,9 +9229,9 @@
           <t>не раскрыт</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>проект / предстарт; в открытых источниках только страница агрегатора (08.09.2026)</t>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>проект / предстарт</t>
         </is>
       </c>
       <c r="G16" s="5" t="n"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="53" customHeight="1">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Льва Толстого, 14–16 (три клубных дома Sminex)</t>
+          <t>Льва Толстого, 14–16</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>участок приобретён (декабрь 2025), проектирование; старт продаж не объявлен (08.09.2026)</t>
+          <t>участок приобретён, проектирование</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -9313,10 +9313,10 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="53" customHeight="1">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>МФК «На Краснопресненской набережной» (Трёхгорная мануфактура)</t>
+          <t>МФК «На Краснопресненской набережной»</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -9339,9 +9339,9 @@
           <t>ГК Ташир</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>проект/анонс; сроки реализации и старт продаж не объявлены, предложений нет (сентябрь 2026)</t>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>проект/анонс</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
@@ -9373,7 +9373,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="40.5" customHeight="1">
+    <row r="19" ht="28" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Малая Дмитровка, 5/9</t>
@@ -9399,9 +9399,9 @@
           <t>Группа «Эталон»</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>предстарт; старт продаж ожидается в 2026 г. (на 08.09.2026 не объявлен)</t>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>предстарт</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
@@ -9433,10 +9433,10 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="53" customHeight="1">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Малая Никитская, 29–31 (ожидаемый делюкс-старт)</t>
+          <t>Малая Никитская, 29–31</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>в списке ожидаемых стартов делюкс-класса 2026 (mskdeluxe.ru); подробностей нет (08.09.2026)</t>
+          <t>в списке ожидаемых стартов делюкс-класса 2026</t>
         </is>
       </c>
       <c r="G20" s="5" t="n"/>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="53" customHeight="1">
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Малая Ордынка, 14/1</t>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>анонс старта продаж 06.04.2026; по novostroev.ru на 03.09.2026 — проект, продажи не начаты</t>
+          <t>анонс старта продаж 06.04.2026</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -9549,7 +9549,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="53" customHeight="1">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Олсуфьевский 10</t>
@@ -9575,9 +9575,9 @@
           <t>Грандор</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>проект (ГПЗУ апрель 2021); продажи не начаты, «скоро в продаже» (08.09.2026)</t>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>проект</t>
         </is>
       </c>
       <c r="G22" s="5" t="n"/>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="53" customHeight="1">
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Полянка-3</t>
@@ -9633,9 +9633,9 @@
           <t>Aurix Development</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>старт продаж 2026 (по сайту проекта); строительство не начато, цены не опубликованы (08.09.2026)</t>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>старт продаж 2026</t>
         </is>
       </c>
       <c r="G23" s="12" t="n"/>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="78" customHeight="1">
+    <row r="24" ht="65.5" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Премиальный квартал на Лужнецкой набережной, 10А</t>
@@ -9691,9 +9691,9 @@
           <t>Sminex</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>проект утверждён (АГР, май 2026); начало строительства 2027, старт продаж ожидается в 2027</t>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>проект утверждён</t>
         </is>
       </c>
       <c r="G24" s="5" t="n"/>
@@ -9727,10 +9727,10 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65.5" customHeight="1">
+    <row r="25" ht="28" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Роден (ранее анонсировался как Veil)</t>
+          <t>Роден</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -9753,9 +9753,9 @@
           <t>MR Group</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>проектирование (kvartiravmoskve.ru, 15.07.2026); старт продаж заявлен на июль–август 2026, цены не опубликованы</t>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>проектирование</t>
         </is>
       </c>
       <c r="G25" s="12" t="n"/>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65.5" customHeight="1">
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Рождественка 8</t>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>проект дорабатывается под стандарты Sminex; по gdeetotdom.ru — возведение стен; продажи по запросу, старт не объявлен</t>
+          <t>проект дорабатывается под стандарты Sminex</t>
         </is>
       </c>
       <c r="G26" s="7" t="n">
@@ -9853,10 +9853,10 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="53" customHeight="1">
+    <row r="27" ht="28" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Тимура Фрунзе, 11 (клубный дом Sminex)</t>
+          <t>Тимура Фрунзе, 11</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>участок приобретён (апрель 2026), проектирование; сроки не объявлены (08.09.2026)</t>
+          <t>участок приобретён, проектирование</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
@@ -9911,15 +9911,15 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="53" customHeight="1">
+    <row r="28" ht="28" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Типография Сытина (Пятницкая, 71/5)</t>
+          <t>Типография Сытина</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ул. Пятницкая, 71/5 (2-й Монетчиковский пер., 5)</t>
+          <t>ул. Пятницкая, 71/5</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>участок приобретён (март 2026), проектирование; параметры и сроки не раскрыты (08.09.2026)</t>
+          <t>участок приобретён, проектирование</t>
         </is>
       </c>
       <c r="G28" s="5" t="n"/>
@@ -9965,15 +9965,15 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="78" customHeight="1">
+    <row r="29" ht="65.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Усадьба в Большом Саввинском переулке (клубный дом VSF)</t>
+          <t>Усадьба в Большом Саввинском переулке</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Большой Саввинский пер. (усадьба купца Якунина)</t>
+          <t>Большой Саввинский пер.</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>концепция бюро МЛА+ опубликована (январь 2026); сроки строительства не объявлены, реализация именно этой концепции не подтверждена</t>
+          <t>концепция бюро МЛА+ опубликована</t>
         </is>
       </c>
       <c r="G29" s="14" t="n">
@@ -10027,7 +10027,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="53" customHeight="1">
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Усачёва, 22</t>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>проект, продажи не начаты (novostroev.ru, 03.09.2026); старт продаж заявлен на 2026</t>
+          <t>проект, продажи не начаты</t>
         </is>
       </c>
       <c r="G30" s="7" t="n">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65.5" customHeight="1">
+    <row r="31" ht="28" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Участок КРТ «Большой Тишинский переулок, 8»</t>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Большой Тишинский переулок, 8 (стр. 1, 2)</t>
+          <t>Большой Тишинский переулок, 8</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -10115,9 +10115,9 @@
           <t>не раскрыт</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>решение о КРТ (август 2026); оператор/правообладатель и торги в открытых источниках не найдены (проверка 08.09.2026)</t>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>решение о КРТ</t>
         </is>
       </c>
       <c r="G31" s="14" t="n">
@@ -10147,10 +10147,10 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="90.5" customHeight="1">
+    <row r="32" ht="28" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Хилков (Хилков переулок, вл. 3)</t>
+          <t>Хилков</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>статус противоречив: novostroy-m.ru — проект 2016 г. «скоро старт»; novostroev.ru (03.09.2026) — «строительство/продажи завершены»; mskdeluxe.ru — старт 2026–2027</t>
+          <t>статус противоречив: novostroy-m.ru</t>
         </is>
       </c>
       <c r="G32" s="7" t="n">

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -607,14 +607,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -726,7 +726,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Резиденция Тверская</t>
@@ -803,7 +803,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>NEVA TOWERS</t>
@@ -880,7 +880,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Sinatra</t>
@@ -957,7 +957,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>LUMIN</t>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Уланский, 13</t>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Современник</t>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Репаблик</t>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>City Park</t>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SkyView</t>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Полянка/44</t>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Титул на Серебрянической</t>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Bogenhouse</t>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Capital Towers</t>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>BALCHUG VIEWPOINT</t>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>A.Residence</t>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Roza Rossa</t>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Собрание клубных домов ORDYNKA</t>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Дом NV/9</t>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Клубный дом Космо 4/22</t>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Софийский</t>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Lucky</t>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Абрикосов</t>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Клубный дом CULT</t>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Пироговская 14</t>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Cloud Nine</t>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
+    <row r="36" ht="30" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Симфония набережных (Котельническая 21)</t>
@@ -3344,7 +3344,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1">
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Малая Ордынка 19</t>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Золотой, жилой квартал</t>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="28" customHeight="1">
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Magnum</t>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Villa Grace</t>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1">
+    <row r="46" ht="30" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Brodsky</t>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1">
+    <row r="49" ht="30" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Дом Лаврушинский</t>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1">
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Хамовники 12</t>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="28" customHeight="1">
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Stella di Mosca Hotel &amp; Residences</t>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1">
+    <row r="52" ht="30" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Большая Дмитровка IX</t>
@@ -4748,14 +4748,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ЖК «Слава»</t>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>ЖК «Дом Дау»</t>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Оне</t>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>АУРУС Резиденции</t>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Тессинский V</t>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="40.5" customHeight="1">
+    <row r="13" ht="43.5" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Резиденция 1864</t>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>ЖК «Элитный квартал Тишинский бульвар»</t>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>ЖК «Дом Франка»</t>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ЖК «Татарская 35»</t>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Клубный дом «Резиденции Воронцова»</t>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ЖК «Дом Соболева»</t>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>ЖК «Климашкина 7/11»</t>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Форум»</t>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>ЖК «Камергер»</t>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Казачий</t>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>ЖК «Садовническая 69»</t>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Саввинская 17</t>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>ЖК «Исторический дом «Чистые Пруды»</t>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>ЖК «PHANTOM»</t>
@@ -6515,7 +6515,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Клубный дом TURGENEV</t>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Кло 17</t>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>ТИТУЛ Империал</t>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Дом Спорта</t>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>«Ильинка 3/8»</t>
@@ -7091,7 +7091,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>ЖК «Николь»</t>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>ЖК «Фрунзенская набережная»</t>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Kuznetsky Most 12 by Lalique</t>
@@ -7451,7 +7451,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Саввинская 27</t>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
           <t>ЖК «Узоры»</t>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Левенсон»</t>
@@ -7883,7 +7883,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="28" customHeight="1">
+    <row r="46" ht="30" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Armani/Casa Moscow Residences</t>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="28" customHeight="1">
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>ЖК «Клубный дом Обыденский №1»</t>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1">
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>ЖК «БРЮСОВ»</t>
@@ -8335,8 +8335,8 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Лёвшинский, 19</t>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Клубный дом «Малая Никитская, 27»</t>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Палашёвский 11</t>
@@ -8639,7 +8639,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>EDEN Private Residence</t>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Большая Ордынка, 25</t>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65.5" customHeight="1">
+    <row r="9" ht="70.5" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Большая Пироговская, 51</t>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Большой Козихинский, 22</t>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Воздвиженка 7/6</t>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="40.5" customHeight="1">
+    <row r="12" ht="57" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Квартал на Савинской набережной</t>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13" ht="43.5" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Клубные дома на Берниковской набережной, 12</t>
@@ -9075,7 +9075,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="53" customHeight="1">
+    <row r="14" ht="70.5" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Клубный дом «Большая Никитская, 16»</t>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Клубный дом «Земледельческий, 15»</t>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Клубный дом на Курсовом переулке, 15</t>
@@ -9255,7 +9255,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Льва Толстого, 14–16</t>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>МФК «На Краснопресненской набережной»</t>
@@ -9373,7 +9373,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Малая Дмитровка, 5/9</t>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Малая Никитская, 29–31</t>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Малая Ордынка, 14/1</t>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Олсуфьевский 10</t>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Полянка-3</t>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65.5" customHeight="1">
+    <row r="24" ht="84" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Премиальный квартал на Лужнецкой набережной, 10А</t>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Роден</t>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
+    <row r="26" ht="43.5" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Рождественка 8</t>
@@ -9853,7 +9853,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Тимура Фрунзе, 11</t>
@@ -9911,7 +9911,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Типография Сытина</t>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65.5" customHeight="1">
+    <row r="29" ht="84" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Усадьба в Большом Саввинском переулке</t>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Усачёва, 22</t>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Участок КРТ «Большой Тишинский переулок, 8»</t>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Хилков</t>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -622,7 +622,7 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="7" customWidth="1" min="16" max="16"/>
-    <col width="84" customWidth="1" min="17" max="17"/>
+    <col width="90" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Резиденция Тверская</t>
@@ -880,7 +880,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Sinatra</t>
@@ -957,7 +957,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>LUMIN</t>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Современник</t>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>City Park</t>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>BALCHUG VIEWPOINT</t>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Roza Rossa</t>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Софийский</t>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Абрикосов</t>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Клубный дом CULT</t>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
+    <row r="45" ht="15" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Villa Grace</t>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
+    <row r="46" ht="15" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Brodsky</t>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Хамовники 12</t>
@@ -4762,7 +4762,7 @@
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="84" customWidth="1" min="16" max="16"/>
+    <col width="90" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5723,7 +5723,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ЖК «Татарская 35»</t>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>ЖК «Климашкина 7/11»</t>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Казачий</t>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Саввинская 17</t>
@@ -6515,7 +6515,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Клубный дом TURGENEV</t>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Дом Спорта</t>
@@ -7451,7 +7451,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Саввинская 27</t>
@@ -8348,7 +8348,7 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="84" customWidth="1" min="16" max="16"/>
+    <col width="90" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -9549,7 +9549,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Олсуфьевский 10</t>

--- a/docs/premium-cao/premium-zhk-cao.xlsx
+++ b/docs/premium-cao/premium-zhk-cao.xlsx
@@ -608,8 +608,8 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Репаблик</t>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SkyView</t>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Полянка/44</t>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Capital Towers</t>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>A.Residence</t>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Клубный дом Космо 4/22</t>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Lucky</t>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="15" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Золотой, жилой квартал</t>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
+    <row r="49" ht="15" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Дом Лаврушинский</t>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
+    <row r="52" ht="15" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Большая Дмитровка IX</t>
@@ -4749,8 +4749,8 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Оне</t>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>ЖК «PHANTOM»</t>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Кло 17</t>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>ЖК «БРЮСОВ»</t>
@@ -8334,7 +8334,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -8344,9 +8344,9 @@
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="90" customWidth="1" min="16" max="16"/>
   </cols>
